--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847156524658</t>
+    <t xml:space="preserve">1.42847192287445</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">1.36014842987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30827271938324</t>
+    <t xml:space="preserve">1.30827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">1.27158045768738</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">1.23931646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21401154994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676331043243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425543308258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831751823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009362697601</t>
+    <t xml:space="preserve">1.21401143074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676354885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425555229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831763744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009326934814</t>
   </si>
   <si>
     <t xml:space="preserve">1.18680846691132</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">1.19439995288849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23299014568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2064197063446</t>
+    <t xml:space="preserve">1.232990026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
     <t xml:space="preserve">1.22097027301788</t>
@@ -104,46 +104,46 @@
     <t xml:space="preserve">1.24437749385834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16087079048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1064647436142</t>
+    <t xml:space="preserve">1.16087067127228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10646486282349</t>
   </si>
   <si>
     <t xml:space="preserve">1.1172194480896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12164771556854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04699790477753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848449707031</t>
+    <t xml:space="preserve">1.12164795398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04699766635895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826295375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11848485469818</t>
   </si>
   <si>
     <t xml:space="preserve">1.11089301109314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13366782665253</t>
+    <t xml:space="preserve">1.13366758823395</t>
   </si>
   <si>
     <t xml:space="preserve">1.17795157432556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19819557666779</t>
+    <t xml:space="preserve">1.19819581508636</t>
   </si>
   <si>
     <t xml:space="preserve">1.21337866783142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16213595867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578706264496</t>
+    <t xml:space="preserve">1.16213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578718185425</t>
   </si>
   <si>
     <t xml:space="preserve">1.17921674251556</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">1.13872873783112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13177001476288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770769119263</t>
+    <t xml:space="preserve">1.13176965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770757198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.24311208724976</t>
@@ -167,130 +167,130 @@
     <t xml:space="preserve">1.29182457923889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29941582679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598638534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525437831879</t>
+    <t xml:space="preserve">1.29941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598626613617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525402069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.27917182445526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25892794132233</t>
+    <t xml:space="preserve">1.25892806053162</t>
   </si>
   <si>
     <t xml:space="preserve">1.20199131965637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22413337230682</t>
+    <t xml:space="preserve">1.22413325309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.20135879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19376718997955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18238008022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464407444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19186949729919</t>
+    <t xml:space="preserve">1.19376730918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18237996101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19186925888062</t>
   </si>
   <si>
     <t xml:space="preserve">1.18554317951202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15264654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123685359955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17984938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17162525653839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1115255355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09571027755737</t>
+    <t xml:space="preserve">1.15264642238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123673439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17984962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17162549495697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11152589321136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09571003913879</t>
   </si>
   <si>
     <t xml:space="preserve">1.07546603679657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10709738731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417829036713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062654972076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719698905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454411506653</t>
+    <t xml:space="preserve">1.10709750652313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417852878571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719686985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1545444726944</t>
   </si>
   <si>
     <t xml:space="preserve">1.19227027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17405796051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24820911884308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406277179718</t>
+    <t xml:space="preserve">1.17405784130096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2482088804245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406301021576</t>
   </si>
   <si>
     <t xml:space="preserve">1.27812933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26837289333344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918719291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138172626495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27682876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25731515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495649337769</t>
+    <t xml:space="preserve">1.26837277412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918707370758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27682864665985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25731492042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495661258698</t>
   </si>
   <si>
     <t xml:space="preserve">1.19031918048859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096958637238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1779602766037</t>
+    <t xml:space="preserve">1.1909693479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796039581299</t>
   </si>
   <si>
     <t xml:space="preserve">1.12527441978455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16690278053284</t>
+    <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.17080557346344</t>
@@ -302,139 +302,139 @@
     <t xml:space="preserve">1.16495144367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17340743541718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18056225776672</t>
+    <t xml:space="preserve">1.17340731620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056237697601</t>
   </si>
   <si>
     <t xml:space="preserve">1.1538941860199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16300022602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649580955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16169941425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17730975151062</t>
+    <t xml:space="preserve">1.16300046443939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16169929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1773099899292</t>
   </si>
   <si>
     <t xml:space="preserve">1.18901801109314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14283609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12852668762207</t>
+    <t xml:space="preserve">1.14283657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12852656841278</t>
   </si>
   <si>
     <t xml:space="preserve">1.11031401157379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0966545343399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10641145706177</t>
+    <t xml:space="preserve">1.09665441513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10641133785248</t>
   </si>
   <si>
     <t xml:space="preserve">1.10055732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1148669719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372512340546</t>
+    <t xml:space="preserve">1.11486721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250878334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372500419617</t>
   </si>
   <si>
     <t xml:space="preserve">1.04657006263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526913166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10185825824738</t>
+    <t xml:space="preserve">1.04526925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185837745667</t>
   </si>
   <si>
     <t xml:space="preserve">1.13177871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10120797157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05307483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255308628082</t>
+    <t xml:space="preserve">1.1012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917673587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05307459831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255249023438</t>
   </si>
   <si>
     <t xml:space="preserve">0.996485531330109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995184719562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640616893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01339721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982826173305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321756839752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968516409397125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977622866630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671172142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00364077091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950954616069794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467865467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166934490204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118211746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965914607048035</t>
+    <t xml:space="preserve">0.99518495798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01339733600616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982826232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321876049042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968516170978546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97762268781662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00364053249359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95095419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9808748960495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166874885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96591454744339</t>
   </si>
   <si>
     <t xml:space="preserve">0.958759605884552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05437552928925</t>
+    <t xml:space="preserve">1.05437541007996</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957889556885</t>
@@ -443,52 +443,52 @@
     <t xml:space="preserve">1.06608355045319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07974290847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283128261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673395633698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340214729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06022942066193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08559679985046</t>
+    <t xml:space="preserve">1.07974302768707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892872810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673407554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340238571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06022953987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08559715747833</t>
   </si>
   <si>
     <t xml:space="preserve">1.09275197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1142166852951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09795546531677</t>
+    <t xml:space="preserve">1.11421680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09795558452606</t>
   </si>
   <si>
     <t xml:space="preserve">1.07779157161713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07388913631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10901319980621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746907234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348685741425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11876976490021</t>
+    <t xml:space="preserve">1.07388889789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10901308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746895313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348673820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1187698841095</t>
   </si>
   <si>
     <t xml:space="preserve">1.13828325271606</t>
@@ -500,61 +500,61 @@
     <t xml:space="preserve">1.14023447036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1278760433197</t>
+    <t xml:space="preserve">1.12787592411041</t>
   </si>
   <si>
     <t xml:space="preserve">1.14218580722809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15129220485687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16234958171844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803993701935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438045978546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0829952955246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315907001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600424766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08169424533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09990656375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0921014547348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1051105260849</t>
+    <t xml:space="preserve">1.15129232406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16234970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14804005622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299517631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315883159637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08169448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09990692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210133552551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511040687561</t>
   </si>
   <si>
     <t xml:space="preserve">1.11356616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949959278107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584047317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234477043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429598808289</t>
+    <t xml:space="preserve">1.08949971199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234465122223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925627708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429610729218</t>
   </si>
   <si>
     <t xml:space="preserve">1.07518970966339</t>
@@ -563,49 +563,49 @@
     <t xml:space="preserve">1.08754813671112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0745393037796</t>
+    <t xml:space="preserve">1.07453918457031</t>
   </si>
   <si>
     <t xml:space="preserve">1.05827808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05762767791748</t>
+    <t xml:space="preserve">1.05762779712677</t>
   </si>
   <si>
     <t xml:space="preserve">1.07323849201202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933557987213</t>
+    <t xml:space="preserve">1.06933605670929</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04722046852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047285556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03421151638031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144576072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175707817078</t>
+    <t xml:space="preserve">1.0472207069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348204612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0342116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175767421722</t>
   </si>
   <si>
     <t xml:space="preserve">0.95680832862854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93339216709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440949440002</t>
+    <t xml:space="preserve">0.933392107486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440770626068</t>
   </si>
   <si>
     <t xml:space="preserve">0.936644494533539</t>
@@ -614,94 +614,94 @@
     <t xml:space="preserve">0.949653446674347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.953556001186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962662398815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957458734512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507516860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986728966236115</t>
+    <t xml:space="preserve">0.95355612039566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962662518024445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956158041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458794116974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507338047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98672890663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.965264081954956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940547168254852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078441143036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835363864899</t>
+    <t xml:space="preserve">0.940547049045563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078560352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835423469543</t>
   </si>
   <si>
     <t xml:space="preserve">1.00429093837738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02315425872803</t>
+    <t xml:space="preserve">1.02315402030945</t>
   </si>
   <si>
     <t xml:space="preserve">1.030308842659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03681325912476</t>
+    <t xml:space="preserve">1.03681349754333</t>
   </si>
   <si>
     <t xml:space="preserve">1.02380454540253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120292186737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04201710224152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917180538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852151870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356122970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03095936775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03160965442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567622184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05502581596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03291070461273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03551244735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01860094070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999087572097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925146579742</t>
+    <t xml:space="preserve">1.0212025642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04201698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917204380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770733833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852163791656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03356111049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03095948696136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03160989284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05502593517303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03291094303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03551232814789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01860082149506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999087393283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925134658813</t>
   </si>
   <si>
     <t xml:space="preserve">0.991932511329651</t>
@@ -710,79 +710,79 @@
     <t xml:space="preserve">1.00494146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0251053571701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999737739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534432888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401238441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905833721161</t>
+    <t xml:space="preserve">1.02510523796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737858772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981114864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534254074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401298046112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905535697937</t>
   </si>
   <si>
     <t xml:space="preserve">1.0166494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01404774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136669635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02965843677521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991282105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00949454307556</t>
+    <t xml:space="preserve">1.01404762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0296585559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991282165050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00949466228485</t>
   </si>
   <si>
     <t xml:space="preserve">1.01795041561127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01469802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226017951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07063698768616</t>
+    <t xml:space="preserve">1.01469814777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226029872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07063663005829</t>
   </si>
   <si>
     <t xml:space="preserve">1.06218087673187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09470307826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14478766918182</t>
+    <t xml:space="preserve">1.09470319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14478778839111</t>
   </si>
   <si>
     <t xml:space="preserve">1.18251359462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23585021495819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845207691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633696556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983242988586</t>
+    <t xml:space="preserve">1.23585033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845231533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2163370847702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983231067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.21438562870026</t>
@@ -791,28 +791,28 @@
     <t xml:space="preserve">1.24755835533142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2130845785141</t>
+    <t xml:space="preserve">1.21308469772339</t>
   </si>
   <si>
     <t xml:space="preserve">1.20072627067566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21893882751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023975849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527911186218</t>
+    <t xml:space="preserve">1.21893870830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527923107147</t>
   </si>
   <si>
     <t xml:space="preserve">1.18381464481354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20267736911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446481227875</t>
+    <t xml:space="preserve">1.20267748832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446516990662</t>
   </si>
   <si>
     <t xml:space="preserve">1.16430115699768</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">1.21999967098236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21194696426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268402576447</t>
+    <t xml:space="preserve">1.21194672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27502703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28777778148651</t>
+    <t xml:space="preserve">1.27502715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28777754306793</t>
   </si>
   <si>
     <t xml:space="preserve">1.26697444915771</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013161659241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2434868812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24415802955627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22738134860992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818456172943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422406196594</t>
+    <t xml:space="preserve">1.2401317358017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24348700046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24415814876556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22738146781921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818444252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422394275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.27368497848511</t>
@@ -869,115 +869,115 @@
     <t xml:space="preserve">1.24147379398346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23006570339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831638813019</t>
+    <t xml:space="preserve">1.23006546497345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831650733948</t>
   </si>
   <si>
     <t xml:space="preserve">1.26294803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31462001800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30992269515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3105936050415</t>
+    <t xml:space="preserve">1.31462013721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3099228143692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059372425079</t>
   </si>
   <si>
     <t xml:space="preserve">1.32200181484222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3414626121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30455410480499</t>
+    <t xml:space="preserve">1.34146285057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3045539855957</t>
   </si>
   <si>
     <t xml:space="preserve">1.35555517673492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018670558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3568971157074</t>
+    <t xml:space="preserve">1.35018682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689735412598</t>
   </si>
   <si>
     <t xml:space="preserve">1.34481811523438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34079146385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32669937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32602834701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3038831949234</t>
+    <t xml:space="preserve">1.34079170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32669949531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3260281085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30388283729553</t>
   </si>
   <si>
     <t xml:space="preserve">1.30925154685974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29650139808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34213399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287125825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031888961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239800930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3743451833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010949134827</t>
+    <t xml:space="preserve">1.29650127887726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34213387966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871222496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864631175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031865119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239789009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434506416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010984897614</t>
   </si>
   <si>
     <t xml:space="preserve">1.43876755237579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45084655284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44816243648529</t>
+    <t xml:space="preserve">1.4508467912674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44816219806671</t>
   </si>
   <si>
     <t xml:space="preserve">1.48976862430573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46158397197723</t>
+    <t xml:space="preserve">1.46158373355865</t>
   </si>
   <si>
     <t xml:space="preserve">1.46024179458618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50721633434296</t>
+    <t xml:space="preserve">1.50721645355225</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453221797943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53540134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51929569244385</t>
+    <t xml:space="preserve">1.53540110588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51929533481598</t>
   </si>
   <si>
     <t xml:space="preserve">1.50050592422485</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">1.45755732059479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48037374019623</t>
+    <t xml:space="preserve">1.48037350177765</t>
   </si>
   <si>
     <t xml:space="preserve">1.44547820091248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44950485229492</t>
+    <t xml:space="preserve">1.44950437545776</t>
   </si>
   <si>
     <t xml:space="preserve">1.45621514320374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45889937877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279396533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290390491486</t>
+    <t xml:space="preserve">1.45889949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279408454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566523551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290366649628</t>
   </si>
   <si>
     <t xml:space="preserve">1.62129771709442</t>
@@ -1025,118 +1025,118 @@
     <t xml:space="preserve">1.59042859077454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61727166175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411401748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6078759431839</t>
+    <t xml:space="preserve">1.61727094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411389827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60787618160248</t>
   </si>
   <si>
     <t xml:space="preserve">1.61458706855774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59713959693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995565891266</t>
+    <t xml:space="preserve">1.5971394777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995553970337</t>
   </si>
   <si>
     <t xml:space="preserve">1.64277184009552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65350914001465</t>
+    <t xml:space="preserve">1.65350878238678</t>
   </si>
   <si>
     <t xml:space="preserve">1.62398207187653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64142978191376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069295883179</t>
+    <t xml:space="preserve">1.64142966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069272041321</t>
   </si>
   <si>
     <t xml:space="preserve">1.72329998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70987844467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558825969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853650569916</t>
+    <t xml:space="preserve">1.70987856388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558802127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853626728058</t>
   </si>
   <si>
     <t xml:space="preserve">1.70048356056213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70719385147095</t>
+    <t xml:space="preserve">1.70719420909882</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732627391815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69108879566193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68572008609772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66693031787872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66424584388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632520198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64679825305939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490616798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7743011713028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75819504261017</t>
+    <t xml:space="preserve">1.69108855724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68572020530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66693007946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66424608230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632508277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753531455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740336894989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64679801464081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67364096641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490581035614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77430105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75819528102875</t>
   </si>
   <si>
     <t xml:space="preserve">1.74880027770996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73806309700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7662478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174888134003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832722663879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161681652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416934490204</t>
+    <t xml:space="preserve">1.73806345462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866857051849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624822616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174864292145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7716166973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416886806488</t>
   </si>
   <si>
     <t xml:space="preserve">1.77564287185669</t>
@@ -1148,316 +1148,316 @@
     <t xml:space="preserve">1.74074769020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73537921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953769683838</t>
+    <t xml:space="preserve">1.7353789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940551280975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953757762909</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503787517548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78772246837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101134300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188070774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79845941066742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261788845062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248558521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067047595978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435578346252</t>
+    <t xml:space="preserve">1.787721991539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7810115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188082695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8226181268692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248606204987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067071437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435566425323</t>
   </si>
   <si>
     <t xml:space="preserve">1.89911949634552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88704037666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569784164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8454338312149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79577505588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598433494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793150901794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001074790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893281936646</t>
+    <t xml:space="preserve">1.88704025745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569796085358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543395042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598421573639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793115139008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893258094788</t>
   </si>
   <si>
     <t xml:space="preserve">1.77698516845703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76222145557404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356375217438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316767692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645738601685</t>
+    <t xml:space="preserve">1.76222169399261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356434822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645726680756</t>
   </si>
   <si>
     <t xml:space="preserve">1.6803514957428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6951150894165</t>
+    <t xml:space="preserve">1.69511497020721</t>
   </si>
   <si>
     <t xml:space="preserve">1.69243109226227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67766726016998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874554634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653436183929</t>
+    <t xml:space="preserve">1.67766714096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874518871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814054965973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653424263</t>
   </si>
   <si>
     <t xml:space="preserve">1.60921859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5702965259552</t>
+    <t xml:space="preserve">1.57029676437378</t>
   </si>
   <si>
     <t xml:space="preserve">1.57432293891907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57969188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345381259918</t>
+    <t xml:space="preserve">1.5796914100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687510967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345369338989</t>
   </si>
   <si>
     <t xml:space="preserve">1.51392710208893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229914665222</t>
+    <t xml:space="preserve">1.63203465938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229902744293</t>
   </si>
   <si>
     <t xml:space="preserve">1.66827249526978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75148487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611592292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7139048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72195792198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658933162689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606131076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385000705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371782302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674328327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197992801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54613816738129</t>
+    <t xml:space="preserve">1.75148451328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7461165189743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390497684479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72195768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7165892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606142997742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60385012626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371794223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53674352169037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546138048172</t>
   </si>
   <si>
     <t xml:space="preserve">1.54882276058197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54748034477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53271698951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895411014557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076969623566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.542111992836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869069576263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56761240959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955958366394</t>
+    <t xml:space="preserve">1.54748046398163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53271675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895434856415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076981544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211175441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56761252880096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955946445465</t>
   </si>
   <si>
     <t xml:space="preserve">1.52600586414337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5877445936203</t>
+    <t xml:space="preserve">1.58774435520172</t>
   </si>
   <si>
     <t xml:space="preserve">1.61190259456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60519218444824</t>
+    <t xml:space="preserve">1.60519206523895</t>
   </si>
   <si>
     <t xml:space="preserve">1.61324489116669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56627023220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782156944275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661121845245</t>
+    <t xml:space="preserve">1.56627070903778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782145023346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661109924316</t>
   </si>
   <si>
     <t xml:space="preserve">1.50319004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49647915363312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990056991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266190052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48171555995941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46695232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4844001531601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.523322224617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405892848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662510871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56837046146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884293556213</t>
+    <t xml:space="preserve">1.49647927284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990080833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266154289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48171579837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.462926030159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46695244312286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305773735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332186698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662498950958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56837058067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884305477142</t>
   </si>
   <si>
     <t xml:space="preserve">1.51609146595001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4995824098587</t>
+    <t xml:space="preserve">1.49958252906799</t>
   </si>
   <si>
     <t xml:space="preserve">1.5628674030304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57387387752533</t>
+    <t xml:space="preserve">1.57387363910675</t>
   </si>
   <si>
     <t xml:space="preserve">1.5518616437912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52159452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5009583234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5023341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49820673465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619426250458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042479991913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656382083893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42804265022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43767297267914</t>
+    <t xml:space="preserve">1.52159440517426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233376026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49820649623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619462013245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042468070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656394004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42804276943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43767321109772</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391550540924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4651882648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106112003326</t>
+    <t xml:space="preserve">1.46518838405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106088161469</t>
   </si>
   <si>
     <t xml:space="preserve">1.42116391658783</t>
@@ -1472,55 +1472,55 @@
     <t xml:space="preserve">1.38814556598663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45280635356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180035591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629717826843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45143043994904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41566097736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904864788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941844463348</t>
+    <t xml:space="preserve">1.45280611515045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180023670197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629729747772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143055915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41566073894501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555794239044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941856384277</t>
   </si>
   <si>
     <t xml:space="preserve">1.41841232776642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.396399974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36613357067108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41428506374359</t>
+    <t xml:space="preserve">1.39640009403229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36613321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41428518295288</t>
   </si>
   <si>
     <t xml:space="preserve">1.53397643566132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46793985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48032188415527</t>
+    <t xml:space="preserve">1.4679399728775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4803215265274</t>
   </si>
   <si>
     <t xml:space="preserve">1.48169755935669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47069132328033</t>
+    <t xml:space="preserve">1.47069144248962</t>
   </si>
   <si>
     <t xml:space="preserve">1.48720037937164</t>
@@ -1529,166 +1529,166 @@
     <t xml:space="preserve">1.49683094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50508534908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54085528850555</t>
+    <t xml:space="preserve">1.50508522987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54085540771484</t>
   </si>
   <si>
     <t xml:space="preserve">1.5312248468399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54223108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54910981655121</t>
+    <t xml:space="preserve">1.54223132133484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54911005496979</t>
   </si>
   <si>
     <t xml:space="preserve">1.54773426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53260064125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900690078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56561923027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746726036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984929084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810381889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461275577545</t>
+    <t xml:space="preserve">1.5326007604599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900713920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5656191110611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746737957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52984917163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810405731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461287498474</t>
   </si>
   <si>
     <t xml:space="preserve">1.53672790527344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45830941200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878224372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3853942155838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851512432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36406970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364862442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40190351009369</t>
+    <t xml:space="preserve">1.45830917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.417036652565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851500511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576365470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3640695810318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364874362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
     <t xml:space="preserve">1.36888492107391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32073318958282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26570236682892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2828996181488</t>
+    <t xml:space="preserve">1.32073307037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2657026052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28289973735809</t>
   </si>
   <si>
     <t xml:space="preserve">1.28909051418304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29665720462799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33724236488342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34343314170837</t>
+    <t xml:space="preserve">1.29665732383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33724224567413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34343326091766</t>
   </si>
   <si>
     <t xml:space="preserve">1.33105134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36200618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37989115715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38264262676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089703559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978800296783</t>
+    <t xml:space="preserve">1.3620058298111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37989091873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3826425075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089715480804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978812217712</t>
   </si>
   <si>
     <t xml:space="preserve">1.42666685581207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43216991424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4349217414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41153383255005</t>
+    <t xml:space="preserve">1.4321700334549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43492138385773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41153347492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.35581505298615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37301206588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35719108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692420482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528176784515</t>
+    <t xml:space="preserve">1.37301218509674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35719084739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565096855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528152942657</t>
   </si>
   <si>
     <t xml:space="preserve">1.28771471977234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24506592750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22924482822418</t>
+    <t xml:space="preserve">1.24506616592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22924494743347</t>
   </si>
   <si>
     <t xml:space="preserve">1.25951159000397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22786903381348</t>
+    <t xml:space="preserve">1.22786927223206</t>
   </si>
   <si>
     <t xml:space="preserve">1.2313084602356</t>
@@ -1700,64 +1700,64 @@
     <t xml:space="preserve">1.19553864002228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19003582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380281925201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30009651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29940891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496313095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30078458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252994060516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26776599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28221154212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088750362396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818707466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25882387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2636387348175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23268437385559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22030246257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.214111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18522047996521</t>
+    <t xml:space="preserve">1.19003570079803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025070667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33380258083344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30009663105011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994087934494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28496325016022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3007847070694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29253005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26776623725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051770687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818743228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25882375240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26363897323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2326842546463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22030258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21204781532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21411180496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18522036075592</t>
   </si>
   <si>
     <t xml:space="preserve">1.18797206878662</t>
@@ -1775,148 +1775,148 @@
     <t xml:space="preserve">1.20104169845581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27808451652527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28083598613739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28152394294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676023960114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23612356185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273577213287</t>
+    <t xml:space="preserve">1.27808439731598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28152358531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676012039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792031288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273565292358</t>
   </si>
   <si>
     <t xml:space="preserve">1.20379340648651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19209933280945</t>
+    <t xml:space="preserve">1.19209921360016</t>
   </si>
   <si>
     <t xml:space="preserve">1.21548712253571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29046618938446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27946019172668</t>
+    <t xml:space="preserve">1.29046642780304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2794600725174</t>
   </si>
   <si>
     <t xml:space="preserve">1.2505692243576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27326929569244</t>
+    <t xml:space="preserve">1.27326917648315</t>
   </si>
   <si>
     <t xml:space="preserve">1.34136962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30216026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353605747223</t>
+    <t xml:space="preserve">1.30216014385223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353617668152</t>
   </si>
   <si>
     <t xml:space="preserve">1.32417249679565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32554829120636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33930599689484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3475604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3317391872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110274791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523013114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34893620014191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38126659393311</t>
+    <t xml:space="preserve">1.32554852962494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34756052494049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33173906803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523001194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3489363193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063039302826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3812667131424</t>
   </si>
   <si>
     <t xml:space="preserve">1.38401830196381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30422377586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623600959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480893611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687268733978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512721538544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957275867462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787880420685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33793020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44455182552338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48307323455811</t>
+    <t xml:space="preserve">1.30422389507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623612880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480881690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34687256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512709617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33792996406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44455170631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307311534882</t>
   </si>
   <si>
     <t xml:space="preserve">1.55323708057404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59588575363159</t>
+    <t xml:space="preserve">1.59588587284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.64128589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.598637342453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57937693595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424295902252</t>
+    <t xml:space="preserve">1.59038281440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276448726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59863722324371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57937681674957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424307823181</t>
   </si>
   <si>
     <t xml:space="preserve">1.52572178840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50921261310577</t>
+    <t xml:space="preserve">1.50921273231506</t>
   </si>
   <si>
     <t xml:space="preserve">1.51333999633789</t>
@@ -1925,115 +1925,115 @@
     <t xml:space="preserve">1.51058852672577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49545478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59726190567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60001337528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340116500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007442474365</t>
+    <t xml:space="preserve">1.49545514583588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5972615480423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.600013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340092658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007430553436</t>
   </si>
   <si>
     <t xml:space="preserve">1.77611064910889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79949867725372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78436541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847651958466</t>
+    <t xml:space="preserve">1.79949915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78436553478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847663879395</t>
   </si>
   <si>
     <t xml:space="preserve">1.77438879013062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78151500225067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719245433807</t>
+    <t xml:space="preserve">1.78151488304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719257354736</t>
   </si>
   <si>
     <t xml:space="preserve">1.76726281642914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75301074981689</t>
+    <t xml:space="preserve">1.7530106306076</t>
   </si>
   <si>
     <t xml:space="preserve">1.77153861522675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7572865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420060157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403638362885</t>
+    <t xml:space="preserve">1.75728642940521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025454998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595537662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420095920563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403650283813</t>
   </si>
   <si>
     <t xml:space="preserve">1.89553201198578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81572020053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434180259705</t>
+    <t xml:space="preserve">1.81572031974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434192180634</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298725605011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74018383026123</t>
+    <t xml:space="preserve">1.74018371105194</t>
   </si>
   <si>
     <t xml:space="preserve">1.70597887039185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73733341693878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73590862751007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579068183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013684272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004274845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79006636142731</t>
+    <t xml:space="preserve">1.73733353614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7359082698822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579092025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013672351837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7900664806366</t>
   </si>
   <si>
     <t xml:space="preserve">1.84422433376312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84137380123138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723956108093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016033649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73020720481873</t>
+    <t xml:space="preserve">1.84137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723920345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016057491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73020756244659</t>
   </si>
   <si>
     <t xml:space="preserve">1.71310496330261</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">1.74588465690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80289316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8456494808197</t>
+    <t xml:space="preserve">1.80289351940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564971923828</t>
   </si>
   <si>
     <t xml:space="preserve">1.83282268047333</t>
@@ -2054,79 +2054,79 @@
     <t xml:space="preserve">1.78294038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80146789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001949310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82854700088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83994853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87415397167206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8841301202774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265822410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562598705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555538654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396554470062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95681631565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94398939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87842977046967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700426578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990178585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978419780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410662651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130320072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524972915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89268112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00954866409302</t>
+    <t xml:space="preserve">1.80146825313568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001925468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82854664325714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83994841575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87415361404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560261249542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265786647797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555550575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396602153778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116235733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95681607723236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9439891576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87842929363251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978443622589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8941068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130343914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01525020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89268183708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543803691864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0095489025116</t>
   </si>
   <si>
     <t xml:space="preserve">1.95111513137817</t>
@@ -2135,52 +2135,52 @@
     <t xml:space="preserve">1.93971335887909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97819435596466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532044887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714522838593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279894828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139729499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94969022274017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106862068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517936706543</t>
+    <t xml:space="preserve">1.97819423675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532021045685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8171454668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279906749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969010353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106850147247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517889022827</t>
   </si>
   <si>
     <t xml:space="preserve">2.00669860839844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0309271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672210216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648704528809</t>
+    <t xml:space="preserve">2.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672198295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0736837387085</t>
+    <t xml:space="preserve">2.06655764579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07368326187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.06228184700012</t>
@@ -2189,88 +2189,88 @@
     <t xml:space="preserve">1.96394228935242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92831170558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123295783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695727825165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263437271118</t>
+    <t xml:space="preserve">1.92831206321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123307704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973697185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91691040992737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263473033905</t>
   </si>
   <si>
     <t xml:space="preserve">1.89125633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90835881233215</t>
+    <t xml:space="preserve">1.90835869312286</t>
   </si>
   <si>
     <t xml:space="preserve">1.9971706867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94335031509399</t>
+    <t xml:space="preserve">1.94334995746613</t>
   </si>
   <si>
     <t xml:space="preserve">1.91425776481628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97971522808075</t>
+    <t xml:space="preserve">1.97971498966217</t>
   </si>
   <si>
     <t xml:space="preserve">1.96371459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97389662265778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9506231546402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989410877228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8938934803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462240695953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680278301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952970504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916868209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953332424164</t>
+    <t xml:space="preserve">1.97389686107635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95062303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989446640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389336109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462264537811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952958583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916880130768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880415916443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953296661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.0204439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735259056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01026177406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98553359508514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00880718231201</t>
+    <t xml:space="preserve">2.00735282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01026129722595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98553335666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00880742073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.02189874649048</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">2.02917146682739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03062653541565</t>
+    <t xml:space="preserve">2.03062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">2.03208088874817</t>
@@ -2288,58 +2288,58 @@
     <t xml:space="preserve">2.05099058151245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10044717788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608364105225</t>
+    <t xml:space="preserve">2.10044741630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608340263367</t>
   </si>
   <si>
     <t xml:space="preserve">2.16881370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08444666862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09753775596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462904930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863458633423</t>
+    <t xml:space="preserve">2.0844464302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09753847122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.080082654953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462881088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863434791565</t>
   </si>
   <si>
     <t xml:space="preserve">2.24736213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18917846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16590452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899282455444</t>
+    <t xml:space="preserve">2.1891782283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899258613586</t>
   </si>
   <si>
     <t xml:space="preserve">2.06844592094421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07717370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07280993461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.128084897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1455397605896</t>
+    <t xml:space="preserve">2.07717347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07280945777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12808513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499333381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14554023742676</t>
   </si>
   <si>
     <t xml:space="preserve">2.14699459075928</t>
@@ -2348,34 +2348,34 @@
     <t xml:space="preserve">2.13390326499939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13099408149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08299207687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05826377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808163642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.023353099823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771711349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06408190727234</t>
+    <t xml:space="preserve">2.13099384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08299231529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07426428794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0582640171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771687507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06408214569092</t>
   </si>
   <si>
     <t xml:space="preserve">2.04226303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99426114559174</t>
+    <t xml:space="preserve">1.99426126480103</t>
   </si>
   <si>
     <t xml:space="preserve">2.03789925575256</t>
@@ -2390,178 +2390,178 @@
     <t xml:space="preserve">2.02626252174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00589823722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862539768219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280667304993</t>
+    <t xml:space="preserve">2.00589776039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862468242645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95935082435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080553531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280679225922</t>
   </si>
   <si>
     <t xml:space="preserve">2.0611732006073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06990051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04080820083618</t>
+    <t xml:space="preserve">2.06990075111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04080843925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96807813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134870052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643837928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098405838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553033351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370795726776</t>
+    <t xml:space="preserve">1.96807849407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91134905815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643826007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098393917084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553057193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370807647705</t>
   </si>
   <si>
     <t xml:space="preserve">1.79352605342865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079913139343</t>
+    <t xml:space="preserve">1.80079901218414</t>
   </si>
   <si>
     <t xml:space="preserve">1.819708943367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84152770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552707195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516278743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83280038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898280143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171020030975</t>
+    <t xml:space="preserve">1.84152781963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8255273103714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516254901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171008110046</t>
   </si>
   <si>
     <t xml:space="preserve">1.84298241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85752844810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83570945262909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880125522614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061989307404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788935184479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460995674133</t>
+    <t xml:space="preserve">1.85752856731415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8357093334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880113601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87062013149261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788947105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460971832275</t>
   </si>
   <si>
     <t xml:space="preserve">1.5986088514328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68152129650116</t>
+    <t xml:space="preserve">1.68152153491974</t>
   </si>
   <si>
     <t xml:space="preserve">1.61751890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5738810300827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56224381923676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770140171051</t>
+    <t xml:space="preserve">1.57388079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351650714874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56224405765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770080566406</t>
   </si>
   <si>
     <t xml:space="preserve">1.52733361721039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50842344760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278280735016</t>
+    <t xml:space="preserve">1.50842368602753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278268814087</t>
   </si>
   <si>
     <t xml:space="preserve">1.36441791057587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35569024085999</t>
+    <t xml:space="preserve">1.35569036006927</t>
   </si>
   <si>
     <t xml:space="preserve">1.19277477264404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21241176128387</t>
+    <t xml:space="preserve">1.21241188049316</t>
   </si>
   <si>
     <t xml:space="preserve">1.16150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15931880474091</t>
+    <t xml:space="preserve">1.1593189239502</t>
   </si>
   <si>
     <t xml:space="preserve">1.13386332988739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10768032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11422598361969</t>
+    <t xml:space="preserve">1.10768043994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1142258644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.08440685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18041062355042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968344688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19713878631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11204421520233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550169467926</t>
+    <t xml:space="preserve">1.1804107427597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968320846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19713854789734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11204433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877213954926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550181388855</t>
   </si>
   <si>
     <t xml:space="preserve">1.10549855232239</t>
@@ -2570,139 +2570,139 @@
     <t xml:space="preserve">1.09022521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04149603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07640647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24514055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641264438629</t>
+    <t xml:space="preserve">1.04149615764618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07640635967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24514043331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641276359558</t>
   </si>
   <si>
     <t xml:space="preserve">1.20077514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22186696529388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24223148822784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47351324558258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.589390873909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649638175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5624772310257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967920780182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080410480499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47575604915619</t>
+    <t xml:space="preserve">1.22186672687531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24223124980927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36005413532257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023790836334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47351312637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649673938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331343650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56247735023499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967908859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080386638641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47575616836548</t>
   </si>
   <si>
     <t xml:space="preserve">1.47500860691071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60284733772278</t>
+    <t xml:space="preserve">1.60284757614136</t>
   </si>
   <si>
     <t xml:space="preserve">1.52061188220978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48397946357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192924022675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473425388336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931597232819</t>
+    <t xml:space="preserve">1.48397958278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473437309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931609153748</t>
   </si>
   <si>
     <t xml:space="preserve">1.46005654335022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44884252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762850761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49519371986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56546795368195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733306407928</t>
+    <t xml:space="preserve">1.44884264469147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762862682343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49519348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56546783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733318328857</t>
   </si>
   <si>
     <t xml:space="preserve">1.62228500843048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64321780204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498703956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807351589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479481697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535702705383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67760717868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65069377422333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976133823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125622272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583782196045</t>
+    <t xml:space="preserve">1.64321744441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498715877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807339668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471304416656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479493618011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7553573846817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67760670185089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65069365501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5849050283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686684608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976098060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125598430634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583794116974</t>
   </si>
   <si>
     <t xml:space="preserve">1.62527537345886</t>
@@ -2714,31 +2714,31 @@
     <t xml:space="preserve">1.59238135814667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60135221481323</t>
+    <t xml:space="preserve">1.60135245323181</t>
   </si>
   <si>
     <t xml:space="preserve">1.64172267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71050155162811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797740459442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7060159444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003497600555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013096809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956851959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788117408752</t>
+    <t xml:space="preserve">1.71050143241882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601618289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003485679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956863880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7478814125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.72545349597931</t>
@@ -2747,46 +2747,46 @@
     <t xml:space="preserve">1.78077566623688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.846564412117</t>
+    <t xml:space="preserve">1.84656417369843</t>
   </si>
   <si>
     <t xml:space="preserve">1.800213098526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78675639629364</t>
+    <t xml:space="preserve">1.78675651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.85403990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86002087593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871785640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423248767853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292934894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881396770477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161222934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104954242706</t>
+    <t xml:space="preserve">1.8600207567215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871773719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8331071138382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292946815491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881384849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161199092865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104978084564</t>
   </si>
   <si>
     <t xml:space="preserve">1.8226410150528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83609783649445</t>
+    <t xml:space="preserve">1.83609771728516</t>
   </si>
   <si>
     <t xml:space="preserve">1.85852563381195</t>
@@ -2795,163 +2795,163 @@
     <t xml:space="preserve">1.89291501045227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90786731243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141976833344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992476463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543951511383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301168680191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912415266037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553514957428</t>
+    <t xml:space="preserve">1.90786671638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039122104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89142000675201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8899245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487694740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543903827667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124176502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553503036499</t>
   </si>
   <si>
     <t xml:space="preserve">1.81666028499603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8076890707016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928054332733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460223674774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170857906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84805941581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84506893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058308601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83908784389496</t>
+    <t xml:space="preserve">1.80768895149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928042411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460259437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170810222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8480589389801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84506905078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646794319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058320522308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83908796310425</t>
   </si>
   <si>
     <t xml:space="preserve">1.82862162590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82114613056183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778542041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947288513184</t>
+    <t xml:space="preserve">1.82114577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778518199921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947252750397</t>
   </si>
   <si>
     <t xml:space="preserve">1.7090060710907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71349203586578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059742450714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7239578962326</t>
+    <t xml:space="preserve">1.71349167823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508303165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442447185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395813465118</t>
   </si>
   <si>
     <t xml:space="preserve">1.87497270107269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84207844734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227066993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582360267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638617038727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685226917267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246289253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63424670696259</t>
+    <t xml:space="preserve">1.84207808971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227090835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638628959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685262680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246277332306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6342465877533</t>
   </si>
   <si>
     <t xml:space="preserve">1.51762139797211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59836196899414</t>
+    <t xml:space="preserve">1.59836184978485</t>
   </si>
   <si>
     <t xml:space="preserve">1.74937641620636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75984299182892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72694861888885</t>
+    <t xml:space="preserve">1.75984287261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72694873809814</t>
   </si>
   <si>
     <t xml:space="preserve">1.75386202335358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80469846725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80918407440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301124095917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235268115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93926596641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.966179728508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159753322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216045856476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056910514832</t>
+    <t xml:space="preserve">1.80469858646393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80918443202972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8196507692337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301112174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93926608562469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617913246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159789085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056934356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345634460449</t>
@@ -2960,109 +2960,109 @@
     <t xml:space="preserve">2.01497268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02710175514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03316617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677860736847</t>
+    <t xml:space="preserve">2.04074740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02710199356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03316640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677884578705</t>
   </si>
   <si>
     <t xml:space="preserve">2.00890803337097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00132703781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981069564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800465583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435972213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01042366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0301342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03468298912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681134223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05136013031006</t>
+    <t xml:space="preserve">2.00132727622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01042413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03013372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03468251228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05136036872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.0437798500061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07561826705933</t>
+    <t xml:space="preserve">2.07561874389648</t>
   </si>
   <si>
     <t xml:space="preserve">2.06803774833679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287623405457</t>
+    <t xml:space="preserve">2.10442566871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287647247314</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261939048767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21358942985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16203927993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14687776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13323283195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15597534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023324012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20145988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27120304107666</t>
+    <t xml:space="preserve">2.21358919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084668159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16203951835632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14687824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1332323551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15597486495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023347854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20145964622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27120327949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.18933057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26362228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21510481834412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21662163734436</t>
+    <t xml:space="preserve">2.26362204551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484610080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2151050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21662139892578</t>
   </si>
   <si>
     <t xml:space="preserve">2.29546141624451</t>
@@ -3071,46 +3071,46 @@
     <t xml:space="preserve">2.30000996589661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32275247573853</t>
+    <t xml:space="preserve">2.32275152206421</t>
   </si>
   <si>
     <t xml:space="preserve">2.31062316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34246230125427</t>
+    <t xml:space="preserve">2.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">2.3576238155365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34852695465088</t>
+    <t xml:space="preserve">2.34852719306946</t>
   </si>
   <si>
     <t xml:space="preserve">2.35913991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38794708251953</t>
+    <t xml:space="preserve">2.38794660568237</t>
   </si>
   <si>
     <t xml:space="preserve">2.36368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39249515533447</t>
+    <t xml:space="preserve">2.39249539375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.33639788627625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38491439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36520481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823701858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430119514465</t>
+    <t xml:space="preserve">2.38491463661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36520457267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823725700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">2.32426834106445</t>
@@ -3119,34 +3119,34 @@
     <t xml:space="preserve">2.35459160804749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34549474716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38036632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44101238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36065649986267</t>
+    <t xml:space="preserve">2.34549450874329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.380366563797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410126209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36065626144409</t>
   </si>
   <si>
     <t xml:space="preserve">2.3727855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.318204164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765738487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41523814201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978621482849</t>
+    <t xml:space="preserve">2.31820368766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41523790359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978645324707</t>
   </si>
   <si>
     <t xml:space="preserve">2.4940779209137</t>
@@ -3155,43 +3155,43 @@
     <t xml:space="preserve">2.43494772911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614080429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30759119987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32730054855347</t>
+    <t xml:space="preserve">2.41827034950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42888307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614104270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32730078697205</t>
   </si>
   <si>
     <t xml:space="preserve">2.34397840499878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35610795021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45314192771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51682043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48649716377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49862670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043298721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44859337806702</t>
+    <t xml:space="preserve">2.35610747337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45314168930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51682019233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48649740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4986264705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043274879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44859313964844</t>
   </si>
   <si>
     <t xml:space="preserve">2.54714345932007</t>
@@ -3200,79 +3200,79 @@
     <t xml:space="preserve">2.58959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685400009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266133308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52038216590881</t>
+    <t xml:space="preserve">2.56685352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327429771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355948448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52038145065308</t>
   </si>
   <si>
     <t xml:space="preserve">2.50052428245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5142719745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49899697303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52343678474426</t>
+    <t xml:space="preserve">2.51579856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49899673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
     <t xml:space="preserve">2.53412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60286688804626</t>
+    <t xml:space="preserve">2.60286712646484</t>
   </si>
   <si>
     <t xml:space="preserve">2.46386408805847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42109370231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553399085999</t>
+    <t xml:space="preserve">2.42109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553375244141</t>
   </si>
   <si>
     <t xml:space="preserve">2.43942403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47761130332947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48066639900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41192865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443398475647</t>
+    <t xml:space="preserve">2.47761154174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48066663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4119291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443374633789</t>
   </si>
   <si>
     <t xml:space="preserve">2.42262125015259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46691942214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
+    <t xml:space="preserve">2.46691870689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775413513184</t>
   </si>
   <si>
     <t xml:space="preserve">2.43025898933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45928120613098</t>
+    <t xml:space="preserve">2.45928144454956</t>
   </si>
   <si>
     <t xml:space="preserve">2.44706153869629</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">2.43331408500671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45622658729553</t>
+    <t xml:space="preserve">2.45622682571411</t>
   </si>
   <si>
     <t xml:space="preserve">2.48372149467468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023957252502</t>
+    <t xml:space="preserve">2.50816130638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023909568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.65938472747803</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.64869213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63799905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67618703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61814188957214</t>
+    <t xml:space="preserve">2.63799953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67618680000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61814212799072</t>
   </si>
   <si>
     <t xml:space="preserve">2.60439443588257</t>
@@ -3326,73 +3326,73 @@
     <t xml:space="preserve">2.63952732086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61966943740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59370160102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54634952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53565692901611</t>
+    <t xml:space="preserve">2.61966919898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59370183944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54634928703308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53565669059753</t>
   </si>
   <si>
     <t xml:space="preserve">2.51885437965393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54482197761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260159492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50663447380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58148217201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54329419136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49135899543762</t>
+    <t xml:space="preserve">2.54482126235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50663423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58148193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54329442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997427940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49135947227478</t>
   </si>
   <si>
     <t xml:space="preserve">2.48830389976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4821937084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40734624862671</t>
+    <t xml:space="preserve">2.48219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40734648704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.37526869773865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41040110588074</t>
+    <t xml:space="preserve">2.41040134429932</t>
   </si>
   <si>
     <t xml:space="preserve">2.38290619850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48524904251099</t>
+    <t xml:space="preserve">2.48524880409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.44247889518738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47455668449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48983144760132</t>
+    <t xml:space="preserve">2.47455644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4898316860199</t>
   </si>
   <si>
     <t xml:space="preserve">2.52649188041687</t>
@@ -3401,94 +3401,94 @@
     <t xml:space="preserve">2.52496409416199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55856919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55398678779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54787683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56162405014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732659339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4516441822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4287314414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42414879798889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42567682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45011615753174</t>
+    <t xml:space="preserve">2.55856895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55398654937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54787707328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56162476539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45164394378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42873167991638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42414927482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45011639595032</t>
   </si>
   <si>
     <t xml:space="preserve">2.4272038936615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40581893920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39818167686462</t>
+    <t xml:space="preserve">2.40581917762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
     <t xml:space="preserve">2.38596129417419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221384048462</t>
+    <t xml:space="preserve">2.38901615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221360206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37355327606201</t>
+    <t xml:space="preserve">2.37355279922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42535662651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791532516479</t>
+    <t xml:space="preserve">2.4253568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791508674622</t>
   </si>
   <si>
     <t xml:space="preserve">2.42378711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40965890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35157561302185</t>
+    <t xml:space="preserve">2.40965914726257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000586509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34372687339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34058737754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33116793632507</t>
+    <t xml:space="preserve">2.34372663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34058713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33116817474365</t>
   </si>
   <si>
     <t xml:space="preserve">2.35471534729004</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44733428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43948531150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4740207195282</t>
+    <t xml:space="preserve">2.4473340511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4394850730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47402095794678</t>
   </si>
   <si>
     <t xml:space="preserve">2.45361351966858</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">2.44105505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45675301551819</t>
+    <t xml:space="preserve">2.45675325393677</t>
   </si>
   <si>
     <t xml:space="preserve">2.46931147575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4677414894104</t>
+    <t xml:space="preserve">2.46774172782898</t>
   </si>
   <si>
     <t xml:space="preserve">2.48814916610718</t>
@@ -3533,31 +3533,31 @@
     <t xml:space="preserve">2.50384712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45047402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27622509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837611198425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2558171749115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738668441772</t>
+    <t xml:space="preserve">2.45047378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27622485160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837587356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25581741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738716125488</t>
   </si>
   <si>
     <t xml:space="preserve">2.31547021865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29977226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29192352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27151584625244</t>
+    <t xml:space="preserve">2.29977202415466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29192304611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27151560783386</t>
   </si>
   <si>
     <t xml:space="preserve">2.36256456375122</t>
@@ -3566,25 +3566,25 @@
     <t xml:space="preserve">2.31076073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32017970085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26994562149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22913074493408</t>
+    <t xml:space="preserve">2.32017993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26994585990906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22913026809692</t>
   </si>
   <si>
     <t xml:space="preserve">2.22442126274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24639844894409</t>
+    <t xml:space="preserve">2.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244359970093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15064024925232</t>
+    <t xml:space="preserve">2.15064001083374</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005897521973</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">2.14122128486633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20401382446289</t>
+    <t xml:space="preserve">2.20401358604431</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16319847106934</t>
+    <t xml:space="preserve">2.16319894790649</t>
   </si>
   <si>
     <t xml:space="preserve">2.17732667922974</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">2.18674564361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18203616142273</t>
+    <t xml:space="preserve">2.18203639984131</t>
   </si>
   <si>
     <t xml:space="preserve">2.16633820533752</t>
@@ -3620,22 +3620,22 @@
     <t xml:space="preserve">2.14750075340271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15848922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814155578613</t>
+    <t xml:space="preserve">2.15848875045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814203262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.21186280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23070025444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21657204627991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22756099700928</t>
+    <t xml:space="preserve">2.23070073127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21657180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22756052017212</t>
   </si>
   <si>
     <t xml:space="preserve">2.26366639137268</t>
@@ -3644,202 +3644,202 @@
     <t xml:space="preserve">2.31860971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29349279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2479681968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2354097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24011898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24482846260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291199684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407430648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11924362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20087361335754</t>
+    <t xml:space="preserve">2.29349303245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24796843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23540997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24011969566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24482870101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291152000427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529662132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11924386024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20087385177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831562995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2212815284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23227000236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23697924613953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19930410385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22599077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27936482429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16476821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03447413444519</t>
+    <t xml:space="preserve">2.22128129005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23697948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1993043422699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22599101066589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27936458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16476798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03447389602661</t>
   </si>
   <si>
     <t xml:space="preserve">2.09255695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953081130981</t>
+    <t xml:space="preserve">2.05802130699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9795309305191</t>
   </si>
   <si>
     <t xml:space="preserve">1.95441365242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01092720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92615723609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766685962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800572514534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592303752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807405948639</t>
+    <t xml:space="preserve">2.0109269618988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92615711688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766662120819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057227611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592315673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254993915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807429790497</t>
   </si>
   <si>
     <t xml:space="preserve">1.91045904159546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91202890872955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00935745239258</t>
+    <t xml:space="preserve">1.91202878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009357213974</t>
   </si>
   <si>
     <t xml:space="preserve">1.9936591386795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97796106338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877617835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01720595359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920893907547</t>
+    <t xml:space="preserve">1.97796082496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01720643043518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99208903312683</t>
   </si>
   <si>
     <t xml:space="preserve">1.98894965648651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99679851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249670982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854197978973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639095783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516852378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301785945892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790034294128</t>
+    <t xml:space="preserve">1.99679839611053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959105491638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220226764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301762104034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790046215057</t>
   </si>
   <si>
     <t xml:space="preserve">1.89947044849396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92124772071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576610088348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01642298698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01158356666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96964204311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543759822845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87608003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9277001619339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91156899929047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8260725736618</t>
+    <t xml:space="preserve">1.92124760150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576633930206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01642322540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01158380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964192390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092656135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543783664703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87607991695404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770040035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91156888008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90188992023468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221131801605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607233524323</t>
   </si>
   <si>
     <t xml:space="preserve">1.77122592926025</t>
@@ -3848,37 +3848,37 @@
     <t xml:space="preserve">1.79703617095947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81316733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801433563232</t>
+    <t xml:space="preserve">1.81316757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801445484161</t>
   </si>
   <si>
     <t xml:space="preserve">1.90672945976257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94383203983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963469982147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382445812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802167892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93253970146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479516029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318924427032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254692554474</t>
+    <t xml:space="preserve">1.9438316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963458061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382469654083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802155971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479551792145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96318936347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254704475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932834625244</t>
@@ -3890,67 +3890,67 @@
     <t xml:space="preserve">2.02448868751526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01481008529663</t>
+    <t xml:space="preserve">2.01480937004089</t>
   </si>
   <si>
     <t xml:space="preserve">1.97448122501373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97770738601685</t>
+    <t xml:space="preserve">1.97770762443542</t>
   </si>
   <si>
     <t xml:space="preserve">1.99061274528503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93415284156799</t>
+    <t xml:space="preserve">1.93415296077728</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124049663544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82929909229279</t>
+    <t xml:space="preserve">1.8292989730835</t>
   </si>
   <si>
     <t xml:space="preserve">1.87285387516022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88898503780365</t>
+    <t xml:space="preserve">1.88898491859436</t>
   </si>
   <si>
     <t xml:space="preserve">1.86317479610443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85833537578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84381699562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672235488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88253271579742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87769329547882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865653514862</t>
+    <t xml:space="preserve">1.85833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381747245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672247409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88253235816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87769317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187559127808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81155455112457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993371009827</t>
+    <t xml:space="preserve">1.8115541934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993394851685</t>
   </si>
   <si>
     <t xml:space="preserve">1.78574419021606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8180068731308</t>
+    <t xml:space="preserve">1.81800711154938</t>
   </si>
   <si>
     <t xml:space="preserve">1.86962723731995</t>
@@ -3962,28 +3962,28 @@
     <t xml:space="preserve">1.82768583297729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90350329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93899238109589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9518975019455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802878379822</t>
+    <t xml:space="preserve">1.90350317955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9389922618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95189762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383866786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802914142609</t>
   </si>
   <si>
     <t xml:space="preserve">1.99222600460052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06643009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0744960308075</t>
+    <t xml:space="preserve">2.06643033027649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449555397034</t>
   </si>
   <si>
     <t xml:space="preserve">2.05029916763306</t>
@@ -3992,19 +3992,19 @@
     <t xml:space="preserve">2.0519118309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03416752815247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01319646835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07288265228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09546685218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07933568954468</t>
+    <t xml:space="preserve">2.03416728973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01319670677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07288289070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09546661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07933521270752</t>
   </si>
   <si>
     <t xml:space="preserve">2.07610893249512</t>
@@ -4019,70 +4019,70 @@
     <t xml:space="preserve">1.98899960517883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95512366294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932076454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866399765015</t>
+    <t xml:space="preserve">1.9551237821579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932064533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866411685944</t>
   </si>
   <si>
     <t xml:space="preserve">1.91318213939667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9293133020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286832332611</t>
+    <t xml:space="preserve">1.92931354045868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286856174469</t>
   </si>
   <si>
     <t xml:space="preserve">1.96480274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94544470310211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83736479282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025590896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81474304199219</t>
+    <t xml:space="preserve">1.9454448223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8373646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025614738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647287845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495913028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474316120148</t>
   </si>
   <si>
     <t xml:space="preserve">1.78290569782257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78458142280579</t>
+    <t xml:space="preserve">1.7845813035965</t>
   </si>
   <si>
     <t xml:space="preserve">1.79128384590149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.776202917099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72928428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73933851718903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74604117870331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79798662662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966223239899</t>
+    <t xml:space="preserve">1.77620279788971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72928416728973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73933839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74604094028473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79798638820648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966235160828</t>
   </si>
   <si>
     <t xml:space="preserve">1.86333739757538</t>
@@ -4091,31 +4091,31 @@
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85663485527039</t>
+    <t xml:space="preserve">1.85663521289825</t>
   </si>
   <si>
     <t xml:space="preserve">1.86166167259216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87674260139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171566486359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517533779144</t>
+    <t xml:space="preserve">1.87674283981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517545700073</t>
   </si>
   <si>
     <t xml:space="preserve">1.91360712051392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93203949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685082435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355336666107</t>
+    <t xml:space="preserve">1.93203961849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685034751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355324745178</t>
   </si>
   <si>
     <t xml:space="preserve">1.92701268196106</t>
@@ -4124,22 +4124,22 @@
     <t xml:space="preserve">1.94879627227783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94376945495605</t>
+    <t xml:space="preserve">1.94376921653748</t>
   </si>
   <si>
     <t xml:space="preserve">2.09625482559204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1783618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19176721572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160535812378</t>
+    <t xml:space="preserve">2.17836213111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19176745414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820027351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16160559654236</t>
   </si>
   <si>
     <t xml:space="preserve">2.18506479263306</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">2.29901003837585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29230761528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28895568847656</t>
+    <t xml:space="preserve">2.29230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
     <t xml:space="preserve">2.3258204460144</t>
@@ -4160,19 +4160,19 @@
     <t xml:space="preserve">2.33419871330261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3425772190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32917189598083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25711822509766</t>
+    <t xml:space="preserve">2.34257745742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32917165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25711846351624</t>
   </si>
   <si>
     <t xml:space="preserve">2.29398274421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30906391143799</t>
+    <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
     <t xml:space="preserve">2.30068564414978</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">2.29733443260193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31409072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30403661727905</t>
+    <t xml:space="preserve">2.31409120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30403709411621</t>
   </si>
   <si>
     <t xml:space="preserve">2.33755016326904</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">2.42636036872864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44981932640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46657633781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490025520325</t>
+    <t xml:space="preserve">2.44981956481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46657586097717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490049362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.4799816608429</t>
@@ -4217,52 +4217,52 @@
     <t xml:space="preserve">2.38614439964294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40122509002686</t>
+    <t xml:space="preserve">2.40122532844543</t>
   </si>
   <si>
     <t xml:space="preserve">2.40290117263794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609028816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38279318809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41295504570007</t>
+    <t xml:space="preserve">2.37609052658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38279294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41295528411865</t>
   </si>
   <si>
     <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36938786506653</t>
+    <t xml:space="preserve">2.36938762664795</t>
   </si>
   <si>
     <t xml:space="preserve">2.37776613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36100935935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3492796421051</t>
+    <t xml:space="preserve">2.36100959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34927940368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.37944149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38782024383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49171090126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45987367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68776345252991</t>
+    <t xml:space="preserve">2.38782000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49171113967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45987391471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371069908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68776392936707</t>
   </si>
   <si>
     <t xml:space="preserve">2.64922332763672</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">2.77824926376343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80170869827271</t>
+    <t xml:space="preserve">2.80170917510986</t>
   </si>
   <si>
     <t xml:space="preserve">2.77322244644165</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">2.83019495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93073463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92905950546265</t>
+    <t xml:space="preserve">2.93073487281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92905902862549</t>
   </si>
   <si>
     <t xml:space="preserve">2.90224838256836</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">3.03295016288757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06311202049255</t>
+    <t xml:space="preserve">3.06311225891113</t>
   </si>
   <si>
     <t xml:space="preserve">3.11840915679932</t>
@@ -4307,16 +4307,16 @@
     <t xml:space="preserve">3.1502468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16030073165894</t>
+    <t xml:space="preserve">3.16030097007751</t>
   </si>
   <si>
     <t xml:space="preserve">3.20554351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20219206809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1435444355011</t>
+    <t xml:space="preserve">3.20219230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14354419708252</t>
   </si>
   <si>
     <t xml:space="preserve">3.20889496803284</t>
@@ -4328,13 +4328,13 @@
     <t xml:space="preserve">3.19213843345642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19884133338928</t>
+    <t xml:space="preserve">3.1988410949707</t>
   </si>
   <si>
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29267811775208</t>
+    <t xml:space="preserve">3.2926778793335</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
@@ -4343,25 +4343,25 @@
     <t xml:space="preserve">3.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35132622718811</t>
+    <t xml:space="preserve">3.35132646560669</t>
   </si>
   <si>
     <t xml:space="preserve">3.40494775772095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34797477722168</t>
+    <t xml:space="preserve">3.25581336021423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34797549247742</t>
   </si>
   <si>
     <t xml:space="preserve">3.3178129196167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39321780204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3647313117981</t>
+    <t xml:space="preserve">3.39321827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36473155021667</t>
   </si>
   <si>
     <t xml:space="preserve">3.35467791557312</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">3.24240827560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13851737976074</t>
+    <t xml:space="preserve">3.13851714134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.23235440254211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13349008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1904628276825</t>
+    <t xml:space="preserve">3.13349032402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19046306610107</t>
   </si>
   <si>
     <t xml:space="preserve">3.23403000831604</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">3.24575972557068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2390570640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2155978679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26419162750244</t>
+    <t xml:space="preserve">3.23905682563782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21559762954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2641921043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.29770517349243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.294353723526</t>
+    <t xml:space="preserve">3.29435396194458</t>
   </si>
   <si>
     <t xml:space="preserve">3.3429479598999</t>
@@ -4418,34 +4418,34 @@
     <t xml:space="preserve">3.40159606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38986659049988</t>
+    <t xml:space="preserve">3.38986682891846</t>
   </si>
   <si>
     <t xml:space="preserve">3.3848397731781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37981247901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640739440918</t>
+    <t xml:space="preserve">3.37981271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3664071559906</t>
   </si>
   <si>
     <t xml:space="preserve">3.37143445014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32619166374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31243968009949</t>
+    <t xml:space="preserve">3.32619142532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31243991851807</t>
   </si>
   <si>
     <t xml:space="preserve">3.23508620262146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21789646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22305369377136</t>
+    <t xml:space="preserve">3.21789693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22305393218994</t>
   </si>
   <si>
     <t xml:space="preserve">3.2041449546814</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">3.21445894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19555044174194</t>
+    <t xml:space="preserve">3.19555020332336</t>
   </si>
   <si>
     <t xml:space="preserve">3.16976594924927</t>
@@ -4472,28 +4472,28 @@
     <t xml:space="preserve">3.05975246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09413170814514</t>
+    <t xml:space="preserve">3.09413146972656</t>
   </si>
   <si>
     <t xml:space="preserve">3.08897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10616421699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13366770744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13194894790649</t>
+    <t xml:space="preserve">3.10616445541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13366746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13194870948792</t>
   </si>
   <si>
     <t xml:space="preserve">3.18867444992065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22649168968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26602792739868</t>
+    <t xml:space="preserve">3.22649145126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2660276889801</t>
   </si>
   <si>
     <t xml:space="preserve">3.24024319648743</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">3.09928846359253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16117095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19383144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1525764465332</t>
+    <t xml:space="preserve">3.16117119789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19383120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15257620811462</t>
   </si>
   <si>
     <t xml:space="preserve">3.11991620063782</t>
@@ -4517,16 +4517,16 @@
     <t xml:space="preserve">3.09756970405579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06834697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429544448853</t>
+    <t xml:space="preserve">3.06834721565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429520606995</t>
   </si>
   <si>
     <t xml:space="preserve">3.14741945266724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10960221290588</t>
+    <t xml:space="preserve">3.10960245132446</t>
   </si>
   <si>
     <t xml:space="preserve">3.12507271766663</t>
@@ -4535,37 +4535,37 @@
     <t xml:space="preserve">3.18695545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17664170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14398121833801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27462244033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24196243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1903932094574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19898796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15601420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26258969306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27290344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12851071357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538670539856</t>
+    <t xml:space="preserve">3.17664194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14398145675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24196267127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19898819923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15601396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26258993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27290368080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12851095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538646697998</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
@@ -4580,58 +4580,58 @@
     <t xml:space="preserve">3.04771971702576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05631422996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01677846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0081832408905</t>
+    <t xml:space="preserve">3.05631446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01677823066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00818347930908</t>
   </si>
   <si>
     <t xml:space="preserve">3.01162123680115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03396797180176</t>
+    <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583698272705</t>
+    <t xml:space="preserve">2.98583674430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.07350397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07006597518921</t>
+    <t xml:space="preserve">3.07006621360779</t>
   </si>
   <si>
     <t xml:space="preserve">3.05287671089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9755232334137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94458198547363</t>
+    <t xml:space="preserve">2.97552299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94458222389221</t>
   </si>
   <si>
     <t xml:space="preserve">2.93083024024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92051649093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87582325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87754225730896</t>
+    <t xml:space="preserve">2.9205162525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87582349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87754249572754</t>
   </si>
   <si>
     <t xml:space="preserve">2.88785624504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91020274162292</t>
+    <t xml:space="preserve">2.91020226478577</t>
   </si>
   <si>
     <t xml:space="preserve">2.95661473274231</t>
@@ -4640,16 +4640,16 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005272865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286322593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05115723609924</t>
+    <t xml:space="preserve">2.96005249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286274909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05115747451782</t>
   </si>
   <si>
     <t xml:space="preserve">3.03053021430969</t>
@@ -4664,19 +4664,19 @@
     <t xml:space="preserve">3.08725571632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04256272315979</t>
+    <t xml:space="preserve">3.04256248474121</t>
   </si>
   <si>
     <t xml:space="preserve">3.02021646499634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99615049362183</t>
+    <t xml:space="preserve">2.99615073204041</t>
   </si>
   <si>
     <t xml:space="preserve">3.03912496566772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06490898132324</t>
+    <t xml:space="preserve">3.06490921974182</t>
   </si>
   <si>
     <t xml:space="preserve">2.9749481678009</t>
@@ -4685,13 +4685,13 @@
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729748725891</t>
+    <t xml:space="preserve">3.03729724884033</t>
   </si>
   <si>
     <t xml:space="preserve">2.99276232719421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9535710811615</t>
+    <t xml:space="preserve">2.95357131958008</t>
   </si>
   <si>
     <t xml:space="preserve">2.79858899116516</t>
@@ -4709,22 +4709,22 @@
     <t xml:space="preserve">2.67032766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6079785823822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58838272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59372711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62579250335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58125758171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64538788795471</t>
+    <t xml:space="preserve">2.60797834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58838295936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59372687339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62579226493835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58125734329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64538812637329</t>
   </si>
   <si>
     <t xml:space="preserve">2.64004373550415</t>
@@ -4736,10 +4736,10 @@
     <t xml:space="preserve">2.52247095108032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47971725463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31939077377319</t>
+    <t xml:space="preserve">2.47971701622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31939101219177</t>
   </si>
   <si>
     <t xml:space="preserve">2.36570715904236</t>
@@ -4748,16 +4748,16 @@
     <t xml:space="preserve">2.32473492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28554391860962</t>
+    <t xml:space="preserve">2.2855441570282</t>
   </si>
   <si>
     <t xml:space="preserve">2.3372049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36392593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26060438156128</t>
+    <t xml:space="preserve">2.36392569541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2606041431427</t>
   </si>
   <si>
     <t xml:space="preserve">2.27663707733154</t>
@@ -4766,16 +4766,16 @@
     <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38708424568176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32829761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32117223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36927008628845</t>
+    <t xml:space="preserve">2.38708400726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32829785346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32117199897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36927032470703</t>
   </si>
   <si>
     <t xml:space="preserve">2.3710515499115</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">2.40667939186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38173985481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39955401420593</t>
+    <t xml:space="preserve">2.3817400932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39955425262451</t>
   </si>
   <si>
     <t xml:space="preserve">2.42449378967285</t>
@@ -4805,19 +4805,19 @@
     <t xml:space="preserve">2.34254908561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39242815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39599132537842</t>
+    <t xml:space="preserve">2.39242839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39599108695984</t>
   </si>
   <si>
     <t xml:space="preserve">2.37461400032043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36036324501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41380548477173</t>
+    <t xml:space="preserve">2.36036348342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41380524635315</t>
   </si>
   <si>
     <t xml:space="preserve">2.51534533500671</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">2.49931263923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56522488594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53494095802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52068972587585</t>
+    <t xml:space="preserve">2.56522464752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53494071960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52068948745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.49753141403198</t>
@@ -4841,22 +4841,22 @@
     <t xml:space="preserve">2.50287556648254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57056856155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58303880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64360642433167</t>
+    <t xml:space="preserve">2.57056903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085320472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5830385684967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64360666275024</t>
   </si>
   <si>
     <t xml:space="preserve">2.64895081520081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65785813331604</t>
+    <t xml:space="preserve">2.65785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">2.65073204040527</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">2.67567205429077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65963935852051</t>
+    <t xml:space="preserve">2.65963912010193</t>
   </si>
   <si>
     <t xml:space="preserve">2.6525137424469</t>
@@ -4874,25 +4874,25 @@
     <t xml:space="preserve">2.63291811943054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55453658103943</t>
+    <t xml:space="preserve">2.55453634262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.61510419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65429496765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60441565513611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60619711875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59550881385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74336528778076</t>
+    <t xml:space="preserve">2.65429520606995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60441541671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60619735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59550857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74336504936218</t>
   </si>
   <si>
     <t xml:space="preserve">2.71664428710938</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">2.68992304801941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70773696899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66676473617554</t>
+    <t xml:space="preserve">2.70773720741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66676497459412</t>
   </si>
   <si>
     <t xml:space="preserve">2.73445820808411</t>
@@ -4916,22 +4916,22 @@
     <t xml:space="preserve">2.76830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7718677520752</t>
+    <t xml:space="preserve">2.77186799049377</t>
   </si>
   <si>
     <t xml:space="preserve">2.76474213600159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72911405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74692821502686</t>
+    <t xml:space="preserve">2.72911429405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74692845344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020673751831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75049114227295</t>
+    <t xml:space="preserve">2.75049138069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.76117944717407</t>
@@ -4940,19 +4940,19 @@
     <t xml:space="preserve">2.78968191146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8235285282135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84846830368042</t>
+    <t xml:space="preserve">2.82352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84846806526184</t>
   </si>
   <si>
     <t xml:space="preserve">2.77008628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8128399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80927753448486</t>
+    <t xml:space="preserve">2.81284022331238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80927729606628</t>
   </si>
   <si>
     <t xml:space="preserve">2.80749607086182</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">2.81996583938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81105852127075</t>
+    <t xml:space="preserve">2.81105875968933</t>
   </si>
   <si>
     <t xml:space="preserve">2.78790044784546</t>
@@ -4973,28 +4973,28 @@
     <t xml:space="preserve">2.84312415122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7576162815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63469958305359</t>
+    <t xml:space="preserve">2.75761651992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63469982147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.55275464057922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54741072654724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53137826919556</t>
+    <t xml:space="preserve">2.54741048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53137803077698</t>
   </si>
   <si>
     <t xml:space="preserve">2.5420663356781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55809903144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57947587966919</t>
+    <t xml:space="preserve">2.55809926986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57947611808777</t>
   </si>
   <si>
     <t xml:space="preserve">2.52781534194946</t>
@@ -5009,16 +5009,16 @@
     <t xml:space="preserve">2.60263419151306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61154127120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58482027053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5776948928833</t>
+    <t xml:space="preserve">2.61154103279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988049507141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58482003211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57769465446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.56878757476807</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">2.5866014957428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56700611114502</t>
+    <t xml:space="preserve">2.5670063495636</t>
   </si>
   <si>
     <t xml:space="preserve">2.51890826225281</t>
@@ -5036,10 +5036,10 @@
     <t xml:space="preserve">2.46724724769592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4708104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48684287071228</t>
+    <t xml:space="preserve">2.47080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48684310913086</t>
   </si>
   <si>
     <t xml:space="preserve">2.48867678642273</t>
@@ -5979,6 +5979,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.93599998950958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95000004768372</t>
   </si>
 </sst>
 </file>
@@ -71005,7 +71008,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6496064815</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1566022</v>
@@ -71026,6 +71029,32 @@
         <v>1988</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6493634259</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>840058</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>1.98800003528595</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>1.94599997997284</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>1.98800003528595</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1991">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847192287445</t>
+    <t xml:space="preserve">1.42847180366516</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.3917795419693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36014842987061</t>
+    <t xml:space="preserve">1.3601485490799</t>
   </si>
   <si>
     <t xml:space="preserve">1.30827283859253</t>
@@ -56,94 +56,94 @@
     <t xml:space="preserve">1.27158045768738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23931646347046</t>
+    <t xml:space="preserve">1.23931634426117</t>
   </si>
   <si>
     <t xml:space="preserve">1.21401143074036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28676354885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425555229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831763744354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18680846691132</t>
+    <t xml:space="preserve">1.28676331043243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425543308258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831751823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009338855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18680810928345</t>
   </si>
   <si>
     <t xml:space="preserve">1.1159542798996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09191429615021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478847503662</t>
+    <t xml:space="preserve">1.09191453456879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478835582733</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644216537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19439995288849</t>
+    <t xml:space="preserve">1.19440019130707</t>
   </si>
   <si>
     <t xml:space="preserve">1.232990026474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20641982555389</t>
+    <t xml:space="preserve">1.20641958713531</t>
   </si>
   <si>
     <t xml:space="preserve">1.22097027301788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24437749385834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087067127228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10646486282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1172194480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12164795398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04699766635895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826295375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848485469818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11089301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366758823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17795157432556</t>
+    <t xml:space="preserve">1.24437761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087090969086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064647436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11721956729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12164783477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04699802398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826283454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11848473548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366770744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17795169353485</t>
   </si>
   <si>
     <t xml:space="preserve">1.19819581508636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21337866783142</t>
+    <t xml:space="preserve">1.21337878704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.16213607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20578718185425</t>
+    <t xml:space="preserve">1.20578730106354</t>
   </si>
   <si>
     <t xml:space="preserve">1.17921674251556</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">1.13872873783112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13176965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770757198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311208724976</t>
+    <t xml:space="preserve">1.1317697763443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770733356476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311220645905</t>
   </si>
   <si>
     <t xml:space="preserve">1.29688549041748</t>
@@ -167,130 +167,130 @@
     <t xml:space="preserve">1.29182457923889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29941606521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598626613617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525402069092</t>
+    <t xml:space="preserve">1.29941618442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598638534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525413990021</t>
   </si>
   <si>
     <t xml:space="preserve">1.27917182445526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25892806053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199131965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413325309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135879516602</t>
+    <t xml:space="preserve">1.25892794132233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199143886566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135867595673</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376730918884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18237996101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554317951202</t>
+    <t xml:space="preserve">1.18238008022308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20452189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464383602142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1918693780899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554306030273</t>
   </si>
   <si>
     <t xml:space="preserve">1.15264642238617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19123673439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17984962463379</t>
+    <t xml:space="preserve">1.19123685359955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1798495054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.17162549495697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11152589321136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09571003913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546603679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709750652313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417852878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062643051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719686985016</t>
+    <t xml:space="preserve">1.11152565479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09570980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709738731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417829036713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062654972076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719698905945</t>
   </si>
   <si>
     <t xml:space="preserve">1.1545444726944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405784130096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2482088804245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406301021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26837277412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918707370758</t>
+    <t xml:space="preserve">1.19227039813995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405760288239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406277179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812945842743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26837289333344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918695449829</t>
   </si>
   <si>
     <t xml:space="preserve">1.28138160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27682864665985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25731492042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495661258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031918048859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1909693479538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527441978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16690289974213</t>
+    <t xml:space="preserve">1.27682852745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25731515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031894207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796051502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527430057526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16690313816071</t>
   </si>
   <si>
     <t xml:space="preserve">1.17080557346344</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">1.16755330562592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16495144367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17340731620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18056237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1538941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16300046443939</t>
+    <t xml:space="preserve">1.16495168209076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17340743541718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15389370918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16300022602081</t>
   </si>
   <si>
     <t xml:space="preserve">1.16950476169586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15649557113647</t>
+    <t xml:space="preserve">1.15649569034576</t>
   </si>
   <si>
     <t xml:space="preserve">1.16169929504395</t>
@@ -326,52 +326,52 @@
     <t xml:space="preserve">1.1773099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18901801109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14283657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12852656841278</t>
+    <t xml:space="preserve">1.18901813030243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14283633232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12852644920349</t>
   </si>
   <si>
     <t xml:space="preserve">1.11031401157379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09665441513062</t>
+    <t xml:space="preserve">1.09665465354919</t>
   </si>
   <si>
     <t xml:space="preserve">1.10641133785248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11486721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250878334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372500419617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04657006263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04526925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10185837745667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1012077331543</t>
+    <t xml:space="preserve">1.10055756568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11486673355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250866413116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372512340546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04657018184662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04526937007904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177895545959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120761394501</t>
   </si>
   <si>
     <t xml:space="preserve">1.12917673587799</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">1.05307459831238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952255249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485531330109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99518495798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01339733600616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982826232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321876049042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968516170978546</t>
+    <t xml:space="preserve">0.952255308628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485650539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640604972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01339721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982826173305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321637630463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851634979248</t>
   </si>
   <si>
     <t xml:space="preserve">0.97762268781662</t>
@@ -410,46 +410,46 @@
     <t xml:space="preserve">0.975671291351318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00364053249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95095419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9808748960495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166874885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118152141571</t>
+    <t xml:space="preserve">1.00364077091217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950954496860504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980874836444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970468044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96916675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118211746216</t>
   </si>
   <si>
     <t xml:space="preserve">0.96591454744339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958759605884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437541007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05957889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06608355045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974302768707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283140182495</t>
+    <t xml:space="preserve">0.958759844303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437564849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05957877635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06608378887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892860889435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283104419708</t>
   </si>
   <si>
     <t xml:space="preserve">1.06673407554626</t>
@@ -458,109 +458,109 @@
     <t xml:space="preserve">1.09340238571167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06022953987122</t>
+    <t xml:space="preserve">1.06022930145264</t>
   </si>
   <si>
     <t xml:space="preserve">1.08559715747833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09275197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11421680450439</t>
+    <t xml:space="preserve">1.09275162220001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1142166852951</t>
   </si>
   <si>
     <t xml:space="preserve">1.09795558452606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07779157161713</t>
+    <t xml:space="preserve">1.07779145240784</t>
   </si>
   <si>
     <t xml:space="preserve">1.07388889789581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10901308059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746895313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348673820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1187698841095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13828325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1454381942749</t>
+    <t xml:space="preserve">1.1090133190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746871471405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348685741425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11876976490021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13828313350677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543831348419</t>
   </si>
   <si>
     <t xml:space="preserve">1.14023447036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12787592411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218580722809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15129232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16234970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14804005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299517631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315883159637</t>
+    <t xml:space="preserve">1.12787616252899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218604564667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15129220485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16234946250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803993701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299505710602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315907001495</t>
   </si>
   <si>
     <t xml:space="preserve">1.09600400924683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08169448375702</t>
+    <t xml:space="preserve">1.08169424533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.09990692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09210133552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11356616020203</t>
+    <t xml:space="preserve">1.0921014547348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11356639862061</t>
   </si>
   <si>
     <t xml:space="preserve">1.08949971199036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234465122223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925627708435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429610729218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07518970966339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08754813671112</t>
+    <t xml:space="preserve">1.07584023475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234477043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925615787506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07518994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0875483751297</t>
   </si>
   <si>
     <t xml:space="preserve">1.07453918457031</t>
@@ -569,67 +569,67 @@
     <t xml:space="preserve">1.05827808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05762779712677</t>
+    <t xml:space="preserve">1.05762755870819</t>
   </si>
   <si>
     <t xml:space="preserve">1.07323849201202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933605670929</t>
+    <t xml:space="preserve">1.06933581829071</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0472207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348204612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0342116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175767421722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95680832862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392107486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440770626068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644494533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653446674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95355612039566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962662518024445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956158041954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957458794116974</t>
+    <t xml:space="preserve">1.04722046852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047285556793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348192691803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03421175479889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144587993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175886631012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956808507442474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93339204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440889835358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644613742828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653327465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95355623960495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962662220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157982349396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458674907684</t>
   </si>
   <si>
     <t xml:space="preserve">0.955507338047028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98672890663147</t>
+    <t xml:space="preserve">0.986729025840759</t>
   </si>
   <si>
     <t xml:space="preserve">0.965264081954956</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">0.986078560352325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995835423469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315402030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.030308842659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03681349754333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02380454540253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0212025642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04201698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917204380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770733833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852163791656</t>
+    <t xml:space="preserve">0.995835304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429105758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315390110016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03030896186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03681337833405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02380442619324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02120268344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04201710224152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917192459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770721912384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852139949799</t>
   </si>
   <si>
     <t xml:space="preserve">1.03356111049652</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">1.03160989284515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05567646026611</t>
+    <t xml:space="preserve">1.05567634105682</t>
   </si>
   <si>
     <t xml:space="preserve">1.05502593517303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03291094303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03551232814789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01860082149506</t>
+    <t xml:space="preserve">1.03291070461273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0355122089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01860094070435</t>
   </si>
   <si>
     <t xml:space="preserve">0.999087393283844</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">1.01925134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991932511329651</t>
+    <t xml:space="preserve">0.991932392120361</t>
   </si>
   <si>
     <t xml:space="preserve">1.00494146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02510523796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999737858772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981114864349</t>
+    <t xml:space="preserve">1.02510547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737799167633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981293678284</t>
   </si>
   <si>
     <t xml:space="preserve">0.994534254074097</t>
@@ -725,25 +725,25 @@
     <t xml:space="preserve">0.988029837608337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946401298046112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905535697937</t>
+    <t xml:space="preserve">0.946401238441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905714511871</t>
   </si>
   <si>
     <t xml:space="preserve">1.0166494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01404762268066</t>
+    <t xml:space="preserve">1.01404774188995</t>
   </si>
   <si>
     <t xml:space="preserve">1.04136657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0296585559845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991282165050507</t>
+    <t xml:space="preserve">1.02965867519379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991281867027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.00949466228485</t>
@@ -755,82 +755,82 @@
     <t xml:space="preserve">1.01469814777374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03226029872894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07063663005829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06218087673187</t>
+    <t xml:space="preserve">1.03226041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07063639163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06218075752258</t>
   </si>
   <si>
     <t xml:space="preserve">1.09470319747925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14478778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18251359462738</t>
+    <t xml:space="preserve">1.1447879076004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18251371383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.23585033416748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845231533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2163370847702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983231067657</t>
+    <t xml:space="preserve">1.23845219612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21633696556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983242988586</t>
   </si>
   <si>
     <t xml:space="preserve">1.21438562870026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24755835533142</t>
+    <t xml:space="preserve">1.24755847454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.21308469772339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20072627067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893870830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527923107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381464481354</t>
+    <t xml:space="preserve">1.20072603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893858909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023940086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527946949005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381452560425</t>
   </si>
   <si>
     <t xml:space="preserve">1.20267748832703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18446516990662</t>
+    <t xml:space="preserve">1.18446505069733</t>
   </si>
   <si>
     <t xml:space="preserve">1.16430115699768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17600917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999967098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482917785645</t>
+    <t xml:space="preserve">1.17600905895233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194684505463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268378734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482893943787</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502715587616</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">1.28777754306793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26697444915771</t>
+    <t xml:space="preserve">1.266974568367</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2401317358017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24348700046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24415814876556</t>
+    <t xml:space="preserve">1.24013185501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24348711967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24415802955627</t>
   </si>
   <si>
     <t xml:space="preserve">1.22738146781921</t>
@@ -860,28 +860,28 @@
     <t xml:space="preserve">1.24818444252014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25422394275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27368497848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24147379398346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006546497345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831650733948</t>
+    <t xml:space="preserve">1.25422418117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2736850976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24147391319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006570339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831638813019</t>
   </si>
   <si>
     <t xml:space="preserve">1.26294803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31462013721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3099228143692</t>
+    <t xml:space="preserve">1.31462001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30992269515991</t>
   </si>
   <si>
     <t xml:space="preserve">1.31059372425079</t>
@@ -890,31 +890,31 @@
     <t xml:space="preserve">1.32200181484222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34146285057068</t>
+    <t xml:space="preserve">1.3414626121521</t>
   </si>
   <si>
     <t xml:space="preserve">1.3045539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35555517673492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481811523438</t>
+    <t xml:space="preserve">1.35555529594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018658638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689723491669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3448178768158</t>
   </si>
   <si>
     <t xml:space="preserve">1.34079170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32669949531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3260281085968</t>
+    <t xml:space="preserve">1.32669937610626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32602834701538</t>
   </si>
   <si>
     <t xml:space="preserve">1.30388283729553</t>
@@ -926,100 +926,100 @@
     <t xml:space="preserve">1.29650127887726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34213387966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871222496033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864631175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300288677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031865119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239789009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37434506416321</t>
+    <t xml:space="preserve">1.34213376045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871234416962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864655017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031877040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239777088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434530258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010984897614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43876755237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4508467912674</t>
+    <t xml:space="preserve">1.43876731395721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45084667205811</t>
   </si>
   <si>
     <t xml:space="preserve">1.44816219806671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48976862430573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46158373355865</t>
+    <t xml:space="preserve">1.48976874351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46158361434937</t>
   </si>
   <si>
     <t xml:space="preserve">1.46024179458618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50721645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453221797943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540110588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51929533481598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050592422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50587403774261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829438209534</t>
+    <t xml:space="preserve">1.50721633434296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51929545402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5058741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829426288605</t>
   </si>
   <si>
     <t xml:space="preserve">1.45755732059479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48037350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44547820091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45621514320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45889949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279408454895</t>
+    <t xml:space="preserve">1.48037374019623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44547808170319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45621538162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45889961719513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279432296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.57566523551941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66290366649628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129771709442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640229701996</t>
+    <t xml:space="preserve">1.66290378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129783630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640217781067</t>
   </si>
   <si>
     <t xml:space="preserve">1.59042859077454</t>
@@ -1028,166 +1028,166 @@
     <t xml:space="preserve">1.61727094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64411389827728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60787618160248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61458706855774</t>
+    <t xml:space="preserve">1.64411401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60787653923035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61458671092987</t>
   </si>
   <si>
     <t xml:space="preserve">1.5971394777298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61995553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277184009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350878238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398207187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069272041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72329998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987856388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558802127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853626728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048356056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719420909882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732627391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108855724335</t>
+    <t xml:space="preserve">1.61995565891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350925922394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6239823102951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142954349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069260120392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72329986095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987844467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558825969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853638648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048344135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719397068024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108843803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.68572020530701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66693007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66424608230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632508277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753531455994</t>
+    <t xml:space="preserve">1.66693019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66424584388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632496356964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753519535065</t>
   </si>
   <si>
     <t xml:space="preserve">1.63740336894989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64679801464081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67364096641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490581035614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77430105209351</t>
+    <t xml:space="preserve">1.64679825305939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67364084720612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490604877472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7743011713028</t>
   </si>
   <si>
     <t xml:space="preserve">1.75819528102875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74880027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73806345462799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866857051849</t>
+    <t xml:space="preserve">1.74880051612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73806309700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866821289062</t>
   </si>
   <si>
     <t xml:space="preserve">1.76624822616577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79174864292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832746505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7716166973114</t>
+    <t xml:space="preserve">1.79174900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832770347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161681652069</t>
   </si>
   <si>
     <t xml:space="preserve">1.75416886806488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77564287185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074769020081</t>
+    <t xml:space="preserve">1.77564322948456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208986759186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074757099152</t>
   </si>
   <si>
     <t xml:space="preserve">1.7353789806366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73940551280975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503787517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.787721991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7810115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188082695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8226181268692</t>
+    <t xml:space="preserve">1.73940575122833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503823280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101134300232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188070774078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79845941066742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261765003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.80248606204987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83067071437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435566425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89911949634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88704025745392</t>
+    <t xml:space="preserve">1.83067035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435590267181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89911961555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88704037666321</t>
   </si>
   <si>
     <t xml:space="preserve">1.88569796085358</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">1.84543395042419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7957751750946</t>
+    <t xml:space="preserve">1.79577541351318</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598421573639</t>
@@ -1205,175 +1205,175 @@
     <t xml:space="preserve">1.71793115139008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893258094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222169399261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356434822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316791534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645726680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6803514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69511497020721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243109226227</t>
+    <t xml:space="preserve">1.73001098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893198490143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698528766632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222157478333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356375217438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316815376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645714759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68035173416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69511473178864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69243061542511</t>
   </si>
   <si>
     <t xml:space="preserve">1.67766714096069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63874518871307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814054965973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653424263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57029676437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57432293891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5796914100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687510967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345369338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51392710208893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63203465938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229902744293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148451328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7461165189743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71390497684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72195768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7165892124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606142997742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385012626648</t>
+    <t xml:space="preserve">1.63874530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814066886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653460025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5702965259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57432305812836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57969152927399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687499046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51392686367035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6320344209671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827237606049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148463249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611592292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390473842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72195756435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71658945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606131076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60385000705719</t>
   </si>
   <si>
     <t xml:space="preserve">1.58371794223785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53674352169037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197968959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.546138048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54882276058197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54748046398163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53271675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895434856415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076981544495</t>
+    <t xml:space="preserve">1.53674328327179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54613816738129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5488224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54748034477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53271687030792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895446777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076969623566</t>
   </si>
   <si>
     <t xml:space="preserve">1.54211175441742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52869033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56761252880096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955946445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600586414337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774435520172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190259456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519206523895</t>
+    <t xml:space="preserve">1.52869069576263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5676121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774447441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6119030714035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519218444824</t>
   </si>
   <si>
     <t xml:space="preserve">1.61324489116669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56627070903778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782145023346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661109924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50319004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647927284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990080833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266154289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48171579837799</t>
+    <t xml:space="preserve">1.56627035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661145687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5031898021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4964793920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990056991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4817156791687</t>
   </si>
   <si>
     <t xml:space="preserve">1.462926030159</t>
@@ -1382,55 +1382,55 @@
     <t xml:space="preserve">1.46695244312286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48305773735046</t>
+    <t xml:space="preserve">1.48305797576904</t>
   </si>
   <si>
     <t xml:space="preserve">1.48439979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52332186698914</t>
+    <t xml:space="preserve">1.52332198619843</t>
   </si>
   <si>
     <t xml:space="preserve">1.53405904769897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57662498950958</t>
+    <t xml:space="preserve">1.57662510871887</t>
   </si>
   <si>
     <t xml:space="preserve">1.56837058067322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53947925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884305477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51609146595001</t>
+    <t xml:space="preserve">1.53947949409485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884293556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5160915851593</t>
   </si>
   <si>
     <t xml:space="preserve">1.49958252906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5628674030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57387363910675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5518616437912</t>
+    <t xml:space="preserve">1.56286752223969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57387387752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55186128616333</t>
   </si>
   <si>
     <t xml:space="preserve">1.52159440517426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50095796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50233376026154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49820649623871</t>
+    <t xml:space="preserve">1.50095808506012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5023341178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498206615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.47619462013245</t>
@@ -1442,85 +1442,85 @@
     <t xml:space="preserve">1.46656394004822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42804276943207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43767321109772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42391550540924</t>
+    <t xml:space="preserve">1.42804265022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43767285346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
     <t xml:space="preserve">1.46518838405609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46931564807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106088161469</t>
+    <t xml:space="preserve">1.46931540966034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106112003326</t>
   </si>
   <si>
     <t xml:space="preserve">1.42116391658783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37370002269745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327882766724</t>
+    <t xml:space="preserve">1.37369990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327894687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.38814556598663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45280611515045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180023670197</t>
+    <t xml:space="preserve">1.45280635356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180035591125</t>
   </si>
   <si>
     <t xml:space="preserve">1.43629729747772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45143055915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41566073894501</t>
+    <t xml:space="preserve">1.45143043994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41566097736359</t>
   </si>
   <si>
     <t xml:space="preserve">1.45555794239044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41841232776642</t>
+    <t xml:space="preserve">1.43904888629913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941844463348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.418412566185</t>
   </si>
   <si>
     <t xml:space="preserve">1.39640009403229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36613321304321</t>
+    <t xml:space="preserve">1.36613345146179</t>
   </si>
   <si>
     <t xml:space="preserve">1.41428518295288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53397643566132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4679399728775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4803215265274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48169755935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069144248962</t>
+    <t xml:space="preserve">1.53397655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46793985366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48032164573669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48169732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069132328033</t>
   </si>
   <si>
     <t xml:space="preserve">1.48720037937164</t>
@@ -1532,61 +1532,61 @@
     <t xml:space="preserve">1.50508522987366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54085540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5312248468399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223132133484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54911005496979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54773426055908</t>
+    <t xml:space="preserve">1.54085528850555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53122508525848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223084449768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54911017417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54773414134979</t>
   </si>
   <si>
     <t xml:space="preserve">1.5326007604599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58900713920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5656191110611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746737957001</t>
+    <t xml:space="preserve">1.58900701999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56561899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5174674987793</t>
   </si>
   <si>
     <t xml:space="preserve">1.52984917163849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53810405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461287498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45830917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.417036652565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38539409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851500511169</t>
+    <t xml:space="preserve">1.53810369968414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672802448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45830929279327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878224372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851512432098</t>
   </si>
   <si>
     <t xml:space="preserve">1.37576365470886</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">1.3640695810318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39364874362946</t>
+    <t xml:space="preserve">1.39364850521088</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36888492107391</t>
+    <t xml:space="preserve">1.3688850402832</t>
   </si>
   <si>
     <t xml:space="preserve">1.32073307037354</t>
@@ -1610,49 +1610,49 @@
     <t xml:space="preserve">1.2657026052475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28289973735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909051418304</t>
+    <t xml:space="preserve">1.2828996181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909063339233</t>
   </si>
   <si>
     <t xml:space="preserve">1.29665732383728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33724224567413</t>
+    <t xml:space="preserve">1.33724212646484</t>
   </si>
   <si>
     <t xml:space="preserve">1.34343326091766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33105134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3620058298111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37989091873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3826425075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089715480804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978812217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42666685581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4321700334549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43492138385773</t>
+    <t xml:space="preserve">1.33105146884918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200594902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37989103794098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38264262676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089703559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978800296783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42666673660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43216991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43492150306702</t>
   </si>
   <si>
     <t xml:space="preserve">1.41153347492218</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">1.35581505298615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37301218509674</t>
+    <t xml:space="preserve">1.37301206588745</t>
   </si>
   <si>
     <t xml:space="preserve">1.35719084739685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32692432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565096855164</t>
+    <t xml:space="preserve">1.32692420482635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565120697021</t>
   </si>
   <si>
     <t xml:space="preserve">1.29528152942657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28771471977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24506616592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22924494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25951159000397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22786927223206</t>
+    <t xml:space="preserve">1.28771460056305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24506604671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22924470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25951170921326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22786891460419</t>
   </si>
   <si>
     <t xml:space="preserve">1.2313084602356</t>
@@ -1697,70 +1697,70 @@
     <t xml:space="preserve">1.18315672874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19553864002228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19003570079803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025070667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380258083344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30009663105011</t>
+    <t xml:space="preserve">1.19553852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19003582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025094509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338029384613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30009651184082</t>
   </si>
   <si>
     <t xml:space="preserve">1.2994087934494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28496325016022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3007847070694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29253005981445</t>
+    <t xml:space="preserve">1.28496313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30078458786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252994060516</t>
   </si>
   <si>
     <t xml:space="preserve">1.26776623725891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822117805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088726520538</t>
+    <t xml:space="preserve">1.28221166133881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088738441467</t>
   </si>
   <si>
     <t xml:space="preserve">1.27051770687103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23818743228912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25882375240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26363897323608</t>
+    <t xml:space="preserve">1.23818731307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25882351398468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26363909244537</t>
   </si>
   <si>
     <t xml:space="preserve">1.2326842546463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22030258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21204781532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18522036075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18797206878662</t>
+    <t xml:space="preserve">1.22030222415924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21204769611359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21411144733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18522071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18797183036804</t>
   </si>
   <si>
     <t xml:space="preserve">1.20172965526581</t>
@@ -1769,94 +1769,94 @@
     <t xml:space="preserve">1.19347500801086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1996659040451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808439731598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28152358531952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676012039185</t>
+    <t xml:space="preserve">1.19966566562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20104193687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28083598613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2815238237381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676000118256</t>
   </si>
   <si>
     <t xml:space="preserve">1.23612380027771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20792031288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273565292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20379340648651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19209921360016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21548712253571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29046642780304</t>
+    <t xml:space="preserve">1.20792055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273553371429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20379328727722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19209909439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548700332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29046607017517</t>
   </si>
   <si>
     <t xml:space="preserve">1.2794600725174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2505692243576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326917648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30216014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353617668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32417249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32554852962494</t>
+    <t xml:space="preserve">1.25056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326929569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136950969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30216026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32417237758636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32554817199707</t>
   </si>
   <si>
     <t xml:space="preserve">1.33930587768555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34756052494049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33173906803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110286712646</t>
+    <t xml:space="preserve">1.34756028652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3317391872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110274791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.31523001194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3489363193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063039302826</t>
+    <t xml:space="preserve">1.34893608093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063027381897</t>
   </si>
   <si>
     <t xml:space="preserve">1.3812667131424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38401830196381</t>
+    <t xml:space="preserve">1.38401818275452</t>
   </si>
   <si>
     <t xml:space="preserve">1.30422389507294</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.32623612880707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34480881690979</t>
+    <t xml:space="preserve">1.34480893611908</t>
   </si>
   <si>
     <t xml:space="preserve">1.34687256813049</t>
@@ -1874,223 +1874,223 @@
     <t xml:space="preserve">1.35512709617615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36957263946533</t>
+    <t xml:space="preserve">1.36957287788391</t>
   </si>
   <si>
     <t xml:space="preserve">1.35787868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33792996406555</t>
+    <t xml:space="preserve">1.33793008327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.44455170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48307311534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323708057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59588587284088</t>
+    <t xml:space="preserve">1.48307323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323719978333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5958856344223</t>
   </si>
   <si>
     <t xml:space="preserve">1.64128589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59038281440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276448726654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59863722324371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57937681674957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424307823181</t>
+    <t xml:space="preserve">1.59038293361664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276484489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.598637342453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57937669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424331665039</t>
   </si>
   <si>
     <t xml:space="preserve">1.52572178840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50921273231506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51333999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058852672577</t>
+    <t xml:space="preserve">1.50921261310577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058840751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.49545514583588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5972615480423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.600013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340092658997</t>
+    <t xml:space="preserve">1.59726178646088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60001337528229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340116500854</t>
   </si>
   <si>
     <t xml:space="preserve">1.71007430553436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77611064910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79949915409088</t>
+    <t xml:space="preserve">1.77611076831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79949903488159</t>
   </si>
   <si>
     <t xml:space="preserve">1.78436553478241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85847663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438879013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151488304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726281642914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7530106306076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153861522675</t>
+    <t xml:space="preserve">1.85847675800323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77438902854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151512145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719233512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726269721985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301098823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153837680817</t>
   </si>
   <si>
     <t xml:space="preserve">1.75728642940521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025454998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595537662506</t>
+    <t xml:space="preserve">1.71025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595513820648</t>
   </si>
   <si>
     <t xml:space="preserve">1.85420095920563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92403650283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89553201198578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572031974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434192180634</t>
+    <t xml:space="preserve">1.92403638362885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89553213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572020053864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434180259705</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298725605011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74018371105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597887039185</t>
+    <t xml:space="preserve">1.74018383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
     <t xml:space="preserve">1.73733353614807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7359082698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579092025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013672351837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7900664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422433376312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137392044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723920345306</t>
+    <t xml:space="preserve">1.73590838909149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579103946686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004239082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79006624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422421455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137403964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723956108093</t>
   </si>
   <si>
     <t xml:space="preserve">1.75016057491302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73020756244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588465690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289351940155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564971923828</t>
+    <t xml:space="preserve">1.7302074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588477611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289328098297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564936161041</t>
   </si>
   <si>
     <t xml:space="preserve">1.83282268047333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78294038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146825313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001925468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82854664325714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83994841575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87415361404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560261249542</t>
+    <t xml:space="preserve">1.78294014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001937389374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8285471200943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83994877338409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87415385246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560201644897</t>
   </si>
   <si>
     <t xml:space="preserve">1.88413047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90265786647797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555550575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396602153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116235733032</t>
+    <t xml:space="preserve">1.90265834331512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562598705292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417734622955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9539657831192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116188049316</t>
   </si>
   <si>
     <t xml:space="preserve">1.95681607723236</t>
@@ -2099,127 +2099,127 @@
     <t xml:space="preserve">1.9439891576767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87842929363251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978443622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8941068649292</t>
+    <t xml:space="preserve">1.8784294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700402736664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978395938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410650730133</t>
   </si>
   <si>
     <t xml:space="preserve">1.87130343914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01525020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89268183708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543803691864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0095489025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971335887909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819423675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532021045685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8171454668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279906749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139753341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94969010353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106850147247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672198295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957263469696</t>
+    <t xml:space="preserve">2.01524996757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89268147945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543791770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111489295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971371650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9781938791275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81714522838593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279930591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94968974590302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106826305389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669884681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092741966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9967223405838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957239627838</t>
   </si>
   <si>
     <t xml:space="preserve">2.09648680686951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09363651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06655764579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07368326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06228184700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394228935242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831206321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123307704926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695715904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973697185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691040992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263473033905</t>
+    <t xml:space="preserve">2.09363627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06655788421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0736837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0622820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695692062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973721027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91691017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263461112976</t>
   </si>
   <si>
     <t xml:space="preserve">1.89125633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90835869312286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9971706867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94334995746613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425776481628</t>
+    <t xml:space="preserve">1.90835905075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99717044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9433501958847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425800323486</t>
   </si>
   <si>
     <t xml:space="preserve">1.97971498966217</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">1.97389686107635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95062303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989446640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462264537811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952958583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916880130768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880415916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0204439163208</t>
+    <t xml:space="preserve">1.95062279701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9098938703537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389371871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462252616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680302143097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8895298242569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916892051697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880427837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953284740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.00735282897949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01026129722595</t>
+    <t xml:space="preserve">2.01026153564453</t>
   </si>
   <si>
     <t xml:space="preserve">1.98553335666656</t>
@@ -2276,40 +2276,40 @@
     <t xml:space="preserve">2.02189874649048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02917146682739</t>
+    <t xml:space="preserve">2.02917170524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208088874817</t>
+    <t xml:space="preserve">2.03208065032959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10044741630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608340263367</t>
+    <t xml:space="preserve">2.10044717788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608316421509</t>
   </si>
   <si>
     <t xml:space="preserve">2.16881370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0844464302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09753847122192</t>
+    <t xml:space="preserve">2.08444666862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09753823280334</t>
   </si>
   <si>
     <t xml:space="preserve">2.080082654953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863434791565</t>
+    <t xml:space="preserve">2.09462928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863458633423</t>
   </si>
   <si>
     <t xml:space="preserve">2.24736213684082</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">2.1891782283783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899258613586</t>
+    <t xml:space="preserve">2.16590452194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899282455444</t>
   </si>
   <si>
     <t xml:space="preserve">2.06844592094421</t>
@@ -2330,43 +2330,43 @@
     <t xml:space="preserve">2.07717347145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07280945777893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12808513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499333381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14699459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390326499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13099384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08299231529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07426428794861</t>
+    <t xml:space="preserve">2.07280969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.128084897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499309539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14553999900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14699482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390278816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13099408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0829918384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.0582640171051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04808139801025</t>
+    <t xml:space="preserve">2.04808187484741</t>
   </si>
   <si>
     <t xml:space="preserve">2.02335357666016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02771687507629</t>
+    <t xml:space="preserve">2.02771735191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.06408214569092</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">2.04226303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99426126480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789925575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03644442558289</t>
+    <t xml:space="preserve">1.99426138401031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789949417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03644466400146</t>
   </si>
   <si>
     <t xml:space="preserve">2.04517245292664</t>
@@ -2390,91 +2390,91 @@
     <t xml:space="preserve">2.02626252174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00589776039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862468242645</t>
+    <t xml:space="preserve">2.00589823722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862504005432</t>
   </si>
   <si>
     <t xml:space="preserve">1.95935082435608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97826075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080553531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280679225922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0611732006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06990075111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04080843925476</t>
+    <t xml:space="preserve">1.97826111316681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9608051776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280655384064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06117272377014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06990051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04080891609192</t>
   </si>
   <si>
     <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96807849407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134905815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098393917084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553057193756</t>
+    <t xml:space="preserve">1.96807861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9113484621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098429679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553033351898</t>
   </si>
   <si>
     <t xml:space="preserve">1.80370807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79352605342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079901218414</t>
+    <t xml:space="preserve">1.79352593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079936981201</t>
   </si>
   <si>
     <t xml:space="preserve">1.819708943367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84152781963348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8255273103714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171008110046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298241138458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752856731415</t>
+    <t xml:space="preserve">1.84152805805206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552742958069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83279991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898315906525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8517097234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752832889557</t>
   </si>
   <si>
     <t xml:space="preserve">1.8357093334198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84880113601685</t>
+    <t xml:space="preserve">1.84880101680756</t>
   </si>
   <si>
     <t xml:space="preserve">1.87062013149261</t>
@@ -2483,37 +2483,37 @@
     <t xml:space="preserve">1.79788947105408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61460971832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5986088514328</t>
+    <t xml:space="preserve">1.61460959911346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860920906067</t>
   </si>
   <si>
     <t xml:space="preserve">1.68152153491974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388079166412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351650714874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56224405765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733361721039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842368602753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278268814087</t>
+    <t xml:space="preserve">1.61751902103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56224417686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770116329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52733314037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278256893158</t>
   </si>
   <si>
     <t xml:space="preserve">1.36441791057587</t>
@@ -2531,25 +2531,25 @@
     <t xml:space="preserve">1.16150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1593189239502</t>
+    <t xml:space="preserve">1.15931880474091</t>
   </si>
   <si>
     <t xml:space="preserve">1.13386332988739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10768043994904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1142258644104</t>
+    <t xml:space="preserve">1.10768055915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11422610282898</t>
   </si>
   <si>
     <t xml:space="preserve">1.08440685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1804107427597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968320846558</t>
+    <t xml:space="preserve">1.18041086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968332767487</t>
   </si>
   <si>
     <t xml:space="preserve">1.19713854789734</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">1.11204433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12877213954926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550181388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10549855232239</t>
+    <t xml:space="preserve">1.12877237796783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550169467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10549867153168</t>
   </si>
   <si>
     <t xml:space="preserve">1.09022521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04149615764618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07640635967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24514043331146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641276359558</t>
+    <t xml:space="preserve">1.0414959192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07640647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24514055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641288280487</t>
   </si>
   <si>
     <t xml:space="preserve">1.20077514648438</t>
@@ -2594,52 +2594,52 @@
     <t xml:space="preserve">1.24223124980927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36005413532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023790836334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47351312637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58939075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649673938751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331343650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56247735023499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967908859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46080386638641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47575616836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500860691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061188220978</t>
+    <t xml:space="preserve">1.36005401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023814678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47351324558258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939063549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649650096893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331379413605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5624772310257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967920780182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4608039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47575604915619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500836849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284745693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061176300049</t>
   </si>
   <si>
     <t xml:space="preserve">1.48397958278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473437309265</t>
+    <t xml:space="preserve">1.42192912101746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473449230194</t>
   </si>
   <si>
     <t xml:space="preserve">1.37931609153748</t>
@@ -2648,55 +2648,55 @@
     <t xml:space="preserve">1.46005654335022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44884264469147</t>
+    <t xml:space="preserve">1.44884240627289</t>
   </si>
   <si>
     <t xml:space="preserve">1.43762862682343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49519348144531</t>
+    <t xml:space="preserve">1.4951936006546</t>
   </si>
   <si>
     <t xml:space="preserve">1.56546783447266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60733318328857</t>
+    <t xml:space="preserve">1.60733342170715</t>
   </si>
   <si>
     <t xml:space="preserve">1.62228500843048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64321744441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498715877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807339668274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471304416656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479493618011</t>
+    <t xml:space="preserve">1.64321780204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498703956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807351589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471316337585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479481697083</t>
   </si>
   <si>
     <t xml:space="preserve">1.7553573846817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67760670185089</t>
+    <t xml:space="preserve">1.67760694026947</t>
   </si>
   <si>
     <t xml:space="preserve">1.65069365501404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5849050283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686684608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976098060608</t>
+    <t xml:space="preserve">1.58490490913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686672687531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976121902466</t>
   </si>
   <si>
     <t xml:space="preserve">1.63125598430634</t>
@@ -2705,145 +2705,145 @@
     <t xml:space="preserve">1.60583794116974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62527537345886</t>
+    <t xml:space="preserve">1.62527549266815</t>
   </si>
   <si>
     <t xml:space="preserve">1.58341002464294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59238135814667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050143241882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70601618289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003485679626</t>
+    <t xml:space="preserve">1.59238123893738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135209560394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172255992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71050155162811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797740459442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003497600555</t>
   </si>
   <si>
     <t xml:space="preserve">1.67013120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68956863880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7478814125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72545349597931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077566623688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656417369843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78675651550293</t>
+    <t xml:space="preserve">1.68956887722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74788129329681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545313835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78077554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80021286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78675639629364</t>
   </si>
   <si>
     <t xml:space="preserve">1.85403990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8600207567215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871773719788</t>
+    <t xml:space="preserve">1.86002087593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871785640717</t>
   </si>
   <si>
     <t xml:space="preserve">1.8331071138382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79423236846924</t>
+    <t xml:space="preserve">1.79423260688782</t>
   </si>
   <si>
     <t xml:space="preserve">1.73292946815491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76881384849548</t>
+    <t xml:space="preserve">1.76881420612335</t>
   </si>
   <si>
     <t xml:space="preserve">1.83161199092865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85104978084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8226410150528</t>
+    <t xml:space="preserve">1.85105001926422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264089584351</t>
   </si>
   <si>
     <t xml:space="preserve">1.83609771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85852563381195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291501045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786671638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039122104645</t>
+    <t xml:space="preserve">1.85852551460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291512966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786719322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039110183716</t>
   </si>
   <si>
     <t xml:space="preserve">1.89142000675201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8899245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487694740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543903827667</t>
+    <t xml:space="preserve">1.88992464542389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487658977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543915748596</t>
   </si>
   <si>
     <t xml:space="preserve">1.83011674880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79124176502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666028499603</t>
+    <t xml:space="preserve">1.79124200344086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553526878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666040420532</t>
   </si>
   <si>
     <t xml:space="preserve">1.80768895149231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77928042411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460259437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8480589389801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84506905078888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646794319153</t>
+    <t xml:space="preserve">1.77928030490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460247516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170798301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84805881977081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84506869316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646818161011</t>
   </si>
   <si>
     <t xml:space="preserve">1.84058320522308</t>
@@ -2855,16 +2855,16 @@
     <t xml:space="preserve">1.82862162590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82114577293396</t>
+    <t xml:space="preserve">1.82114589214325</t>
   </si>
   <si>
     <t xml:space="preserve">1.77778518199921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71947252750397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7090060710907</t>
+    <t xml:space="preserve">1.71947276592255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900630950928</t>
   </si>
   <si>
     <t xml:space="preserve">1.71349167823792</t>
@@ -2876,37 +2876,37 @@
     <t xml:space="preserve">1.68059754371643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73442447185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395813465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497270107269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582384109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638628959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685262680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246277332306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6342465877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51762139797211</t>
+    <t xml:space="preserve">1.73442423343658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395825386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497293949127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207880496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227066993713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582360267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638617038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685226917267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63424670696259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5176215171814</t>
   </si>
   <si>
     <t xml:space="preserve">1.59836184978485</t>
@@ -2915,61 +2915,61 @@
     <t xml:space="preserve">1.74937641620636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75984287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72694873809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386202335358</t>
+    <t xml:space="preserve">1.75984299182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72694838047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386226177216</t>
   </si>
   <si>
     <t xml:space="preserve">1.80469858646393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80918443202972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8196507692337</t>
+    <t xml:space="preserve">1.80918431282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81965065002441</t>
   </si>
   <si>
     <t xml:space="preserve">1.86301112174988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91235256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93926608562469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617913246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159789085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056934356689</t>
+    <t xml:space="preserve">1.91235268115997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93926584720612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617960929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159777164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216010093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056910514832</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01497268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04074740409851</t>
+    <t xml:space="preserve">2.01497220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04074716567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710199356079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316640853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677884578705</t>
+    <t xml:space="preserve">2.03316593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677860736847</t>
   </si>
   <si>
     <t xml:space="preserve">2.00890803337097</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">2.00132727622986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99981081485748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435924530029</t>
+    <t xml:space="preserve">1.99981069564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800465583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435972213745</t>
   </si>
   <si>
     <t xml:space="preserve">2.01042413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03013372421265</t>
+    <t xml:space="preserve">2.03013396263123</t>
   </si>
   <si>
     <t xml:space="preserve">2.03468251228333</t>
@@ -3005,46 +3005,46 @@
     <t xml:space="preserve">2.05136036872864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0437798500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07561874389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06803774833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442566871643</t>
+    <t xml:space="preserve">2.04377937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07561850547791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06803798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">2.05287647247314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261939048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21358919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084668159485</t>
+    <t xml:space="preserve">2.12261962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21358871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084692001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.16203951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14687824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1332323551178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15597486495972</t>
+    <t xml:space="preserve">2.1468780040741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13323283195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1559751033783</t>
   </si>
   <si>
     <t xml:space="preserve">2.18023347854614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20145964622498</t>
+    <t xml:space="preserve">2.20146012306213</t>
   </si>
   <si>
     <t xml:space="preserve">2.27120327949524</t>
@@ -3053,16 +3053,16 @@
     <t xml:space="preserve">2.18933057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26362204551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2484610080719</t>
+    <t xml:space="preserve">2.26362252235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24846053123474</t>
   </si>
   <si>
     <t xml:space="preserve">2.2151050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21662139892578</t>
+    <t xml:space="preserve">2.21662187576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.29546141624451</t>
@@ -3071,28 +3071,28 @@
     <t xml:space="preserve">2.30000996589661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32275152206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3576238155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34852719306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35913991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38794660568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36368823051453</t>
+    <t xml:space="preserve">2.32275199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31062293052673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246206283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35762357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3485267162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35914015769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38794755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36368870735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.39249539375305</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">2.38491463661194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36520457267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823725700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430143356323</t>
+    <t xml:space="preserve">2.36520481109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823701858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.32426834106445</t>
@@ -3119,40 +3119,40 @@
     <t xml:space="preserve">2.35459160804749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34549450874329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.380366563797</t>
+    <t xml:space="preserve">2.34549522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38036680221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.4410126209259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36065626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3727855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31820368766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40007615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41523790359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4940779209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43494772911072</t>
+    <t xml:space="preserve">2.36065602302551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37278580665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31820392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40007638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765690803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41523766517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49407839775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4349479675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.41827034950256</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">2.42888307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40614104270935</t>
+    <t xml:space="preserve">2.40614128112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.30759072303772</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">2.32730078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34397840499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35610747337341</t>
+    <t xml:space="preserve">2.34397864341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35610795021057</t>
   </si>
   <si>
     <t xml:space="preserve">2.45314168930054</t>
@@ -3185,46 +3185,46 @@
     <t xml:space="preserve">2.48649740219116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4986264705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043274879456</t>
+    <t xml:space="preserve">2.49862670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043251037598</t>
   </si>
   <si>
     <t xml:space="preserve">2.44859313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54714345932007</t>
+    <t xml:space="preserve">2.54714322090149</t>
   </si>
   <si>
     <t xml:space="preserve">2.58959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685352325439</t>
+    <t xml:space="preserve">2.56685328483582</t>
   </si>
   <si>
     <t xml:space="preserve">2.64266109466553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65327429771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355948448181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52038145065308</t>
+    <t xml:space="preserve">2.65327477455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52038168907166</t>
   </si>
   <si>
     <t xml:space="preserve">2.50052428245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51579856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51427173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49899673461914</t>
+    <t xml:space="preserve">2.51579904556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427125930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49899649620056</t>
   </si>
   <si>
     <t xml:space="preserve">2.52343654632568</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">2.53412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60286712646484</t>
+    <t xml:space="preserve">2.60286688804626</t>
   </si>
   <si>
     <t xml:space="preserve">2.46386408805847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553375244141</t>
+    <t xml:space="preserve">2.42109417915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553422927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.43942403793335</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">2.48066663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4119291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262125015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46691870689392</t>
+    <t xml:space="preserve">2.41192889213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443350791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262148857117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46691918373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.45775413513184</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">2.43025898933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45928144454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706153869629</t>
+    <t xml:space="preserve">2.45928168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.43331408500671</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">2.45622682571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48372149467468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50816130638123</t>
+    <t xml:space="preserve">2.48372173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50816178321838</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023909568787</t>
@@ -3299,16 +3299,16 @@
     <t xml:space="preserve">2.64869213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63799953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67618680000305</t>
+    <t xml:space="preserve">2.63799929618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67618727684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.61814212799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60439443588257</t>
+    <t xml:space="preserve">2.60439467430115</t>
   </si>
   <si>
     <t xml:space="preserve">2.65632963180542</t>
@@ -3323,40 +3323,40 @@
     <t xml:space="preserve">2.68840718269348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63952732086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61966919898987</t>
+    <t xml:space="preserve">2.63952708244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61966967582703</t>
   </si>
   <si>
     <t xml:space="preserve">2.59370183944702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54634928703308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53565669059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885437965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482126235962</t>
+    <t xml:space="preserve">2.54634952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53565621376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885390281677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5448215007782</t>
   </si>
   <si>
     <t xml:space="preserve">2.53260183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50663423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54329442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997427940369</t>
+    <t xml:space="preserve">2.5066339969635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58148169517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54329419136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997404098511</t>
   </si>
   <si>
     <t xml:space="preserve">2.49135947227478</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">2.48830389976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48219394683838</t>
+    <t xml:space="preserve">2.48219418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.40734648704529</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">2.38290619850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48524880409241</t>
+    <t xml:space="preserve">2.48524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.44247889518738</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">2.47455644607544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52801918983459</t>
+    <t xml:space="preserve">2.52801895141602</t>
   </si>
   <si>
     <t xml:space="preserve">2.4898316860199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52649188041687</t>
+    <t xml:space="preserve">2.52649164199829</t>
   </si>
   <si>
     <t xml:space="preserve">2.52496409416199</t>
@@ -3404,52 +3404,52 @@
     <t xml:space="preserve">2.55856895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55398654937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54787707328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56162476539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52954649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45164394378662</t>
+    <t xml:space="preserve">2.5539870262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54787659645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56162428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732635498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45164370536804</t>
   </si>
   <si>
     <t xml:space="preserve">2.42873167991638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42414927482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42567658424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45011639595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4272038936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40581917762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510716438293</t>
+    <t xml:space="preserve">2.42414903640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4256763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4501166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42720437049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40581893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5051064491272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596129417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901615142822</t>
+    <t xml:space="preserve">2.38596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901662826538</t>
   </si>
   <si>
     <t xml:space="preserve">2.37221360206604</t>
@@ -3458,31 +3458,31 @@
     <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37355279922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36727380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4253568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791508674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40965914726257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35157585144043</t>
+    <t xml:space="preserve">2.37355327606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36727404594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42535662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791532516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42378735542297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40965867042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35157561302185</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000586509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34372663497925</t>
+    <t xml:space="preserve">2.34372687339783</t>
   </si>
   <si>
     <t xml:space="preserve">2.34058713912964</t>
@@ -3497,22 +3497,22 @@
     <t xml:space="preserve">2.34686636924744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39396071434021</t>
+    <t xml:space="preserve">2.39396095275879</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4473340511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4394850730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47402095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361351966858</t>
+    <t xml:space="preserve">2.44733428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43948531150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4740207195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361328125</t>
   </si>
   <si>
     <t xml:space="preserve">2.44105505943298</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">2.45675325393677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46931147575378</t>
+    <t xml:space="preserve">2.46931171417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.46774172782898</t>
@@ -3536,28 +3536,28 @@
     <t xml:space="preserve">2.45047378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27622485160828</t>
+    <t xml:space="preserve">2.27622509002686</t>
   </si>
   <si>
     <t xml:space="preserve">2.26837587356567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25581741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29977202415466</t>
+    <t xml:space="preserve">2.25581765174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738668441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547045707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29977178573608</t>
   </si>
   <si>
     <t xml:space="preserve">2.29192304611206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27151560783386</t>
+    <t xml:space="preserve">2.27151536941528</t>
   </si>
   <si>
     <t xml:space="preserve">2.36256456375122</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">2.31076073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26994585990906</t>
+    <t xml:space="preserve">2.32017946243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26994562149048</t>
   </si>
   <si>
     <t xml:space="preserve">2.22913026809692</t>
@@ -3581,28 +3581,28 @@
     <t xml:space="preserve">2.24639868736267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244359970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15064001083374</t>
+    <t xml:space="preserve">2.20244383811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15064024925232</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14122128486633</t>
+    <t xml:space="preserve">2.14122104644775</t>
   </si>
   <si>
     <t xml:space="preserve">2.20401358604431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16319894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732667922974</t>
+    <t xml:space="preserve">2.19773459434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16319870948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732691764832</t>
   </si>
   <si>
     <t xml:space="preserve">2.18674564361572</t>
@@ -3617,52 +3617,52 @@
     <t xml:space="preserve">2.15534973144531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14750075340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15848875045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21186280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23070073127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21657180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22756052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26366639137268</t>
+    <t xml:space="preserve">2.14750027656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15848922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814179420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23070025444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21657204627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2275607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26366662979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.31860971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29349303245544</t>
+    <t xml:space="preserve">2.29349255561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.24796843528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23540997505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24011969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24482870101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291152000427</t>
+    <t xml:space="preserve">2.2354097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24011898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24482846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291175842285</t>
   </si>
   <si>
     <t xml:space="preserve">2.34529662132263</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">2.20087385177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831562995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22128129005432</t>
+    <t xml:space="preserve">2.18831515312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2212815284729</t>
   </si>
   <si>
     <t xml:space="preserve">2.23227047920227</t>
@@ -3689,16 +3689,16 @@
     <t xml:space="preserve">2.23697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1993043422699</t>
+    <t xml:space="preserve">2.19930410385132</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599101066589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27936458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16476798057556</t>
+    <t xml:space="preserve">2.27936434745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16476845741272</t>
   </si>
   <si>
     <t xml:space="preserve">2.03447389602661</t>
@@ -3707,103 +3707,103 @@
     <t xml:space="preserve">2.09255695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05802130699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9795309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441365242004</t>
+    <t xml:space="preserve">2.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953069210052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441389083862</t>
   </si>
   <si>
     <t xml:space="preserve">2.0109269618988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92615711688995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766662120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057227611542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254993915558</t>
+    <t xml:space="preserve">1.92615723609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592327594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254981994629</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807429790497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91045904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009357213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9936591386795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796082496643</t>
+    <t xml:space="preserve">1.91045892238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202914714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00935745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99365890026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9779611825943</t>
   </si>
   <si>
     <t xml:space="preserve">2.01877593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01720643043518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99208903312683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98894965648651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99679839611053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959105491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854209899902</t>
+    <t xml:space="preserve">2.01720595359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9920893907547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9889497756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99679827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854186058044</t>
   </si>
   <si>
     <t xml:space="preserve">1.97639083862305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88220226764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301762104034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790046215057</t>
+    <t xml:space="preserve">1.88220238685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516840457916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301797866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790034294128</t>
   </si>
   <si>
     <t xml:space="preserve">1.89947044849396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92124760150909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576633930206</t>
+    <t xml:space="preserve">1.92124783992767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576622009277</t>
   </si>
   <si>
     <t xml:space="preserve">2.01642322540283</t>
@@ -3812,91 +3812,91 @@
     <t xml:space="preserve">2.01158380508423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96964192390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543783664703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87607991695404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770040035248</t>
+    <t xml:space="preserve">1.969642162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543759822845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87608003616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770028114319</t>
   </si>
   <si>
     <t xml:space="preserve">1.91156888008118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90188992023468</t>
+    <t xml:space="preserve">1.90189015865326</t>
   </si>
   <si>
     <t xml:space="preserve">1.89221131801605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84704339504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607233524323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77122592926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79703617095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81316757202148</t>
+    <t xml:space="preserve">1.84704375267029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77122604846954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79703605175018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81316721439362</t>
   </si>
   <si>
     <t xml:space="preserve">1.86801445484161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90672945976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9438316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963458061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382469654083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802155971527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93253993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479551792145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318936347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254704475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02932834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609448432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448868751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480937004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448122501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97770762443542</t>
+    <t xml:space="preserve">1.90672981739044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963481903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802179813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9325395822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479527950287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254680633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02932858467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609460353851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448892593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480984687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448134422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97770738601685</t>
   </si>
   <si>
     <t xml:space="preserve">1.99061274528503</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">1.87124049663544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8292989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285387516022</t>
+    <t xml:space="preserve">1.82929921150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285375595093</t>
   </si>
   <si>
     <t xml:space="preserve">1.88898491859436</t>
@@ -3920,61 +3920,61 @@
     <t xml:space="preserve">1.86317479610443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85833549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84381747245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672247409821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88253235816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87769317626953</t>
+    <t xml:space="preserve">1.85833537578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381687641144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87769305706024</t>
   </si>
   <si>
     <t xml:space="preserve">1.84865665435791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80187559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8115541934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78574419021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81800711154938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86962723731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8357515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768583297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350317955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9389922618866</t>
+    <t xml:space="preserve">1.80187547206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81155455112457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993382930756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78574407100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81800675392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86962735652924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575165271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768595218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93899250030518</t>
   </si>
   <si>
     <t xml:space="preserve">1.95189762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99383866786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802914142609</t>
+    <t xml:space="preserve">1.99383902549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802890300751</t>
   </si>
   <si>
     <t xml:space="preserve">1.99222600460052</t>
@@ -3983,28 +3983,28 @@
     <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07449555397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05029916763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0519118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03416728973389</t>
+    <t xml:space="preserve">2.07449626922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05029892921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05191206932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03416776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.01319670677185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07288289070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09546661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07933521270752</t>
+    <t xml:space="preserve">2.07288265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09546709060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07933568954468</t>
   </si>
   <si>
     <t xml:space="preserve">2.07610893249512</t>
@@ -4016,40 +4016,40 @@
     <t xml:space="preserve">2.00835704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98899960517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9551237821579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932064533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866411685944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91318213939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931354045868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286856174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9454448223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8373646736145</t>
+    <t xml:space="preserve">1.98899972438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512366294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932088375092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866399765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91318237781525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931377887726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286808490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9648026227951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94544470310211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83736479282379</t>
   </si>
   <si>
     <t xml:space="preserve">1.91025614738464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82647287845612</t>
+    <t xml:space="preserve">1.82647299766541</t>
   </si>
   <si>
     <t xml:space="preserve">1.85495913028717</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">1.81474316120148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78290569782257</t>
+    <t xml:space="preserve">1.78290557861328</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845813035965</t>
@@ -4067,61 +4067,61 @@
     <t xml:space="preserve">1.79128384590149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77620279788971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72928416728973</t>
+    <t xml:space="preserve">1.776202917099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72928428649902</t>
   </si>
   <si>
     <t xml:space="preserve">1.73933839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74604094028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79798638820648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966235160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333739757538</t>
+    <t xml:space="preserve">1.74604117870331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79798662662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966223239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85663521289825</t>
+    <t xml:space="preserve">1.85663461685181</t>
   </si>
   <si>
     <t xml:space="preserve">1.86166167259216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87674283981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171578407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517545700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360712051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203961849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685034751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355324745178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879627227783</t>
+    <t xml:space="preserve">1.87674260139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171566486359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517521858215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9136073589325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203949928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8968505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355336666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701256275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879651069641</t>
   </si>
   <si>
     <t xml:space="preserve">1.94376921653748</t>
@@ -4133,22 +4133,22 @@
     <t xml:space="preserve">2.17836213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19176745414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160559654236</t>
+    <t xml:space="preserve">2.19176697731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16160535812378</t>
   </si>
   <si>
     <t xml:space="preserve">2.18506479263306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29901003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29230737686157</t>
+    <t xml:space="preserve">2.29900979995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29230713844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.28895592689514</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">2.3258204460144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33419871330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34257745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32917165756226</t>
+    <t xml:space="preserve">2.33419895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34257698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32917213439941</t>
   </si>
   <si>
     <t xml:space="preserve">2.25711846351624</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30068564414978</t>
+    <t xml:space="preserve">2.3006854057312</t>
   </si>
   <si>
     <t xml:space="preserve">2.31576633453369</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">2.29733443260193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31409120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30403709411621</t>
+    <t xml:space="preserve">2.31409096717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30403661727905</t>
   </si>
   <si>
     <t xml:space="preserve">2.33755016326904</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">2.44981956481934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46657586097717</t>
+    <t xml:space="preserve">2.46657609939575</t>
   </si>
   <si>
     <t xml:space="preserve">2.46490049362183</t>
@@ -4208,16 +4208,16 @@
     <t xml:space="preserve">2.4799816608429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4632248878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38614439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40122532844543</t>
+    <t xml:space="preserve">2.46322512626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306279182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38614463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40122509002686</t>
   </si>
   <si>
     <t xml:space="preserve">2.40290117263794</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">2.38279294967651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295528411865</t>
+    <t xml:space="preserve">2.41295504570007</t>
   </si>
   <si>
     <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36938762664795</t>
+    <t xml:space="preserve">2.36938786506653</t>
   </si>
   <si>
     <t xml:space="preserve">2.37776613235474</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">2.36100959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34927940368652</t>
+    <t xml:space="preserve">2.34927988052368</t>
   </si>
   <si>
     <t xml:space="preserve">2.37944149971008</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">2.38782000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49171113967896</t>
+    <t xml:space="preserve">2.49171090126038</t>
   </si>
   <si>
     <t xml:space="preserve">2.45987391471863</t>
@@ -4262,25 +4262,25 @@
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776392936707</t>
+    <t xml:space="preserve">2.68776345252991</t>
   </si>
   <si>
     <t xml:space="preserve">2.64922332763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77824926376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80170917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77322244644165</t>
+    <t xml:space="preserve">2.77824950218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80170893669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77322268486023</t>
   </si>
   <si>
     <t xml:space="preserve">2.78160095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83019495010376</t>
+    <t xml:space="preserve">2.83019518852234</t>
   </si>
   <si>
     <t xml:space="preserve">2.93073487281799</t>
@@ -4289,13 +4289,13 @@
     <t xml:space="preserve">2.92905902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224838256836</t>
+    <t xml:space="preserve">2.90224862098694</t>
   </si>
   <si>
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03295016288757</t>
+    <t xml:space="preserve">3.03294992446899</t>
   </si>
   <si>
     <t xml:space="preserve">3.06311225891113</t>
@@ -4304,13 +4304,13 @@
     <t xml:space="preserve">3.11840915679932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1502468585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16030097007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20554351806641</t>
+    <t xml:space="preserve">3.15024709701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16030120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554375648499</t>
   </si>
   <si>
     <t xml:space="preserve">3.20219230651855</t>
@@ -4325,43 +4325,43 @@
     <t xml:space="preserve">3.18878698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19213843345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1988410949707</t>
+    <t xml:space="preserve">3.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19884085655212</t>
   </si>
   <si>
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2926778793335</t>
+    <t xml:space="preserve">3.29267811775208</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33792114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132646560669</t>
+    <t xml:space="preserve">3.3379213809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132622718811</t>
   </si>
   <si>
     <t xml:space="preserve">3.40494775772095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25581336021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34797549247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3178129196167</t>
+    <t xml:space="preserve">3.25581312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34797501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781315803528</t>
   </si>
   <si>
     <t xml:space="preserve">3.39321827888489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36473155021667</t>
+    <t xml:space="preserve">3.3647313117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.35467791557312</t>
@@ -4382,13 +4382,13 @@
     <t xml:space="preserve">3.13349032402039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19046306610107</t>
+    <t xml:space="preserve">3.1904628276825</t>
   </si>
   <si>
     <t xml:space="preserve">3.23403000831604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24575972557068</t>
+    <t xml:space="preserve">3.2457594871521</t>
   </si>
   <si>
     <t xml:space="preserve">3.23905682563782</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">3.21559762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2641921043396</t>
+    <t xml:space="preserve">3.26419186592102</t>
   </si>
   <si>
     <t xml:space="preserve">3.29770517349243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29435396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3429479598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510961532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30105638504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40159606933594</t>
+    <t xml:space="preserve">3.294353723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34294819831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510985374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30105662345886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40159583091736</t>
   </si>
   <si>
     <t xml:space="preserve">3.38986682891846</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">3.37981271743774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3664071559906</t>
+    <t xml:space="preserve">3.36640739440918</t>
   </si>
   <si>
     <t xml:space="preserve">3.37143445014954</t>
@@ -4436,16 +4436,16 @@
     <t xml:space="preserve">3.32619142532349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31243991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23508620262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21789693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22305393218994</t>
+    <t xml:space="preserve">3.31243968009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23508644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2178966999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22305369377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.2041449546814</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">3.12335395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05975246429443</t>
+    <t xml:space="preserve">3.05975222587585</t>
   </si>
   <si>
     <t xml:space="preserve">3.09413146972656</t>
@@ -4484,10 +4484,10 @@
     <t xml:space="preserve">3.13366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194870948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18867444992065</t>
+    <t xml:space="preserve">3.13194894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18867468833923</t>
   </si>
   <si>
     <t xml:space="preserve">3.22649145126343</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">3.09928846359253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16117119789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19383120536804</t>
+    <t xml:space="preserve">3.16117095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
     <t xml:space="preserve">3.15257620811462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11991620063782</t>
+    <t xml:space="preserve">3.11991596221924</t>
   </si>
   <si>
     <t xml:space="preserve">3.09756970405579</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">3.14741945266724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10960245132446</t>
+    <t xml:space="preserve">3.10960221290588</t>
   </si>
   <si>
     <t xml:space="preserve">3.12507271766663</t>
@@ -4589,13 +4589,13 @@
     <t xml:space="preserve">3.00818347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01162123680115</t>
+    <t xml:space="preserve">3.01162147521973</t>
   </si>
   <si>
     <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98755621910095</t>
+    <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583674430847</t>
@@ -4613,13 +4613,13 @@
     <t xml:space="preserve">2.97552299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94458222389221</t>
+    <t xml:space="preserve">2.94458198547363</t>
   </si>
   <si>
     <t xml:space="preserve">2.93083024024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9205162525177</t>
+    <t xml:space="preserve">2.92051649093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.87582349777222</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">2.87754249572754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88785624504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91020226478577</t>
+    <t xml:space="preserve">2.88785600662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91020250320435</t>
   </si>
   <si>
     <t xml:space="preserve">2.95661473274231</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005249023438</t>
+    <t xml:space="preserve">2.96005272865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.94286274909973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99786996841431</t>
+    <t xml:space="preserve">2.99786972999573</t>
   </si>
   <si>
     <t xml:space="preserve">3.05115747451782</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">3.03053021430969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04943871498108</t>
+    <t xml:space="preserve">3.0494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">3.05459523200989</t>
@@ -4664,19 +4664,19 @@
     <t xml:space="preserve">3.08725571632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04256248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02021646499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99615073204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03912496566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06490921974182</t>
+    <t xml:space="preserve">3.04256272315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02021622657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99615049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03912472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0649094581604</t>
   </si>
   <si>
     <t xml:space="preserve">2.9749481678009</t>
@@ -5982,6 +5982,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.95000004768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95500004291534</t>
   </si>
 </sst>
 </file>
@@ -71034,7 +71037,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6493634259</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>840058</v>
@@ -71055,6 +71058,32 @@
         <v>1989</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493171296</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>818502</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>1.99399995803833</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>1.94400000572205</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>1.95899999141693</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>1.95500004291534</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847180366516</t>
+    <t xml:space="preserve">1.42847192287445</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3917795419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3601485490799</t>
+    <t xml:space="preserve">1.39177942276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36014819145203</t>
   </si>
   <si>
     <t xml:space="preserve">1.30827283859253</t>
@@ -65,70 +65,70 @@
     <t xml:space="preserve">1.28676331043243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23425543308258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831751823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009338855743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18680810928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1159542798996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09191453456879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478835582733</t>
+    <t xml:space="preserve">1.23425555229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009350776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18680846691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11595416069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09191417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478847503662</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644216537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19440019130707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.232990026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20641958713531</t>
+    <t xml:space="preserve">1.1943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23299026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20641946792603</t>
   </si>
   <si>
     <t xml:space="preserve">1.22097027301788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24437761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087090969086</t>
+    <t xml:space="preserve">1.24437737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087067127228</t>
   </si>
   <si>
     <t xml:space="preserve">1.1064647436142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11721956729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12164783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04699802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826283454895</t>
+    <t xml:space="preserve">1.1172194480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12164795398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04699778556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826307296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.11848473548889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11089324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366770744324</t>
+    <t xml:space="preserve">1.11089313030243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366782665253</t>
   </si>
   <si>
     <t xml:space="preserve">1.17795169353485</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">1.21337878704071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16213607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17921674251556</t>
+    <t xml:space="preserve">1.16213583946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578718185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17921698093414</t>
   </si>
   <si>
     <t xml:space="preserve">1.13872873783112</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">1.1317697763443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15770733356476</t>
+    <t xml:space="preserve">1.15770745277405</t>
   </si>
   <si>
     <t xml:space="preserve">1.24311220645905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29688549041748</t>
+    <t xml:space="preserve">1.29688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.29182457923889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29941618442535</t>
+    <t xml:space="preserve">1.29941582679749</t>
   </si>
   <si>
     <t xml:space="preserve">1.32598638534546</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">1.26525413990021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27917182445526</t>
+    <t xml:space="preserve">1.27917194366455</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892794132233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20199143886566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135867595673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376730918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18238008022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464383602142</t>
+    <t xml:space="preserve">1.20199131965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413313388824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135903358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1823798418045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20452225208282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464407444</t>
   </si>
   <si>
     <t xml:space="preserve">1.1918693780899</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.18554306030273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15264642238617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123685359955</t>
+    <t xml:space="preserve">1.15264654159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123673439026</t>
   </si>
   <si>
     <t xml:space="preserve">1.1798495054245</t>
@@ -224,79 +224,79 @@
     <t xml:space="preserve">1.11152565479279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09570980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709738731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417829036713</t>
+    <t xml:space="preserve">1.09571015834808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546591758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709750652313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417817115784</t>
   </si>
   <si>
     <t xml:space="preserve">1.14062654972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16719698905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1545444726944</t>
+    <t xml:space="preserve">1.16719722747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15454459190369</t>
   </si>
   <si>
     <t xml:space="preserve">1.19227039813995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17405760288239</t>
+    <t xml:space="preserve">1.17405784130096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24820899963379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25406277179718</t>
+    <t xml:space="preserve">1.25406289100647</t>
   </si>
   <si>
     <t xml:space="preserve">1.27812945842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26837289333344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918695449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138160705566</t>
+    <t xml:space="preserve">1.26837277412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918719291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138184547424</t>
   </si>
   <si>
     <t xml:space="preserve">1.27682852745056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25731515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495649337769</t>
+    <t xml:space="preserve">1.2573150396347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495661258698</t>
   </si>
   <si>
     <t xml:space="preserve">1.19031894207001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19096946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796051502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527430057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16690313816071</t>
+    <t xml:space="preserve">1.1909693479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.17080557346344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16755330562592</t>
+    <t xml:space="preserve">1.16755342483521</t>
   </si>
   <si>
     <t xml:space="preserve">1.16495168209076</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">1.18056225776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15389370918274</t>
+    <t xml:space="preserve">1.1538941860199</t>
   </si>
   <si>
     <t xml:space="preserve">1.16300022602081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16950476169586</t>
+    <t xml:space="preserve">1.16950464248657</t>
   </si>
   <si>
     <t xml:space="preserve">1.15649569034576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16169929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1773099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901813030243</t>
+    <t xml:space="preserve">1.16169941425323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17731010913849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18901801109314</t>
   </si>
   <si>
     <t xml:space="preserve">1.14283633232117</t>
@@ -335,58 +335,58 @@
     <t xml:space="preserve">1.12852644920349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11031401157379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09665465354919</t>
+    <t xml:space="preserve">1.11031377315521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0966545343399</t>
   </si>
   <si>
     <t xml:space="preserve">1.10641133785248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055756568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11486673355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250866413116</t>
+    <t xml:space="preserve">1.10055720806122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11486721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250890254974</t>
   </si>
   <si>
     <t xml:space="preserve">1.05112314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05372512340546</t>
+    <t xml:space="preserve">1.05372488498688</t>
   </si>
   <si>
     <t xml:space="preserve">1.04657018184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526937007904</t>
+    <t xml:space="preserve">1.04526925086975</t>
   </si>
   <si>
     <t xml:space="preserve">1.10185813903809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13177895545959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120761394501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12917673587799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05307459831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255308628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485650539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184898376465</t>
+    <t xml:space="preserve">1.13177871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120785236359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05307447910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184659957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.02640604972839</t>
@@ -395,211 +395,211 @@
     <t xml:space="preserve">1.01339721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982826173305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321637630463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97762268781662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00364077091217</t>
+    <t xml:space="preserve">0.982826232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321697235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968516409397125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671231746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00364053249359</t>
   </si>
   <si>
     <t xml:space="preserve">0.950954496860504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980874836444855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970468044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96916675567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118211746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96591454744339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759844303131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437564849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05957877635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06608378887177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892860889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283104419708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673407554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340238571167</t>
+    <t xml:space="preserve">0.980874717235565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118032932281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965914607048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958759665489197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437552928925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05957901477814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06608366966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974302768707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892872810364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283116340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673419475555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340214729309</t>
   </si>
   <si>
     <t xml:space="preserve">1.06022930145264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08559715747833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09275162220001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1142166852951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09795558452606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07779145240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07388889789581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1090133190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746871471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348685741425</t>
+    <t xml:space="preserve">1.08559703826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0927517414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11421692371368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09795534610748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07779157161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0738890171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10901319980621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746919155121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348673820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.11876976490021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13828313350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14543831348419</t>
+    <t xml:space="preserve">1.13828337192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543807506561</t>
   </si>
   <si>
     <t xml:space="preserve">1.14023447036743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12787616252899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218604564667</t>
+    <t xml:space="preserve">1.1278760433197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218592643738</t>
   </si>
   <si>
     <t xml:space="preserve">1.15129220485687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16234946250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803993701935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299505710602</t>
+    <t xml:space="preserve">1.16234982013702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14804005622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0829952955246</t>
   </si>
   <si>
     <t xml:space="preserve">1.10315907001495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09600400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08169424533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09990692138672</t>
+    <t xml:space="preserve">1.09600424766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08169436454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09990668296814</t>
   </si>
   <si>
     <t xml:space="preserve">1.0921014547348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10511064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11356639862061</t>
+    <t xml:space="preserve">1.10511028766632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11356627941132</t>
   </si>
   <si>
     <t xml:space="preserve">1.08949971199036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07584023475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234477043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925615787506</t>
+    <t xml:space="preserve">1.07584011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234488964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07518994808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0875483751297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07453918457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762755870819</t>
+    <t xml:space="preserve">1.07518970966339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08754813671112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07453942298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827820301056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762779712677</t>
   </si>
   <si>
     <t xml:space="preserve">1.07323849201202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933581829071</t>
+    <t xml:space="preserve">1.06933605670929</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04722046852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047285556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348192691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03421175479889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144587993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175886631012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956808507442474</t>
+    <t xml:space="preserve">1.04722058773041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348168849945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0342116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144576072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175767421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95680832862854</t>
   </si>
   <si>
     <t xml:space="preserve">0.93339204788208</t>
@@ -608,46 +608,46 @@
     <t xml:space="preserve">0.931440889835358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936644613742828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653327465057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95355623960495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962662220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157982349396</t>
+    <t xml:space="preserve">0.93664425611496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653267860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953556060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9626624584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157922744751</t>
   </si>
   <si>
     <t xml:space="preserve">0.957458674907684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955507338047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986729025840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965264081954956</t>
+    <t xml:space="preserve">0.955507576465607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986728966236115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965264141559601</t>
   </si>
   <si>
     <t xml:space="preserve">0.940547049045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986078560352325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315390110016</t>
+    <t xml:space="preserve">0.98607861995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835244655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429093837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315402030945</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
@@ -662,76 +662,76 @@
     <t xml:space="preserve">1.02120268344879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04201710224152</t>
+    <t xml:space="preserve">1.04201686382294</t>
   </si>
   <si>
     <t xml:space="preserve">1.04917192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02770721912384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852139949799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356111049652</t>
+    <t xml:space="preserve">1.02770709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852163791656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0335613489151</t>
   </si>
   <si>
     <t xml:space="preserve">1.03095948696136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03160989284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567634105682</t>
+    <t xml:space="preserve">1.03161013126373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567622184753</t>
   </si>
   <si>
     <t xml:space="preserve">1.05502593517303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03291070461273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0355122089386</t>
+    <t xml:space="preserve">1.03291082382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03551244735718</t>
   </si>
   <si>
     <t xml:space="preserve">1.01860094070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999087393283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932392120361</t>
+    <t xml:space="preserve">0.999087333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925146579742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932451725006</t>
   </si>
   <si>
     <t xml:space="preserve">1.00494146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02510547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999737799167633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981293678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534254074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029837608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401238441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905714511871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0166494846344</t>
+    <t xml:space="preserve">1.0251053571701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737918376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534194469452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029778003693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401178836823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905476093292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01664936542511</t>
   </si>
   <si>
     <t xml:space="preserve">1.01404774188995</t>
@@ -740,34 +740,34 @@
     <t xml:space="preserve">1.04136657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02965867519379</t>
+    <t xml:space="preserve">1.0296585559845</t>
   </si>
   <si>
     <t xml:space="preserve">0.991281867027283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00949466228485</t>
+    <t xml:space="preserve">1.00949454307556</t>
   </si>
   <si>
     <t xml:space="preserve">1.01795041561127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01469814777374</t>
+    <t xml:space="preserve">1.01469826698303</t>
   </si>
   <si>
     <t xml:space="preserve">1.03226041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07063639163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06218075752258</t>
+    <t xml:space="preserve">1.070636510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06218099594116</t>
   </si>
   <si>
     <t xml:space="preserve">1.09470319747925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1447879076004</t>
+    <t xml:space="preserve">1.14478743076324</t>
   </si>
   <si>
     <t xml:space="preserve">1.18251371383667</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">1.23585033416748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845219612122</t>
+    <t xml:space="preserve">1.23845243453979</t>
   </si>
   <si>
     <t xml:space="preserve">1.21633696556091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20983242988586</t>
+    <t xml:space="preserve">1.20983254909515</t>
   </si>
   <si>
     <t xml:space="preserve">1.21438562870026</t>
@@ -794,52 +794,52 @@
     <t xml:space="preserve">1.21308469772339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20072603225708</t>
+    <t xml:space="preserve">1.20072615146637</t>
   </si>
   <si>
     <t xml:space="preserve">1.21893858909607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22023940086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527946949005</t>
+    <t xml:space="preserve">1.22023963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527923107147</t>
   </si>
   <si>
     <t xml:space="preserve">1.18381452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20267748832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446505069733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16430115699768</t>
+    <t xml:space="preserve">1.20267760753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446493148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16430127620697</t>
   </si>
   <si>
     <t xml:space="preserve">1.17600905895233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21999979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194684505463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268378734589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482893943787</t>
+    <t xml:space="preserve">1.21999967098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268402576447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482929706573</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28777754306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.266974568367</t>
+    <t xml:space="preserve">1.28777766227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26697432994843</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">1.24348711967468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24415802955627</t>
+    <t xml:space="preserve">1.24415814876556</t>
   </si>
   <si>
     <t xml:space="preserve">1.22738146781921</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">1.24818444252014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25422418117523</t>
+    <t xml:space="preserve">1.25422406196594</t>
   </si>
   <si>
     <t xml:space="preserve">1.2736850976944</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">1.24147391319275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23006570339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831638813019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26294803619385</t>
+    <t xml:space="preserve">1.23006546497345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831650733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26294791698456</t>
   </si>
   <si>
     <t xml:space="preserve">1.31462001800537</t>
@@ -884,70 +884,70 @@
     <t xml:space="preserve">1.30992269515991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059372425079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200181484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3414626121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3045539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35555529594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018658638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689723491669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3448178768158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34079170227051</t>
+    <t xml:space="preserve">1.3105936050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200193405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146296977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30455422401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35555517673492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689747333527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481799602509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3407918214798</t>
   </si>
   <si>
     <t xml:space="preserve">1.32669937610626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32602834701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30388283729553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925154685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29650127887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34213376045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871234416962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864655017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031877040863</t>
+    <t xml:space="preserve">1.32602822780609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30388295650482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925142765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29650151729584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34213399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031865119934</t>
   </si>
   <si>
     <t xml:space="preserve">1.38239777088165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37434530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010984897614</t>
+    <t xml:space="preserve">1.3743451833725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010949134827</t>
   </si>
   <si>
     <t xml:space="preserve">1.43876731395721</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">1.48976874351501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46158361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46024179458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50721633434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540134429932</t>
+    <t xml:space="preserve">1.46158385276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46024167537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50721621513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453245639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540110588074</t>
   </si>
   <si>
     <t xml:space="preserve">1.51929545402527</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">1.50050568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5058741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829426288605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45755732059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48037374019623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44547808170319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45621538162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45889961719513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279432296753</t>
+    <t xml:space="preserve">1.50587439537048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829438209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45755743980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48037362098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44547820091248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950473308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45621514320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45889937877655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279396533966</t>
   </si>
   <si>
     <t xml:space="preserve">1.57566523551941</t>
@@ -1016,73 +1016,73 @@
     <t xml:space="preserve">1.66290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62129783630371</t>
+    <t xml:space="preserve">1.62129747867584</t>
   </si>
   <si>
     <t xml:space="preserve">1.58640217781067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59042859077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727094650269</t>
+    <t xml:space="preserve">1.59042835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727166175842</t>
   </si>
   <si>
     <t xml:space="preserve">1.64411401748657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60787653923035</t>
+    <t xml:space="preserve">1.60787642002106</t>
   </si>
   <si>
     <t xml:space="preserve">1.61458671092987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5971394777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995565891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277195930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350925922394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6239823102951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72329986095428</t>
+    <t xml:space="preserve">1.59713935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277160167694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350866317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398219108582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6306928396225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.723299741745</t>
   </si>
   <si>
     <t xml:space="preserve">1.70987844467163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66558825969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853638648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048344135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719397068024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108843803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68572020530701</t>
+    <t xml:space="preserve">1.66558837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853626728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048367977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732651233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108879566193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6857203245163</t>
   </si>
   <si>
     <t xml:space="preserve">1.66693019866943</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">1.66424584388733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67632496356964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753519535065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740336894989</t>
+    <t xml:space="preserve">1.67632520198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753531455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740313053131</t>
   </si>
   <si>
     <t xml:space="preserve">1.64679825305939</t>
@@ -1112,88 +1112,88 @@
     <t xml:space="preserve">1.7743011713028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75819528102875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74880051612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73806309700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624822616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832770347595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161681652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416886806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564322948456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208986759186</t>
+    <t xml:space="preserve">1.75819504261017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74880027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73806345462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7286684513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624834537506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174876213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832734584808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161633968353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564311027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208974838257</t>
   </si>
   <si>
     <t xml:space="preserve">1.74074757099152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7353789806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940575122833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503823280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772211074829</t>
+    <t xml:space="preserve">1.73537933826447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940551280975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953757762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503811359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772222995758</t>
   </si>
   <si>
     <t xml:space="preserve">1.78101134300232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81188070774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79845941066742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261765003204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248606204987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435590267181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89911961555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88704037666321</t>
+    <t xml:space="preserve">1.81188094615936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.798459649086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802485704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067071437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435566425323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88704013824463</t>
   </si>
   <si>
     <t xml:space="preserve">1.88569796085358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84543395042419</t>
+    <t xml:space="preserve">1.84543430805206</t>
   </si>
   <si>
     <t xml:space="preserve">1.79577541351318</t>
@@ -1202,118 +1202,118 @@
     <t xml:space="preserve">1.72598421573639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71793115139008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893198490143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698528766632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222157478333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356375217438</t>
+    <t xml:space="preserve">1.71793138980865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001062870026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893210411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698493003845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222169399261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356387138367</t>
   </si>
   <si>
     <t xml:space="preserve">1.70316815376282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69645714759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68035173416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69511473178864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243061542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766714096069</t>
+    <t xml:space="preserve">1.69645762443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68035125732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6951150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69243085384369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67766761779785</t>
   </si>
   <si>
     <t xml:space="preserve">1.63874530792236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64814066886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653460025787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5702965259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57432305812836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57969152927399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687499046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51392686367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6320344209671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229866981506</t>
+    <t xml:space="preserve">1.64814054965973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57029640674591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57432281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5796914100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345393180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51392710208893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63203477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229902744293</t>
   </si>
   <si>
     <t xml:space="preserve">1.66827237606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75148463249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611592292786</t>
+    <t xml:space="preserve">1.75148499011993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611604213715</t>
   </si>
   <si>
     <t xml:space="preserve">1.71390473842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72195756435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606131076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385000705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371794223785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674328327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197933197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54613816738129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5488224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54748034477234</t>
+    <t xml:space="preserve">1.72195792198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71658909320831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384976863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371782302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53674304485321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546138048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54882264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54748022556305</t>
   </si>
   <si>
     <t xml:space="preserve">1.53271687030792</t>
@@ -1325,82 +1325,82 @@
     <t xml:space="preserve">1.54076969623566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54211175441742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869069576263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5676121711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955934524536</t>
+    <t xml:space="preserve">1.54211187362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869057655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56761229038239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955982208252</t>
   </si>
   <si>
     <t xml:space="preserve">1.52600622177124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58774447441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6119030714035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324489116669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56627035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782133102417</t>
+    <t xml:space="preserve">1.58774435520172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190283298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519230365753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324512958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56626999378204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782145023346</t>
   </si>
   <si>
     <t xml:space="preserve">1.51661145687103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5031898021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4964793920517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990056991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266178131104</t>
+    <t xml:space="preserve">1.50318992137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49647927284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990068912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266190052032</t>
   </si>
   <si>
     <t xml:space="preserve">1.4817156791687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.462926030159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46695244312286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48439979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52332198619843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405904769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662510871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56837058067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947949409485</t>
+    <t xml:space="preserve">1.46292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46695232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305773735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439991474152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332186698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405928611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662498950958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56837069988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947937488556</t>
   </si>
   <si>
     <t xml:space="preserve">1.51884293556213</t>
@@ -1412,31 +1412,31 @@
     <t xml:space="preserve">1.49958252906799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56286752223969</t>
+    <t xml:space="preserve">1.56286764144897</t>
   </si>
   <si>
     <t xml:space="preserve">1.57387387752533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55186128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52159440517426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095808506012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5023341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619462013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042468070984</t>
+    <t xml:space="preserve">1.55186140537262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233387947083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49820673465729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619426250458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042456150055</t>
   </si>
   <si>
     <t xml:space="preserve">1.46656394004822</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">1.42804265022278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43767285346985</t>
+    <t xml:space="preserve">1.43767297267914</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391526699066</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">1.46518838405609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46931540966034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106112003326</t>
+    <t xml:space="preserve">1.46931576728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106088161469</t>
   </si>
   <si>
     <t xml:space="preserve">1.42116391658783</t>
@@ -1466,82 +1466,82 @@
     <t xml:space="preserve">1.37369990348816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40327894687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814556598663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280635356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180035591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629729747772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45143043994904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41566097736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555794239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904888629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941844463348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.418412566185</t>
+    <t xml:space="preserve">1.40327882766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814532756805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180047512054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4362975358963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143067836761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4156608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555782318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41841232776642</t>
   </si>
   <si>
     <t xml:space="preserve">1.39640009403229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36613345146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41428518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53397655487061</t>
+    <t xml:space="preserve">1.36613321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4142849445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5339766740799</t>
   </si>
   <si>
     <t xml:space="preserve">1.46793985366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48032164573669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48169732093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069132328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48720037937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50508522987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54085528850555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53122508525848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223084449768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54911017417908</t>
+    <t xml:space="preserve">1.4803215265274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48169755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069144248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48720073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683082103729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50508546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54085540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53122496604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223132133484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5491099357605</t>
   </si>
   <si>
     <t xml:space="preserve">1.54773414134979</t>
@@ -1550,58 +1550,58 @@
     <t xml:space="preserve">1.5326007604599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58900701999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56561899185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5174674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984917163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810369968414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672802448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45830929279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878224372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38539397716522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851512432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576365470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3640695810318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364850521088</t>
+    <t xml:space="preserve">1.58900690078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112169265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5656191110611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746726036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52984929084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810381889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461287498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672850131989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45830953121185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.417036652565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878188610077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576341629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364862442017</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3688850402832</t>
+    <t xml:space="preserve">1.36888480186462</t>
   </si>
   <si>
     <t xml:space="preserve">1.32073307037354</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">1.2657026052475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2828996181488</t>
+    <t xml:space="preserve">1.28289949893951</t>
   </si>
   <si>
     <t xml:space="preserve">1.28909063339233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29665732383728</t>
+    <t xml:space="preserve">1.29665720462799</t>
   </si>
   <si>
     <t xml:space="preserve">1.33724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34343326091766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33105146884918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200594902039</t>
+    <t xml:space="preserve">1.34343314170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33105134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200606822968</t>
   </si>
   <si>
     <t xml:space="preserve">1.37989103794098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38264262676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089703559875</t>
+    <t xml:space="preserve">1.38264226913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089727401733</t>
   </si>
   <si>
     <t xml:space="preserve">1.41978800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42666673660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43216991424561</t>
+    <t xml:space="preserve">1.42666709423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4321700334549</t>
   </si>
   <si>
     <t xml:space="preserve">1.4307941198349</t>
@@ -1655,40 +1655,40 @@
     <t xml:space="preserve">1.43492150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41153347492218</t>
+    <t xml:space="preserve">1.41153359413147</t>
   </si>
   <si>
     <t xml:space="preserve">1.35581505298615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37301206588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35719084739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692420482635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528152942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771460056305</t>
+    <t xml:space="preserve">1.37301242351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35719096660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692408561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565108776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771471977234</t>
   </si>
   <si>
     <t xml:space="preserve">1.24506604671478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924470901489</t>
+    <t xml:space="preserve">1.22924482822418</t>
   </si>
   <si>
     <t xml:space="preserve">1.25951170921326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22786891460419</t>
+    <t xml:space="preserve">1.22786915302277</t>
   </si>
   <si>
     <t xml:space="preserve">1.2313084602356</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">1.18315672874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19553852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19003582000732</t>
+    <t xml:space="preserve">1.19553875923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19003558158875</t>
   </si>
   <si>
     <t xml:space="preserve">1.24025094509125</t>
@@ -1709,82 +1709,82 @@
     <t xml:space="preserve">1.3338029384613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30009651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2994087934494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496313095093</t>
+    <t xml:space="preserve">1.3000967502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29940891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28496325016022</t>
   </si>
   <si>
     <t xml:space="preserve">1.30078458786011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29252994060516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26776623725891</t>
+    <t xml:space="preserve">1.29253005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26776611804962</t>
   </si>
   <si>
     <t xml:space="preserve">1.28221166133881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088738441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051770687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818731307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25882351398468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26363909244537</t>
+    <t xml:space="preserve">1.26088726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818719387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25882375240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26363897323608</t>
   </si>
   <si>
     <t xml:space="preserve">1.2326842546463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22030222415924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21204769611359</t>
+    <t xml:space="preserve">1.22030258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2120475769043</t>
   </si>
   <si>
     <t xml:space="preserve">1.21411144733429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18522071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18797183036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20172965526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19347500801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19966566562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104193687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28083598613739</t>
+    <t xml:space="preserve">1.18522036075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18797194957733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20172941684723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19347512722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19966578483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2010418176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808463573456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28083574771881</t>
   </si>
   <si>
     <t xml:space="preserve">1.2815238237381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25676000118256</t>
+    <t xml:space="preserve">1.25676035881042</t>
   </si>
   <si>
     <t xml:space="preserve">1.23612380027771</t>
@@ -1793,115 +1793,115 @@
     <t xml:space="preserve">1.20792055130005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21273553371429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20379328727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19209909439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21548700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29046607017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2794600725174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25056934356689</t>
+    <t xml:space="preserve">1.21273577213287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19209945201874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548712253571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29046630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27946031093597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2505692243576</t>
   </si>
   <si>
     <t xml:space="preserve">1.27326929569244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34136950969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30216026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32417237758636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32554817199707</t>
+    <t xml:space="preserve">1.34136974811554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3021605014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32417249679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32554841041565</t>
   </si>
   <si>
     <t xml:space="preserve">1.33930587768555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34756028652191</t>
+    <t xml:space="preserve">1.3475604057312</t>
   </si>
   <si>
     <t xml:space="preserve">1.3317391872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31110274791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523001194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34893608093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3812667131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38401818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422389507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623612880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480893611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687256813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512709617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957287788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787868499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33793008327484</t>
+    <t xml:space="preserve">1.31110286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523013114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34893620014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063039302826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38126659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3840184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623600959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480929374695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34687280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512721538544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957275867462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787856578827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33793032169342</t>
   </si>
   <si>
     <t xml:space="preserve">1.44455170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48307323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323719978333</t>
+    <t xml:space="preserve">1.48307311534882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323708057404</t>
   </si>
   <si>
     <t xml:space="preserve">1.5958856344223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64128589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59038293361664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276484489441</t>
+    <t xml:space="preserve">1.64128613471985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59038281440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276460647583</t>
   </si>
   <si>
     <t xml:space="preserve">1.598637342453</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">1.52572178840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50921261310577</t>
+    <t xml:space="preserve">1.50921249389648</t>
   </si>
   <si>
     <t xml:space="preserve">1.51334011554718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51058840751648</t>
+    <t xml:space="preserve">1.51058828830719</t>
   </si>
   <si>
     <t xml:space="preserve">1.49545514583588</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">1.59726178646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60001337528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340116500854</t>
+    <t xml:space="preserve">1.60001313686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340080738068</t>
   </si>
   <si>
     <t xml:space="preserve">1.71007430553436</t>
@@ -1943,91 +1943,91 @@
     <t xml:space="preserve">1.77611076831818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79949903488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78436553478241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847675800323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151512145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719233512878</t>
+    <t xml:space="preserve">1.79949915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7843656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847687721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77438879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151500225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719245433807</t>
   </si>
   <si>
     <t xml:space="preserve">1.76726269721985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75301098823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153837680817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728642940521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595513820648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420095920563</t>
+    <t xml:space="preserve">1.75301086902618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153861522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7572865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025454998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595537662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420119762421</t>
   </si>
   <si>
     <t xml:space="preserve">1.92403638362885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89553213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572020053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018383026123</t>
+    <t xml:space="preserve">1.89553201198578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572031974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434168338776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018359184265</t>
   </si>
   <si>
     <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73733353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73590838909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579103946686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004239082336</t>
+    <t xml:space="preserve">1.73733329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73590850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579068183899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013684272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004262924194</t>
   </si>
   <si>
     <t xml:space="preserve">1.79006624221802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84422421455383</t>
+    <t xml:space="preserve">1.8442245721817</t>
   </si>
   <si>
     <t xml:space="preserve">1.84137403964996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77723956108093</t>
+    <t xml:space="preserve">1.77723932266235</t>
   </si>
   <si>
     <t xml:space="preserve">1.75016057491302</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">1.7302074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310484409332</t>
+    <t xml:space="preserve">1.71310496330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.74588477611542</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">1.80289328098297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84564936161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282268047333</t>
+    <t xml:space="preserve">1.84564971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282244205475</t>
   </si>
   <si>
     <t xml:space="preserve">1.78294014930725</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">1.80146789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81001937389374</t>
+    <t xml:space="preserve">1.81001913547516</t>
   </si>
   <si>
     <t xml:space="preserve">1.8285471200943</t>
@@ -2066,193 +2066,193 @@
     <t xml:space="preserve">1.83994877338409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87415385246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560201644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265834331512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562598705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417734622955</t>
+    <t xml:space="preserve">1.87415397167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413035869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265810489655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417746543884</t>
   </si>
   <si>
     <t xml:space="preserve">1.88555574417114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9539657831192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95681607723236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9439891576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8784294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700402736664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990166664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978395938873</t>
+    <t xml:space="preserve">1.95396602153778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116223812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95681667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94398903846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87842917442322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700414657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990178585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978407859802</t>
   </si>
   <si>
     <t xml:space="preserve">1.89410650730133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87130343914032</t>
+    <t xml:space="preserve">1.87130331993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89268147945404</t>
+    <t xml:space="preserve">1.89268159866333</t>
   </si>
   <si>
     <t xml:space="preserve">1.93543791770935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00954914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111489295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971371650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9781938791275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532056808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714522838593</t>
+    <t xml:space="preserve">2.0095489025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971359729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819399833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532032966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8171454668045</t>
   </si>
   <si>
     <t xml:space="preserve">1.84279930591583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83139705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94968974590302</t>
+    <t xml:space="preserve">1.83139777183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969010353088</t>
   </si>
   <si>
     <t xml:space="preserve">1.97106826305389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669884681702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092741966248</t>
+    <t xml:space="preserve">2.04517889022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669836997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092670440674</t>
   </si>
   <si>
     <t xml:space="preserve">1.9967223405838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99957239627838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648680686951</t>
+    <t xml:space="preserve">1.99957251548767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0736837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0622820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123271942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695692062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973721027374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263461112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89125633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835905075073</t>
+    <t xml:space="preserve">2.06655764579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07368350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06228184700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394217014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831206321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123295783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695727825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9169100522995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263473033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89125657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835881233215</t>
   </si>
   <si>
     <t xml:space="preserve">1.99717044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9433501958847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425800323486</t>
+    <t xml:space="preserve">1.94335007667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425824165344</t>
   </si>
   <si>
     <t xml:space="preserve">1.97971498966217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96371459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389686107635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95062279701233</t>
+    <t xml:space="preserve">1.96371483802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389674186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9506231546402</t>
   </si>
   <si>
     <t xml:space="preserve">1.9098938703537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89389371871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462252616882</t>
+    <t xml:space="preserve">1.8938934803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462264537811</t>
   </si>
   <si>
     <t xml:space="preserve">1.89680302143097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8895298242569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916892051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880427837372</t>
+    <t xml:space="preserve">1.88952994346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916868209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880392074585</t>
   </si>
   <si>
     <t xml:space="preserve">1.96953284740448</t>
@@ -2261,28 +2261,28 @@
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01026153564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98553335666656</t>
+    <t xml:space="preserve">2.00735235214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01026201248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98553359508514</t>
   </si>
   <si>
     <t xml:space="preserve">2.00880742073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02189874649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02917170524597</t>
+    <t xml:space="preserve">2.02189898490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02917146682739</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208065032959</t>
+    <t xml:space="preserve">2.03208112716675</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.10044717788696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09608316421509</t>
+    <t xml:space="preserve">2.09608364105225</t>
   </si>
   <si>
     <t xml:space="preserve">2.16881370544434</t>
@@ -2300,43 +2300,43 @@
     <t xml:space="preserve">2.08444666862488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09753823280334</t>
+    <t xml:space="preserve">2.09753799438477</t>
   </si>
   <si>
     <t xml:space="preserve">2.080082654953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1891782283783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16590452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899282455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06844592094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07717347145081</t>
+    <t xml:space="preserve">2.09462904930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863482475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2473623752594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18917798995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16590428352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899258613586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06844615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07717370986938</t>
   </si>
   <si>
     <t xml:space="preserve">2.07280969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.128084897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499309539795</t>
+    <t xml:space="preserve">2.12808537483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499357223511</t>
   </si>
   <si>
     <t xml:space="preserve">2.14553999900818</t>
@@ -2345,40 +2345,40 @@
     <t xml:space="preserve">2.14699482917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390278816223</t>
+    <t xml:space="preserve">2.13390326499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.13099408149719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0829918384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0582640171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808187484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02335357666016</t>
+    <t xml:space="preserve">2.08299207687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07426428794861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05826377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335333824158</t>
   </si>
   <si>
     <t xml:space="preserve">2.02771735191345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06408214569092</t>
+    <t xml:space="preserve">2.06408166885376</t>
   </si>
   <si>
     <t xml:space="preserve">2.04226303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99426138401031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789949417114</t>
+    <t xml:space="preserve">1.99426186084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789925575256</t>
   </si>
   <si>
     <t xml:space="preserve">2.03644466400146</t>
@@ -2387,157 +2387,157 @@
     <t xml:space="preserve">2.04517245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589823722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862504005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935082435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826111316681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9608051776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280655384064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06117272377014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06990051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04080891609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03353548049927</t>
+    <t xml:space="preserve">2.02626276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589776039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862492084503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95935070514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080553531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280667304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0611732006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06990075111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04080867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03353571891785</t>
   </si>
   <si>
     <t xml:space="preserve">1.96807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9113484621048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553033351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370807647705</t>
+    <t xml:space="preserve">1.91134870052338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643826007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553021430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370819568634</t>
   </si>
   <si>
     <t xml:space="preserve">1.79352593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.819708943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152805805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552742958069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83279991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898315906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8517097234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752832889557</t>
+    <t xml:space="preserve">1.80079913139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81970882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516266822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83279979228973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171020030975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298264980316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752856731415</t>
   </si>
   <si>
     <t xml:space="preserve">1.8357093334198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84880101680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87062013149261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460959911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860920906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152153491974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751902103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388091087341</t>
+    <t xml:space="preserve">1.84880089759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061965465546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788994789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460995674133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860932826996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152165412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388067245483</t>
   </si>
   <si>
     <t xml:space="preserve">1.55351638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56224417686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770116329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733314037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842356681824</t>
+    <t xml:space="preserve">1.56224405765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770128250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52733337879181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842368602753</t>
   </si>
   <si>
     <t xml:space="preserve">1.39278256893158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36441791057587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35569036006927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19277477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21241188049316</t>
+    <t xml:space="preserve">1.36441802978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35569024085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19277465343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21241211891174</t>
   </si>
   <si>
     <t xml:space="preserve">1.16150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15931880474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13386332988739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10768055915833</t>
+    <t xml:space="preserve">1.1593189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10768043994904</t>
   </si>
   <si>
     <t xml:space="preserve">1.11422610282898</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">1.08440685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18041086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968332767487</t>
+    <t xml:space="preserve">1.1804107427597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968344688416</t>
   </si>
   <si>
     <t xml:space="preserve">1.19713854789734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11204433441162</t>
+    <t xml:space="preserve">1.11204421520233</t>
   </si>
   <si>
     <t xml:space="preserve">1.12877237796783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550169467926</t>
+    <t xml:space="preserve">1.18550181388855</t>
   </si>
   <si>
     <t xml:space="preserve">1.10549867153168</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">1.09022521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0414959192276</t>
+    <t xml:space="preserve">1.04149603843689</t>
   </si>
   <si>
     <t xml:space="preserve">1.07640647888184</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">1.23059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24514055252075</t>
+    <t xml:space="preserve">1.24514043331146</t>
   </si>
   <si>
     <t xml:space="preserve">1.23641288280487</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">1.20077514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22186672687531</t>
+    <t xml:space="preserve">1.22186696529388</t>
   </si>
   <si>
     <t xml:space="preserve">1.24223124980927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36005401611328</t>
+    <t xml:space="preserve">1.36005389690399</t>
   </si>
   <si>
     <t xml:space="preserve">1.41023814678192</t>
@@ -2603,64 +2603,64 @@
     <t xml:space="preserve">1.47351324558258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58939063549042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649650096893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331379413605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5624772310257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967920780182</t>
+    <t xml:space="preserve">1.58939075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56247746944427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967908859253</t>
   </si>
   <si>
     <t xml:space="preserve">1.4608039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47575604915619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500836849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284745693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48397958278656</t>
+    <t xml:space="preserve">1.4757559299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061188220978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48397982120514</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192912101746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40473449230194</t>
+    <t xml:space="preserve">1.40473425388336</t>
   </si>
   <si>
     <t xml:space="preserve">1.37931609153748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46005654335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44884240627289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762862682343</t>
+    <t xml:space="preserve">1.46005642414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44884252548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762850761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.4951936006546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56546783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733342170715</t>
+    <t xml:space="preserve">1.56546771526337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733306407928</t>
   </si>
   <si>
     <t xml:space="preserve">1.62228500843048</t>
@@ -2669,46 +2669,46 @@
     <t xml:space="preserve">1.64321780204773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71498703956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807351589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471316337585</t>
+    <t xml:space="preserve">1.71498715877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471292495728</t>
   </si>
   <si>
     <t xml:space="preserve">1.77479481697083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7553573846817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67760694026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65069365501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490490913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686672687531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976121902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125598430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583794116974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62527549266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58341002464294</t>
+    <t xml:space="preserve">1.75535762310028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67760717868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65069353580475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58490526676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686660766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976086139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62527525424957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58341014385223</t>
   </si>
   <si>
     <t xml:space="preserve">1.59238123893738</t>
@@ -2717,196 +2717,196 @@
     <t xml:space="preserve">1.60135209560394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64172255992889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050155162811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797740459442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70601606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003497600555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956887722015</t>
+    <t xml:space="preserve">1.6417224407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71050143241882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7060159444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003485679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013108730316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956851959229</t>
   </si>
   <si>
     <t xml:space="preserve">1.74788129329681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72545313835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077554702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80021286010742</t>
+    <t xml:space="preserve">1.7254536151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78077530860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656417369843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.800213098526</t>
   </si>
   <si>
     <t xml:space="preserve">1.78675639629364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85403990745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002087593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871785640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8331071138382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423260688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292946815491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881420612335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161199092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85105001926422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264089584351</t>
+    <t xml:space="preserve">1.85404002666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8600207567215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871773719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310723304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423213005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292934894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881396770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161211013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104978084564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264077663422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83609771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85852551460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291512966156</t>
+    <t xml:space="preserve">1.85852587223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291501045227</t>
   </si>
   <si>
     <t xml:space="preserve">1.90786719322205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90039110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89142000675201</t>
+    <t xml:space="preserve">1.90039145946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141988754272</t>
   </si>
   <si>
     <t xml:space="preserve">1.88992464542389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90487658977509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543915748596</t>
+    <t xml:space="preserve">1.90487682819366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543879985809</t>
   </si>
   <si>
     <t xml:space="preserve">1.83011674880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79124200344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553526878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666040420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80768895149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928030490875</t>
+    <t xml:space="preserve">1.79124188423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8555349111557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666016578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8076890707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928054332733</t>
   </si>
   <si>
     <t xml:space="preserve">1.83460247516632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80170798301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84805881977081</t>
+    <t xml:space="preserve">1.80170810222626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84805905818939</t>
   </si>
   <si>
     <t xml:space="preserve">1.84506869316101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87646818161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058320522308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83908796310425</t>
+    <t xml:space="preserve">1.87646794319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83908820152283</t>
   </si>
   <si>
     <t xml:space="preserve">1.82862162590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82114589214325</t>
+    <t xml:space="preserve">1.82114565372467</t>
   </si>
   <si>
     <t xml:space="preserve">1.77778518199921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71947276592255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349167823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508303165436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442423343658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395825386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497293949127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207880496979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227066993713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582360267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638617038727</t>
+    <t xml:space="preserve">1.71947264671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900654792786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71349191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508315086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059766292572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442471027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395813465118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497246265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207844734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227055072784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582372188568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638628959656</t>
   </si>
   <si>
     <t xml:space="preserve">1.75685226917267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63424670696259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5176215171814</t>
+    <t xml:space="preserve">1.72246289253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6342465877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51762139797211</t>
   </si>
   <si>
     <t xml:space="preserve">1.59836184978485</t>
@@ -2918,40 +2918,40 @@
     <t xml:space="preserve">1.75984299182892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72694838047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386226177216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469858646393</t>
+    <t xml:space="preserve">1.72694861888885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386202335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80469870567322</t>
   </si>
   <si>
     <t xml:space="preserve">1.80918431282043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301112174988</t>
+    <t xml:space="preserve">1.81965053081512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301100254059</t>
   </si>
   <si>
     <t xml:space="preserve">1.91235268115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93926584720612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617960929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159777164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216010093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056910514832</t>
+    <t xml:space="preserve">1.93926620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617937088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159789085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216022014618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056886672974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345634460449</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">2.01497220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02710199356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677860736847</t>
+    <t xml:space="preserve">2.04074692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02710175514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03316640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677872657776</t>
   </si>
   <si>
     <t xml:space="preserve">2.00890803337097</t>
@@ -2978,67 +2978,67 @@
     <t xml:space="preserve">2.00132727622986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99981069564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800465583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435972213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01042413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03013396263123</t>
+    <t xml:space="preserve">1.99981081485748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165006637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800441741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01042366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03013372421265</t>
   </si>
   <si>
     <t xml:space="preserve">2.03468251228333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04681205749512</t>
+    <t xml:space="preserve">2.04681181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.05136036872864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04377937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07561850547791</t>
+    <t xml:space="preserve">2.04377961158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07561874389648</t>
   </si>
   <si>
     <t xml:space="preserve">2.06803798675537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12261962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21358871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16203951835632</t>
+    <t xml:space="preserve">2.10442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287599563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12261986732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21358895301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13323283195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1559751033783</t>
+    <t xml:space="preserve">2.13323259353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15597534179688</t>
   </si>
   <si>
     <t xml:space="preserve">2.18023347854614</t>
@@ -3047,52 +3047,52 @@
     <t xml:space="preserve">2.20146012306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27120327949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933057785034</t>
+    <t xml:space="preserve">2.27120304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933033943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.26362252235413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24846053123474</t>
+    <t xml:space="preserve">2.2484610080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.2151050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21662187576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546141624451</t>
+    <t xml:space="preserve">2.21662092208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546165466309</t>
   </si>
   <si>
     <t xml:space="preserve">2.30000996589661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32275199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31062293052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246206283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35762357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3485267162323</t>
+    <t xml:space="preserve">2.32275223731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31062316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576238155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34852695465088</t>
   </si>
   <si>
     <t xml:space="preserve">2.35914015769958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38794755935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36368870735168</t>
+    <t xml:space="preserve">2.38794732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36368846893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.39249539375305</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">2.36520481109619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36823701858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
+    <t xml:space="preserve">2.36823678016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">2.32426834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35459160804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38036680221558</t>
+    <t xml:space="preserve">2.35459184646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549474716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38036632537842</t>
   </si>
   <si>
     <t xml:space="preserve">2.4410126209259</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">2.36065602302551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37278580665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31820392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765690803528</t>
+    <t xml:space="preserve">2.3727855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.318204164505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765714645386</t>
   </si>
   <si>
     <t xml:space="preserve">2.41523766517639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49407839775085</t>
+    <t xml:space="preserve">2.41978621482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49407815933228</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349479675293</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">2.42888307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40614128112793</t>
+    <t xml:space="preserve">2.40614104270935</t>
   </si>
   <si>
     <t xml:space="preserve">2.30759072303772</t>
@@ -3173,55 +3173,55 @@
     <t xml:space="preserve">2.34397864341736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35610795021057</t>
+    <t xml:space="preserve">2.35610771179199</t>
   </si>
   <si>
     <t xml:space="preserve">2.45314168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51682019233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48649740219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49862670898438</t>
+    <t xml:space="preserve">2.51682043075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48649716377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4986264705658</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44859313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54714322090149</t>
+    <t xml:space="preserve">2.44859337806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54714393615723</t>
   </si>
   <si>
     <t xml:space="preserve">2.58959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685328483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327477455139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355972290039</t>
+    <t xml:space="preserve">2.56685352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266157150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355924606323</t>
   </si>
   <si>
     <t xml:space="preserve">2.52038168907166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50052428245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51579904556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51427125930786</t>
+    <t xml:space="preserve">2.50052404403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51579928398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427173614502</t>
   </si>
   <si>
     <t xml:space="preserve">2.49899649620056</t>
@@ -3230,64 +3230,64 @@
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286688804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386408805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109417915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48066663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41192889213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443350791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262148857117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46691918373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43025898933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43331408500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45622682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50816178321838</t>
+    <t xml:space="preserve">2.53412938117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286664962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942427635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761130332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48066639900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41192865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262125015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4669189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775365829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43025875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928144454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706177711487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43331384658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45622658729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48372197151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5081615447998</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023909568787</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">2.65938472747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64869213104248</t>
+    <t xml:space="preserve">2.6486918926239</t>
   </si>
   <si>
     <t xml:space="preserve">2.63799929618835</t>
@@ -3326,31 +3326,31 @@
     <t xml:space="preserve">2.63952708244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61966967582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59370183944702</t>
+    <t xml:space="preserve">2.61966943740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59370160102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.54634952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53565621376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885390281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5448215007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5066339969635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58148169517517</t>
+    <t xml:space="preserve">2.53565669059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260207176208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50663447380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.54329419136047</t>
@@ -3362,46 +3362,46 @@
     <t xml:space="preserve">2.49135947227478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48830389976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48219418525696</t>
+    <t xml:space="preserve">2.48830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48219394683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.40734648704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37526869773865</t>
+    <t xml:space="preserve">2.37526845932007</t>
   </si>
   <si>
     <t xml:space="preserve">2.41040134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38290619850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48524904251099</t>
+    <t xml:space="preserve">2.38290643692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48524880409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.44247889518738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47455644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4898316860199</t>
+    <t xml:space="preserve">2.47455668449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48983192443848</t>
   </si>
   <si>
     <t xml:space="preserve">2.52649164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52496409416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55856895446777</t>
+    <t xml:space="preserve">2.52496433258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55856943130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.5539870262146</t>
@@ -3410,61 +3410,61 @@
     <t xml:space="preserve">2.54787659645081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56162428855896</t>
+    <t xml:space="preserve">2.56162452697754</t>
   </si>
   <si>
     <t xml:space="preserve">2.5295467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51732635498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45164370536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42873167991638</t>
+    <t xml:space="preserve">2.51732683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4516441822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4287314414978</t>
   </si>
   <si>
     <t xml:space="preserve">2.42414903640747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4256763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4501166343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42720437049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40581893920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5051064491272</t>
+    <t xml:space="preserve">2.42567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45011639595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42720365524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40581917762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510668754578</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40887403488159</t>
+    <t xml:space="preserve">2.38596129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40887355804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.37355327606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36727404594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42535662651062</t>
+    <t xml:space="preserve">2.36727380752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42535710334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.43791532516479</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">2.40965867042542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35157561302185</t>
+    <t xml:space="preserve">2.35157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000586509705</t>
@@ -3491,34 +3491,34 @@
     <t xml:space="preserve">2.33116817474365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35471534729004</t>
+    <t xml:space="preserve">2.35471558570862</t>
   </si>
   <si>
     <t xml:space="preserve">2.34686636924744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39396095275879</t>
+    <t xml:space="preserve">2.39396071434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44733428955078</t>
+    <t xml:space="preserve">2.44733452796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.43948531150818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4740207195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361328125</t>
+    <t xml:space="preserve">2.47402048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361351966858</t>
   </si>
   <si>
     <t xml:space="preserve">2.44105505943298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45675325393677</t>
+    <t xml:space="preserve">2.45675301551819</t>
   </si>
   <si>
     <t xml:space="preserve">2.46931171417236</t>
@@ -3527,37 +3527,37 @@
     <t xml:space="preserve">2.46774172782898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48814916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50384712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45047378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27622509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25581765174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738668441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547045707703</t>
+    <t xml:space="preserve">2.4881489276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50384736061096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45047402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837539672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25581741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738716125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.29977178573608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29192304611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27151536941528</t>
+    <t xml:space="preserve">2.29192328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2715151309967</t>
   </si>
   <si>
     <t xml:space="preserve">2.36256456375122</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">2.32017946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26994562149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22913026809692</t>
+    <t xml:space="preserve">2.2699453830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2291305065155</t>
   </si>
   <si>
     <t xml:space="preserve">2.22442126274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24639868736267</t>
+    <t xml:space="preserve">2.24639844894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244383811951</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">2.16005897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14122104644775</t>
+    <t xml:space="preserve">2.14122128486633</t>
   </si>
   <si>
     <t xml:space="preserve">2.20401358604431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773459434509</t>
+    <t xml:space="preserve">2.19773411750793</t>
   </si>
   <si>
     <t xml:space="preserve">2.16319870948792</t>
@@ -3605,82 +3605,82 @@
     <t xml:space="preserve">2.17732691764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18674564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18203639984131</t>
+    <t xml:space="preserve">2.1867458820343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18203616142273</t>
   </si>
   <si>
     <t xml:space="preserve">2.16633820533752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15534973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14750027656555</t>
+    <t xml:space="preserve">2.15534949302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14750051498413</t>
   </si>
   <si>
     <t xml:space="preserve">2.15848922729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21814179420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21186304092407</t>
+    <t xml:space="preserve">2.21814203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21186280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.23070025444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21657204627991</t>
+    <t xml:space="preserve">2.21657228469849</t>
   </si>
   <si>
     <t xml:space="preserve">2.2275607585907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26366662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860971450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29349255561829</t>
+    <t xml:space="preserve">2.26366639137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860947608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29349279403687</t>
   </si>
   <si>
     <t xml:space="preserve">2.24796843528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2354097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24011898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24482846260071</t>
+    <t xml:space="preserve">2.23541021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24011921882629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24482870101929</t>
   </si>
   <si>
     <t xml:space="preserve">2.26052689552307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30291175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529662132263</t>
+    <t xml:space="preserve">2.30291152000427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529638290405</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407406806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11924386024475</t>
+    <t xml:space="preserve">2.11924338340759</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087385177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831515312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2212815284729</t>
+    <t xml:space="preserve">2.18831562995911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22128176689148</t>
   </si>
   <si>
     <t xml:space="preserve">2.23227047920227</t>
@@ -3692,151 +3692,151 @@
     <t xml:space="preserve">2.19930410385132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22599101066589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27936434745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16476845741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03447389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09255695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953069210052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441389083862</t>
+    <t xml:space="preserve">2.22599077224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27936458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03447437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0925567150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05802130699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953057289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441377162933</t>
   </si>
   <si>
     <t xml:space="preserve">2.0109269618988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92615723609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057239532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592327594757</t>
+    <t xml:space="preserve">1.92615735530853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766685962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.800572514534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86807429790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045892238617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202914714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00935745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99365890026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9779611825943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01720595359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920893907547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9889497756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99679827690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959129333496</t>
+    <t xml:space="preserve">1.86807441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045880317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202867031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.009357213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99365925788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97796106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877617835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0172061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99208950996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894941806793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9967987537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0595908164978</t>
   </si>
   <si>
     <t xml:space="preserve">2.01249694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01406621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854186058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516840457916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301797866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790034294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947044849396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92124783992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01642322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01158380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.969642162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543759822845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87608003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770028114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91156888008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189015865326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221131801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704375267029</t>
+    <t xml:space="preserve">2.01406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854197978973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639107704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220226764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650431156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516864299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301774024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947056770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92124795913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576610088348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01642298698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964204311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092656135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543783664703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87607991695404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9277001619339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91156899929047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189027786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221107959747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.847043633461</t>
   </si>
   <si>
     <t xml:space="preserve">1.82607269287109</t>
@@ -3845,28 +3845,28 @@
     <t xml:space="preserve">1.77122604846954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79703605175018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81316721439362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801445484161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672981739044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94383192062378</t>
+    <t xml:space="preserve">1.79703593254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81316745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672969818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9438316822052</t>
   </si>
   <si>
     <t xml:space="preserve">1.91963481903076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89382457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802179813385</t>
+    <t xml:space="preserve">1.89382433891296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802144050598</t>
   </si>
   <si>
     <t xml:space="preserve">1.9325395822525</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">1.91479527950287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254680633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02932858467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609460353851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448892593384</t>
+    <t xml:space="preserve">1.96318924427032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254704475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02932810783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609448432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448844909668</t>
   </si>
   <si>
     <t xml:space="preserve">2.01480984687805</t>
@@ -3896,25 +3896,25 @@
     <t xml:space="preserve">1.97448134422302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97770738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99061274528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415296077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124049663544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82929921150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285375595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88898491859436</t>
+    <t xml:space="preserve">1.97770762443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99061298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9341527223587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124037742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82929873466492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285387516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88898503780365</t>
   </si>
   <si>
     <t xml:space="preserve">1.86317479610443</t>
@@ -3923,19 +3923,19 @@
     <t xml:space="preserve">1.85833537578583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84381687641144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672235488892</t>
+    <t xml:space="preserve">1.84381723403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672247409821</t>
   </si>
   <si>
     <t xml:space="preserve">1.88253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87769305706024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865665435791</t>
+    <t xml:space="preserve">1.87769317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486567735672</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187547206879</t>
@@ -3956,43 +3956,43 @@
     <t xml:space="preserve">1.86962735652924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575165271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768595218658</t>
+    <t xml:space="preserve">1.8357515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768571376801</t>
   </si>
   <si>
     <t xml:space="preserve">1.90350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93899250030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95189762115479</t>
+    <t xml:space="preserve">1.93899214267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95189738273621</t>
   </si>
   <si>
     <t xml:space="preserve">1.99383902549744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96802890300751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222600460052</t>
+    <t xml:space="preserve">1.96802914142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99222588539124</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07449626922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05029892921448</t>
+    <t xml:space="preserve">2.0744960308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05029916763306</t>
   </si>
   <si>
     <t xml:space="preserve">2.05191206932068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03416776657104</t>
+    <t xml:space="preserve">2.03416728973389</t>
   </si>
   <si>
     <t xml:space="preserve">2.01319670677185</t>
@@ -4010,37 +4010,37 @@
     <t xml:space="preserve">2.07610893249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00351762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00835704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98899972438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95512366294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932088375092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866399765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91318237781525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931377887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286808490753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9648026227951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94544470310211</t>
+    <t xml:space="preserve">2.00351786613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00835728645325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98899984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512342453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932076454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866411685944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91318225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9728684425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96480214595795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9454448223114</t>
   </si>
   <si>
     <t xml:space="preserve">1.83736479282379</t>
@@ -4058,82 +4058,82 @@
     <t xml:space="preserve">1.81474316120148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78290557861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845813035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79128384590149</t>
+    <t xml:space="preserve">1.78290569782257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78458142280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79128396511078</t>
   </si>
   <si>
     <t xml:space="preserve">1.776202917099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72928428649902</t>
+    <t xml:space="preserve">1.72928440570831</t>
   </si>
   <si>
     <t xml:space="preserve">1.73933839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74604117870331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79798662662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966223239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333751678467</t>
+    <t xml:space="preserve">1.74604105949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79798674583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966235160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333739757538</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85663461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86166167259216</t>
+    <t xml:space="preserve">1.8566347360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86166155338287</t>
   </si>
   <si>
     <t xml:space="preserve">1.87674260139465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87171566486359</t>
+    <t xml:space="preserve">1.87171578407288</t>
   </si>
   <si>
     <t xml:space="preserve">1.89517521858215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9136073589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8968505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355336666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701256275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879651069641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94376921653748</t>
+    <t xml:space="preserve">1.91360723972321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203961849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685070514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355324745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701280117035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879639148712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94376933574677</t>
   </si>
   <si>
     <t xml:space="preserve">2.09625482559204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17836213111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19176697731018</t>
+    <t xml:space="preserve">2.1783618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19176721572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820003509521</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">2.18506479263306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29900979995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29230713844299</t>
+    <t xml:space="preserve">2.29901003837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29230737686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3258204460144</t>
+    <t xml:space="preserve">2.32582068443298</t>
   </si>
   <si>
     <t xml:space="preserve">2.33419895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34257698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32917213439941</t>
+    <t xml:space="preserve">2.34257745742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32917189598083</t>
   </si>
   <si>
     <t xml:space="preserve">2.25711846351624</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3006854057312</t>
+    <t xml:space="preserve">2.30068588256836</t>
   </si>
   <si>
     <t xml:space="preserve">2.31576633453369</t>
@@ -4184,61 +4184,61 @@
     <t xml:space="preserve">2.29733443260193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31409096717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30403661727905</t>
+    <t xml:space="preserve">2.31409120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
     <t xml:space="preserve">2.33755016326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42636036872864</t>
+    <t xml:space="preserve">2.42636013031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981956481934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46657609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4799816608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46322512626648</t>
+    <t xml:space="preserve">2.46657633781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490025520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47998142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4632248878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.43306279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38614463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40122509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40290117263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38279294967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41295504570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35430669784546</t>
+    <t xml:space="preserve">2.38614416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40122532844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609028816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38279318809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41295480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35430693626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.36938786506653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37776613235474</t>
+    <t xml:space="preserve">2.37776589393616</t>
   </si>
   <si>
     <t xml:space="preserve">2.36100959777832</t>
@@ -4250,31 +4250,31 @@
     <t xml:space="preserve">2.37944149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38782000541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49171090126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45987391471863</t>
+    <t xml:space="preserve">2.38781976699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49171113967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45987343788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776345252991</t>
+    <t xml:space="preserve">2.68776369094849</t>
   </si>
   <si>
     <t xml:space="preserve">2.64922332763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77824950218201</t>
+    <t xml:space="preserve">2.77824926376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.80170893669128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77322268486023</t>
+    <t xml:space="preserve">2.77322244644165</t>
   </si>
   <si>
     <t xml:space="preserve">2.78160095214844</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">2.93073487281799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92905902862549</t>
+    <t xml:space="preserve">2.92905950546265</t>
   </si>
   <si>
     <t xml:space="preserve">2.90224862098694</t>
@@ -4295,28 +4295,28 @@
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03294992446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06311225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11840915679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15024709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16030120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20554375648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20219230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14354419708252</t>
+    <t xml:space="preserve">3.03295016288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06311202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11840891838074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1502468585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16030097007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20219254493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1435444355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.20889496803284</t>
@@ -4325,40 +4325,40 @@
     <t xml:space="preserve">3.18878698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19884085655212</t>
+    <t xml:space="preserve">3.19213843345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1988410949707</t>
   </si>
   <si>
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29267811775208</t>
+    <t xml:space="preserve">3.29267835617065</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3379213809967</t>
+    <t xml:space="preserve">3.33792090415955</t>
   </si>
   <si>
     <t xml:space="preserve">3.35132622718811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40494775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25581312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34797501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31781315803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39321827888489</t>
+    <t xml:space="preserve">3.40494751930237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25581336021423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34797477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39321804046631</t>
   </si>
   <si>
     <t xml:space="preserve">3.3647313117981</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">3.18543577194214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24240827560425</t>
+    <t xml:space="preserve">3.24240851402283</t>
   </si>
   <si>
     <t xml:space="preserve">3.13851714134216</t>
@@ -4397,52 +4397,52 @@
     <t xml:space="preserve">3.21559762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26419186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29770517349243</t>
+    <t xml:space="preserve">3.26419162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29770541191101</t>
   </si>
   <si>
     <t xml:space="preserve">3.294353723526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34294819831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510985374451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30105662345886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40159583091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38986682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3848397731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981271743774</t>
+    <t xml:space="preserve">3.3429479598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510961532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30105686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40159606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38986659049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38483953475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981224060059</t>
   </si>
   <si>
     <t xml:space="preserve">3.36640739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37143445014954</t>
+    <t xml:space="preserve">3.37143421173096</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619142532349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31243968009949</t>
+    <t xml:space="preserve">3.31243991851807</t>
   </si>
   <si>
     <t xml:space="preserve">3.23508644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2178966999054</t>
+    <t xml:space="preserve">3.21789646148682</t>
   </si>
   <si>
     <t xml:space="preserve">3.22305369377136</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">3.2041449546814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21445894241333</t>
+    <t xml:space="preserve">3.21445918083191</t>
   </si>
   <si>
     <t xml:space="preserve">3.19555020332336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16976594924927</t>
+    <t xml:space="preserve">3.16976571083069</t>
   </si>
   <si>
     <t xml:space="preserve">3.25571417808533</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">3.10616445541382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13366746902466</t>
+    <t xml:space="preserve">3.13366770744324</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18867468833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22649145126343</t>
+    <t xml:space="preserve">3.18867444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22649192810059</t>
   </si>
   <si>
     <t xml:space="preserve">3.2660276889801</t>
@@ -4499,25 +4499,25 @@
     <t xml:space="preserve">3.24024319648743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09928846359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16117095947266</t>
+    <t xml:space="preserve">3.09928822517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16117119789124</t>
   </si>
   <si>
     <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15257620811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11991596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09756970405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06834721565247</t>
+    <t xml:space="preserve">3.1525764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11991620063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09756946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06834673881531</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429520606995</t>
@@ -4529,13 +4529,13 @@
     <t xml:space="preserve">3.10960221290588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12507271766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17664194107056</t>
+    <t xml:space="preserve">3.12507295608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18695569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17664217948914</t>
   </si>
   <si>
     <t xml:space="preserve">3.14398145675659</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">3.27462267875671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24196267127991</t>
+    <t xml:space="preserve">3.24196243286133</t>
   </si>
   <si>
     <t xml:space="preserve">3.19039344787598</t>
@@ -4556,19 +4556,19 @@
     <t xml:space="preserve">3.15601396560669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26258993148804</t>
+    <t xml:space="preserve">3.26258969306946</t>
   </si>
   <si>
     <t xml:space="preserve">3.27290368080139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538646697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10272622108459</t>
+    <t xml:space="preserve">3.12851071357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10272669792175</t>
   </si>
   <si>
     <t xml:space="preserve">3.08209872245789</t>
@@ -4580,52 +4580,52 @@
     <t xml:space="preserve">3.04771971702576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05631446838379</t>
+    <t xml:space="preserve">3.05631422996521</t>
   </si>
   <si>
     <t xml:space="preserve">3.01677823066711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01162147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03396773338318</t>
+    <t xml:space="preserve">3.0081832408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01162123680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03396797180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583674430847</t>
+    <t xml:space="preserve">2.98583698272705</t>
   </si>
   <si>
     <t xml:space="preserve">3.07350397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07006621360779</t>
+    <t xml:space="preserve">3.07006597518921</t>
   </si>
   <si>
     <t xml:space="preserve">3.05287671089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97552299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94458198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93083024024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92051649093628</t>
+    <t xml:space="preserve">2.9755232334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94458222389221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93083047866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9205162525177</t>
   </si>
   <si>
     <t xml:space="preserve">2.87582349777222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87754249572754</t>
+    <t xml:space="preserve">2.87754225730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.88785600662231</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005272865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286274909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786972999573</t>
+    <t xml:space="preserve">2.96005249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286322593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786949157715</t>
   </si>
   <si>
     <t xml:space="preserve">3.05115747451782</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">3.03053021430969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05459523200989</t>
+    <t xml:space="preserve">3.04943871498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05459547042847</t>
   </si>
   <si>
     <t xml:space="preserve">3.08725571632385</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">3.02021622657776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99615049362183</t>
+    <t xml:space="preserve">2.99615073204041</t>
   </si>
   <si>
     <t xml:space="preserve">3.03912472724915</t>
@@ -4685,16 +4685,16 @@
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99276232719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95357131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79858899116516</t>
+    <t xml:space="preserve">3.03729748725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99276208877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9535710811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79858875274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.67210912704468</t>
@@ -4703,28 +4703,28 @@
     <t xml:space="preserve">2.67923450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69526743888855</t>
+    <t xml:space="preserve">2.69526720046997</t>
   </si>
   <si>
     <t xml:space="preserve">2.67032766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60797834396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58838295936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59372687339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62579226493835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58125734329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64538812637329</t>
+    <t xml:space="preserve">2.6079785823822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58838272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59372711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58125758171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64538788795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.64004373550415</t>
@@ -4736,52 +4736,52 @@
     <t xml:space="preserve">2.52247095108032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47971701622009</t>
+    <t xml:space="preserve">2.47971725463867</t>
   </si>
   <si>
     <t xml:space="preserve">2.31939101219177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36570715904236</t>
+    <t xml:space="preserve">2.36570739746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.32473492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2855441570282</t>
+    <t xml:space="preserve">2.28554391860962</t>
   </si>
   <si>
     <t xml:space="preserve">2.3372049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36392569541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2606041431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27663707733154</t>
+    <t xml:space="preserve">2.36392593383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26060438156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27663683891296</t>
   </si>
   <si>
     <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38708400726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32829785346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32117199897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36927032470703</t>
+    <t xml:space="preserve">2.38708424568176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32829761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32117223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36927008628845</t>
   </si>
   <si>
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323739051819</t>
+    <t xml:space="preserve">2.35323762893677</t>
   </si>
   <si>
     <t xml:space="preserve">2.35145616531372</t>
@@ -4790,13 +4790,13 @@
     <t xml:space="preserve">2.43161916732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40667939186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3817400932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39955425262451</t>
+    <t xml:space="preserve">2.40667963027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38173985481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39955401420593</t>
   </si>
   <si>
     <t xml:space="preserve">2.42449378967285</t>
@@ -4805,16 +4805,16 @@
     <t xml:space="preserve">2.34254908561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39242839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39599108695984</t>
+    <t xml:space="preserve">2.39242815971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39599132537842</t>
   </si>
   <si>
     <t xml:space="preserve">2.37461400032043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36036348342896</t>
+    <t xml:space="preserve">2.3603630065918</t>
   </si>
   <si>
     <t xml:space="preserve">2.41380524635315</t>
@@ -4835,22 +4835,22 @@
     <t xml:space="preserve">2.52068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49753141403198</t>
+    <t xml:space="preserve">2.4975311756134</t>
   </si>
   <si>
     <t xml:space="preserve">2.50287556648254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085320472717</t>
+    <t xml:space="preserve">2.57056879997253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085296630859</t>
   </si>
   <si>
     <t xml:space="preserve">2.5830385684967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64360666275024</t>
+    <t xml:space="preserve">2.64360642433167</t>
   </si>
   <si>
     <t xml:space="preserve">2.64895081520081</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">2.65785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67567205429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65963912010193</t>
+    <t xml:space="preserve">2.65073227882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67567181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65963935852051</t>
   </si>
   <si>
     <t xml:space="preserve">2.6525137424469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63291811943054</t>
+    <t xml:space="preserve">2.63291835784912</t>
   </si>
   <si>
     <t xml:space="preserve">2.55453634262085</t>
@@ -4880,19 +4880,19 @@
     <t xml:space="preserve">2.61510419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65429520606995</t>
+    <t xml:space="preserve">2.65429496765137</t>
   </si>
   <si>
     <t xml:space="preserve">2.60441541671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60619735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59550857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74336504936218</t>
+    <t xml:space="preserve">2.60619711875916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59550881385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74336528778076</t>
   </si>
   <si>
     <t xml:space="preserve">2.71664428710938</t>
@@ -4901,37 +4901,37 @@
     <t xml:space="preserve">2.68992304801941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70773720741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66676497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445820808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77721214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76830530166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77186799049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76474213600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72911429405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74692845344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020673751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75049138069153</t>
+    <t xml:space="preserve">2.70773696899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66676473617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73445844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77721190452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76830506324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7718677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76474237442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72911405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74692821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020697593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75049114227295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76117944717407</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">2.77008628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81284022331238</t>
+    <t xml:space="preserve">2.8128399848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.80927729606628</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">2.81996583938599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81105875968933</t>
+    <t xml:space="preserve">2.81105852127075</t>
   </si>
   <si>
     <t xml:space="preserve">2.78790044784546</t>
@@ -4973,16 +4973,16 @@
     <t xml:space="preserve">2.84312415122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75761651992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63469982147217</t>
+    <t xml:space="preserve">2.7576162815094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63469958305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.55275464057922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54741048812866</t>
+    <t xml:space="preserve">2.54741072654724</t>
   </si>
   <si>
     <t xml:space="preserve">2.53137803077698</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">2.5420663356781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55809926986694</t>
+    <t xml:space="preserve">2.55809903144836</t>
   </si>
   <si>
     <t xml:space="preserve">2.57947611808777</t>
@@ -5006,10 +5006,10 @@
     <t xml:space="preserve">2.50821971893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60263419151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61154103279114</t>
+    <t xml:space="preserve">2.60263395309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61154127120972</t>
   </si>
   <si>
     <t xml:space="preserve">2.55988049507141</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">2.58482003211975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57769465446472</t>
+    <t xml:space="preserve">2.5776948928833</t>
   </si>
   <si>
     <t xml:space="preserve">2.56878757476807</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">2.5866014957428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5670063495636</t>
+    <t xml:space="preserve">2.56700611114502</t>
   </si>
   <si>
     <t xml:space="preserve">2.51890826225281</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">2.46724724769592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47080993652344</t>
+    <t xml:space="preserve">2.47081017494202</t>
   </si>
   <si>
     <t xml:space="preserve">2.48684310913086</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">2.48867678642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49051070213318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47400522232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43916010856628</t>
+    <t xml:space="preserve">2.49051094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47400498390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43915987014771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49417877197266</t>
@@ -5063,22 +5063,22 @@
     <t xml:space="preserve">2.51618599891663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52718997001648</t>
+    <t xml:space="preserve">2.5271897315979</t>
   </si>
   <si>
     <t xml:space="preserve">2.54002737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58587622642517</t>
+    <t xml:space="preserve">2.58587646484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.59871411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61521983146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6243896484375</t>
+    <t xml:space="preserve">2.6152195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62438941001892</t>
   </si>
   <si>
     <t xml:space="preserve">2.67390608787537</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">2.62255525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63172507286072</t>
+    <t xml:space="preserve">2.6317253112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.60971760749817</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">2.57303857803345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5510311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60604977607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58404231071472</t>
+    <t xml:space="preserve">2.55103135108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60605001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5840425491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.5675368309021</t>
@@ -5114,10 +5114,10 @@
     <t xml:space="preserve">2.5748724937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60054802894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63355922698975</t>
+    <t xml:space="preserve">2.6005482673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63355898857117</t>
   </si>
   <si>
     <t xml:space="preserve">2.61705350875854</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">2.6115517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5308575630188</t>
+    <t xml:space="preserve">2.53085780143738</t>
   </si>
   <si>
     <t xml:space="preserve">2.54736351966858</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">2.51802015304565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48500895500183</t>
+    <t xml:space="preserve">2.48500871658325</t>
   </si>
   <si>
     <t xml:space="preserve">2.51251816749573</t>
@@ -5153,19 +5153,19 @@
     <t xml:space="preserve">2.58037447929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59321236610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64089488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60238218307495</t>
+    <t xml:space="preserve">2.59321212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64089512825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60238194465637</t>
   </si>
   <si>
     <t xml:space="preserve">2.56386876106262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5602011680603</t>
+    <t xml:space="preserve">2.56020092964172</t>
   </si>
   <si>
     <t xml:space="preserve">2.54552936553955</t>
@@ -5180,13 +5180,13 @@
     <t xml:space="preserve">2.61338567733765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47583889961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48684239387512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4795069694519</t>
+    <t xml:space="preserve">2.47583913803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4868426322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47950673103333</t>
   </si>
   <si>
     <t xml:space="preserve">2.45383167266846</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.5033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767281532288</t>
+    <t xml:space="preserve">2.47767305374146</t>
   </si>
   <si>
     <t xml:space="preserve">2.49234461784363</t>
@@ -5207,19 +5207,19 @@
     <t xml:space="preserve">2.46116757392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40798282623291</t>
+    <t xml:space="preserve">2.40798258781433</t>
   </si>
   <si>
     <t xml:space="preserve">2.34196043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34562802314758</t>
+    <t xml:space="preserve">2.34562826156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462452888489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33645844459534</t>
+    <t xml:space="preserve">2.33645868301392</t>
   </si>
   <si>
     <t xml:space="preserve">2.31261706352234</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">2.27777194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29611134529114</t>
+    <t xml:space="preserve">2.29611158370972</t>
   </si>
   <si>
     <t xml:space="preserve">2.28694176673889</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">2.33095669746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36763548851013</t>
+    <t xml:space="preserve">2.36763572692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.35113000869751</t>
@@ -5264,13 +5264,13 @@
     <t xml:space="preserve">2.39881277084351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4024806022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40981674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41898655891418</t>
+    <t xml:space="preserve">2.40248084068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40981650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41898632049561</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732595443726</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">2.42815613746643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41531848907471</t>
+    <t xml:space="preserve">2.41531872749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.42448830604553</t>
@@ -5291,31 +5291,31 @@
     <t xml:space="preserve">2.39697909355164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39514517784119</t>
+    <t xml:space="preserve">2.39514493942261</t>
   </si>
   <si>
     <t xml:space="preserve">2.37863945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38780951499939</t>
+    <t xml:space="preserve">2.38780927658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.44099402427673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43182396888733</t>
+    <t xml:space="preserve">2.43182420730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.44466161727905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4428277015686</t>
+    <t xml:space="preserve">2.44282793998718</t>
   </si>
   <si>
     <t xml:space="preserve">2.31064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30297493934631</t>
+    <t xml:space="preserve">2.30297470092773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37008905410767</t>
@@ -5336,22 +5336,22 @@
     <t xml:space="preserve">2.43720316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38926458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43145036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46021366119385</t>
+    <t xml:space="preserve">2.38926482200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43145060539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46021389961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.41994524002075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41227531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40460467338562</t>
+    <t xml:space="preserve">2.41227507591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4046049118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.42569804191589</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">2.3643364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29722213745117</t>
+    <t xml:space="preserve">2.29722189903259</t>
   </si>
   <si>
     <t xml:space="preserve">2.197509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18408703804016</t>
+    <t xml:space="preserve">2.16491150856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18408679962158</t>
   </si>
   <si>
     <t xml:space="preserve">2.18792200088501</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">2.13806581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12272524833679</t>
+    <t xml:space="preserve">2.12272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">2.09012699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09971499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10354971885681</t>
+    <t xml:space="preserve">2.09971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10354995727539</t>
   </si>
   <si>
     <t xml:space="preserve">2.08053946495056</t>
@@ -5441,10 +5441,10 @@
     <t xml:space="preserve">2.00767254829407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95781636238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424970149994</t>
+    <t xml:space="preserve">1.95781624317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424946308136</t>
   </si>
   <si>
     <t xml:space="preserve">1.99808490276337</t>
@@ -5474,31 +5474,31 @@
     <t xml:space="preserve">2.07095170021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08820939064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07862186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04410600662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0306830406189</t>
+    <t xml:space="preserve">2.08820962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07862162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04410576820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03068327903748</t>
   </si>
   <si>
     <t xml:space="preserve">1.97315657138824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01534271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06903386116028</t>
+    <t xml:space="preserve">2.01534247398376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06903409957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.05561113357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10546731948853</t>
+    <t xml:space="preserve">2.1054675579071</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930252075195</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">2.05369353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752873420715</t>
+    <t xml:space="preserve">2.05752849578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.06136393547058</t>
@@ -5531,22 +5531,22 @@
     <t xml:space="preserve">2.03835320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02301287651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05177617073059</t>
+    <t xml:space="preserve">2.02301263809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05177640914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.05944633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643584251404</t>
+    <t xml:space="preserve">2.03643560409546</t>
   </si>
   <si>
     <t xml:space="preserve">2.07286906242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03260040283203</t>
+    <t xml:space="preserve">2.03260064125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.02876543998718</t>
@@ -5561,16 +5561,16 @@
     <t xml:space="preserve">2.09587979316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14573574066162</t>
+    <t xml:space="preserve">2.1457359790802</t>
   </si>
   <si>
     <t xml:space="preserve">2.11889028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12080788612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09204459190369</t>
+    <t xml:space="preserve">2.12080764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09204435348511</t>
   </si>
   <si>
     <t xml:space="preserve">1.85906255245209</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">1.9271354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94439351558685</t>
+    <t xml:space="preserve">1.94439363479614</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165144443512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93672323226929</t>
+    <t xml:space="preserve">1.93672311306</t>
   </si>
   <si>
     <t xml:space="preserve">1.92905306816101</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">1.87823808193207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87919688224792</t>
+    <t xml:space="preserve">1.87919676303864</t>
   </si>
   <si>
     <t xml:space="preserve">1.83029937744141</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">1.71812283992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73825693130493</t>
+    <t xml:space="preserve">1.73825705051422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75167989730835</t>
@@ -5985,6 +5985,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.95500004291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97599995136261</t>
   </si>
 </sst>
 </file>
@@ -71063,13 +71066,13 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6493171296</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>818502</v>
       </c>
       <c r="C2491" t="n">
-        <v>1.99399995803833</v>
+        <v>1.99600005149841</v>
       </c>
       <c r="D2491" t="n">
         <v>1.94400000572205</v>
@@ -71084,6 +71087,32 @@
         <v>1990</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6495717593</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>647324</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>1.97800004482269</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>1.97599995136261</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="1993">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847192287445</t>
+    <t xml:space="preserve">1.42847216129303</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177942276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36014819145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30827283859253</t>
+    <t xml:space="preserve">1.39177966117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3601485490799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30827295780182</t>
   </si>
   <si>
     <t xml:space="preserve">1.27158045768738</t>
@@ -62,70 +62,70 @@
     <t xml:space="preserve">1.21401143074036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28676331043243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425555229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009350776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18680846691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11595416069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09191417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15644216537476</t>
+    <t xml:space="preserve">1.28676342964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831763744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009338855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18680858612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1159542798996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09191429615021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478835582733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15644228458405</t>
   </si>
   <si>
     <t xml:space="preserve">1.1943998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23299026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20641946792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22097027301788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437737464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087067127228</t>
+    <t xml:space="preserve">1.232990026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20641994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22097015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437725543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087055206299</t>
   </si>
   <si>
     <t xml:space="preserve">1.1064647436142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1172194480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12164795398712</t>
+    <t xml:space="preserve">1.11721932888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12164783477783</t>
   </si>
   <si>
     <t xml:space="preserve">1.04699778556824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04826307296753</t>
+    <t xml:space="preserve">1.04826295375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.11848473548889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11089313030243</t>
+    <t xml:space="preserve">1.11089324951172</t>
   </si>
   <si>
     <t xml:space="preserve">1.13366782665253</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">1.19819581508636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21337878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213583946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578718185425</t>
+    <t xml:space="preserve">1.21337854862213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213619709015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578730106354</t>
   </si>
   <si>
     <t xml:space="preserve">1.17921698093414</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">1.13872873783112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1317697763443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770745277405</t>
+    <t xml:space="preserve">1.13176989555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770757198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.24311220645905</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.29182457923889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29941582679749</t>
+    <t xml:space="preserve">1.29941606521606</t>
   </si>
   <si>
     <t xml:space="preserve">1.32598638534546</t>
@@ -176,49 +176,49 @@
     <t xml:space="preserve">1.26525413990021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27917194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892794132233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199131965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413313388824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135903358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376718997955</t>
+    <t xml:space="preserve">1.27917182445526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892770290375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199120044708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135891437531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376742839813</t>
   </si>
   <si>
     <t xml:space="preserve">1.1823798418045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20452225208282</t>
+    <t xml:space="preserve">1.20452201366425</t>
   </si>
   <si>
     <t xml:space="preserve">1.21464407444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1918693780899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123673439026</t>
+    <t xml:space="preserve">1.19186913967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554294109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264666080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123661518097</t>
   </si>
   <si>
     <t xml:space="preserve">1.1798495054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17162549495697</t>
+    <t xml:space="preserve">1.17162537574768</t>
   </si>
   <si>
     <t xml:space="preserve">1.11152565479279</t>
@@ -227,76 +227,76 @@
     <t xml:space="preserve">1.09571015834808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07546591758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709750652313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417817115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062654972076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719722747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454459190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227039813995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405784130096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24820899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406289100647</t>
+    <t xml:space="preserve">1.07546603679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709738731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062666893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719675064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15454471111298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2482088804245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406301021576</t>
   </si>
   <si>
     <t xml:space="preserve">1.27812945842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26837277412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918719291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138184547424</t>
+    <t xml:space="preserve">1.26837289333344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138160705566</t>
   </si>
   <si>
     <t xml:space="preserve">1.27682852745056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2573150396347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495661258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031894207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1909693479538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527418136597</t>
+    <t xml:space="preserve">1.25731515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2449563741684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031882286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796063423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527406215668</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080557346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755342483521</t>
+    <t xml:space="preserve">1.17080581188202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755366325378</t>
   </si>
   <si>
     <t xml:space="preserve">1.16495168209076</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">1.18056225776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1538941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16300022602081</t>
+    <t xml:space="preserve">1.15389394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16300010681152</t>
   </si>
   <si>
     <t xml:space="preserve">1.16950464248657</t>
@@ -323,115 +323,115 @@
     <t xml:space="preserve">1.16169941425323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17731010913849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901801109314</t>
+    <t xml:space="preserve">1.1773099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18901813030243</t>
   </si>
   <si>
     <t xml:space="preserve">1.14283633232117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12852644920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11031377315521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0966545343399</t>
+    <t xml:space="preserve">1.12852656841278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1103138923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09665465354919</t>
   </si>
   <si>
     <t xml:space="preserve">1.10641133785248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055720806122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11486721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250890254974</t>
+    <t xml:space="preserve">1.10055732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1148669719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250866413116</t>
   </si>
   <si>
     <t xml:space="preserve">1.05112314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05372488498688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04657018184662</t>
+    <t xml:space="preserve">1.05372512340546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04657006263733</t>
   </si>
   <si>
     <t xml:space="preserve">1.04526925086975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10185813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120785236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12917685508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05307447910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640604972839</t>
+    <t xml:space="preserve">1.1018580198288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177883625031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120761394501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917697429657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05307471752167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255308628082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485590934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99518483877182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640616893768</t>
   </si>
   <si>
     <t xml:space="preserve">1.01339721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982826232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321697235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968516409397125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977622509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671231746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00364053249359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950954496860504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980874717235565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166994094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118032932281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965914607048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759665489197</t>
+    <t xml:space="preserve">0.982826173305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321637630463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851646900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97762268781662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00364077091217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950954675674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980875015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467984676361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166874885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965914487838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958759784698486</t>
   </si>
   <si>
     <t xml:space="preserve">1.05437552928925</t>
@@ -440,34 +440,34 @@
     <t xml:space="preserve">1.05957901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608366966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974302768707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283116340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673419475555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340214729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06022930145264</t>
+    <t xml:space="preserve">1.06608355045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892860889435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283128261566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340238571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06022953987122</t>
   </si>
   <si>
     <t xml:space="preserve">1.08559703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0927517414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11421692371368</t>
+    <t xml:space="preserve">1.09275186061859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11421656608582</t>
   </si>
   <si>
     <t xml:space="preserve">1.09795534610748</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">1.07779157161713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0738890171051</t>
+    <t xml:space="preserve">1.07388913631439</t>
   </si>
   <si>
     <t xml:space="preserve">1.10901319980621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11746919155121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348673820496</t>
+    <t xml:space="preserve">1.11746907234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348685741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.11876976490021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13828337192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14543807506561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278760433197</t>
+    <t xml:space="preserve">1.13828325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543795585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14023470878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12787628173828</t>
   </si>
   <si>
     <t xml:space="preserve">1.14218592643738</t>
@@ -509,55 +509,55 @@
     <t xml:space="preserve">1.15129220485687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16234982013702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14804005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0829952955246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315907001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600424766541</t>
+    <t xml:space="preserve">1.16234958171844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438045978546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299517631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600412845612</t>
   </si>
   <si>
     <t xml:space="preserve">1.08169436454773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990668296814</t>
+    <t xml:space="preserve">1.09990704059601</t>
   </si>
   <si>
     <t xml:space="preserve">1.0921014547348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10511028766632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11356627941132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08949971199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234488964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07518970966339</t>
+    <t xml:space="preserve">1.10511064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11356604099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08949983119965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584023475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234477043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925627708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429610729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0751895904541</t>
   </si>
   <si>
     <t xml:space="preserve">1.08754813671112</t>
@@ -575,58 +575,58 @@
     <t xml:space="preserve">1.07323849201202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933605670929</t>
+    <t xml:space="preserve">1.0693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04722058773041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348168849945</t>
+    <t xml:space="preserve">1.04722046852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047297477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348180770874</t>
   </si>
   <si>
     <t xml:space="preserve">1.0342116355896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01144576072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175767421722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95680832862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93339204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440889835358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93664425611496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653267860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9626624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957458674907684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507576465607</t>
+    <t xml:space="preserve">1.01144587993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982176005840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956808388233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392226696014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440949440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644494533539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95355612039566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96266233921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157803535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95745861530304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507457256317</t>
   </si>
   <si>
     <t xml:space="preserve">0.986728966236115</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">0.965264141559601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940547049045563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98607861995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835244655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429093837738</t>
+    <t xml:space="preserve">0.940547287464142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078441143036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835363864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429105758667</t>
   </si>
   <si>
     <t xml:space="preserve">1.02315402030945</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">1.03681337833405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02380442619324</t>
+    <t xml:space="preserve">1.02380454540253</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120268344879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04201686382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917192459106</t>
+    <t xml:space="preserve">1.04201698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917204380035</t>
   </si>
   <si>
     <t xml:space="preserve">1.02770709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04852163791656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0335613489151</t>
+    <t xml:space="preserve">1.04852151870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03356122970581</t>
   </si>
   <si>
     <t xml:space="preserve">1.03095948696136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03161013126373</t>
+    <t xml:space="preserve">1.03160977363586</t>
   </si>
   <si>
     <t xml:space="preserve">1.05567622184753</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.05502593517303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03291082382202</t>
+    <t xml:space="preserve">1.03291058540344</t>
   </si>
   <si>
     <t xml:space="preserve">1.03551244735718</t>
@@ -698,169 +698,169 @@
     <t xml:space="preserve">1.01860094070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999087333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925146579742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932451725006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00494146347046</t>
+    <t xml:space="preserve">0.999087512493134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925134658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932332515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00494134426117</t>
   </si>
   <si>
     <t xml:space="preserve">1.0251053571701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999737918376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534194469452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029778003693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401178836823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905476093292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01664936542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0296585559845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991281867027283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00949454307556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01795041561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01469826698303</t>
+    <t xml:space="preserve">0.999737739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981234073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534373283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905774116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0166494846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136669635773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02965831756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991282105445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00949466228485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01795053482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01469814777374</t>
   </si>
   <si>
     <t xml:space="preserve">1.03226041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.070636510849</t>
+    <t xml:space="preserve">1.07063674926758</t>
   </si>
   <si>
     <t xml:space="preserve">1.06218099594116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09470319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14478743076324</t>
+    <t xml:space="preserve">1.09470331668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14478766918182</t>
   </si>
   <si>
     <t xml:space="preserve">1.18251371383667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23585033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845243453979</t>
+    <t xml:space="preserve">1.23585021495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845219612122</t>
   </si>
   <si>
     <t xml:space="preserve">1.21633696556091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20983254909515</t>
+    <t xml:space="preserve">1.20983231067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.21438562870026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24755847454071</t>
+    <t xml:space="preserve">1.24755835533142</t>
   </si>
   <si>
     <t xml:space="preserve">1.21308469772339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20072615146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893858909607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527923107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20267760753632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446493148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16430127620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17600905895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999967098236</t>
+    <t xml:space="preserve">1.20072627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893846988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023975849152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381464481354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20267748832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446505069733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16430139541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17600929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999955177307</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22268402576447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482929706573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28777766227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26697432994843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27435612678528</t>
+    <t xml:space="preserve">1.22268414497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28777742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26697421073914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27435624599457</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013185501099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24348711967468</t>
+    <t xml:space="preserve">1.24348700046539</t>
   </si>
   <si>
     <t xml:space="preserve">1.24415814876556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22738146781921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818444252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422406196594</t>
+    <t xml:space="preserve">1.22738122940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818432331085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422394275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.2736850976944</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">1.24147391319275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23006546497345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831650733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26294791698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31462001800537</t>
+    <t xml:space="preserve">1.23006570339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831638813019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26294803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31462013721466</t>
   </si>
   <si>
     <t xml:space="preserve">1.30992269515991</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">1.3105936050415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32200193405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146296977997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30455422401428</t>
+    <t xml:space="preserve">1.32200181484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146273136139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
     <t xml:space="preserve">1.35555517673492</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">1.35018682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35689747333527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481799602509</t>
+    <t xml:space="preserve">1.35689735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481811523438</t>
   </si>
   <si>
     <t xml:space="preserve">1.3407918214798</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">1.32669937610626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32602822780609</t>
+    <t xml:space="preserve">1.32602834701538</t>
   </si>
   <si>
     <t xml:space="preserve">1.30388295650482</t>
@@ -923,67 +923,67 @@
     <t xml:space="preserve">1.30925142765045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29650151729584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34213399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300288677216</t>
+    <t xml:space="preserve">1.29650115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34213387966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287125825882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864655017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300300598145</t>
   </si>
   <si>
     <t xml:space="preserve">1.37031865119934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38239777088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3743451833725</t>
+    <t xml:space="preserve">1.38239789009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434506416321</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010949134827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43876731395721</t>
+    <t xml:space="preserve">1.43876755237579</t>
   </si>
   <si>
     <t xml:space="preserve">1.45084667205811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44816219806671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48976874351501</t>
+    <t xml:space="preserve">1.44816243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48976850509644</t>
   </si>
   <si>
     <t xml:space="preserve">1.46158385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46024167537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50721621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453245639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540110588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51929545402527</t>
+    <t xml:space="preserve">1.46024191379547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50721633434296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453197956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540122509003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51929569244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.50050568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50587439537048</t>
+    <t xml:space="preserve">1.50587391853333</t>
   </si>
   <si>
     <t xml:space="preserve">1.46829438209534</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">1.45755743980408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48037362098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44547820091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950473308563</t>
+    <t xml:space="preserve">1.48037374019623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44547808170319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950461387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.45621514320374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45889937877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279396533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566523551941</t>
+    <t xml:space="preserve">1.45889949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279432296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5756653547287</t>
   </si>
   <si>
     <t xml:space="preserve">1.66290378570557</t>
@@ -1019,220 +1019,220 @@
     <t xml:space="preserve">1.62129747867584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58640217781067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727166175842</t>
+    <t xml:space="preserve">1.58640241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042870998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727118492126</t>
   </si>
   <si>
     <t xml:space="preserve">1.64411401748657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60787642002106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61458671092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277160167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398219108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142990112305</t>
+    <t xml:space="preserve">1.60787630081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61458694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713959693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995577812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398207187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142954349518</t>
   </si>
   <si>
     <t xml:space="preserve">1.6306928396225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.723299741745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987844467163</t>
+    <t xml:space="preserve">1.72330009937286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7098788022995</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70853626728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048367977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732651233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108879566193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6857203245163</t>
+    <t xml:space="preserve">1.70853638648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048344135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719408988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732603549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68571996688843</t>
   </si>
   <si>
     <t xml:space="preserve">1.66693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66424584388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632520198822</t>
+    <t xml:space="preserve">1.66424596309662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632532119751</t>
   </si>
   <si>
     <t xml:space="preserve">1.65753531455994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740313053131</t>
+    <t xml:space="preserve">1.63740336894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.64679825305939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67364084720612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490604877472</t>
+    <t xml:space="preserve">1.67364072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7649062871933</t>
   </si>
   <si>
     <t xml:space="preserve">1.7743011713028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75819504261017</t>
+    <t xml:space="preserve">1.75819551944733</t>
   </si>
   <si>
     <t xml:space="preserve">1.74880027770996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73806345462799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7286684513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624834537506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174876213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832734584808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161633968353</t>
+    <t xml:space="preserve">1.73806285858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866833209991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624846458435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174888134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161681652069</t>
   </si>
   <si>
     <t xml:space="preserve">1.75416898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77564311027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074757099152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73537933826447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940551280975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953757762909</t>
+    <t xml:space="preserve">1.77564334869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208998680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7407478094101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940539360046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953769683838</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503811359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78772222995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101134300232</t>
+    <t xml:space="preserve">1.78772246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7810115814209</t>
   </si>
   <si>
     <t xml:space="preserve">1.81188094615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.798459649086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802485704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067071437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435566425323</t>
+    <t xml:space="preserve">1.79845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261788845062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248558521271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067059516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435578346252</t>
   </si>
   <si>
     <t xml:space="preserve">1.89911937713623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88704013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569796085358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84543430805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79577541351318</t>
+    <t xml:space="preserve">1.88704073429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569808006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79577493667603</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598421573639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71793138980865</t>
+    <t xml:space="preserve">1.71793127059937</t>
   </si>
   <si>
     <t xml:space="preserve">1.73001062870026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893210411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698493003845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222169399261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356387138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316815376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645762443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68035125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6951150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243085384369</t>
+    <t xml:space="preserve">1.76893246173859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698504924774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222145557404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356375217438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645702838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6803514957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69511532783508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69243049621582</t>
   </si>
   <si>
     <t xml:space="preserve">1.67766761779785</t>
@@ -1241,31 +1241,31 @@
     <t xml:space="preserve">1.63874530792236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64814054965973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653448104858</t>
+    <t xml:space="preserve">1.64814043045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653412342072</t>
   </si>
   <si>
     <t xml:space="preserve">1.60921835899353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57029640674591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57432281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5796914100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687522888184</t>
+    <t xml:space="preserve">1.57029628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57432293891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57969176769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687510967255</t>
   </si>
   <si>
     <t xml:space="preserve">1.54345393180847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51392710208893</t>
+    <t xml:space="preserve">1.51392698287964</t>
   </si>
   <si>
     <t xml:space="preserve">1.63203477859497</t>
@@ -1277,31 +1277,31 @@
     <t xml:space="preserve">1.66827237606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75148499011993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611604213715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71390473842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72195792198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658909320831</t>
+    <t xml:space="preserve">1.75148463249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611628055573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7139048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72195780277252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7165892124176</t>
   </si>
   <si>
     <t xml:space="preserve">1.63606119155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60384976863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371782302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674304485321</t>
+    <t xml:space="preserve">1.60385000705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371794223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53674328327179</t>
   </si>
   <si>
     <t xml:space="preserve">1.52197968959808</t>
@@ -1310,88 +1310,88 @@
     <t xml:space="preserve">1.546138048172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54882264137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54748022556305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53271687030792</t>
+    <t xml:space="preserve">1.54882276058197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54748046398163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53271698951721</t>
   </si>
   <si>
     <t xml:space="preserve">1.56895446777344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54076969623566</t>
+    <t xml:space="preserve">1.54076981544495</t>
   </si>
   <si>
     <t xml:space="preserve">1.54211187362671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52869057655334</t>
+    <t xml:space="preserve">1.52869033813477</t>
   </si>
   <si>
     <t xml:space="preserve">1.56761229038239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55955982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600622177124</t>
+    <t xml:space="preserve">1.55955946445465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600610256195</t>
   </si>
   <si>
     <t xml:space="preserve">1.58774435520172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61190283298492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519230365753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324512958527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56626999378204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782145023346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661145687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50318992137909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647927284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990068912506</t>
+    <t xml:space="preserve">1.61190295219421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56627035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50319004058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4964793920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990045070648</t>
   </si>
   <si>
     <t xml:space="preserve">1.42266190052032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4817156791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292591094971</t>
+    <t xml:space="preserve">1.48171591758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46292614936829</t>
   </si>
   <si>
     <t xml:space="preserve">1.46695232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48305773735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48439991474152</t>
+    <t xml:space="preserve">1.48305797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439979553223</t>
   </si>
   <si>
     <t xml:space="preserve">1.52332186698914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53405928611755</t>
+    <t xml:space="preserve">1.53405916690826</t>
   </si>
   <si>
     <t xml:space="preserve">1.57662498950958</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">1.56837069988251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53947937488556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884293556213</t>
+    <t xml:space="preserve">1.53947949409485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884317398071</t>
   </si>
   <si>
     <t xml:space="preserve">1.5160915851593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49958252906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56286764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57387387752533</t>
+    <t xml:space="preserve">1.49958264827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56286752223969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57387375831604</t>
   </si>
   <si>
     <t xml:space="preserve">1.55186140537262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52159452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095796585083</t>
+    <t xml:space="preserve">1.52159440517426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095808506012</t>
   </si>
   <si>
     <t xml:space="preserve">1.50233387947083</t>
@@ -1436,64 +1436,64 @@
     <t xml:space="preserve">1.47619426250458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44042456150055</t>
+    <t xml:space="preserve">1.44042491912842</t>
   </si>
   <si>
     <t xml:space="preserve">1.46656394004822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42804265022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43767297267914</t>
+    <t xml:space="preserve">1.42804253101349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43767273426056</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46518838405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931576728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106088161469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42116391658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37369990348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327882766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814532756805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180047512054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4362975358963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45143067836761</t>
+    <t xml:space="preserve">1.4651882648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106112003326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42116379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37370002269745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327894687653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280659198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180035591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629729747772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143091678619</t>
   </si>
   <si>
     <t xml:space="preserve">1.4156608581543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45555782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941856384277</t>
+    <t xml:space="preserve">1.45555794239044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904900550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941844463348</t>
   </si>
   <si>
     <t xml:space="preserve">1.41841232776642</t>
@@ -1502,67 +1502,67 @@
     <t xml:space="preserve">1.39640009403229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36613321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4142849445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5339766740799</t>
+    <t xml:space="preserve">1.3661333322525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41428506374359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53397655487061</t>
   </si>
   <si>
     <t xml:space="preserve">1.46793985366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4803215265274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48169755935669</t>
+    <t xml:space="preserve">1.48032188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4816974401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.47069144248962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48720073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50508546829224</t>
+    <t xml:space="preserve">1.48720049858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683117866516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50508534908295</t>
   </si>
   <si>
     <t xml:space="preserve">1.54085540771484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53122496604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223132133484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5491099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54773414134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5326007604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900690078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112169265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5656191110611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746726036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984929084778</t>
+    <t xml:space="preserve">1.5312248468399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223096370697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54911017417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5477340221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53260064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900678157806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56561899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746737957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52984941005707</t>
   </si>
   <si>
     <t xml:space="preserve">1.53810381889343</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">1.55461287498474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53672850131989</t>
+    <t xml:space="preserve">1.53672790527344</t>
   </si>
   <si>
     <t xml:space="preserve">1.45830953121185</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">1.40878188610077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38539409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576341629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36406970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364862442017</t>
+    <t xml:space="preserve">1.38539397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851512432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576365470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3640695810318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364874362946</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">1.36888480186462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32073307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2657026052475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28289949893951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909063339233</t>
+    <t xml:space="preserve">1.32073330879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26570272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28289973735809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909039497375</t>
   </si>
   <si>
     <t xml:space="preserve">1.29665720462799</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">1.33724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34343314170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33105134963989</t>
+    <t xml:space="preserve">1.34343302249908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3310512304306</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200606822968</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">1.37989103794098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38264226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089727401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978800296783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42666709423065</t>
+    <t xml:space="preserve">1.3826425075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089703559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978824138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42666661739349</t>
   </si>
   <si>
     <t xml:space="preserve">1.4321700334549</t>
@@ -1658,61 +1658,61 @@
     <t xml:space="preserve">1.41153359413147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35581505298615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37301242351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35719096660614</t>
+    <t xml:space="preserve">1.35581517219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37301206588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35719084739685</t>
   </si>
   <si>
     <t xml:space="preserve">1.32692408561707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28565108776093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771471977234</t>
+    <t xml:space="preserve">1.28565084934235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.295281291008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771483898163</t>
   </si>
   <si>
     <t xml:space="preserve">1.24506604671478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924482822418</t>
+    <t xml:space="preserve">1.22924470901489</t>
   </si>
   <si>
     <t xml:space="preserve">1.25951170921326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22786915302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2313084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18315672874451</t>
+    <t xml:space="preserve">1.22786891460419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130857944489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18315660953522</t>
   </si>
   <si>
     <t xml:space="preserve">1.19553875923157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19003558158875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025094509125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3338029384613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3000967502594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29940891265869</t>
+    <t xml:space="preserve">1.19003546237946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025106430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33380281925201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30009663105011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29940903186798</t>
   </si>
   <si>
     <t xml:space="preserve">1.28496325016022</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">1.29253005981445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26776611804962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28221166133881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818719387054</t>
+    <t xml:space="preserve">1.26776623725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088738441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051758766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818743228912</t>
   </si>
   <si>
     <t xml:space="preserve">1.25882375240326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26363897323608</t>
+    <t xml:space="preserve">1.26363921165466</t>
   </si>
   <si>
     <t xml:space="preserve">1.2326842546463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22030258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2120475769043</t>
+    <t xml:space="preserve">1.22030246257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21204781532288</t>
   </si>
   <si>
     <t xml:space="preserve">1.21411144733429</t>
@@ -1760,142 +1760,142 @@
     <t xml:space="preserve">1.18522036075592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18797194957733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20172941684723</t>
+    <t xml:space="preserve">1.18797183036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20172965526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.19347512722015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19966578483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2010418176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808463573456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28083574771881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2815238237381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273577213287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20379304885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19209945201874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21548712253571</t>
+    <t xml:space="preserve">1.1996659040451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20104169845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808439731598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28083598613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28152394294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676000118256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23612368106842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792067050934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273565292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20379316806793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19209921360016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.215487241745</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27946031093597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2505692243576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326929569244</t>
+    <t xml:space="preserve">1.27945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25056898593903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326941490173</t>
   </si>
   <si>
     <t xml:space="preserve">1.34136974811554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3021605014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353581905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32417249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32554841041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33930587768555</t>
+    <t xml:space="preserve">1.30216026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32417213916779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32554829120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33930611610413</t>
   </si>
   <si>
     <t xml:space="preserve">1.3475604057312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3317391872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110286712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523013114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34893620014191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063039302826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38126659393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3840184211731</t>
+    <t xml:space="preserve">1.33173930644989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110274791718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523001194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3489363193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063027381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3812667131424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38401830196381</t>
   </si>
   <si>
     <t xml:space="preserve">1.30422401428223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32623600959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480929374695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512721538544</t>
+    <t xml:space="preserve">1.32623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480917453766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34687256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512709617615</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957275867462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35787856578827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33793032169342</t>
+    <t xml:space="preserve">1.35787868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33793008327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.44455170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48307311534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323708057404</t>
+    <t xml:space="preserve">1.48307287693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323731899261</t>
   </si>
   <si>
     <t xml:space="preserve">1.5958856344223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64128613471985</t>
+    <t xml:space="preserve">1.64128589630127</t>
   </si>
   <si>
     <t xml:space="preserve">1.59038281440735</t>
@@ -1907,91 +1907,91 @@
     <t xml:space="preserve">1.598637342453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57937669754028</t>
+    <t xml:space="preserve">1.57937681674957</t>
   </si>
   <si>
     <t xml:space="preserve">1.56424331665039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52572178840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51334011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058828830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49545514583588</t>
+    <t xml:space="preserve">1.52572190761566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921273231506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334023475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058852672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49545502662659</t>
   </si>
   <si>
     <t xml:space="preserve">1.59726178646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60001313686371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340080738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007430553436</t>
+    <t xml:space="preserve">1.60001289844513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340092658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007418632507</t>
   </si>
   <si>
     <t xml:space="preserve">1.77611076831818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79949915409088</t>
+    <t xml:space="preserve">1.7994989156723</t>
   </si>
   <si>
     <t xml:space="preserve">1.7843656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85847687721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438879013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151500225067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719245433807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726269721985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75301086902618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153861522675</t>
+    <t xml:space="preserve">1.85847640037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7743889093399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719209671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726281642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7530106306076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153849601746</t>
   </si>
   <si>
     <t xml:space="preserve">1.7572865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025454998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595537662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420119762421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403638362885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89553201198578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572031974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434168338776</t>
+    <t xml:space="preserve">1.71025443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595513820648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420095920563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403650283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89553213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8157205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434180259705</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298713684082</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73733329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73590850830078</t>
+    <t xml:space="preserve">1.73733353614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7359082698822</t>
   </si>
   <si>
     <t xml:space="preserve">1.78579068183899</t>
@@ -2015,52 +2015,52 @@
     <t xml:space="preserve">1.76013684272766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80004262924194</t>
+    <t xml:space="preserve">1.80004286766052</t>
   </si>
   <si>
     <t xml:space="preserve">1.79006624221802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8442245721817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137403964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723932266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
+    <t xml:space="preserve">1.84422469139099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137427806854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723920345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016033649445</t>
   </si>
   <si>
     <t xml:space="preserve">1.7302074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310496330261</t>
+    <t xml:space="preserve">1.7131050825119</t>
   </si>
   <si>
     <t xml:space="preserve">1.74588477611542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80289328098297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282244205475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78294014930725</t>
+    <t xml:space="preserve">1.80289316177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564936161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282268047333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294026851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.80146789550781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81001913547516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8285471200943</t>
+    <t xml:space="preserve">1.81001925468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82854700088501</t>
   </si>
   <si>
     <t xml:space="preserve">1.83994877338409</t>
@@ -2072,34 +2072,34 @@
     <t xml:space="preserve">1.86560249328613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413035869598</t>
+    <t xml:space="preserve">1.88413023948669</t>
   </si>
   <si>
     <t xml:space="preserve">1.90265810489655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85562610626221</t>
+    <t xml:space="preserve">1.8556262254715</t>
   </si>
   <si>
     <t xml:space="preserve">1.86417746543884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88555574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396602153778</t>
+    <t xml:space="preserve">1.88555562496185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396566390991</t>
   </si>
   <si>
     <t xml:space="preserve">1.93116223812103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95681667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94398903846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87842917442322</t>
+    <t xml:space="preserve">1.95681619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94398939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87842953205109</t>
   </si>
   <si>
     <t xml:space="preserve">1.87700414657593</t>
@@ -2108,34 +2108,34 @@
     <t xml:space="preserve">1.85990178585052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90978407859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410650730133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130331993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524996757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89268159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543791770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0095489025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971359729767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819399833679</t>
+    <t xml:space="preserve">1.9097843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410638809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01525020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89268136024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00954866409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111477375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971383571625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819435596466</t>
   </si>
   <si>
     <t xml:space="preserve">1.98532032966614</t>
@@ -2144,91 +2144,91 @@
     <t xml:space="preserve">1.8171454668045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84279930591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139777183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94969010353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106826305389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669836997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9967223405838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957251548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648704528809</t>
+    <t xml:space="preserve">1.84279894828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139717578888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94968974590302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106850147247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672186374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648656845093</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655764579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07368350028992</t>
+    <t xml:space="preserve">2.06655740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07368326187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.06228184700012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96394217014313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831206321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123295783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695727825165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9169100522995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263473033905</t>
+    <t xml:space="preserve">1.96394205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831218242645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123331546783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695751667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973697185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91691029071808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263461112976</t>
   </si>
   <si>
     <t xml:space="preserve">1.89125657081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90835881233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99717044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94335007667542</t>
+    <t xml:space="preserve">1.90835928916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99717056751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9433501958847</t>
   </si>
   <si>
     <t xml:space="preserve">1.91425824165344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97971498966217</t>
+    <t xml:space="preserve">1.97971558570862</t>
   </si>
   <si>
     <t xml:space="preserve">1.96371483802795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97389674186707</t>
+    <t xml:space="preserve">1.97389662265778</t>
   </si>
   <si>
     <t xml:space="preserve">1.9506231546402</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">1.9098938703537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8938934803009</t>
+    <t xml:space="preserve">1.89389371871948</t>
   </si>
   <si>
     <t xml:space="preserve">1.93462264537811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89680302143097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952994346619</t>
+    <t xml:space="preserve">1.8968026638031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952958583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.94916868209839</t>
@@ -2261,28 +2261,28 @@
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735235214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01026201248169</t>
+    <t xml:space="preserve">2.00735259056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01026177406311</t>
   </si>
   <si>
     <t xml:space="preserve">1.98553359508514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00880742073059</t>
+    <t xml:space="preserve">2.00880718231201</t>
   </si>
   <si>
     <t xml:space="preserve">2.02189898490906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02917146682739</t>
+    <t xml:space="preserve">2.02917170524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208112716675</t>
+    <t xml:space="preserve">2.03208065032959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">2.10044717788696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09608364105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881370544434</t>
+    <t xml:space="preserve">2.09608340263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881394386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.08444666862488</t>
@@ -2303,22 +2303,22 @@
     <t xml:space="preserve">2.09753799438477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.080082654953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462904930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863482475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2473623752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18917798995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16590428352356</t>
+    <t xml:space="preserve">2.08008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462881088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1891782283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16590452194214</t>
   </si>
   <si>
     <t xml:space="preserve">2.09899258613586</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">2.06844615936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07717370986938</t>
+    <t xml:space="preserve">2.07717347145081</t>
   </si>
   <si>
     <t xml:space="preserve">2.07280969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12808537483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499357223511</t>
+    <t xml:space="preserve">2.12808513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">2.14553999900818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14699482917786</t>
+    <t xml:space="preserve">2.1469943523407</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390326499939</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">2.08299207687378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07426428794861</t>
+    <t xml:space="preserve">2.07426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.05826377868652</t>
@@ -2363,49 +2363,49 @@
     <t xml:space="preserve">2.04808139801025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335333824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771735191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06408166885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04226303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99426186084747</t>
+    <t xml:space="preserve">2.023353099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771687507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0640823841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04226326942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99426114559174</t>
   </si>
   <si>
     <t xml:space="preserve">2.03789925575256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03644466400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02626276016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589776039124</t>
+    <t xml:space="preserve">2.03644418716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02626252174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589799880981</t>
   </si>
   <si>
     <t xml:space="preserve">1.99862492084503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95935070514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080553531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280667304993</t>
+    <t xml:space="preserve">1.95935094356537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826039791107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280655384064</t>
   </si>
   <si>
     <t xml:space="preserve">2.0611732006073</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">2.06990075111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04080867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03353571891785</t>
+    <t xml:space="preserve">2.04080843925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
     <t xml:space="preserve">1.96807861328125</t>
@@ -2426,100 +2426,100 @@
     <t xml:space="preserve">1.91134870052338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370819568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79352593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079913139343</t>
+    <t xml:space="preserve">1.87643814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553057193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79352605342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079936981201</t>
   </si>
   <si>
     <t xml:space="preserve">1.81970882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84152793884277</t>
+    <t xml:space="preserve">1.84152805805206</t>
   </si>
   <si>
     <t xml:space="preserve">1.82552719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80516266822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83279979228973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171020030975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298264980316</t>
+    <t xml:space="preserve">1.80516302585602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83280026912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898315906525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171008110046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298229217529</t>
   </si>
   <si>
     <t xml:space="preserve">1.85752856731415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8357093334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880089759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061965465546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788994789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460995674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860932826996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152165412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388067245483</t>
+    <t xml:space="preserve">1.83570957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880077838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061989307404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460959911346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860920906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152129650116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388091087341</t>
   </si>
   <si>
     <t xml:space="preserve">1.55351638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56224405765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733337879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842368602753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278256893158</t>
+    <t xml:space="preserve">1.56224393844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770092487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5273334980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278268814087</t>
   </si>
   <si>
     <t xml:space="preserve">1.36441802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35569024085999</t>
+    <t xml:space="preserve">1.35569047927856</t>
   </si>
   <si>
     <t xml:space="preserve">1.19277465343475</t>
@@ -2528,37 +2528,37 @@
     <t xml:space="preserve">1.21241211891174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16150081157684</t>
+    <t xml:space="preserve">1.16150069236755</t>
   </si>
   <si>
     <t xml:space="preserve">1.1593189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13386344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10768043994904</t>
+    <t xml:space="preserve">1.1338632106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10768055915833</t>
   </si>
   <si>
     <t xml:space="preserve">1.11422610282898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1804107427597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968344688416</t>
+    <t xml:space="preserve">1.08440697193146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18041050434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968320846558</t>
   </si>
   <si>
     <t xml:space="preserve">1.19713854789734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11204421520233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877237796783</t>
+    <t xml:space="preserve">1.11204433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877225875854</t>
   </si>
   <si>
     <t xml:space="preserve">1.18550181388855</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">1.10549867153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09022521972656</t>
+    <t xml:space="preserve">1.09022510051727</t>
   </si>
   <si>
     <t xml:space="preserve">1.04149603843689</t>
@@ -2576,136 +2576,136 @@
     <t xml:space="preserve">1.07640647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23059463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24514043331146</t>
+    <t xml:space="preserve">1.23059451580048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24514055252075</t>
   </si>
   <si>
     <t xml:space="preserve">1.23641288280487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20077514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22186696529388</t>
+    <t xml:space="preserve">1.20077526569366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22186672687531</t>
   </si>
   <si>
     <t xml:space="preserve">1.24223124980927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36005389690399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023814678192</t>
+    <t xml:space="preserve">1.36005413532257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023802757263</t>
   </si>
   <si>
     <t xml:space="preserve">1.47351324558258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58939075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649662017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56247746944427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967908859253</t>
+    <t xml:space="preserve">1.58939063549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649650096893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331379413605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56247711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967920780182</t>
   </si>
   <si>
     <t xml:space="preserve">1.4608039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4757559299469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061188220978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48397982120514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192912101746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473425388336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46005642414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44884252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762850761414</t>
+    <t xml:space="preserve">1.47575604915619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500860691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284769535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48397958278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192900180817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473437309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931597232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46005630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44884240627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762862682343</t>
   </si>
   <si>
     <t xml:space="preserve">1.4951936006546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56546771526337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733306407928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228500843048</t>
+    <t xml:space="preserve">1.56546783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733342170715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228488922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.64321780204773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71498715877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807315826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479481697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535762310028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67760717868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65069353580475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490526676178</t>
+    <t xml:space="preserve">1.71498680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807375431061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471304416656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535726547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67760694026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65069365501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5849050283432</t>
   </si>
   <si>
     <t xml:space="preserve">1.59686660766602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62976086139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125610351562</t>
+    <t xml:space="preserve">1.62976109981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125598430634</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62527525424957</t>
+    <t xml:space="preserve">1.62527549266815</t>
   </si>
   <si>
     <t xml:space="preserve">1.58341014385223</t>
@@ -2714,40 +2714,40 @@
     <t xml:space="preserve">1.59238123893738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60135209560394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6417224407196</t>
+    <t xml:space="preserve">1.60135221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172232151031</t>
   </si>
   <si>
     <t xml:space="preserve">1.71050143241882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71797776222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7060159444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003485679626</t>
+    <t xml:space="preserve">1.71797752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003521442413</t>
   </si>
   <si>
     <t xml:space="preserve">1.67013108730316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68956851959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788129329681</t>
+    <t xml:space="preserve">1.68956875801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7478814125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.7254536151886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78077530860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656417369843</t>
+    <t xml:space="preserve">1.78077554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656381607056</t>
   </si>
   <si>
     <t xml:space="preserve">1.800213098526</t>
@@ -2762,67 +2762,67 @@
     <t xml:space="preserve">1.8600207567215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79871773719788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310723304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292934894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881396770477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104978084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264077663422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85852587223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291501045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786719322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039145946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992464542389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487682819366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543879985809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83011674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79124188423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8555349111557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666016578674</t>
+    <t xml:space="preserve">1.7987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8331071138382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292946815491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881432533264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161246776581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104990005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264065742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609783649445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85852563381195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039122104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141964912415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992476463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8301168680191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124176502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666028499603</t>
   </si>
   <si>
     <t xml:space="preserve">1.8076890707016</t>
@@ -2831,58 +2831,58 @@
     <t xml:space="preserve">1.77928054332733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83460247516632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170810222626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84805905818939</t>
+    <t xml:space="preserve">1.8346027135849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170798301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8480589389801</t>
   </si>
   <si>
     <t xml:space="preserve">1.84506869316101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87646794319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058332443237</t>
+    <t xml:space="preserve">1.87646782398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058308601379</t>
   </si>
   <si>
     <t xml:space="preserve">1.83908820152283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82862162590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947264671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900654792786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508315086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059766292572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442471027374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395813465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497246265411</t>
+    <t xml:space="preserve">1.82862174510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778494358063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947252750397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71349167823792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508303165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442435264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395825386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8749725818634</t>
   </si>
   <si>
     <t xml:space="preserve">1.84207844734192</t>
@@ -2891,25 +2891,25 @@
     <t xml:space="preserve">1.78227055072784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76582372188568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638628959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685226917267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246289253235</t>
+    <t xml:space="preserve">1.76582336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638617038727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246253490448</t>
   </si>
   <si>
     <t xml:space="preserve">1.6342465877533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51762139797211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836184978485</t>
+    <t xml:space="preserve">1.51762163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836196899414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74937641620636</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">1.75984299182892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72694861888885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386202335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469870567322</t>
+    <t xml:space="preserve">1.72694838047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80469882488251</t>
   </si>
   <si>
     <t xml:space="preserve">1.80918431282043</t>
@@ -2933,40 +2933,40 @@
     <t xml:space="preserve">1.81965053081512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86301100254059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235268115997</t>
+    <t xml:space="preserve">1.86301171779633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235244274139</t>
   </si>
   <si>
     <t xml:space="preserve">1.93926620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96617937088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159789085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216022014618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056886672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01345634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01497220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04074692726135</t>
+    <t xml:space="preserve">1.96617949008942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159753322601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216057777405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01345610618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.014972448349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04074716567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710175514221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316640853882</t>
+    <t xml:space="preserve">2.03316617012024</t>
   </si>
   <si>
     <t xml:space="preserve">1.99677872657776</t>
@@ -2975,37 +2975,37 @@
     <t xml:space="preserve">2.00890803337097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00132727622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981081485748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165006637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435924530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01042366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03013372421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03468251228333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05136036872864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04377961158752</t>
+    <t xml:space="preserve">2.00132703781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435972213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01042413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0301342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0346827507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0513608455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0437798500061</t>
   </si>
   <si>
     <t xml:space="preserve">2.07561874389648</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">2.06803798675537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12261986732483</t>
+    <t xml:space="preserve">2.10442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287671089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12261939048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.21358895301819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19084644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1620397567749</t>
+    <t xml:space="preserve">2.19084692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16203951835632</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">2.13323259353638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15597534179688</t>
+    <t xml:space="preserve">2.1559751033783</t>
   </si>
   <si>
     <t xml:space="preserve">2.18023347854614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20146012306213</t>
+    <t xml:space="preserve">2.20145964622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.27120304107666</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">2.18933033943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26362252235413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2484610080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2151050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21662092208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30000996589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32275223731995</t>
+    <t xml:space="preserve">2.26362204551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24846053123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21510529518127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21662187576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546141624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30000972747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32275247573853</t>
   </si>
   <si>
     <t xml:space="preserve">2.31062316894531</t>
@@ -3083,52 +3083,52 @@
     <t xml:space="preserve">2.3576238155365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34852695465088</t>
+    <t xml:space="preserve">2.3485267162323</t>
   </si>
   <si>
     <t xml:space="preserve">2.35914015769958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38794732093811</t>
+    <t xml:space="preserve">2.38794684410095</t>
   </si>
   <si>
     <t xml:space="preserve">2.36368846893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39249539375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639788627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491463661194</t>
+    <t xml:space="preserve">2.39249515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491487503052</t>
   </si>
   <si>
     <t xml:space="preserve">2.36520481109619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36823678016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430143356323</t>
+    <t xml:space="preserve">2.36823725700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.32426834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35459184646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549474716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38036632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4410126209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36065602302551</t>
+    <t xml:space="preserve">2.35459160804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549498558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.380366563797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44101238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36065626144409</t>
   </si>
   <si>
     <t xml:space="preserve">2.3727855682373</t>
@@ -3137,34 +3137,34 @@
     <t xml:space="preserve">2.318204164505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40007615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765714645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41523766517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978621482849</t>
+    <t xml:space="preserve">2.40007638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765738487244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41523814201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978645324707</t>
   </si>
   <si>
     <t xml:space="preserve">2.49407815933228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4349479675293</t>
+    <t xml:space="preserve">2.43494749069214</t>
   </si>
   <si>
     <t xml:space="preserve">2.41827034950256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42888307571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614104270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30759072303772</t>
+    <t xml:space="preserve">2.42888331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.32730078697205</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">2.35610771179199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45314168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51682043075562</t>
+    <t xml:space="preserve">2.45314192771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51681995391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.48649716377258</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">2.44859337806702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56685352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266157150269</t>
+    <t xml:space="preserve">2.54714369773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58959603309631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56685328483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266109466553</t>
   </si>
   <si>
     <t xml:space="preserve">2.65327453613281</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">2.61355924606323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52038168907166</t>
+    <t xml:space="preserve">2.52038145065308</t>
   </si>
   <si>
     <t xml:space="preserve">2.50052404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51579928398132</t>
+    <t xml:space="preserve">2.51579904556274</t>
   </si>
   <si>
     <t xml:space="preserve">2.51427173614502</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">2.49899649620056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52343654632568</t>
+    <t xml:space="preserve">2.52343678474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.53412938117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60286664962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386384963989</t>
+    <t xml:space="preserve">2.60286688804626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386432647705</t>
   </si>
   <si>
     <t xml:space="preserve">2.42109394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44553375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942427635193</t>
+    <t xml:space="preserve">2.44553422927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942379951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.47761130332947</t>
@@ -3254,19 +3254,19 @@
     <t xml:space="preserve">2.48066639900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41192865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262125015259</t>
+    <t xml:space="preserve">2.4119291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262148857117</t>
   </si>
   <si>
     <t xml:space="preserve">2.4669189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45775365829468</t>
+    <t xml:space="preserve">2.45775389671326</t>
   </si>
   <si>
     <t xml:space="preserve">2.43025875091553</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">2.45928144454956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44706177711487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43331384658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45622658729553</t>
+    <t xml:space="preserve">2.44706153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43331408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45622634887695</t>
   </si>
   <si>
     <t xml:space="preserve">2.48372197151184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023909568787</t>
+    <t xml:space="preserve">2.50816130638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023933410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.65938472747803</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.6486918926239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63799929618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67618727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61814212799072</t>
+    <t xml:space="preserve">2.63799953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67618703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61814188957214</t>
   </si>
   <si>
     <t xml:space="preserve">2.60439467430115</t>
@@ -3314,40 +3314,40 @@
     <t xml:space="preserve">2.65632963180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68382453918457</t>
+    <t xml:space="preserve">2.68382430076599</t>
   </si>
   <si>
     <t xml:space="preserve">2.73575949668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840718269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63952708244324</t>
+    <t xml:space="preserve">2.6884069442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63952732086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.61966943740845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59370160102844</t>
+    <t xml:space="preserve">2.59370183944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.54634952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53565669059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260207176208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50663447380066</t>
+    <t xml:space="preserve">2.53565645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885437965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50663423538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.58148193359375</t>
@@ -3359,55 +3359,55 @@
     <t xml:space="preserve">2.46997404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49135947227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48830413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48219394683838</t>
+    <t xml:space="preserve">2.49135899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48830389976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48219418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.40734648704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37526845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41040134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38290643692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48524880409241</t>
+    <t xml:space="preserve">2.37526869773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41040110588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38290619850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.44247889518738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47455668449402</t>
+    <t xml:space="preserve">2.47455644607544</t>
   </si>
   <si>
     <t xml:space="preserve">2.52801918983459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983192443848</t>
+    <t xml:space="preserve">2.4898316860199</t>
   </si>
   <si>
     <t xml:space="preserve">2.52649164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52496433258057</t>
+    <t xml:space="preserve">2.52496385574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.55856943130493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5539870262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54787659645081</t>
+    <t xml:space="preserve">2.55398678779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54787683486938</t>
   </si>
   <si>
     <t xml:space="preserve">2.56162452697754</t>
@@ -3416,46 +3416,46 @@
     <t xml:space="preserve">2.5295467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51732683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4516441822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4287314414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42414903640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42567658424377</t>
+    <t xml:space="preserve">2.51732635498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45164394378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42873191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42414927482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42567682266235</t>
   </si>
   <si>
     <t xml:space="preserve">2.45011639595032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42720365524292</t>
+    <t xml:space="preserve">2.4272038936615</t>
   </si>
   <si>
     <t xml:space="preserve">2.40581917762756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510668754578</t>
+    <t xml:space="preserve">2.5051064491272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596129417419</t>
+    <t xml:space="preserve">2.38596153259277</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901615142822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40887355804443</t>
+    <t xml:space="preserve">2.37221360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.37355327606201</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42535710334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791532516479</t>
+    <t xml:space="preserve">2.4253568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791484832764</t>
   </si>
   <si>
     <t xml:space="preserve">2.42378735542297</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">2.40965867042542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35000586509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34372687339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34058713912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33116817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35471558570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34686636924744</t>
+    <t xml:space="preserve">2.35157537460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35000610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34372663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34058737754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33116841316223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35471534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34686613082886</t>
   </si>
   <si>
     <t xml:space="preserve">2.39396071434021</t>
@@ -3503,25 +3503,25 @@
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44733452796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43948531150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47402048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105505943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45675301551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46931171417236</t>
+    <t xml:space="preserve">2.4473340511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4394850730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47402119636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410548210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45675325393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46931195259094</t>
   </si>
   <si>
     <t xml:space="preserve">2.46774172782898</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">2.4881489276886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50384736061096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45047402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837539672852</t>
+    <t xml:space="preserve">2.50384759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45047378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27622485160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837587356567</t>
   </si>
   <si>
     <t xml:space="preserve">2.25581741333008</t>
@@ -3551,25 +3551,25 @@
     <t xml:space="preserve">2.31547021865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29977178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29192328453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2715151309967</t>
+    <t xml:space="preserve">2.29977202415466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29192304611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27151584625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.36256456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31076073646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32017946243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2699453830719</t>
+    <t xml:space="preserve">2.31076049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32017970085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26994562149048</t>
   </si>
   <si>
     <t xml:space="preserve">2.2291305065155</t>
@@ -3590,49 +3590,49 @@
     <t xml:space="preserve">2.16005897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14122128486633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20401358604431</t>
+    <t xml:space="preserve">2.14122104644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20401406288147</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773411750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16319870948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732691764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1867458820343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18203616142273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16633820533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15534949302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14750051498413</t>
+    <t xml:space="preserve">2.16319847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732667922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18674564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18203592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1663384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15534973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14750027656555</t>
   </si>
   <si>
     <t xml:space="preserve">2.15848922729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21814203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21186280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23070025444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21657228469849</t>
+    <t xml:space="preserve">2.21814179420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23070049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21657204627991</t>
   </si>
   <si>
     <t xml:space="preserve">2.2275607585907</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">2.26366639137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31860947608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29349279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24796843528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23541021347046</t>
+    <t xml:space="preserve">2.31860971450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29349255561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2479681968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2354097366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.24011921882629</t>
@@ -3659,37 +3659,37 @@
     <t xml:space="preserve">2.24482870101929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26052689552307</t>
+    <t xml:space="preserve">2.26052665710449</t>
   </si>
   <si>
     <t xml:space="preserve">2.30291152000427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34529638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11924338340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20087385177612</t>
+    <t xml:space="preserve">2.34529662132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11924362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2008740901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831562995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22128176689148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23227047920227</t>
+    <t xml:space="preserve">2.22128200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23227024078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.23697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19930410385132</t>
+    <t xml:space="preserve">2.1993043422699</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599077224731</t>
@@ -3704,52 +3704,52 @@
     <t xml:space="preserve">2.03447437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0925567150116</t>
+    <t xml:space="preserve">2.09255719184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.05802130699158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97953057289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441377162933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0109269618988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92615735530853</t>
+    <t xml:space="preserve">1.97953081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441389083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01092672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92615723609924</t>
   </si>
   <si>
     <t xml:space="preserve">1.84766685962677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.800572514534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807441711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045880317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202867031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009357213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99365925788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796106338501</t>
+    <t xml:space="preserve">1.80057227611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592327594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254993915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807429790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045916080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202914714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00935745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9936591386795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97796082496643</t>
   </si>
   <si>
     <t xml:space="preserve">2.01877617835999</t>
@@ -3758,52 +3758,52 @@
     <t xml:space="preserve">2.0172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99208950996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98894941806793</t>
+    <t xml:space="preserve">1.99208891391754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98895001411438</t>
   </si>
   <si>
     <t xml:space="preserve">1.9967987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0595908164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249694824219</t>
+    <t xml:space="preserve">2.05959129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249599456787</t>
   </si>
   <si>
     <t xml:space="preserve">2.01406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96854197978973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639107704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220226764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650431156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516864299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301774024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947056770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92124795913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576610088348</t>
+    <t xml:space="preserve">1.96854221820831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639095783234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220298290253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650454998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516852378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301738262177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790081977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947068691254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92124760150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576598167419</t>
   </si>
   <si>
     <t xml:space="preserve">2.01642298698425</t>
@@ -3815,31 +3815,31 @@
     <t xml:space="preserve">1.96964204311371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93092656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543783664703</t>
+    <t xml:space="preserve">1.93092668056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543771743774</t>
   </si>
   <si>
     <t xml:space="preserve">1.87607991695404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277001619339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91156899929047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221107959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.847043633461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607269287109</t>
+    <t xml:space="preserve">1.92770040035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91156888008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189003944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704315662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8260725736618</t>
   </si>
   <si>
     <t xml:space="preserve">1.77122604846954</t>
@@ -3848,61 +3848,61 @@
     <t xml:space="preserve">1.79703593254089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81316745281219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672969818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9438316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382433891296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802144050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9325395822525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479527950287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318924427032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254704475403</t>
+    <t xml:space="preserve">1.81316733360291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801409721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672945976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383180141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963469982147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382445812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802179813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253970146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96318960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254692554474</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932810783386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609448432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448844909668</t>
+    <t xml:space="preserve">1.97609436511993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448892593384</t>
   </si>
   <si>
     <t xml:space="preserve">2.01480984687805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97448134422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97770762443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99061298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9341527223587</t>
+    <t xml:space="preserve">1.97448122501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97770738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9906131029129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93415331840515</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124037742615</t>
@@ -3917,16 +3917,16 @@
     <t xml:space="preserve">1.88898503780365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86317479610443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85833537578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84381723403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672247409821</t>
+    <t xml:space="preserve">1.86317491531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85833525657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8438173532486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672235488892</t>
   </si>
   <si>
     <t xml:space="preserve">1.88253259658813</t>
@@ -3935,64 +3935,64 @@
     <t xml:space="preserve">1.87769317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8486567735672</t>
+    <t xml:space="preserve">1.84865629673004</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187547206879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81155455112457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993382930756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78574407100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81800675392151</t>
+    <t xml:space="preserve">1.81155431270599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993371009827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78574419021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8180068731308</t>
   </si>
   <si>
     <t xml:space="preserve">1.86962735652924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8357515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768571376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93899214267731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95189738273621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383902549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802914142609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222588539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06643033027649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0744960308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05029916763306</t>
+    <t xml:space="preserve">1.83575141429901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768595218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350317955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93899238109589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95189774036407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99222576618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06643009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07449626922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0502986907959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05191206932068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03416728973389</t>
+    <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.01319670677185</t>
@@ -4001,28 +4001,28 @@
     <t xml:space="preserve">2.07288265228271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09546709060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07933568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07610893249512</t>
+    <t xml:space="preserve">2.09546685218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0793354511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0761091709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.00351786613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00835728645325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98899984359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95512342453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932076454163</t>
+    <t xml:space="preserve">2.00835752487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98899972438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512402057648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932052612305</t>
   </si>
   <si>
     <t xml:space="preserve">1.89866411685944</t>
@@ -4031,31 +4031,31 @@
     <t xml:space="preserve">1.91318225860596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92931318283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9728684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480214595795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9454448223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83736479282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025614738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647299766541</t>
+    <t xml:space="preserve">1.92931354045868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286868095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96480274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94544517993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83736455440521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025590896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647275924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.85495913028717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81474316120148</t>
+    <t xml:space="preserve">1.81474328041077</t>
   </si>
   <si>
     <t xml:space="preserve">1.78290569782257</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">1.78458142280579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79128396511078</t>
+    <t xml:space="preserve">1.79128384590149</t>
   </si>
   <si>
     <t xml:space="preserve">1.776202917099</t>
@@ -4079,28 +4079,28 @@
     <t xml:space="preserve">1.74604105949402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79798674583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966235160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333739757538</t>
+    <t xml:space="preserve">1.79798662662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966223239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8566347360611</t>
+    <t xml:space="preserve">1.85663497447968</t>
   </si>
   <si>
     <t xml:space="preserve">1.86166155338287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87674260139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171578407288</t>
+    <t xml:space="preserve">1.87674283981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171566486359</t>
   </si>
   <si>
     <t xml:space="preserve">1.89517521858215</t>
@@ -4109,28 +4109,28 @@
     <t xml:space="preserve">1.91360723972321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93203961849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685070514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355324745178</t>
+    <t xml:space="preserve">1.93203949928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8968505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355336666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.92701280117035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94879639148712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94376933574677</t>
+    <t xml:space="preserve">1.94879627227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94376921653748</t>
   </si>
   <si>
     <t xml:space="preserve">2.09625482559204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1783618927002</t>
+    <t xml:space="preserve">2.17836213111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.19176721572876</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">2.14820003509521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16160535812378</t>
+    <t xml:space="preserve">2.16160559654236</t>
   </si>
   <si>
     <t xml:space="preserve">2.18506479263306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29901003837585</t>
+    <t xml:space="preserve">2.29900979995728</t>
   </si>
   <si>
     <t xml:space="preserve">2.29230737686157</t>
@@ -4157,31 +4157,31 @@
     <t xml:space="preserve">2.32582068443298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33419895172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34257745742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32917189598083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25711846351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29398274421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30906414985657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30068588256836</t>
+    <t xml:space="preserve">2.33419871330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3425772190094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32917165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25711822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2939829826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30906391143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30068564414978</t>
   </si>
   <si>
     <t xml:space="preserve">2.31576633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29733443260193</t>
+    <t xml:space="preserve">2.29733419418335</t>
   </si>
   <si>
     <t xml:space="preserve">2.31409120559692</t>
@@ -4190,31 +4190,31 @@
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33755016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42636013031006</t>
+    <t xml:space="preserve">2.33754968643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42636036872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981956481934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46657633781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490025520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47998142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4632248878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306279182434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38614416122437</t>
+    <t xml:space="preserve">2.46657586097717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4799816608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46322512626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38614439964294</t>
   </si>
   <si>
     <t xml:space="preserve">2.40122532844543</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">2.40290093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609028816223</t>
+    <t xml:space="preserve">2.37609004974365</t>
   </si>
   <si>
     <t xml:space="preserve">2.38279318809509</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">2.41295480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35430693626404</t>
+    <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
     <t xml:space="preserve">2.36938786506653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37776589393616</t>
+    <t xml:space="preserve">2.37776637077332</t>
   </si>
   <si>
     <t xml:space="preserve">2.36100959777832</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">2.34927988052368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37944149971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38781976699829</t>
+    <t xml:space="preserve">2.37944173812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38782000541687</t>
   </si>
   <si>
     <t xml:space="preserve">2.49171113967896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45987343788147</t>
+    <t xml:space="preserve">2.45987391471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371069908142</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">2.77322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78160095214844</t>
+    <t xml:space="preserve">2.78160119056702</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019518852234</t>
@@ -4286,19 +4286,19 @@
     <t xml:space="preserve">2.93073487281799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92905950546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90224862098694</t>
+    <t xml:space="preserve">2.92905926704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90224838256836</t>
   </si>
   <si>
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03295016288757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06311202049255</t>
+    <t xml:space="preserve">3.03295040130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06311225891113</t>
   </si>
   <si>
     <t xml:space="preserve">3.11840891838074</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">3.1502468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16030097007751</t>
+    <t xml:space="preserve">3.16030120849609</t>
   </si>
   <si>
     <t xml:space="preserve">3.20554351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20219254493713</t>
+    <t xml:space="preserve">3.20219230651855</t>
   </si>
   <si>
     <t xml:space="preserve">3.1435444355011</t>
@@ -4325,7 +4325,7 @@
     <t xml:space="preserve">3.18878698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19213843345642</t>
+    <t xml:space="preserve">3.19213819503784</t>
   </si>
   <si>
     <t xml:space="preserve">3.1988410949707</t>
@@ -4334,43 +4334,43 @@
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29267835617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30608367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33792090415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132622718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40494751930237</t>
+    <t xml:space="preserve">3.29267811775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3060839176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33792114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132670402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40494775772095</t>
   </si>
   <si>
     <t xml:space="preserve">3.25581336021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34797477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31781339645386</t>
+    <t xml:space="preserve">3.34797501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781315803528</t>
   </si>
   <si>
     <t xml:space="preserve">3.39321804046631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3647313117981</t>
+    <t xml:space="preserve">3.36473178863525</t>
   </si>
   <si>
     <t xml:space="preserve">3.35467791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18543577194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24240851402283</t>
+    <t xml:space="preserve">3.18543529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24240827560425</t>
   </si>
   <si>
     <t xml:space="preserve">3.13851714134216</t>
@@ -4379,13 +4379,13 @@
     <t xml:space="preserve">3.23235440254211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13349032402039</t>
+    <t xml:space="preserve">3.13349008560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.1904628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23403000831604</t>
+    <t xml:space="preserve">3.23402976989746</t>
   </si>
   <si>
     <t xml:space="preserve">3.2457594871521</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">3.23905682563782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21559762954712</t>
+    <t xml:space="preserve">3.2155978679657</t>
   </si>
   <si>
     <t xml:space="preserve">3.26419162750244</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">3.43510961532593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30105686187744</t>
+    <t xml:space="preserve">3.30105662345886</t>
   </si>
   <si>
     <t xml:space="preserve">3.40159606933594</t>
@@ -4424,40 +4424,40 @@
     <t xml:space="preserve">3.38483953475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37981224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37143421173096</t>
+    <t xml:space="preserve">3.37981247901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36640763282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37143492698669</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619142532349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31243991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23508644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21789646148682</t>
+    <t xml:space="preserve">3.31243968009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23508620262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2178966999054</t>
   </si>
   <si>
     <t xml:space="preserve">3.22305369377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2041449546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21445918083191</t>
+    <t xml:space="preserve">3.20414519309998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21445870399475</t>
   </si>
   <si>
     <t xml:space="preserve">3.19555020332336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16976571083069</t>
+    <t xml:space="preserve">3.16976594924927</t>
   </si>
   <si>
     <t xml:space="preserve">3.25571417808533</t>
@@ -4466,40 +4466,40 @@
     <t xml:space="preserve">3.20070719718933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12335395812988</t>
+    <t xml:space="preserve">3.12335419654846</t>
   </si>
   <si>
     <t xml:space="preserve">3.05975222587585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09413146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08897495269775</t>
+    <t xml:space="preserve">3.09413170814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08897471427917</t>
   </si>
   <si>
     <t xml:space="preserve">3.10616445541382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13366770744324</t>
+    <t xml:space="preserve">3.13366746902466</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18867444992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22649192810059</t>
+    <t xml:space="preserve">3.18867468833923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22649168968201</t>
   </si>
   <si>
     <t xml:space="preserve">3.2660276889801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24024319648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09928822517395</t>
+    <t xml:space="preserve">3.24024343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09928846359253</t>
   </si>
   <si>
     <t xml:space="preserve">3.16117119789124</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">3.09756946563721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06834673881531</t>
+    <t xml:space="preserve">3.06834697723389</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429520606995</t>
@@ -4526,19 +4526,19 @@
     <t xml:space="preserve">3.14741945266724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10960221290588</t>
+    <t xml:space="preserve">3.10960245132446</t>
   </si>
   <si>
     <t xml:space="preserve">3.12507295608521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18695569038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17664217948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14398145675659</t>
+    <t xml:space="preserve">3.18695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17664194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14398169517517</t>
   </si>
   <si>
     <t xml:space="preserve">3.27462267875671</t>
@@ -4547,13 +4547,13 @@
     <t xml:space="preserve">3.24196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19039344787598</t>
+    <t xml:space="preserve">3.1903932094574</t>
   </si>
   <si>
     <t xml:space="preserve">3.19898819923401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15601396560669</t>
+    <t xml:space="preserve">3.15601420402527</t>
   </si>
   <si>
     <t xml:space="preserve">3.26258969306946</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">3.27290368080139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12851071357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10272669792175</t>
+    <t xml:space="preserve">3.12851095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10272622108459</t>
   </si>
   <si>
     <t xml:space="preserve">3.08209872245789</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">3.0081832408905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01162123680115</t>
+    <t xml:space="preserve">3.01162147521973</t>
   </si>
   <si>
     <t xml:space="preserve">3.03396797180176</t>
@@ -4598,13 +4598,13 @@
     <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583698272705</t>
+    <t xml:space="preserve">2.98583674430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.07350397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07006597518921</t>
+    <t xml:space="preserve">3.07006621360779</t>
   </si>
   <si>
     <t xml:space="preserve">3.05287671089172</t>
@@ -4613,22 +4613,22 @@
     <t xml:space="preserve">2.9755232334137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94458222389221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93083047866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9205162525177</t>
+    <t xml:space="preserve">2.94458198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93083024024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92051649093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.87582349777222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87754225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88785600662231</t>
+    <t xml:space="preserve">2.87754249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88785624504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.91020250320435</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286322593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786949157715</t>
+    <t xml:space="preserve">2.96005272865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786972999573</t>
   </si>
   <si>
     <t xml:space="preserve">3.05115747451782</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">3.05459547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08725571632385</t>
+    <t xml:space="preserve">3.08725595474243</t>
   </si>
   <si>
     <t xml:space="preserve">3.04256272315979</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">3.03912472724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0649094581604</t>
+    <t xml:space="preserve">3.06490898132324</t>
   </si>
   <si>
     <t xml:space="preserve">2.9749481678009</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">3.03729748725891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99276208877563</t>
+    <t xml:space="preserve">2.99276232719421</t>
   </si>
   <si>
     <t xml:space="preserve">2.9535710811615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79858875274658</t>
+    <t xml:space="preserve">2.79858899116516</t>
   </si>
   <si>
     <t xml:space="preserve">2.67210912704468</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">2.69526720046997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67032766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6079785823822</t>
+    <t xml:space="preserve">2.67032742500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60797834396362</t>
   </si>
   <si>
     <t xml:space="preserve">2.58838272094727</t>
@@ -4745,16 +4745,16 @@
     <t xml:space="preserve">2.36570739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32473492622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28554391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3372049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392593383789</t>
+    <t xml:space="preserve">2.32473468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2855441570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720517158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392569541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.26060438156128</t>
@@ -4769,10 +4769,10 @@
     <t xml:space="preserve">2.38708424568176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32829761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32117223739624</t>
+    <t xml:space="preserve">2.32829785346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32117199897766</t>
   </si>
   <si>
     <t xml:space="preserve">2.36927008628845</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955401420593</t>
+    <t xml:space="preserve">2.39955425262451</t>
   </si>
   <si>
     <t xml:space="preserve">2.42449378967285</t>
@@ -4817,10 +4817,10 @@
     <t xml:space="preserve">2.3603630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41380524635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51534533500671</t>
+    <t xml:space="preserve">2.41380500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51534509658813</t>
   </si>
   <si>
     <t xml:space="preserve">2.49931263923645</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">2.5830385684967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64360642433167</t>
+    <t xml:space="preserve">2.64360666275024</t>
   </si>
   <si>
     <t xml:space="preserve">2.64895081520081</t>
@@ -4883,16 +4883,16 @@
     <t xml:space="preserve">2.65429496765137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60441541671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60619711875916</t>
+    <t xml:space="preserve">2.60441565513611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60619735717773</t>
   </si>
   <si>
     <t xml:space="preserve">2.59550881385803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74336528778076</t>
+    <t xml:space="preserve">2.74336504936218</t>
   </si>
   <si>
     <t xml:space="preserve">2.71664428710938</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">2.66676473617554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73445844650269</t>
+    <t xml:space="preserve">2.73445820808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.77721190452576</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">2.76474237442017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72911405563354</t>
+    <t xml:space="preserve">2.72911381721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.74692821502686</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">2.82352876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84846806526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77008628845215</t>
+    <t xml:space="preserve">2.84846830368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77008652687073</t>
   </si>
   <si>
     <t xml:space="preserve">2.8128399848938</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">2.84312415122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7576162815094</t>
+    <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
     <t xml:space="preserve">2.63469958305359</t>
@@ -4988,7 +4988,7 @@
     <t xml:space="preserve">2.53137803077698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5420663356781</t>
+    <t xml:space="preserve">2.54206657409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.55809903144836</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">2.52781534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51178240776062</t>
+    <t xml:space="preserve">2.5117826461792</t>
   </si>
   <si>
     <t xml:space="preserve">2.50821971893311</t>
@@ -5009,19 +5009,19 @@
     <t xml:space="preserve">2.60263395309448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61154127120972</t>
+    <t xml:space="preserve">2.61154103279114</t>
   </si>
   <si>
     <t xml:space="preserve">2.55988049507141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58482003211975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5776948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56878757476807</t>
+    <t xml:space="preserve">2.58482027053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57769465446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56878733634949</t>
   </si>
   <si>
     <t xml:space="preserve">2.5866014957428</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">2.56700611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51890826225281</t>
+    <t xml:space="preserve">2.51890802383423</t>
   </si>
   <si>
     <t xml:space="preserve">2.46724724769592</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">2.47081017494202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48684310913086</t>
+    <t xml:space="preserve">2.48684287071228</t>
   </si>
   <si>
     <t xml:space="preserve">2.48867678642273</t>
@@ -5988,6 +5988,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.97599995136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98199999332428</t>
   </si>
 </sst>
 </file>
@@ -71092,7 +71095,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495717593</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>647324</v>
@@ -71113,6 +71116,32 @@
         <v>1991</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496296296</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>509256</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>2.00600004196167</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>1.96800005435944</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1992</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847216129303</t>
+    <t xml:space="preserve">1.42847192287445</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177966117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3601485490799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30827295780182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158045768738</t>
+    <t xml:space="preserve">1.3917795419693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36014831066132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158081531525</t>
   </si>
   <si>
     <t xml:space="preserve">1.23931634426117</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">1.21401143074036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28676342964172</t>
+    <t xml:space="preserve">1.28676331043243</t>
   </si>
   <si>
     <t xml:space="preserve">1.23425531387329</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">1.20831763744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20009338855743</t>
+    <t xml:space="preserve">1.20009350776672</t>
   </si>
   <si>
     <t xml:space="preserve">1.18680858612061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1159542798996</t>
+    <t xml:space="preserve">1.11595416069031</t>
   </si>
   <si>
     <t xml:space="preserve">1.09191429615021</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">1.17478835582733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644228458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1943998336792</t>
+    <t xml:space="preserve">1.15644240379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19439995288849</t>
   </si>
   <si>
     <t xml:space="preserve">1.232990026474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20641994476318</t>
+    <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
     <t xml:space="preserve">1.22097015380859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24437725543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087055206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1064647436142</t>
+    <t xml:space="preserve">1.24437761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087090969086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10646462440491</t>
   </si>
   <si>
     <t xml:space="preserve">1.11721932888031</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">1.04699778556824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04826295375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848473548889</t>
+    <t xml:space="preserve">1.04826307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11848449707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.11089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13366782665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17795169353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19819581508636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21337854862213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213619709015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578730106354</t>
+    <t xml:space="preserve">1.13366770744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17795145511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19819569587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213572025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578718185425</t>
   </si>
   <si>
     <t xml:space="preserve">1.17921698093414</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">1.13872873783112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13176989555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770757198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688537120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29182457923889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29941606521606</t>
+    <t xml:space="preserve">1.13176965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770769119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311232566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688560962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29182434082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994157075882</t>
   </si>
   <si>
     <t xml:space="preserve">1.32598638534546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26525413990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27917182445526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892770290375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199120044708</t>
+    <t xml:space="preserve">1.2652542591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27917206287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892794132233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199143886566</t>
   </si>
   <si>
     <t xml:space="preserve">1.22413337230682</t>
@@ -197,145 +197,145 @@
     <t xml:space="preserve">1.1823798418045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20452201366425</t>
+    <t xml:space="preserve">1.20452189445496</t>
   </si>
   <si>
     <t xml:space="preserve">1.21464407444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19186913967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554294109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264666080475</t>
+    <t xml:space="preserve">1.1918693780899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264654159546</t>
   </si>
   <si>
     <t xml:space="preserve">1.19123661518097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1798495054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17162537574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11152565479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09571015834808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546603679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709738731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417840957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062666893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719675064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454471111298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405796051025</t>
+    <t xml:space="preserve">1.17984938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17162561416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1115255355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09571003913879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546591758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709726810455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417817115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062654972076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719698905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15454435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227039813995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405772209167</t>
   </si>
   <si>
     <t xml:space="preserve">1.2482088804245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25406301021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812945842743</t>
+    <t xml:space="preserve">1.25406312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812957763672</t>
   </si>
   <si>
     <t xml:space="preserve">1.26837289333344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28918695449829</t>
+    <t xml:space="preserve">1.28918707370758</t>
   </si>
   <si>
     <t xml:space="preserve">1.28138160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27682852745056</t>
+    <t xml:space="preserve">1.27682864665985</t>
   </si>
   <si>
     <t xml:space="preserve">1.25731515884399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2449563741684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031882286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19096946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796063423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527406215668</t>
+    <t xml:space="preserve">1.24495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031929969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1909693479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527430057526</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080581188202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755366325378</t>
+    <t xml:space="preserve">1.17080557346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755330562592</t>
   </si>
   <si>
     <t xml:space="preserve">1.16495168209076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17340743541718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18056225776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15389394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16300010681152</t>
+    <t xml:space="preserve">1.17340755462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056237697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15389406681061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16300022602081</t>
   </si>
   <si>
     <t xml:space="preserve">1.16950464248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15649569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16169941425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1773099899292</t>
+    <t xml:space="preserve">1.15649592876434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16169929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17731010913849</t>
   </si>
   <si>
     <t xml:space="preserve">1.18901813030243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14283633232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12852656841278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1103138923645</t>
+    <t xml:space="preserve">1.14283621311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11031401157379</t>
   </si>
   <si>
     <t xml:space="preserve">1.09665465354919</t>
@@ -347,94 +347,94 @@
     <t xml:space="preserve">1.10055732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1148669719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250866413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372512340546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04657006263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04526925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1018580198288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177883625031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120761394501</t>
+    <t xml:space="preserve">1.11486709117889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250878334045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372500419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04657018184662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04526901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1012077331543</t>
   </si>
   <si>
     <t xml:space="preserve">1.12917697429657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05307471752167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255308628082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485590934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99518483877182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640616893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01339721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982826173305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321637630463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851646900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97762268781662</t>
+    <t xml:space="preserve">1.05307459831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485769748688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184779167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01339733600616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982826352119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321995258331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977622628211975</t>
   </si>
   <si>
     <t xml:space="preserve">0.975671291351318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00364077091217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950954675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467984676361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166874885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118152141571</t>
+    <t xml:space="preserve">1.00364053249359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95095431804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980874836444855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467865467072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969167172908783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118032932281</t>
   </si>
   <si>
     <t xml:space="preserve">0.965914487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958759784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437552928925</t>
+    <t xml:space="preserve">0.958759546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437564849854</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957901477814</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">1.06608355045319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07974278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892860889435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283128261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673383712769</t>
+    <t xml:space="preserve">1.07974302768707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892848968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283140182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673407554626</t>
   </si>
   <si>
     <t xml:space="preserve">1.09340238571167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06022953987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08559703826904</t>
+    <t xml:space="preserve">1.06022942066193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08559691905975</t>
   </si>
   <si>
     <t xml:space="preserve">1.09275186061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11421656608582</t>
+    <t xml:space="preserve">1.11421692371368</t>
   </si>
   <si>
     <t xml:space="preserve">1.09795534610748</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">1.07779157161713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07388913631439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10901319980621</t>
+    <t xml:space="preserve">1.07388889789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10901308059692</t>
   </si>
   <si>
     <t xml:space="preserve">1.11746907234192</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">1.11876976490021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13828325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14543795585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14023470878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12787628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218592643738</t>
+    <t xml:space="preserve">1.13828313350677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543831348419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1402348279953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1278760433197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218616485596</t>
   </si>
   <si>
     <t xml:space="preserve">1.15129220485687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16234958171844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438045978546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299517631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600412845612</t>
+    <t xml:space="preserve">1.16234982013702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14804005622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315907001495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600400924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.08169436454773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990704059601</t>
+    <t xml:space="preserve">1.09990692138672</t>
   </si>
   <si>
     <t xml:space="preserve">1.0921014547348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10511064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11356604099274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08949983119965</t>
+    <t xml:space="preserve">1.10511040687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11356616020203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08949971199036</t>
   </si>
   <si>
     <t xml:space="preserve">1.07584023475647</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">1.08234477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925627708435</t>
+    <t xml:space="preserve">1.09925651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.08429610729218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0751895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08754813671112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07453942298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827820301056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762779712677</t>
+    <t xml:space="preserve">1.07519006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0875483751297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0745393037796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827832221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762767791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.07323849201202</t>
@@ -590,61 +590,61 @@
     <t xml:space="preserve">1.06348180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0342116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144587993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982176005840302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956808388233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392226696014</t>
+    <t xml:space="preserve">1.03421175479889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0114461183548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95680820941925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392107486725</t>
   </si>
   <si>
     <t xml:space="preserve">0.931440949440002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.936644494533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95355612039566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96266233921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157803535461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95745861530304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507457256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986728966236115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965264141559601</t>
+    <t xml:space="preserve">0.936644434928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653685092926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953556001186371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962662220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157863140106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986728727817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965264201164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.940547287464142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986078441143036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835363864899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429105758667</t>
+    <t xml:space="preserve">0.986078560352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429117679596</t>
   </si>
   <si>
     <t xml:space="preserve">1.02315402030945</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">1.03681337833405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02380454540253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02120268344879</t>
+    <t xml:space="preserve">1.02380442619324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02120280265808</t>
   </si>
   <si>
     <t xml:space="preserve">1.04201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04917204380035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770709991455</t>
+    <t xml:space="preserve">1.04917192459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770733833313</t>
   </si>
   <si>
     <t xml:space="preserve">1.04852151870728</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">1.03095948696136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03160977363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567622184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05502593517303</t>
+    <t xml:space="preserve">1.03160989284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05502581596375</t>
   </si>
   <si>
     <t xml:space="preserve">1.03291058540344</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">1.03551244735718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01860094070435</t>
+    <t xml:space="preserve">1.01860082149506</t>
   </si>
   <si>
     <t xml:space="preserve">0.999087512493134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01925134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932332515717</t>
+    <t xml:space="preserve">1.01925146579742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932451725006</t>
   </si>
   <si>
     <t xml:space="preserve">1.00494134426117</t>
@@ -713,70 +713,70 @@
     <t xml:space="preserve">1.0251053571701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999737739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981234073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534373283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029837608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905774116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0166494846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136669635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02965831756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991282105445862</t>
+    <t xml:space="preserve">0.999737977981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981055259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401178836823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905714511871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01664972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404786109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02965819835663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991282045841217</t>
   </si>
   <si>
     <t xml:space="preserve">1.00949466228485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01795053482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01469814777374</t>
+    <t xml:space="preserve">1.01795041561127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01469790935516</t>
   </si>
   <si>
     <t xml:space="preserve">1.03226041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07063674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06218099594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09470331668854</t>
+    <t xml:space="preserve">1.070636510849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06218087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09470319747925</t>
   </si>
   <si>
     <t xml:space="preserve">1.14478766918182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18251371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23585021495819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845219612122</t>
+    <t xml:space="preserve">1.18251359462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23585033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845231533051</t>
   </si>
   <si>
     <t xml:space="preserve">1.21633696556091</t>
@@ -785,64 +785,64 @@
     <t xml:space="preserve">1.20983231067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21438562870026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755835533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21308469772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20072627067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893846988678</t>
+    <t xml:space="preserve">1.21438539028168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21308445930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20072615146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893858909607</t>
   </si>
   <si>
     <t xml:space="preserve">1.22023975849152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20527935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381464481354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20267748832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446505069733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16430139541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17600929737091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999955177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194696426392</t>
+    <t xml:space="preserve">1.20527946949005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20267736911774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446528911591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16430115699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17600905895233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999943256378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194684505463</t>
   </si>
   <si>
     <t xml:space="preserve">1.22268414497375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24482917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502703666687</t>
+    <t xml:space="preserve">1.24482905864716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502715587616</t>
   </si>
   <si>
     <t xml:space="preserve">1.28777742385864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26697421073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27435624599457</t>
+    <t xml:space="preserve">1.26697432994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013185501099</t>
@@ -851,58 +851,58 @@
     <t xml:space="preserve">1.24348700046539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24415814876556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22738122940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818432331085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422394275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2736850976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24147391319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006570339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831638813019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26294803619385</t>
+    <t xml:space="preserve">1.2441577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2273815870285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818444252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422406196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27368497848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24147367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006546497345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26294791698456</t>
   </si>
   <si>
     <t xml:space="preserve">1.31462013721466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30992269515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3105936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200181484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146273136139</t>
+    <t xml:space="preserve">1.30992257595062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059384346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200169563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3414626121521</t>
   </si>
   <si>
     <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35555517673492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689735412598</t>
+    <t xml:space="preserve">1.35555493831635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018658638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689747333527</t>
   </si>
   <si>
     <t xml:space="preserve">1.34481811523438</t>
@@ -911,85 +911,85 @@
     <t xml:space="preserve">1.3407918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32669937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32602834701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30388295650482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925142765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29650115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34213387966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287125825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864655017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031865119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239789009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37434506416321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010949134827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43876755237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45084667205811</t>
+    <t xml:space="preserve">1.32669925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32602822780609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30388307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925130844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29650127887726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34213411808014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871270179749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864678859711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300312519073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031853199005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239800930023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010961055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4387674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45084655284882</t>
   </si>
   <si>
     <t xml:space="preserve">1.44816243648529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48976850509644</t>
+    <t xml:space="preserve">1.48976874351501</t>
   </si>
   <si>
     <t xml:space="preserve">1.46158385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46024191379547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50721633434296</t>
+    <t xml:space="preserve">1.46024167537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50721621513367</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453197956085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53540122509003</t>
+    <t xml:space="preserve">1.53540134429932</t>
   </si>
   <si>
     <t xml:space="preserve">1.51929569244385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50587391853333</t>
+    <t xml:space="preserve">1.5005054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50587427616119</t>
   </si>
   <si>
     <t xml:space="preserve">1.46829438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45755743980408</t>
+    <t xml:space="preserve">1.4575572013855</t>
   </si>
   <si>
     <t xml:space="preserve">1.48037374019623</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">1.44950461387634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45621514320374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45889949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279432296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5756653547287</t>
+    <t xml:space="preserve">1.45621526241302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45889961719513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279372692108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566511631012</t>
   </si>
   <si>
     <t xml:space="preserve">1.66290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62129747867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042870998383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727118492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411401748657</t>
+    <t xml:space="preserve">1.621297955513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640217781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042859077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727130413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411377906799</t>
   </si>
   <si>
     <t xml:space="preserve">1.60787630081177</t>
@@ -1037,52 +1037,52 @@
     <t xml:space="preserve">1.61458694934845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59713959693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995577812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277195930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398207187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142954349518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6306928396225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72330009937286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7098788022995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853638648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048344135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719408988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732603549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68571996688843</t>
+    <t xml:space="preserve">1.59713935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6427720785141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350890159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398183345795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142978191376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069260120392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.723299741745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558802127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853650569916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108843803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68572020530701</t>
   </si>
   <si>
     <t xml:space="preserve">1.66693019866943</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">1.66424596309662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67632532119751</t>
+    <t xml:space="preserve">1.67632508277893</t>
   </si>
   <si>
     <t xml:space="preserve">1.65753531455994</t>
@@ -1106,28 +1106,28 @@
     <t xml:space="preserve">1.67364072799683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7649062871933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7743011713028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75819551944733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74880027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73806285858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866833209991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624846458435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174888134003</t>
+    <t xml:space="preserve">1.76490604877472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77430081367493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75819563865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74880051612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7380633354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866880893707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624822616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174852371216</t>
   </si>
   <si>
     <t xml:space="preserve">1.77832746505737</t>
@@ -1136,244 +1136,244 @@
     <t xml:space="preserve">1.77161681652069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75416898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208998680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7407478094101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7353789806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503811359406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772246837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7810115814209</t>
+    <t xml:space="preserve">1.75416886806488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564311027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208962917328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73537909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940551280975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7595374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503835201263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101146221161</t>
   </si>
   <si>
     <t xml:space="preserve">1.81188094615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261788845062</t>
+    <t xml:space="preserve">1.79845929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261776924133</t>
   </si>
   <si>
     <t xml:space="preserve">1.80248558521271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83067059516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435578346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88704073429108</t>
+    <t xml:space="preserve">1.83067083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8843560218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8991197347641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870404958725</t>
   </si>
   <si>
     <t xml:space="preserve">1.88569808006287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84543418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79577493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598421573639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793127059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001062870026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893246173859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698504924774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222145557404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356375217438</t>
+    <t xml:space="preserve">1.84543454647064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598433494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793150901794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001074790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893258094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356363296509</t>
   </si>
   <si>
     <t xml:space="preserve">1.70316791534424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69645702838898</t>
+    <t xml:space="preserve">1.69645738601685</t>
   </si>
   <si>
     <t xml:space="preserve">1.6803514957428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69511532783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653412342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57029628753662</t>
+    <t xml:space="preserve">1.6951150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69243085384369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67766773700714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874554634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814019203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5702965259552</t>
   </si>
   <si>
     <t xml:space="preserve">1.57432293891907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57969176769257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687510967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345393180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51392698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63203477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229902744293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827237606049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148463249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611628055573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7139048576355</t>
+    <t xml:space="preserve">1.57969152927399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687534809113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345405101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51392722129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63203489780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827261447906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611616134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390473842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.72195780277252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7165892124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606119155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385000705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371794223785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674328327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197968959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.546138048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54882276058197</t>
+    <t xml:space="preserve">1.71658933162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606107234955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60385024547577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371770381927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5367431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197957038879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54613792896271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54882264137268</t>
   </si>
   <si>
     <t xml:space="preserve">1.54748046398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53271698951721</t>
+    <t xml:space="preserve">1.53271675109863</t>
   </si>
   <si>
     <t xml:space="preserve">1.56895446777344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54076981544495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56761229038239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955946445465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600610256195</t>
+    <t xml:space="preserve">1.54076969623566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.542111992836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869021892548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56761252880096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600634098053</t>
   </si>
   <si>
     <t xml:space="preserve">1.58774435520172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61190295219421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56627035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661109924316</t>
+    <t xml:space="preserve">1.61190247535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519194602966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324524879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5662704706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782168865204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661133766174</t>
   </si>
   <si>
     <t xml:space="preserve">1.50319004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4964793920517</t>
+    <t xml:space="preserve">1.49647915363312</t>
   </si>
   <si>
     <t xml:space="preserve">1.50990045070648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42266190052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48171591758728</t>
+    <t xml:space="preserve">1.42266178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48171555995941</t>
   </si>
   <si>
     <t xml:space="preserve">1.46292614936829</t>
@@ -1382,31 +1382,31 @@
     <t xml:space="preserve">1.46695232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48305797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48439979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52332186698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405916690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662498950958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56837069988251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947949409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884317398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5160915851593</t>
+    <t xml:space="preserve">1.48305773735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4844001531601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332198619843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5340588092804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662510871887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947961330414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884305477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51609146595001</t>
   </si>
   <si>
     <t xml:space="preserve">1.49958264827728</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">1.56286752223969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57387375831604</t>
+    <t xml:space="preserve">1.57387387752533</t>
   </si>
   <si>
     <t xml:space="preserve">1.55186140537262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52159440517426</t>
+    <t xml:space="preserve">1.52159464359283</t>
   </si>
   <si>
     <t xml:space="preserve">1.50095808506012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50233387947083</t>
+    <t xml:space="preserve">1.5023341178894</t>
   </si>
   <si>
     <t xml:space="preserve">1.49820673465729</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">1.47619426250458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44042491912842</t>
+    <t xml:space="preserve">1.44042456150055</t>
   </si>
   <si>
     <t xml:space="preserve">1.46656394004822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42804253101349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43767273426056</t>
+    <t xml:space="preserve">1.4280424118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43767309188843</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4651882648468</t>
+    <t xml:space="preserve">1.46518862247467</t>
   </si>
   <si>
     <t xml:space="preserve">1.46931564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46106112003326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42116379737854</t>
+    <t xml:space="preserve">1.46106123924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42116391658783</t>
   </si>
   <si>
     <t xml:space="preserve">1.37370002269745</t>
@@ -1469,64 +1469,64 @@
     <t xml:space="preserve">1.40327894687653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38814544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280659198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180035591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629729747772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45143091678619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4156608581543</t>
+    <t xml:space="preserve">1.38814532756805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280635356903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180047512054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629717826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143067836761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41566097736359</t>
   </si>
   <si>
     <t xml:space="preserve">1.45555794239044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43904900550842</t>
+    <t xml:space="preserve">1.43904888629913</t>
   </si>
   <si>
     <t xml:space="preserve">1.42941844463348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41841232776642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39640009403229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3661333322525</t>
+    <t xml:space="preserve">1.41841220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.396399974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36613321304321</t>
   </si>
   <si>
     <t xml:space="preserve">1.41428506374359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53397655487061</t>
+    <t xml:space="preserve">1.53397643566132</t>
   </si>
   <si>
     <t xml:space="preserve">1.46793985366821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48032188415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4816974401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069144248962</t>
+    <t xml:space="preserve">1.48032164573669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48169755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069120407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.48720049858093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49683117866516</t>
+    <t xml:space="preserve">1.49683082103729</t>
   </si>
   <si>
     <t xml:space="preserve">1.50508534908295</t>
@@ -1535,184 +1535,184 @@
     <t xml:space="preserve">1.54085540771484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5312248468399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223096370697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54911017417908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5477340221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53260064125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900678157806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112216949463</t>
+    <t xml:space="preserve">1.53122508525848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223120212555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5491099357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54773426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53260052204132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900690078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112193107605</t>
   </si>
   <si>
     <t xml:space="preserve">1.56561899185181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51746737957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984941005707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810381889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461287498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45830953121185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.417036652565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878188610077</t>
+    <t xml:space="preserve">1.51746761798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52984917163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810393810272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461275577545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672802448273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45830917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878212451935</t>
   </si>
   <si>
     <t xml:space="preserve">1.38539397716522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37851512432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576365470886</t>
+    <t xml:space="preserve">1.37851536273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576389312744</t>
   </si>
   <si>
     <t xml:space="preserve">1.3640695810318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39364874362946</t>
+    <t xml:space="preserve">1.39364862442017</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36888480186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073330879211</t>
+    <t xml:space="preserve">1.36888492107391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073295116425</t>
   </si>
   <si>
     <t xml:space="preserve">1.26570272445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28289973735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909039497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29665720462799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33724212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34343302249908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3310512304306</t>
+    <t xml:space="preserve">1.28289937973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909075260162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29665732383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33724224567413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34343314170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33105134963989</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200606822968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37989103794098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3826425075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089703559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978824138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42666661739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4321700334549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4307941198349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43492150306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41153359413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37301206588745</t>
+    <t xml:space="preserve">1.37989115715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38264238834381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089715480804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978788375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4266664981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43216991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43079400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43492162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41153371334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581505298615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37301218509674</t>
   </si>
   <si>
     <t xml:space="preserve">1.35719084739685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32692408561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565084934235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.295281291008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771483898163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24506604671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22924470901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25951170921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22786891460419</t>
+    <t xml:space="preserve">1.32692396640778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565108776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528152942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771471977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24506616592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22924482822418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25951159000397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22786903381348</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130857944489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18315660953522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19553875923157</t>
+    <t xml:space="preserve">1.1831568479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19553864002228</t>
   </si>
   <si>
     <t xml:space="preserve">1.19003546237946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24025106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380281925201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30009663105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29940903186798</t>
+    <t xml:space="preserve">1.24025082588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33380305767059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30009651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29940891265869</t>
   </si>
   <si>
     <t xml:space="preserve">1.28496325016022</t>
@@ -1721,40 +1721,40 @@
     <t xml:space="preserve">1.30078458786011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29253005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26776623725891</t>
+    <t xml:space="preserve">1.29252994060516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26776647567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.2822117805481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088738441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051758766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818743228912</t>
+    <t xml:space="preserve">1.26088726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051770687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818707466125</t>
   </si>
   <si>
     <t xml:space="preserve">1.25882375240326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26363921165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2326842546463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22030246257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21204781532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21411144733429</t>
+    <t xml:space="preserve">1.26363885402679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23268449306488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22030222415924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21411120891571</t>
   </si>
   <si>
     <t xml:space="preserve">1.18522036075592</t>
@@ -1763,25 +1763,25 @@
     <t xml:space="preserve">1.18797183036804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20172965526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19347512722015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1996659040451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808439731598</t>
+    <t xml:space="preserve">1.20172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19347488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19966566562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20104157924652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808451652527</t>
   </si>
   <si>
     <t xml:space="preserve">1.28083598613739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28152394294739</t>
+    <t xml:space="preserve">1.2815238237381</t>
   </si>
   <si>
     <t xml:space="preserve">1.25676000118256</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">1.23612368106842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20792067050934</t>
+    <t xml:space="preserve">1.20792055130005</t>
   </si>
   <si>
     <t xml:space="preserve">1.21273565292358</t>
@@ -1805,46 +1805,46 @@
     <t xml:space="preserve">1.215487241745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29046630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27945995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25056898593903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326941490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136974811554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30216026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32417213916779</t>
+    <t xml:space="preserve">1.29046642780304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27946031093597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25056910514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326929569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30216038227081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32417237758636</t>
   </si>
   <si>
     <t xml:space="preserve">1.32554829120636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33930611610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3475604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33173930644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110274791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523001194</t>
+    <t xml:space="preserve">1.33930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34756052494049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33173942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523013114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.3489363193512</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">1.36063027381897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3812667131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38401830196381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480917453766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687256813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512709617615</t>
+    <t xml:space="preserve">1.38126683235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38401818275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422389507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623600959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3468724489212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512721538544</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957275867462</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">1.35787868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33793008327484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44455170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48307287693024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323731899261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958856344223</t>
+    <t xml:space="preserve">1.33793032169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44455182552338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307347297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59588575363159</t>
   </si>
   <si>
     <t xml:space="preserve">1.64128589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59038281440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276460647583</t>
+    <t xml:space="preserve">1.59038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276484489441</t>
   </si>
   <si>
     <t xml:space="preserve">1.598637342453</t>
@@ -1913,25 +1913,25 @@
     <t xml:space="preserve">1.56424331665039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52572190761566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921273231506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51334023475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058852672577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49545502662659</t>
+    <t xml:space="preserve">1.52572178840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334035396576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49545514583588</t>
   </si>
   <si>
     <t xml:space="preserve">1.59726178646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60001289844513</t>
+    <t xml:space="preserve">1.600013256073</t>
   </si>
   <si>
     <t xml:space="preserve">1.62340092658997</t>
@@ -1940,136 +1940,136 @@
     <t xml:space="preserve">1.71007418632507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77611076831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7994989156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7843656539917</t>
+    <t xml:space="preserve">1.77611112594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79949855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78436553478241</t>
   </si>
   <si>
     <t xml:space="preserve">1.85847640037537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7743889093399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719209671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726281642914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7530106306076</t>
+    <t xml:space="preserve">1.77438902854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151524066925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719221591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726305484772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301086902618</t>
   </si>
   <si>
     <t xml:space="preserve">1.77153849601746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7572865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025443077087</t>
+    <t xml:space="preserve">1.75728642940521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025431156158</t>
   </si>
   <si>
     <t xml:space="preserve">1.71595513820648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85420095920563</t>
+    <t xml:space="preserve">1.85420072078705</t>
   </si>
   <si>
     <t xml:space="preserve">1.92403650283813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89553213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8157205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018359184265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597875118256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73733353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7359082698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579068183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013684272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79006624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422469139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137427806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723920345306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016033649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7302074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131050825119</t>
+    <t xml:space="preserve">1.89553225040436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572008132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434192180634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298725605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018406867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597887039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73733365535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73590850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579080104828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004251003265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79006636142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422421455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137415885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723932266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016069412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73020720481873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310496330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.74588477611542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80289316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564936161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282268047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78294026851654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001925468445</t>
+    <t xml:space="preserve">1.80289328098297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564924240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282256126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146825313568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001901626587</t>
   </si>
   <si>
     <t xml:space="preserve">1.82854700088501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83994877338409</t>
+    <t xml:space="preserve">1.83994889259338</t>
   </si>
   <si>
     <t xml:space="preserve">1.87415397167206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86560249328613</t>
+    <t xml:space="preserve">1.86560261249542</t>
   </si>
   <si>
     <t xml:space="preserve">1.88413023948669</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">1.90265810489655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8556262254715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417746543884</t>
+    <t xml:space="preserve">1.85562598705292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417710781097</t>
   </si>
   <si>
     <t xml:space="preserve">1.88555562496185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95396566390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116223812103</t>
+    <t xml:space="preserve">1.95396602153778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9311625957489</t>
   </si>
   <si>
     <t xml:space="preserve">1.95681619644165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94398939609528</t>
+    <t xml:space="preserve">1.9439891576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.87842953205109</t>
@@ -2105,139 +2105,139 @@
     <t xml:space="preserve">1.87700414657593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990178585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410638809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01525020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89268136024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543815612793</t>
+    <t xml:space="preserve">1.85990166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978407859802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410674571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524972915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89268147945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543791770935</t>
   </si>
   <si>
     <t xml:space="preserve">2.00954866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95111477375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971383571625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819435596466</t>
+    <t xml:space="preserve">1.95111548900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819471359253</t>
   </si>
   <si>
     <t xml:space="preserve">1.98532032966614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8171454668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279894828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139717578888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94968974590302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106850147247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669860839844</t>
+    <t xml:space="preserve">1.81714534759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279930591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139729499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969010353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517889022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669836997986</t>
   </si>
   <si>
     <t xml:space="preserve">2.03092694282532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99672186374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957263469696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648656845093</t>
+    <t xml:space="preserve">1.99672162532806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07368326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06228184700012</t>
+    <t xml:space="preserve">2.06655764579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07368350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0622820854187</t>
   </si>
   <si>
     <t xml:space="preserve">1.96394205093384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92831218242645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123331546783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695751667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973697185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691029071808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263461112976</t>
+    <t xml:space="preserve">1.92831194400787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123295783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695727825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91691017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263449192047</t>
   </si>
   <si>
     <t xml:space="preserve">1.89125657081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90835928916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99717056751251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9433501958847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425824165344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971558570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96371483802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389662265778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9506231546402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9098938703537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389371871948</t>
+    <t xml:space="preserve">1.90835881233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9971706867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94334995746613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96371471881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389674186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95062327384949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989446640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389336109161</t>
   </si>
   <si>
     <t xml:space="preserve">1.93462264537811</t>
@@ -2246,19 +2246,19 @@
     <t xml:space="preserve">1.8968026638031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88952958583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916868209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953284740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02044415473938</t>
+    <t xml:space="preserve">1.8895298242569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916844367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880427837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02044439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.00735259056091</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">2.01026177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98553359508514</t>
+    <t xml:space="preserve">1.98553347587585</t>
   </si>
   <si>
     <t xml:space="preserve">2.00880718231201</t>
@@ -2276,22 +2276,22 @@
     <t xml:space="preserve">2.02189898490906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02917170524597</t>
+    <t xml:space="preserve">2.02917194366455</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208065032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05099058151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10044717788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608340263367</t>
+    <t xml:space="preserve">2.03208088874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05099081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10044693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608364105225</t>
   </si>
   <si>
     <t xml:space="preserve">2.16881394386292</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">2.08444666862488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09753799438477</t>
+    <t xml:space="preserve">2.09753775596619</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008241653442</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">2.24736213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1891782283783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16590452194214</t>
+    <t xml:space="preserve">2.18917751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1659038066864</t>
   </si>
   <si>
     <t xml:space="preserve">2.09899258613586</t>
@@ -2333,82 +2333,82 @@
     <t xml:space="preserve">2.07280969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12808513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499309539795</t>
+    <t xml:space="preserve">2.128084897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499357223511</t>
   </si>
   <si>
     <t xml:space="preserve">2.14553999900818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1469943523407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390326499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13099408149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08299207687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05826377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.023353099823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771687507629</t>
+    <t xml:space="preserve">2.14699482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13099384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0829918384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07426404953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05826354026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808115959167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335381507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771759033203</t>
   </si>
   <si>
     <t xml:space="preserve">2.0640823841095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04226326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99426114559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789925575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03644418716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517269134521</t>
+    <t xml:space="preserve">2.04226303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99426138401031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03644466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517245292664</t>
   </si>
   <si>
     <t xml:space="preserve">2.02626252174377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00589799880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862492084503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935094356537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826039791107</t>
+    <t xml:space="preserve">2.00589823722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9986252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95935070514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826063632965</t>
   </si>
   <si>
     <t xml:space="preserve">1.96080541610718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99280655384064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0611732006073</t>
+    <t xml:space="preserve">1.99280667304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06117272377014</t>
   </si>
   <si>
     <t xml:space="preserve">2.06990075111389</t>
@@ -2417,142 +2417,142 @@
     <t xml:space="preserve">2.04080843925476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03353548049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96807861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134870052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098405838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553057193756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79352605342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81970882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152805805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516302585602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83280026912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898315906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171008110046</t>
+    <t xml:space="preserve">2.03353571891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96807813644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9113484621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643826007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098429679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553033351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370819568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79352593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079865455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.819708943367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152746200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8255273103714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516254901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83279991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898339748383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171020030975</t>
   </si>
   <si>
     <t xml:space="preserve">1.84298229217529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85752856731415</t>
+    <t xml:space="preserve">1.85752820968628</t>
   </si>
   <si>
     <t xml:space="preserve">1.83570957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84880077838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061989307404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788970947266</t>
+    <t xml:space="preserve">1.84880101680756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061977386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788947105408</t>
   </si>
   <si>
     <t xml:space="preserve">1.61460959911346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59860920906067</t>
+    <t xml:space="preserve">1.59860932826996</t>
   </si>
   <si>
     <t xml:space="preserve">1.68152129650116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61751914024353</t>
+    <t xml:space="preserve">1.61751878261566</t>
   </si>
   <si>
     <t xml:space="preserve">1.57388091087341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55351638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56224393844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770092487335</t>
+    <t xml:space="preserve">1.55351626873016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56224405765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770116329193</t>
   </si>
   <si>
     <t xml:space="preserve">1.5273334980011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50842332839966</t>
+    <t xml:space="preserve">1.50842344760895</t>
   </si>
   <si>
     <t xml:space="preserve">1.39278268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36441802978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35569047927856</t>
+    <t xml:space="preserve">1.36441814899445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35569036006927</t>
   </si>
   <si>
     <t xml:space="preserve">1.19277465343475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21241211891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16150069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1593189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1338632106781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10768055915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11422610282898</t>
+    <t xml:space="preserve">1.21241188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16150081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15931880474091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13386332988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10768043994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11422634124756</t>
   </si>
   <si>
     <t xml:space="preserve">1.08440697193146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18041050434113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19713854789734</t>
+    <t xml:space="preserve">1.1804107427597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968332767487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19713842868805</t>
   </si>
   <si>
     <t xml:space="preserve">1.11204433441162</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">1.12877225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550181388855</t>
+    <t xml:space="preserve">1.18550157546997</t>
   </si>
   <si>
     <t xml:space="preserve">1.10549867153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09022510051727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04149603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07640647888184</t>
+    <t xml:space="preserve">1.09022521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0414959192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07640635967255</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059451580048</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">1.20077526569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22186672687531</t>
+    <t xml:space="preserve">1.22186660766602</t>
   </si>
   <si>
     <t xml:space="preserve">1.24223124980927</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">1.61331379413605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56247711181641</t>
+    <t xml:space="preserve">1.5624772310257</t>
   </si>
   <si>
     <t xml:space="preserve">1.49967920780182</t>
@@ -2621,16 +2621,16 @@
     <t xml:space="preserve">1.4608039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47575604915619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500860691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284769535065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061176300049</t>
+    <t xml:space="preserve">1.4757559299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061188220978</t>
   </si>
   <si>
     <t xml:space="preserve">1.48397958278656</t>
@@ -2639,58 +2639,58 @@
     <t xml:space="preserve">1.42192900180817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40473437309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931597232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46005630493164</t>
+    <t xml:space="preserve">1.40473449230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931609153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46005642414093</t>
   </si>
   <si>
     <t xml:space="preserve">1.44884240627289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43762862682343</t>
+    <t xml:space="preserve">1.43762850761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.4951936006546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56546783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733342170715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64321780204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807375431061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471304416656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479457855225</t>
+    <t xml:space="preserve">1.56546759605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733306407928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228500843048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64321792125702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498692035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807327747345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471328258514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479493618011</t>
   </si>
   <si>
     <t xml:space="preserve">1.75535726547241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67760694026947</t>
+    <t xml:space="preserve">1.67760717868805</t>
   </si>
   <si>
     <t xml:space="preserve">1.65069365501404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5849050283432</t>
+    <t xml:space="preserve">1.58490478992462</t>
   </si>
   <si>
     <t xml:space="preserve">1.59686660766602</t>
@@ -2699,76 +2699,76 @@
     <t xml:space="preserve">1.62976109981537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63125598430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583782196045</t>
+    <t xml:space="preserve">1.63125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583794116974</t>
   </si>
   <si>
     <t xml:space="preserve">1.62527549266815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59238123893738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135221481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172232151031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050143241882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70601582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003521442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013108730316</t>
+    <t xml:space="preserve">1.58340978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59238147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135209560394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7105016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797740459442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7060159444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013120651245</t>
   </si>
   <si>
     <t xml:space="preserve">1.68956875801086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7478814125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7254536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077554702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78675639629364</t>
+    <t xml:space="preserve">1.74788117408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545349597931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7807754278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656369686127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80021286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78675651550293</t>
   </si>
   <si>
     <t xml:space="preserve">1.85404002666473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8600207567215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8331071138382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423236846924</t>
+    <t xml:space="preserve">1.86002063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871761798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310759067535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423213005066</t>
   </si>
   <si>
     <t xml:space="preserve">1.73292946815491</t>
@@ -2777,145 +2777,145 @@
     <t xml:space="preserve">1.76881432533264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83161246776581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104990005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264065742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609783649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85852563381195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786695480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039122104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141964912415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992476463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301168680191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79124176502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553538799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666028499603</t>
+    <t xml:space="preserve">1.83161222934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104930400848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264113426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609795570374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85852539539337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8929146528244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786683559418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992500305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487658977509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543903827667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011710643768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7912415266037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8555349111557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666016578674</t>
   </si>
   <si>
     <t xml:space="preserve">1.8076890707016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77928054332733</t>
+    <t xml:space="preserve">1.77928042411804</t>
   </si>
   <si>
     <t xml:space="preserve">1.8346027135849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80170798301697</t>
+    <t xml:space="preserve">1.80170834064484</t>
   </si>
   <si>
     <t xml:space="preserve">1.8480589389801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84506869316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646782398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058308601379</t>
+    <t xml:space="preserve">1.8450688123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646806240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058320522308</t>
   </si>
   <si>
     <t xml:space="preserve">1.83908820152283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82862174510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778494358063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947252750397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349167823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508303165436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059754371643</t>
+    <t xml:space="preserve">1.82862186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114589214325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778518199921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900619029999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7134917974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508315086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059766292572</t>
   </si>
   <si>
     <t xml:space="preserve">1.73442435264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72395825386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8749725818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207844734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227055072784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638617038727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246253490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6342465877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51762163639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74937641620636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75984299182892</t>
+    <t xml:space="preserve">1.72395801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497234344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207808971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.782271027565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685226917267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246289253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63424670696259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51762139797211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836173057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74937629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">1.72694838047028</t>
@@ -2924,34 +2924,34 @@
     <t xml:space="preserve">1.75386190414429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80469882488251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80918431282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81965053081512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301171779633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235244274139</t>
+    <t xml:space="preserve">1.80469834804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80918407440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301112174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235256195068</t>
   </si>
   <si>
     <t xml:space="preserve">1.93926620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96617949008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159753322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216057777405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056934356689</t>
+    <t xml:space="preserve">1.96617960929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056886672974</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345610618591</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">2.014972448349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074716567993</t>
+    <t xml:space="preserve">2.04074692726135</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710175514221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677872657776</t>
+    <t xml:space="preserve">2.03316640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677836894989</t>
   </si>
   <si>
     <t xml:space="preserve">2.00890803337097</t>
@@ -2978,34 +2978,34 @@
     <t xml:space="preserve">2.00132703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99981117248535</t>
+    <t xml:space="preserve">1.99981093406677</t>
   </si>
   <si>
     <t xml:space="preserve">2.03165030479431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01800489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435972213745</t>
+    <t xml:space="preserve">2.01800465583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435924530029</t>
   </si>
   <si>
     <t xml:space="preserve">2.01042413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0301342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0346827507019</t>
+    <t xml:space="preserve">2.03013372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03468251228333</t>
   </si>
   <si>
     <t xml:space="preserve">2.04681205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0513608455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0437798500061</t>
+    <t xml:space="preserve">2.05136013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04377937316895</t>
   </si>
   <si>
     <t xml:space="preserve">2.07561874389648</t>
@@ -3014,76 +3014,76 @@
     <t xml:space="preserve">2.06803798675537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287671089172</t>
+    <t xml:space="preserve">2.10442614555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287647247314</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261939048767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21358895301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084692001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16203951835632</t>
+    <t xml:space="preserve">2.21358942985535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16203927993774</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13323259353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1559751033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023347854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20145964622498</t>
+    <t xml:space="preserve">2.1332323551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15597534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023371696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20145988464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.27120304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18933033943176</t>
+    <t xml:space="preserve">2.18933057785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.26362204551697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24846053123474</t>
+    <t xml:space="preserve">2.24846076965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.21510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21662187576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546141624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30000972747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32275247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3576238155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3485267162323</t>
+    <t xml:space="preserve">2.21662139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30000996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32275223731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31062340736389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246230125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35762405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34852719306946</t>
   </si>
   <si>
     <t xml:space="preserve">2.35914015769958</t>
@@ -3095,37 +3095,37 @@
     <t xml:space="preserve">2.36368846893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39249515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639764785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491487503052</t>
+    <t xml:space="preserve">2.39249563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639788627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491463661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.36520481109619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36823725700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32426834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35459160804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549498558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.380366563797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44101238250732</t>
+    <t xml:space="preserve">2.36823701858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32426857948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35459184646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549474716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38036632537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44101214408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.36065626144409</t>
@@ -3137,25 +3137,25 @@
     <t xml:space="preserve">2.318204164505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765738487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41523814201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978645324707</t>
+    <t xml:space="preserve">2.40007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765714645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41523766517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978597640991</t>
   </si>
   <si>
     <t xml:space="preserve">2.49407815933228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43494749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41827034950256</t>
+    <t xml:space="preserve">2.4349479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41827011108398</t>
   </si>
   <si>
     <t xml:space="preserve">2.42888331413269</t>
@@ -3164,187 +3164,187 @@
     <t xml:space="preserve">2.40614128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30759048461914</t>
+    <t xml:space="preserve">2.3075909614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.32730078697205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34397864341736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35610771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45314192771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51681995391846</t>
+    <t xml:space="preserve">2.34397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35610795021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45314168930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51682043075562</t>
   </si>
   <si>
     <t xml:space="preserve">2.48649716377258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4986264705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44859337806702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54714369773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58959603309631</t>
+    <t xml:space="preserve">2.49862670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043274879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44859313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54714345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58959627151489</t>
   </si>
   <si>
     <t xml:space="preserve">2.56685328483582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64266109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52038145065308</t>
+    <t xml:space="preserve">2.64266133308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327429771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355996131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52038192749023</t>
   </si>
   <si>
     <t xml:space="preserve">2.50052404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51579904556274</t>
+    <t xml:space="preserve">2.51579928398132</t>
   </si>
   <si>
     <t xml:space="preserve">2.51427173614502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49899649620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52343678474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53412938117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286688804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386432647705</t>
+    <t xml:space="preserve">2.49899673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52343654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286736488342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386408805847</t>
   </si>
   <si>
     <t xml:space="preserve">2.42109394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44553422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942379951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761130332947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48066639900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4119291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262148857117</t>
+    <t xml:space="preserve">2.44553399085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761178016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4806661605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41192889213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262125015259</t>
   </si>
   <si>
     <t xml:space="preserve">2.4669189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45775389671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43025875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928144454956</t>
+    <t xml:space="preserve">2.45775413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43025898933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928120613098</t>
   </si>
   <si>
     <t xml:space="preserve">2.44706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43331408500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45622634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48372197151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50816130638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65938472747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6486918926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63799953460693</t>
+    <t xml:space="preserve">2.43331384658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45622682571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48372173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50816178321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023909568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65938425064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64869213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63799929618835</t>
   </si>
   <si>
     <t xml:space="preserve">2.67618703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61814188957214</t>
+    <t xml:space="preserve">2.6181423664093</t>
   </si>
   <si>
     <t xml:space="preserve">2.60439467430115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65632963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68382430076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73575949668884</t>
+    <t xml:space="preserve">2.65632939338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68382453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73575973510742</t>
   </si>
   <si>
     <t xml:space="preserve">2.6884069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63952732086182</t>
+    <t xml:space="preserve">2.63952708244324</t>
   </si>
   <si>
     <t xml:space="preserve">2.61966943740845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59370183944702</t>
+    <t xml:space="preserve">2.5937020778656</t>
   </si>
   <si>
     <t xml:space="preserve">2.54634952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53565645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885437965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482173919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260183334351</t>
+    <t xml:space="preserve">2.53565669059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482197761536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260135650635</t>
   </si>
   <si>
     <t xml:space="preserve">2.50663423538208</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54329419136047</t>
+    <t xml:space="preserve">2.54329395294189</t>
   </si>
   <si>
     <t xml:space="preserve">2.46997404098511</t>
@@ -3362,25 +3362,25 @@
     <t xml:space="preserve">2.49135899543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48830389976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48219418525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40734648704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526869773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41040110588074</t>
+    <t xml:space="preserve">2.48830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48219442367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40734624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4104015827179</t>
   </si>
   <si>
     <t xml:space="preserve">2.38290619850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48524904251099</t>
+    <t xml:space="preserve">2.48524928092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.44247889518738</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">2.47455644607544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52801918983459</t>
+    <t xml:space="preserve">2.52801895141602</t>
   </si>
   <si>
     <t xml:space="preserve">2.4898316860199</t>
@@ -3398,37 +3398,37 @@
     <t xml:space="preserve">2.52649164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52496385574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55856943130493</t>
+    <t xml:space="preserve">2.52496409416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55856919288635</t>
   </si>
   <si>
     <t xml:space="preserve">2.55398678779602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54787683486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56162452697754</t>
+    <t xml:space="preserve">2.54787659645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56162405014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.5295467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51732635498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45164394378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42873191833496</t>
+    <t xml:space="preserve">2.51732683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4516441822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42873120307922</t>
   </si>
   <si>
     <t xml:space="preserve">2.42414927482605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42567682266235</t>
+    <t xml:space="preserve">2.42567658424377</t>
   </si>
   <si>
     <t xml:space="preserve">2.45011639595032</t>
@@ -3437,46 +3437,46 @@
     <t xml:space="preserve">2.4272038936615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40581917762756</t>
+    <t xml:space="preserve">2.40581870079041</t>
   </si>
   <si>
     <t xml:space="preserve">2.5051064491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39818143844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38596153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221360206604</t>
+    <t xml:space="preserve">2.39818120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38596129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3890163898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221384048462</t>
   </si>
   <si>
     <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37355327606201</t>
+    <t xml:space="preserve">2.37355303764343</t>
   </si>
   <si>
     <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4253568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42378735542297</t>
+    <t xml:space="preserve">2.42535662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791532516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42378711700439</t>
   </si>
   <si>
     <t xml:space="preserve">2.40965867042542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35157537460327</t>
+    <t xml:space="preserve">2.35157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000610351562</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">2.35471534729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34686613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39396071434021</t>
+    <t xml:space="preserve">2.34686636924744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39396095275879</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593813896179</t>
@@ -3506,43 +3506,43 @@
     <t xml:space="preserve">2.4473340511322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4394850730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47402119636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4410548210144</t>
+    <t xml:space="preserve">2.43948531150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4740207195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361351966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44105505943298</t>
   </si>
   <si>
     <t xml:space="preserve">2.45675325393677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46931195259094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46774172782898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4881489276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50384759902954</t>
+    <t xml:space="preserve">2.46931147575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4677414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48814940452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50384736061096</t>
   </si>
   <si>
     <t xml:space="preserve">2.45047378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27622485160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25581741333008</t>
+    <t xml:space="preserve">2.27622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25581765174866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738716125488</t>
@@ -3554,34 +3554,34 @@
     <t xml:space="preserve">2.29977202415466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29192304611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27151584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36256456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31076049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32017970085144</t>
+    <t xml:space="preserve">2.29192328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27151560783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36256408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31076097488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32017946243286</t>
   </si>
   <si>
     <t xml:space="preserve">2.26994562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2291305065155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22442126274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24639844894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20244383811951</t>
+    <t xml:space="preserve">2.22913026809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22442102432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20244359970093</t>
   </si>
   <si>
     <t xml:space="preserve">2.15064024925232</t>
@@ -3590,97 +3590,97 @@
     <t xml:space="preserve">2.16005897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14122104644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20401406288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19773411750793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16319847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732667922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18674564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18203592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1663384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15534973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14750027656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15848922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814179420471</t>
+    <t xml:space="preserve">2.14122128486633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20401358604431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19773435592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16319870948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732644081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1867458820343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18203616142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16633796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15534949302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14750051498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1584894657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814203262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.21186304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23070049285889</t>
+    <t xml:space="preserve">2.23070001602173</t>
   </si>
   <si>
     <t xml:space="preserve">2.21657204627991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2275607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26366639137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860971450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29349255561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2479681968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2354097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24011921882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24482870101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291152000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529662132263</t>
+    <t xml:space="preserve">2.22756099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2636661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860995292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29349279403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24796843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23540997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24011945724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24482846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052713394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529685974121</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407382965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11924362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2008740901947</t>
+    <t xml:space="preserve">2.11924409866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20087385177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831562995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22128200531006</t>
+    <t xml:space="preserve">2.2212815284729</t>
   </si>
   <si>
     <t xml:space="preserve">2.23227024078369</t>
@@ -3689,136 +3689,136 @@
     <t xml:space="preserve">2.23697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1993043422699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22599077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27936458587646</t>
+    <t xml:space="preserve">2.19930386543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22599101066589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27936434745789</t>
   </si>
   <si>
     <t xml:space="preserve">2.16476821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03447437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09255719184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05802130699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953081130981</t>
+    <t xml:space="preserve">2.03447389602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09255695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953069210052</t>
   </si>
   <si>
     <t xml:space="preserve">1.95441389083862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01092672348022</t>
+    <t xml:space="preserve">2.01092720031738</t>
   </si>
   <si>
     <t xml:space="preserve">1.92615723609924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84766685962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057227611542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592327594757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254993915558</t>
+    <t xml:space="preserve">1.84766662120819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592339515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254981994629</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807429790497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91045916080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202914714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00935745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9936591386795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796082496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877617835999</t>
+    <t xml:space="preserve">1.91045904159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202902793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00935697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99365890026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97796070575714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877593994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.0172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99208891391754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98895001411438</t>
+    <t xml:space="preserve">1.99208962917328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894953727722</t>
   </si>
   <si>
     <t xml:space="preserve">1.9967987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05959129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249599456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854221820831</t>
+    <t xml:space="preserve">2.05959153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249670982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406645774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854186058044</t>
   </si>
   <si>
     <t xml:space="preserve">1.97639095783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88220298290253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650454998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516852378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301738262177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790081977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947068691254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92124760150909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576598167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01642298698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96964204311371</t>
+    <t xml:space="preserve">1.88220274448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650431156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516864299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301762104034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790070056915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947044849396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92124772071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01642274856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01158380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.969642162323</t>
   </si>
   <si>
     <t xml:space="preserve">1.93092668056488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89543771743774</t>
+    <t xml:space="preserve">1.89543759822845</t>
   </si>
   <si>
     <t xml:space="preserve">1.87607991695404</t>
@@ -3827,64 +3827,64 @@
     <t xml:space="preserve">1.92770040035248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91156888008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704315662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8260725736618</t>
+    <t xml:space="preserve">1.91156876087189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189051628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221131801605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607269287109</t>
   </si>
   <si>
     <t xml:space="preserve">1.77122604846954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79703593254089</t>
+    <t xml:space="preserve">1.7970358133316</t>
   </si>
   <si>
     <t xml:space="preserve">1.81316733360291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801409721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672945976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94383180141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963469982147</t>
+    <t xml:space="preserve">1.86801421642303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672957897186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963481903076</t>
   </si>
   <si>
     <t xml:space="preserve">1.89382445812225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91802179813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93253970146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254692554474</t>
+    <t xml:space="preserve">1.91802167892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9325395822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479516029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96318936347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254728317261</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932810783386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609436511993</t>
+    <t xml:space="preserve">1.97609460353851</t>
   </si>
   <si>
     <t xml:space="preserve">2.02448892593384</t>
@@ -3893,58 +3893,58 @@
     <t xml:space="preserve">2.01480984687805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97448122501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97770738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9906131029129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415331840515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124037742615</t>
+    <t xml:space="preserve">1.97448134422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97770762443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99061298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93415284156799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124049663544</t>
   </si>
   <si>
     <t xml:space="preserve">1.82929873466492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87285387516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88898503780365</t>
+    <t xml:space="preserve">1.87285363674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88898479938507</t>
   </si>
   <si>
     <t xml:space="preserve">1.86317491531372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85833525657654</t>
+    <t xml:space="preserve">1.85833549499512</t>
   </si>
   <si>
     <t xml:space="preserve">1.8438173532486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85672235488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88253259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87769317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865629673004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80187547206879</t>
+    <t xml:space="preserve">1.85672223567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88253283500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87769341468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486567735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80187559127808</t>
   </si>
   <si>
     <t xml:space="preserve">1.81155431270599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75993371009827</t>
+    <t xml:space="preserve">1.75993394851685</t>
   </si>
   <si>
     <t xml:space="preserve">1.78574419021606</t>
@@ -3956,22 +3956,22 @@
     <t xml:space="preserve">1.86962735652924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575141429901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768595218658</t>
+    <t xml:space="preserve">1.83575165271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768583297729</t>
   </si>
   <si>
     <t xml:space="preserve">1.90350317955017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93899238109589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95189774036407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383878707886</t>
+    <t xml:space="preserve">1.9389922618866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95189726352692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383902549744</t>
   </si>
   <si>
     <t xml:space="preserve">1.96802890300751</t>
@@ -3980,25 +3980,25 @@
     <t xml:space="preserve">1.99222576618195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06643009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07449626922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0502986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05191206932068</t>
+    <t xml:space="preserve">2.06643056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0744960308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05029892921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0519118309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01319670677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07288265228271</t>
+    <t xml:space="preserve">2.01319646835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07288289070129</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546685218811</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">2.0793354511261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0761091709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00351786613464</t>
+    <t xml:space="preserve">2.07610893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00351762771606</t>
   </si>
   <si>
     <t xml:space="preserve">2.00835752487183</t>
@@ -4019,64 +4019,64 @@
     <t xml:space="preserve">1.98899972438812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95512402057648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866411685944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91318225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931354045868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286868095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94544517993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83736455440521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025590896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495913028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81474328041077</t>
+    <t xml:space="preserve">1.95512366294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932088375092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866399765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91318190097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9293133020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286832332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96480286121368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94544470310211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83736479282379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025626659393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647299766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474304199219</t>
   </si>
   <si>
     <t xml:space="preserve">1.78290569782257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78458142280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79128384590149</t>
+    <t xml:space="preserve">1.7845813035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79128396511078</t>
   </si>
   <si>
     <t xml:space="preserve">1.776202917099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72928440570831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73933839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74604105949402</t>
+    <t xml:space="preserve">1.72928428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73933827877045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74604117870331</t>
   </si>
   <si>
     <t xml:space="preserve">1.79798662662506</t>
@@ -4088,61 +4088,61 @@
     <t xml:space="preserve">1.86333751678467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83820247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85663497447968</t>
+    <t xml:space="preserve">1.83820259571075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8566347360611</t>
   </si>
   <si>
     <t xml:space="preserve">1.86166155338287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87674283981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171566486359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517521858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360723972321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8968505859375</t>
+    <t xml:space="preserve">1.87674307823181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517498016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9136073589325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203961849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685094356537</t>
   </si>
   <si>
     <t xml:space="preserve">1.90355336666107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92701280117035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879627227783</t>
+    <t xml:space="preserve">1.92701268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879603385925</t>
   </si>
   <si>
     <t xml:space="preserve">1.94376921653748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09625482559204</t>
+    <t xml:space="preserve">2.09625506401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.17836213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19176721572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160559654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18506479263306</t>
+    <t xml:space="preserve">2.19176745414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820027351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16160535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18506455421448</t>
   </si>
   <si>
     <t xml:space="preserve">2.29900979995728</t>
@@ -4154,61 +4154,61 @@
     <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32582068443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33419871330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3425772190094</t>
+    <t xml:space="preserve">2.3258204460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33419895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34257698059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917165756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25711822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2939829826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30906391143799</t>
+    <t xml:space="preserve">2.25711846351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29398274421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
     <t xml:space="preserve">2.30068564414978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31576633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29733419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31409120559692</t>
+    <t xml:space="preserve">2.31576657295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29733443260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31409096717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33754968643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42636036872864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46657586097717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490073204041</t>
+    <t xml:space="preserve">2.33754992485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42636013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44981980323792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46657633781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490049362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.4799816608429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46322512626648</t>
+    <t xml:space="preserve">2.4632248878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.43306303024292</t>
@@ -4223,52 +4223,52 @@
     <t xml:space="preserve">2.40290093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609004974365</t>
+    <t xml:space="preserve">2.37609052658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.38279318809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295480728149</t>
+    <t xml:space="preserve">2.41295504570007</t>
   </si>
   <si>
     <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36938786506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37776637077332</t>
+    <t xml:space="preserve">2.36938762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37776589393616</t>
   </si>
   <si>
     <t xml:space="preserve">2.36100959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34927988052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37944173812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38782000541687</t>
+    <t xml:space="preserve">2.3492796421051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37944149971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38781976699829</t>
   </si>
   <si>
     <t xml:space="preserve">2.49171113967896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45987391471863</t>
+    <t xml:space="preserve">2.45987367630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776369094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64922332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77824926376343</t>
+    <t xml:space="preserve">2.68776392936707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6492235660553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77824974060059</t>
   </si>
   <si>
     <t xml:space="preserve">2.80170893669128</t>
@@ -4277,13 +4277,13 @@
     <t xml:space="preserve">2.77322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78160119056702</t>
+    <t xml:space="preserve">2.78160095214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019518852234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93073487281799</t>
+    <t xml:space="preserve">2.93073511123657</t>
   </si>
   <si>
     <t xml:space="preserve">2.92905926704407</t>
@@ -4298,55 +4298,55 @@
     <t xml:space="preserve">3.03295040130615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06311225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11840891838074</t>
+    <t xml:space="preserve">3.06311202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1184093952179</t>
   </si>
   <si>
     <t xml:space="preserve">3.1502468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16030120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20554351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20219230651855</t>
+    <t xml:space="preserve">3.16030097007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554375648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20219254493713</t>
   </si>
   <si>
     <t xml:space="preserve">3.1435444355011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20889496803284</t>
+    <t xml:space="preserve">3.20889472961426</t>
   </si>
   <si>
     <t xml:space="preserve">3.18878698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19213819503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1988410949707</t>
+    <t xml:space="preserve">3.19213843345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19884085655212</t>
   </si>
   <si>
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29267811775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3060839176178</t>
+    <t xml:space="preserve">3.2926778793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
     <t xml:space="preserve">3.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35132670402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40494775772095</t>
+    <t xml:space="preserve">3.35132622718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40494799613953</t>
   </si>
   <si>
     <t xml:space="preserve">3.25581336021423</t>
@@ -4355,28 +4355,28 @@
     <t xml:space="preserve">3.34797501564026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31781315803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39321804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36473178863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35467791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18543529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24240827560425</t>
+    <t xml:space="preserve">3.3178129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39321827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3647313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3546781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18543601036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24240803718567</t>
   </si>
   <si>
     <t xml:space="preserve">3.13851714134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23235440254211</t>
+    <t xml:space="preserve">3.23235416412354</t>
   </si>
   <si>
     <t xml:space="preserve">3.13349008560181</t>
@@ -4385,31 +4385,31 @@
     <t xml:space="preserve">3.1904628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23402976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2457594871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23905682563782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2155978679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26419162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29770541191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.294353723526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3429479598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510961532593</t>
+    <t xml:space="preserve">3.23403000831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24575972557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2390570640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21559762954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26419186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29770517349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34294819831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510913848877</t>
   </si>
   <si>
     <t xml:space="preserve">3.30105662345886</t>
@@ -4421,16 +4421,16 @@
     <t xml:space="preserve">3.38986659049988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38483953475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981247901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640763282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37143492698669</t>
+    <t xml:space="preserve">3.3848397731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3664071559906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37143445014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619142532349</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">3.31243968009949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23508620262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2178966999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22305369377136</t>
+    <t xml:space="preserve">3.23508644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21789693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22305393218994</t>
   </si>
   <si>
     <t xml:space="preserve">3.20414519309998</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">3.16976594924927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25571417808533</t>
+    <t xml:space="preserve">3.25571441650391</t>
   </si>
   <si>
     <t xml:space="preserve">3.20070719718933</t>
@@ -4472,34 +4472,34 @@
     <t xml:space="preserve">3.05975222587585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09413170814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08897471427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10616445541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13366746902466</t>
+    <t xml:space="preserve">3.09413146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08897495269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1061646938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13366770744324</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18867468833923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22649168968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2660276889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24024343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09928846359253</t>
+    <t xml:space="preserve">3.18867421150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22649145126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26602792739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24024319648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09928870201111</t>
   </si>
   <si>
     <t xml:space="preserve">3.16117119789124</t>
@@ -4508,31 +4508,31 @@
     <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1525764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11991620063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09756946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06834697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429520606995</t>
+    <t xml:space="preserve">3.15257596969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11991596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09756922721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06834721565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1542956829071</t>
   </si>
   <si>
     <t xml:space="preserve">3.14741945266724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10960245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12507295608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18695545196533</t>
+    <t xml:space="preserve">3.10960221290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12507271766663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18695569038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.17664194107056</t>
@@ -4541,22 +4541,22 @@
     <t xml:space="preserve">3.14398169517517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27462267875671</t>
+    <t xml:space="preserve">3.27462244033813</t>
   </si>
   <si>
     <t xml:space="preserve">3.24196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1903932094574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19898819923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15601420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26258969306946</t>
+    <t xml:space="preserve">3.19039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19898796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15601396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26258993148804</t>
   </si>
   <si>
     <t xml:space="preserve">3.27290368080139</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">3.12851095199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13538646697998</t>
+    <t xml:space="preserve">3.13538670539856</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
@@ -4574,61 +4574,61 @@
     <t xml:space="preserve">3.08209872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04084372520447</t>
+    <t xml:space="preserve">3.04084396362305</t>
   </si>
   <si>
     <t xml:space="preserve">3.04771971702576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05631422996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01677823066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0081832408905</t>
+    <t xml:space="preserve">3.05631446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01677846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00818347930908</t>
   </si>
   <si>
     <t xml:space="preserve">3.01162147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03396797180176</t>
+    <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583674430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07350397109985</t>
+    <t xml:space="preserve">2.98583698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07350420951843</t>
   </si>
   <si>
     <t xml:space="preserve">3.07006621360779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05287671089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9755232334137</t>
+    <t xml:space="preserve">3.05287647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97552299499512</t>
   </si>
   <si>
     <t xml:space="preserve">2.94458198547363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93083024024963</t>
+    <t xml:space="preserve">2.93083047866821</t>
   </si>
   <si>
     <t xml:space="preserve">2.92051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87582349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87754249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88785624504089</t>
+    <t xml:space="preserve">2.87582325935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87754225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88785600662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.91020250320435</t>
@@ -4640,28 +4640,28 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005272865295</t>
+    <t xml:space="preserve">2.96005249023438</t>
   </si>
   <si>
     <t xml:space="preserve">2.94286298751831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99786972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05115747451782</t>
+    <t xml:space="preserve">2.99786949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0511577129364</t>
   </si>
   <si>
     <t xml:space="preserve">3.03053021430969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04943871498108</t>
+    <t xml:space="preserve">3.0494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">3.05459547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08725595474243</t>
+    <t xml:space="preserve">3.08725547790527</t>
   </si>
   <si>
     <t xml:space="preserve">3.04256272315979</t>
@@ -4673,10 +4673,10 @@
     <t xml:space="preserve">2.99615073204041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03912472724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06490898132324</t>
+    <t xml:space="preserve">3.03912448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06490921974182</t>
   </si>
   <si>
     <t xml:space="preserve">2.9749481678009</t>
@@ -4685,13 +4685,13 @@
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729748725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99276232719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9535710811615</t>
+    <t xml:space="preserve">3.03729724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99276208877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95357131958008</t>
   </si>
   <si>
     <t xml:space="preserve">2.79858899116516</t>
@@ -4700,19 +4700,19 @@
     <t xml:space="preserve">2.67210912704468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69526720046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67032742500305</t>
+    <t xml:space="preserve">2.67923474311829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69526743888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67032766342163</t>
   </si>
   <si>
     <t xml:space="preserve">2.60797834396362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58838272094727</t>
+    <t xml:space="preserve">2.58838295936584</t>
   </si>
   <si>
     <t xml:space="preserve">2.59372711181641</t>
@@ -4721,10 +4721,10 @@
     <t xml:space="preserve">2.62579250335693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58125758171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64538788795471</t>
+    <t xml:space="preserve">2.58125710487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64538812637329</t>
   </si>
   <si>
     <t xml:space="preserve">2.64004373550415</t>
@@ -4733,28 +4733,28 @@
     <t xml:space="preserve">2.60976004600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52247095108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47971725463867</t>
+    <t xml:space="preserve">2.5224711894989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47971701622009</t>
   </si>
   <si>
     <t xml:space="preserve">2.31939101219177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36570739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32473468780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2855441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33720517158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392569541931</t>
+    <t xml:space="preserve">2.36570715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32473516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28554391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720469474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392593383789</t>
   </si>
   <si>
     <t xml:space="preserve">2.26060438156128</t>
@@ -4766,10 +4766,10 @@
     <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38708424568176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32829785346985</t>
+    <t xml:space="preserve">2.38708400726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32829761505127</t>
   </si>
   <si>
     <t xml:space="preserve">2.32117199897766</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323762893677</t>
+    <t xml:space="preserve">2.35323739051819</t>
   </si>
   <si>
     <t xml:space="preserve">2.35145616531372</t>
@@ -4790,28 +4790,28 @@
     <t xml:space="preserve">2.43161916732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40667963027954</t>
+    <t xml:space="preserve">2.40667939186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42449378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34254908561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39242815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39599132537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37461400032043</t>
+    <t xml:space="preserve">2.39955401420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34254932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39242839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39599108695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37461423873901</t>
   </si>
   <si>
     <t xml:space="preserve">2.3603630065918</t>
@@ -4823,10 +4823,10 @@
     <t xml:space="preserve">2.51534509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49931263923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56522464752197</t>
+    <t xml:space="preserve">2.49931287765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56522488594055</t>
   </si>
   <si>
     <t xml:space="preserve">2.53494071960449</t>
@@ -4835,19 +4835,19 @@
     <t xml:space="preserve">2.52068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4975311756134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50287556648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57056879997253</t>
+    <t xml:space="preserve">2.49753093719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57056903839111</t>
   </si>
   <si>
     <t xml:space="preserve">2.60085296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5830385684967</t>
+    <t xml:space="preserve">2.58303880691528</t>
   </si>
   <si>
     <t xml:space="preserve">2.64360666275024</t>
@@ -4859,22 +4859,22 @@
     <t xml:space="preserve">2.65785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65073227882385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67567181587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65963935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6525137424469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55453634262085</t>
+    <t xml:space="preserve">2.65073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67567205429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65963912010193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291811943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55453610420227</t>
   </si>
   <si>
     <t xml:space="preserve">2.61510419845581</t>
@@ -4889,19 +4889,19 @@
     <t xml:space="preserve">2.60619735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59550881385803</t>
+    <t xml:space="preserve">2.59550857543945</t>
   </si>
   <si>
     <t xml:space="preserve">2.74336504936218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71664428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68992304801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70773696899414</t>
+    <t xml:space="preserve">2.7166440486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68992328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70773720741272</t>
   </si>
   <si>
     <t xml:space="preserve">2.66676473617554</t>
@@ -4910,34 +4910,34 @@
     <t xml:space="preserve">2.73445820808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77721190452576</t>
+    <t xml:space="preserve">2.77721238136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.76830506324768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7718677520752</t>
+    <t xml:space="preserve">2.77186799049377</t>
   </si>
   <si>
     <t xml:space="preserve">2.76474237442017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72911381721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74692821502686</t>
+    <t xml:space="preserve">2.72911405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74692845344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.72020697593689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75049114227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76117944717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78968191146851</t>
+    <t xml:space="preserve">2.75049090385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76117920875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78968167304993</t>
   </si>
   <si>
     <t xml:space="preserve">2.82352876663208</t>
@@ -4946,22 +4946,22 @@
     <t xml:space="preserve">2.84846830368042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77008652687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8128399848938</t>
+    <t xml:space="preserve">2.77008605003357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81284022331238</t>
   </si>
   <si>
     <t xml:space="preserve">2.80927729606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80749607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81996583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81105852127075</t>
+    <t xml:space="preserve">2.80749583244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81996560096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81105875968933</t>
   </si>
   <si>
     <t xml:space="preserve">2.78790044784546</t>
@@ -4976,13 +4976,13 @@
     <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63469958305359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55275464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54741072654724</t>
+    <t xml:space="preserve">2.63469934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5527548789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54741048812866</t>
   </si>
   <si>
     <t xml:space="preserve">2.53137803077698</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">2.54206657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55809903144836</t>
+    <t xml:space="preserve">2.55809926986694</t>
   </si>
   <si>
     <t xml:space="preserve">2.57947611808777</t>
@@ -5000,28 +5000,28 @@
     <t xml:space="preserve">2.52781534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5117826461792</t>
+    <t xml:space="preserve">2.51178240776062</t>
   </si>
   <si>
     <t xml:space="preserve">2.50821971893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60263395309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61154103279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988049507141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58482027053833</t>
+    <t xml:space="preserve">2.60263419151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61154127120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58482003211975</t>
   </si>
   <si>
     <t xml:space="preserve">2.57769465446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56878733634949</t>
+    <t xml:space="preserve">2.56878757476807</t>
   </si>
   <si>
     <t xml:space="preserve">2.5866014957428</t>
@@ -5030,25 +5030,25 @@
     <t xml:space="preserve">2.56700611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51890802383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46724724769592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47081017494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48684287071228</t>
+    <t xml:space="preserve">2.51890826225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4672474861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48684310913086</t>
   </si>
   <si>
     <t xml:space="preserve">2.48867678642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49051094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47400498390198</t>
+    <t xml:space="preserve">2.49051070213318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47400522232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.43915987014771</t>
@@ -5060,16 +5060,16 @@
     <t xml:space="preserve">2.55469918251038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51618599891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5271897315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54002737998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58587646484375</t>
+    <t xml:space="preserve">2.51618623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52718997001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5400276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58587622642517</t>
   </si>
   <si>
     <t xml:space="preserve">2.59871411323547</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">2.6152195930481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62438941001892</t>
+    <t xml:space="preserve">2.62438917160034</t>
   </si>
   <si>
     <t xml:space="preserve">2.67390608787537</t>
@@ -5090,19 +5090,19 @@
     <t xml:space="preserve">2.62255525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6317253112793</t>
+    <t xml:space="preserve">2.63172507286072</t>
   </si>
   <si>
     <t xml:space="preserve">2.60971760749817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57303857803345</t>
+    <t xml:space="preserve">2.57303881645203</t>
   </si>
   <si>
     <t xml:space="preserve">2.55103135108948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60605001449585</t>
+    <t xml:space="preserve">2.60604977607727</t>
   </si>
   <si>
     <t xml:space="preserve">2.5840425491333</t>
@@ -5111,16 +5111,16 @@
     <t xml:space="preserve">2.5675368309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5748724937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6005482673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63355898857117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705350875854</t>
+    <t xml:space="preserve">2.57487273216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60054802894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63355922698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705374717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.63722705841064</t>
@@ -5135,10 +5135,10 @@
     <t xml:space="preserve">2.54736351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57670664787292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51802015304565</t>
+    <t xml:space="preserve">2.57670640945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51801991462708</t>
   </si>
   <si>
     <t xml:space="preserve">2.48500871658325</t>
@@ -5153,19 +5153,19 @@
     <t xml:space="preserve">2.58037447929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59321212768555</t>
+    <t xml:space="preserve">2.59321236610413</t>
   </si>
   <si>
     <t xml:space="preserve">2.64089512825012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60238194465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56386876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56020092964172</t>
+    <t xml:space="preserve">2.60238218307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5638689994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5602011680603</t>
   </si>
   <si>
     <t xml:space="preserve">2.54552936553955</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">2.56937074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58771014213562</t>
+    <t xml:space="preserve">2.5877103805542</t>
   </si>
   <si>
     <t xml:space="preserve">2.61338567733765</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">2.4868426322937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47950673103333</t>
+    <t xml:space="preserve">2.4795069694519</t>
   </si>
   <si>
     <t xml:space="preserve">2.45383167266846</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.5033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767305374146</t>
+    <t xml:space="preserve">2.47767281532288</t>
   </si>
   <si>
     <t xml:space="preserve">2.49234461784363</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">2.46116757392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40798258781433</t>
+    <t xml:space="preserve">2.40798282623291</t>
   </si>
   <si>
     <t xml:space="preserve">2.34196043014526</t>
@@ -5225,13 +5225,13 @@
     <t xml:space="preserve">2.31261706352234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31078338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27777194976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29611158370972</t>
+    <t xml:space="preserve">2.31078290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27777171134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29611134529114</t>
   </si>
   <si>
     <t xml:space="preserve">2.28694176673889</t>
@@ -5243,10 +5243,10 @@
     <t xml:space="preserve">2.29427766799927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30344724655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32728862762451</t>
+    <t xml:space="preserve">2.30344748497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32728886604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.34746217727661</t>
@@ -5267,7 +5267,7 @@
     <t xml:space="preserve">2.40248084068298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981650352478</t>
+    <t xml:space="preserve">2.40981674194336</t>
   </si>
   <si>
     <t xml:space="preserve">2.41898632049561</t>
@@ -5279,16 +5279,16 @@
     <t xml:space="preserve">2.46666932106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42815613746643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41531872749329</t>
+    <t xml:space="preserve">2.42815637588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41531848907471</t>
   </si>
   <si>
     <t xml:space="preserve">2.42448830604553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39697909355164</t>
+    <t xml:space="preserve">2.39697885513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.39514493942261</t>
@@ -5297,16 +5297,16 @@
     <t xml:space="preserve">2.37863945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38780927658081</t>
+    <t xml:space="preserve">2.38780951499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.44099402427673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43182420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44466161727905</t>
+    <t xml:space="preserve">2.43182396888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44466185569763</t>
   </si>
   <si>
     <t xml:space="preserve">2.44282793998718</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">2.31064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30297470092773</t>
+    <t xml:space="preserve">2.30297493934631</t>
   </si>
   <si>
     <t xml:space="preserve">2.37008905410767</t>
@@ -5336,22 +5336,22 @@
     <t xml:space="preserve">2.43720316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38926482200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43145060539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46021389961243</t>
+    <t xml:space="preserve">2.38926458358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43145036697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46021366119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.41994524002075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41227507591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4046049118042</t>
+    <t xml:space="preserve">2.41227531433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40460467338562</t>
   </si>
   <si>
     <t xml:space="preserve">2.42569804191589</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">2.3643364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29722189903259</t>
+    <t xml:space="preserve">2.29722213745117</t>
   </si>
   <si>
     <t xml:space="preserve">2.197509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16491150856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18408679962158</t>
+    <t xml:space="preserve">2.1649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18408703804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.18792200088501</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">2.13806581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12272548675537</t>
+    <t xml:space="preserve">2.12272524833679</t>
   </si>
   <si>
     <t xml:space="preserve">2.09012699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09971475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10354995727539</t>
+    <t xml:space="preserve">2.09971499443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10354971885681</t>
   </si>
   <si>
     <t xml:space="preserve">2.08053946495056</t>
@@ -5441,10 +5441,10 @@
     <t xml:space="preserve">2.00767254829407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95781624317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424946308136</t>
+    <t xml:space="preserve">1.95781636238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424970149994</t>
   </si>
   <si>
     <t xml:space="preserve">1.99808490276337</t>
@@ -5474,31 +5474,31 @@
     <t xml:space="preserve">2.07095170021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08820962905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07862162590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04410576820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03068327903748</t>
+    <t xml:space="preserve">2.08820939064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07862186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04410600662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0306830406189</t>
   </si>
   <si>
     <t xml:space="preserve">1.97315657138824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01534247398376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06903409957886</t>
+    <t xml:space="preserve">2.01534271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06903386116028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05561113357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1054675579071</t>
+    <t xml:space="preserve">2.10546731948853</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930252075195</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">2.05369353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752849578857</t>
+    <t xml:space="preserve">2.05752873420715</t>
   </si>
   <si>
     <t xml:space="preserve">2.06136393547058</t>
@@ -5531,22 +5531,22 @@
     <t xml:space="preserve">2.03835320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02301263809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05177640914917</t>
+    <t xml:space="preserve">2.02301287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05177617073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.05944633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643560409546</t>
+    <t xml:space="preserve">2.03643584251404</t>
   </si>
   <si>
     <t xml:space="preserve">2.07286906242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03260064125061</t>
+    <t xml:space="preserve">2.03260040283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.02876543998718</t>
@@ -5561,16 +5561,16 @@
     <t xml:space="preserve">2.09587979316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1457359790802</t>
+    <t xml:space="preserve">2.14573574066162</t>
   </si>
   <si>
     <t xml:space="preserve">2.11889028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12080764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09204435348511</t>
+    <t xml:space="preserve">2.12080788612366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09204459190369</t>
   </si>
   <si>
     <t xml:space="preserve">1.85906255245209</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">1.9271354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94439363479614</t>
+    <t xml:space="preserve">1.94439351558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165144443512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93672311306</t>
+    <t xml:space="preserve">1.93672323226929</t>
   </si>
   <si>
     <t xml:space="preserve">1.92905306816101</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">1.87823808193207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87919676303864</t>
+    <t xml:space="preserve">1.87919688224792</t>
   </si>
   <si>
     <t xml:space="preserve">1.83029937744141</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">1.71812283992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73825705051422</t>
+    <t xml:space="preserve">1.73825693130493</t>
   </si>
   <si>
     <t xml:space="preserve">1.75167989730835</t>
@@ -71121,7 +71121,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6496296296</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>509256</v>
@@ -71142,6 +71142,32 @@
         <v>1992</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6495949074</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>1335652</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>1.99600005149841</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>1.95099997520447</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="1993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847192287445</t>
+    <t xml:space="preserve">1.42847216129303</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3917795419693</t>
+    <t xml:space="preserve">1.39177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">1.36014831066132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30827271938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158081531525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23931634426117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21401143074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676331043243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831763744354</t>
+    <t xml:space="preserve">1.30827295780182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158045768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23931622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21401119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676342964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425555229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831775665283</t>
   </si>
   <si>
     <t xml:space="preserve">1.20009350776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18680858612061</t>
+    <t xml:space="preserve">1.18680846691132</t>
   </si>
   <si>
     <t xml:space="preserve">1.11595416069031</t>
@@ -86,88 +86,88 @@
     <t xml:space="preserve">1.17478835582733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644240379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19439995288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.232990026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20641982555389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22097015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087090969086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10646462440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11721932888031</t>
+    <t xml:space="preserve">1.15644216537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23299014568329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20641994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22097039222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087102890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064647436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1172194480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.12164783477783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04699778556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848449707031</t>
+    <t xml:space="preserve">1.04699790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826295375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1184846162796</t>
   </si>
   <si>
     <t xml:space="preserve">1.11089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13366770744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17795145511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19819569587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213572025299</t>
+    <t xml:space="preserve">1.13366782665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17795133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19819581508636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21337854862213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213595867157</t>
   </si>
   <si>
     <t xml:space="preserve">1.20578718185425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17921698093414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13872873783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13176965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770769119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311232566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688560962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29182434082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2994157075882</t>
+    <t xml:space="preserve">1.17921686172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13872861862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13176989555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770757198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311208724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688537120819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29182457923889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29941582679749</t>
   </si>
   <si>
     <t xml:space="preserve">1.32598638534546</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">1.2652542591095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27917206287384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892794132233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199143886566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135891437531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376742839813</t>
+    <t xml:space="preserve">1.27917194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892782211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199131965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413325309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376730918884</t>
   </si>
   <si>
     <t xml:space="preserve">1.1823798418045</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">1.21464407444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1918693780899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264654159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123661518097</t>
+    <t xml:space="preserve">1.19186949729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554294109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264642238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123673439026</t>
   </si>
   <si>
     <t xml:space="preserve">1.17984938621521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17162561416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1115255355835</t>
+    <t xml:space="preserve">1.17162549495697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11152565479279</t>
   </si>
   <si>
     <t xml:space="preserve">1.09571003913879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07546591758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709726810455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417817115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062654972076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719698905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454435348511</t>
+    <t xml:space="preserve">1.07546603679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709738731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719686985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1545444726944</t>
   </si>
   <si>
     <t xml:space="preserve">1.19227039813995</t>
@@ -251,88 +251,88 @@
     <t xml:space="preserve">1.17405772209167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2482088804245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812957763672</t>
+    <t xml:space="preserve">1.24820876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406289100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812933921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.26837289333344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28918707370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27682864665985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25731515884399</t>
+    <t xml:space="preserve">1.28918695449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138172626495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27682876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2573150396347</t>
   </si>
   <si>
     <t xml:space="preserve">1.24495649337769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19031929969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1909693479538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527430057526</t>
+    <t xml:space="preserve">1.1903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796063423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527453899384</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080557346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755330562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495168209076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17340755462646</t>
+    <t xml:space="preserve">1.17080545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495144367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17340707778931</t>
   </si>
   <si>
     <t xml:space="preserve">1.18056237697601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15389406681061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16300022602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649592876434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16169929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17731010913849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901813030243</t>
+    <t xml:space="preserve">1.15389382839203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1630003452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649580955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16169941425323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17731022834778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18901801109314</t>
   </si>
   <si>
     <t xml:space="preserve">1.14283621311188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12852668762207</t>
+    <t xml:space="preserve">1.12852621078491</t>
   </si>
   <si>
     <t xml:space="preserve">1.11031401157379</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">1.10055732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11486709117889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250878334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112326145172</t>
+    <t xml:space="preserve">1.11486721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250866413116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112338066101</t>
   </si>
   <si>
     <t xml:space="preserve">1.05372500419617</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.04657018184662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526901245117</t>
+    <t xml:space="preserve">1.04526913166046</t>
   </si>
   <si>
     <t xml:space="preserve">1.10185813903809</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">1.13177871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1012077331543</t>
+    <t xml:space="preserve">1.10120761394501</t>
   </si>
   <si>
     <t xml:space="preserve">1.12917697429657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05307459831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485769748688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184779167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640628814697</t>
+    <t xml:space="preserve">1.05307471752167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255368232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485650539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184719562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640616893768</t>
   </si>
   <si>
     <t xml:space="preserve">1.01339733600616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982826352119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321995258331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851634979248</t>
+    <t xml:space="preserve">0.982826173305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321756839752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851646900177</t>
   </si>
   <si>
     <t xml:space="preserve">0.977622628211975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975671291351318</t>
+    <t xml:space="preserve">0.975671172142029</t>
   </si>
   <si>
     <t xml:space="preserve">1.00364053249359</t>
@@ -416,49 +416,49 @@
     <t xml:space="preserve">0.95095431804657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.980874836444855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467865467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969167172908783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118032932281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965914487838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437564849854</t>
+    <t xml:space="preserve">0.98087477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467507839203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166874885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118330955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965914726257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958759844303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437552928925</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957901477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608355045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974302768707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892848968506</t>
+    <t xml:space="preserve">1.06608366966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974290847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892872810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.06283140182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06673407554626</t>
+    <t xml:space="preserve">1.0667337179184</t>
   </si>
   <si>
     <t xml:space="preserve">1.09340238571167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06022942066193</t>
+    <t xml:space="preserve">1.06022930145264</t>
   </si>
   <si>
     <t xml:space="preserve">1.08559691905975</t>
@@ -467,112 +467,112 @@
     <t xml:space="preserve">1.09275186061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11421692371368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09795534610748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07779157161713</t>
+    <t xml:space="preserve">1.11421704292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09795522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07779145240784</t>
   </si>
   <si>
     <t xml:space="preserve">1.07388889789581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10901308059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746907234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348685741425</t>
+    <t xml:space="preserve">1.10901296138763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348673820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.11876976490021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13828313350677</t>
+    <t xml:space="preserve">1.13828325271606</t>
   </si>
   <si>
     <t xml:space="preserve">1.14543831348419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1402348279953</t>
+    <t xml:space="preserve">1.14023458957672</t>
   </si>
   <si>
     <t xml:space="preserve">1.1278760433197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14218616485596</t>
+    <t xml:space="preserve">1.14218604564667</t>
   </si>
   <si>
     <t xml:space="preserve">1.15129220485687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16234982013702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14804005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438057899475</t>
+    <t xml:space="preserve">1.16234958171844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803993701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438045978546</t>
   </si>
   <si>
     <t xml:space="preserve">1.08299493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10315907001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08169436454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09990692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0921014547348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511040687561</t>
+    <t xml:space="preserve">1.10315918922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600389003754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08169412612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09990680217743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210169315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511028766632</t>
   </si>
   <si>
     <t xml:space="preserve">1.11356616020203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949971199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584023475647</t>
+    <t xml:space="preserve">1.08949959278107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584035396576</t>
   </si>
   <si>
     <t xml:space="preserve">1.08234477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925651550293</t>
+    <t xml:space="preserve">1.09925639629364</t>
   </si>
   <si>
     <t xml:space="preserve">1.08429610729218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07519006729126</t>
+    <t xml:space="preserve">1.07518982887268</t>
   </si>
   <si>
     <t xml:space="preserve">1.0875483751297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0745393037796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827832221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07323849201202</t>
+    <t xml:space="preserve">1.07453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827820301056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762779712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07323861122131</t>
   </si>
   <si>
     <t xml:space="preserve">1.0693359375</t>
@@ -581,64 +581,64 @@
     <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04722046852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047297477722</t>
+    <t xml:space="preserve">1.04722058773041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047273635864</t>
   </si>
   <si>
     <t xml:space="preserve">1.06348180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03421175479889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0114461183548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95680820941925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392107486725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440949440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644434928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653685092926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953556001186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962662220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157863140106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957458972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986728727817535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965264201164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940547287464142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078560352325</t>
+    <t xml:space="preserve">1.0342116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144576072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175946235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956808269023895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392226696014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440889835358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653327465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95355612039566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962662637233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157982349396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458853721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507397651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986728847026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965264141559601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940546989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078500747681</t>
   </si>
   <si>
     <t xml:space="preserve">0.995835065841675</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">1.00429117679596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02315402030945</t>
+    <t xml:space="preserve">1.02315390110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.03681337833405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02380442619324</t>
+    <t xml:space="preserve">1.02380454540253</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120280265808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04201698303223</t>
+    <t xml:space="preserve">1.04201710224152</t>
   </si>
   <si>
     <t xml:space="preserve">1.04917192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02770733833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852151870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356122970581</t>
+    <t xml:space="preserve">1.02770686149597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852139949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03356111049652</t>
   </si>
   <si>
     <t xml:space="preserve">1.03095948696136</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">1.03160989284515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05567646026611</t>
+    <t xml:space="preserve">1.05567634105682</t>
   </si>
   <si>
     <t xml:space="preserve">1.05502581596375</t>
@@ -692,73 +692,73 @@
     <t xml:space="preserve">1.03291058540344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03551244735718</t>
+    <t xml:space="preserve">1.03551256656647</t>
   </si>
   <si>
     <t xml:space="preserve">1.01860082149506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999087512493134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925146579742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932451725006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00494134426117</t>
+    <t xml:space="preserve">0.999087393283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925134658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932272911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00494170188904</t>
   </si>
   <si>
     <t xml:space="preserve">1.0251053571701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999737977981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981055259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401178836823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905714511871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01664972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404786109924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02965819835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991282045841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00949466228485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01795041561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01469790935516</t>
+    <t xml:space="preserve">0.999737739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981234073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534373283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029897212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401238441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905774116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0166494846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404798030853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136645793915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02965843677521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991282165050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00949478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01795053482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01469802856445</t>
   </si>
   <si>
     <t xml:space="preserve">1.03226041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.070636510849</t>
+    <t xml:space="preserve">1.07063663005829</t>
   </si>
   <si>
     <t xml:space="preserve">1.06218087673187</t>
@@ -770,28 +770,28 @@
     <t xml:space="preserve">1.14478766918182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18251359462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23585033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845231533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633696556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983231067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21438539028168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21308445930481</t>
+    <t xml:space="preserve">1.18251383304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23585021495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845207691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2163370847702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983254909515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21438562870026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755823612213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2130845785141</t>
   </si>
   <si>
     <t xml:space="preserve">1.20072615146637</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">1.22023975849152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20527946949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20267736911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446528911591</t>
+    <t xml:space="preserve">1.20527935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381440639496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20267748832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446493148804</t>
   </si>
   <si>
     <t xml:space="preserve">1.16430115699768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17600905895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999943256378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194684505463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268414497375</t>
+    <t xml:space="preserve">1.17600917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999967098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268402576447</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482905864716</t>
@@ -836,40 +836,40 @@
     <t xml:space="preserve">1.27502715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28777742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26697432994843</t>
+    <t xml:space="preserve">1.28777730464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26697444915771</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013185501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24348700046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2273815870285</t>
+    <t xml:space="preserve">1.24013161659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2434868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24415802955627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22738146781921</t>
   </si>
   <si>
     <t xml:space="preserve">1.24818444252014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25422406196594</t>
+    <t xml:space="preserve">1.25422418117523</t>
   </si>
   <si>
     <t xml:space="preserve">1.27368497848511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24147367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006546497345</t>
+    <t xml:space="preserve">1.24147391319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006570339203</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831674575806</t>
@@ -881,94 +881,94 @@
     <t xml:space="preserve">1.31462013721466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30992257595062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31059384346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200169563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3414626121521</t>
+    <t xml:space="preserve">1.30992269515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059372425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200181484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146285057068</t>
   </si>
   <si>
     <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35555493831635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018658638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689747333527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3407918214798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32669925689697</t>
+    <t xml:space="preserve">1.35555529594421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018670558929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481799602509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34079170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32669949531555</t>
   </si>
   <si>
     <t xml:space="preserve">1.32602822780609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30388307571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925130844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29650127887726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34213411808014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32871270179749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864678859711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300312519073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031853199005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239800930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37434530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44010961055756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4387674331665</t>
+    <t xml:space="preserve">1.30388295650482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925166606903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29650163650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34213387966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287125825882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864655017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031877040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239789009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434506416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43876755237579</t>
   </si>
   <si>
     <t xml:space="preserve">1.45084655284882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44816243648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48976874351501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46158385276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46024167537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50721621513367</t>
+    <t xml:space="preserve">1.448162317276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48976862430573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46158373355865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46024179458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50721609592438</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453197956085</t>
@@ -977,64 +977,64 @@
     <t xml:space="preserve">1.53540134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51929569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5005054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50587427616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829438209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4575572013855</t>
+    <t xml:space="preserve">1.51929581165314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50587403774261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829450130463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45755732059479</t>
   </si>
   <si>
     <t xml:space="preserve">1.48037374019623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44547808170319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950461387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45621526241302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45889961719513</t>
+    <t xml:space="preserve">1.44547843933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950473308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45621514320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45889949798584</t>
   </si>
   <si>
     <t xml:space="preserve">1.44279372692108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57566511631012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.621297955513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640217781067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042859077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727130413055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411377906799</t>
+    <t xml:space="preserve">1.57566499710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290390491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129735946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042823314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727118492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411413669586</t>
   </si>
   <si>
     <t xml:space="preserve">1.60787630081177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61458694934845</t>
+    <t xml:space="preserve">1.61458706855774</t>
   </si>
   <si>
     <t xml:space="preserve">1.59713935852051</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">1.61995553970337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6427720785141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350890159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398183345795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142978191376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.723299741745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987892150879</t>
+    <t xml:space="preserve">1.64277195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350878238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398207187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64143002033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72329986095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987868309021</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558802127838</t>
@@ -1070,103 +1070,103 @@
     <t xml:space="preserve">1.70853650569916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108843803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68572020530701</t>
+    <t xml:space="preserve">1.70048367977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719420909882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732615470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108855724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68571996688843</t>
   </si>
   <si>
     <t xml:space="preserve">1.66693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66424596309662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632508277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753531455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740336894989</t>
+    <t xml:space="preserve">1.66424584388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632496356964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753519535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740313053131</t>
   </si>
   <si>
     <t xml:space="preserve">1.64679825305939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67364072799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490604877472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77430081367493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75819563865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74880051612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7380633354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866880893707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624822616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832746505737</t>
+    <t xml:space="preserve">1.67364096641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490616798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7743011713028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75819528102875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74880015850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73806357383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866857051849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624810695648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174876213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832734584808</t>
   </si>
   <si>
     <t xml:space="preserve">1.77161681652069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75416886806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564311027527</t>
+    <t xml:space="preserve">1.75416922569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564263343811</t>
   </si>
   <si>
     <t xml:space="preserve">1.74208962917328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74074745178223</t>
+    <t xml:space="preserve">1.74074757099152</t>
   </si>
   <si>
     <t xml:space="preserve">1.73537909984589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73940551280975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7595374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503835201263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101146221161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188094615936</t>
+    <t xml:space="preserve">1.73940527439117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953710079193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503787517548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101193904877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188058853149</t>
   </si>
   <si>
     <t xml:space="preserve">1.79845929145813</t>
@@ -1175,94 +1175,94 @@
     <t xml:space="preserve">1.82261776924133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80248558521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067083358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8843560218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8991197347641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8870404958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569808006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84543454647064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957751750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598433494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793150901794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001074790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893258094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698540687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222133636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316791534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6803514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6951150894165</t>
+    <t xml:space="preserve">1.80248606204987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067047595978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435649871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88704013824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543371200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79577529430389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598457336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793127059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001039028168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893198490143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698528766632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222205162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356422901154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316779613495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645762443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68035161495209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69511485099792</t>
   </si>
   <si>
     <t xml:space="preserve">1.69243085384369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67766773700714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874554634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814019203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653424263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5702965259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57432293891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57969152927399</t>
+    <t xml:space="preserve">1.67766726016998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814031124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653460025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57029676437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57432281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57969164848328</t>
   </si>
   <si>
     <t xml:space="preserve">1.55687534809113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54345405101776</t>
+    <t xml:space="preserve">1.54345393180847</t>
   </si>
   <si>
     <t xml:space="preserve">1.51392722129822</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">1.63203489780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67229843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827261447906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148439407349</t>
+    <t xml:space="preserve">1.67229878902435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827249526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148475170135</t>
   </si>
   <si>
     <t xml:space="preserve">1.74611616134644</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">1.71390473842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72195780277252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658933162689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606107234955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385024547577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371770381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197957038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54613792896271</t>
+    <t xml:space="preserve">1.72195768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7165892124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60385012626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371794223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53674292564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546138048172</t>
   </si>
   <si>
     <t xml:space="preserve">1.54882264137268</t>
@@ -1316,73 +1316,73 @@
     <t xml:space="preserve">1.54748046398163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53271675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895446777344</t>
+    <t xml:space="preserve">1.53271687030792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895458698273</t>
   </si>
   <si>
     <t xml:space="preserve">1.54076969623566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.542111992836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869021892548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56761252880096</t>
+    <t xml:space="preserve">1.54211211204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869069576263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56761229038239</t>
   </si>
   <si>
     <t xml:space="preserve">1.55955934524536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52600634098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774435520172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190247535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519194602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324524879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5662704706192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782168865204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661133766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50319004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647915363312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990045070648</t>
+    <t xml:space="preserve">1.52600586414337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774423599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190295219421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519206523895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324512958527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56627011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50319015979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4964793920517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990068912506</t>
   </si>
   <si>
     <t xml:space="preserve">1.42266178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48171555995941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292614936829</t>
+    <t xml:space="preserve">1.48171579837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46292579174042</t>
   </si>
   <si>
     <t xml:space="preserve">1.46695232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48305773735046</t>
+    <t xml:space="preserve">1.48305809497833</t>
   </si>
   <si>
     <t xml:space="preserve">1.4844001531601</t>
@@ -1391,28 +1391,28 @@
     <t xml:space="preserve">1.52332198619843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5340588092804</t>
+    <t xml:space="preserve">1.53405892848969</t>
   </si>
   <si>
     <t xml:space="preserve">1.57662510871887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5683708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947961330414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884305477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51609146595001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49958264827728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56286752223969</t>
+    <t xml:space="preserve">1.56837069988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947937488556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884293556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5160915851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5628674030304</t>
   </si>
   <si>
     <t xml:space="preserve">1.57387387752533</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">1.55186140537262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52159464359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095808506012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5023341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49820673465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619426250458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042456150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656394004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4280424118042</t>
+    <t xml:space="preserve">1.52159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095820426941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233399868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49820649623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619414329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042468070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4665641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42804265022278</t>
   </si>
   <si>
     <t xml:space="preserve">1.43767309188843</t>
@@ -1451,64 +1451,64 @@
     <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46518862247467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931564807892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106123924255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42116391658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37370002269745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327894687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814532756805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280635356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180047512054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629717826843</t>
+    <t xml:space="preserve">1.46518850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42116379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37369990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327882766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814556598663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280659198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180035591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629729747772</t>
   </si>
   <si>
     <t xml:space="preserve">1.45143067836761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41566097736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555794239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904888629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941844463348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41841220855713</t>
+    <t xml:space="preserve">1.41566073894501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555770397186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904864788055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41841232776642</t>
   </si>
   <si>
     <t xml:space="preserve">1.396399974823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36613321304321</t>
+    <t xml:space="preserve">1.3661333322525</t>
   </si>
   <si>
     <t xml:space="preserve">1.41428506374359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53397643566132</t>
+    <t xml:space="preserve">1.53397655487061</t>
   </si>
   <si>
     <t xml:space="preserve">1.46793985366821</t>
@@ -1520,25 +1520,25 @@
     <t xml:space="preserve">1.48169755935669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47069120407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48720049858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50508534908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54085540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53122508525848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223120212555</t>
+    <t xml:space="preserve">1.47069132328033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48720026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50508558750153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54085528850555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53122520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223108291626</t>
   </si>
   <si>
     <t xml:space="preserve">1.5491099357605</t>
@@ -1547,34 +1547,34 @@
     <t xml:space="preserve">1.54773426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53260052204132</t>
+    <t xml:space="preserve">1.53260087966919</t>
   </si>
   <si>
     <t xml:space="preserve">1.58900690078735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57112193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56561899185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746761798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984917163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810393810272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461275577545</t>
+    <t xml:space="preserve">1.57112216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746737957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52984929084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810381889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461263656616</t>
   </si>
   <si>
     <t xml:space="preserve">1.53672802448273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45830917358398</t>
+    <t xml:space="preserve">1.45830941200256</t>
   </si>
   <si>
     <t xml:space="preserve">1.41703653335571</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">1.40878212451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38539397716522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851536273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576389312744</t>
+    <t xml:space="preserve">1.38539409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851512432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576365470886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3640695810318</t>
@@ -1598,22 +1598,22 @@
     <t xml:space="preserve">1.39364862442017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40190327167511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36888492107391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073295116425</t>
+    <t xml:space="preserve">1.40190315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36888480186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073318958282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26570272445679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28289937973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909075260162</t>
+    <t xml:space="preserve">1.28289973735809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909051418304</t>
   </si>
   <si>
     <t xml:space="preserve">1.29665732383728</t>
@@ -1622,37 +1622,37 @@
     <t xml:space="preserve">1.33724224567413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34343314170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33105134963989</t>
+    <t xml:space="preserve">1.34343338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33105146884918</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200606822968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37989115715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38264238834381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089715480804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978788375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4266664981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43216991424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43492162227631</t>
+    <t xml:space="preserve">1.37989091873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3826425075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089703559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978800296783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42666685581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4321700334549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43492138385773</t>
   </si>
   <si>
     <t xml:space="preserve">1.41153371334076</t>
@@ -1661,40 +1661,40 @@
     <t xml:space="preserve">1.35581505298615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37301218509674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35719084739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692396640778</t>
+    <t xml:space="preserve">1.37301242351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35719096660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692408561707</t>
   </si>
   <si>
     <t xml:space="preserve">1.28565108776093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528152942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771471977234</t>
+    <t xml:space="preserve">1.29528164863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771495819092</t>
   </si>
   <si>
     <t xml:space="preserve">1.24506616592407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924482822418</t>
+    <t xml:space="preserve">1.22924494743347</t>
   </si>
   <si>
     <t xml:space="preserve">1.25951159000397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22786903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130857944489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1831568479538</t>
+    <t xml:space="preserve">1.22786927223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2313084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18315696716309</t>
   </si>
   <si>
     <t xml:space="preserve">1.19553864002228</t>
@@ -1703,79 +1703,79 @@
     <t xml:space="preserve">1.19003546237946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24025082588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380305767059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30009651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29940891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496325016022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30078458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252994060516</t>
+    <t xml:space="preserve">1.24025094509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33380281925201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3000967502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994087934494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2849634885788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3007847070694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252982139587</t>
   </si>
   <si>
     <t xml:space="preserve">1.26776647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822117805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051770687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818707466125</t>
+    <t xml:space="preserve">1.28221189975739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088750362396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051794528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818719387054</t>
   </si>
   <si>
     <t xml:space="preserve">1.25882375240326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26363885402679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23268449306488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22030222415924</t>
+    <t xml:space="preserve">1.26363909244537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2326842546463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22030246257782</t>
   </si>
   <si>
     <t xml:space="preserve">1.2120475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21411120891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18522036075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18797183036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20172953605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19347488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19966566562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104157924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808451652527</t>
+    <t xml:space="preserve">1.21411144733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18797218799591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20172941684723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19347500801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1996659040451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2010418176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808439731598</t>
   </si>
   <si>
     <t xml:space="preserve">1.28083598613739</t>
@@ -1793,43 +1793,43 @@
     <t xml:space="preserve">1.20792055130005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21273565292358</t>
+    <t xml:space="preserve">1.21273577213287</t>
   </si>
   <si>
     <t xml:space="preserve">1.20379316806793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19209921360016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.215487241745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29046642780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27946031093597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25056910514832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326929569244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136962890625</t>
+    <t xml:space="preserve">1.19209909439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548736095428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29046654701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2794600725174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326917648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136974811554</t>
   </si>
   <si>
     <t xml:space="preserve">1.30216038227081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30353593826294</t>
+    <t xml:space="preserve">1.30353605747223</t>
   </si>
   <si>
     <t xml:space="preserve">1.32417237758636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32554829120636</t>
+    <t xml:space="preserve">1.32554841041565</t>
   </si>
   <si>
     <t xml:space="preserve">1.33930587768555</t>
@@ -1838,130 +1838,130 @@
     <t xml:space="preserve">1.34756052494049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33173942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110286712646</t>
+    <t xml:space="preserve">1.3317391872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110274791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.31523013114929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3489363193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063027381897</t>
+    <t xml:space="preserve">1.34893620014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063039302826</t>
   </si>
   <si>
     <t xml:space="preserve">1.38126683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38401818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422389507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623600959778</t>
+    <t xml:space="preserve">1.38401830196381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422377586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623624801636</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3468724489212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512721538544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957275867462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787868499756</t>
+    <t xml:space="preserve">1.34687256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957287788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787892341614</t>
   </si>
   <si>
     <t xml:space="preserve">1.33793032169342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44455182552338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48307347297668</t>
+    <t xml:space="preserve">1.4445515871048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307311534882</t>
   </si>
   <si>
     <t xml:space="preserve">1.55323696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59588575363159</t>
+    <t xml:space="preserve">1.59588599205017</t>
   </si>
   <si>
     <t xml:space="preserve">1.64128589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276484489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.598637342453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57937681674957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52572178840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51334035396576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058864593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49545514583588</t>
+    <t xml:space="preserve">1.59038281440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276436805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59863710403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57937633991241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424307823181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52572202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921261310577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058852672577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49545502662659</t>
   </si>
   <si>
     <t xml:space="preserve">1.59726178646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.600013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340092658997</t>
+    <t xml:space="preserve">1.60001301765442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340116500854</t>
   </si>
   <si>
     <t xml:space="preserve">1.71007418632507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77611112594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79949855804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78436553478241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847640037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151524066925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719221591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726305484772</t>
+    <t xml:space="preserve">1.77611076831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7994989156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78436517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847651958466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7743889093399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151488304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719233512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726269721985</t>
   </si>
   <si>
     <t xml:space="preserve">1.75301086902618</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.75728642940521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025431156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595513820648</t>
+    <t xml:space="preserve">1.71025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595525741577</t>
   </si>
   <si>
     <t xml:space="preserve">1.85420072078705</t>
@@ -1985,166 +1985,166 @@
     <t xml:space="preserve">1.92403650283813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89553225040436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572008132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434192180634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018406867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597887039185</t>
+    <t xml:space="preserve">1.89553201198578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572031974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434168338776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298749446869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018371105194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
     <t xml:space="preserve">1.73733365535736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73590850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579080104828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004251003265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79006636142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422421455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137415885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723932266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016069412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73020720481873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588477611542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289328098297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564924240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282256126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78294038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146825313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001901626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82854700088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83994889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87415397167206</t>
+    <t xml:space="preserve">1.73590838909149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7857905626297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013684272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004274845123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79006659984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137356281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723956108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016045570374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73020708560944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588453769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289351940155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564960002899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282291889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294026851654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001925468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82854688167572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83994901180267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87415373325348</t>
   </si>
   <si>
     <t xml:space="preserve">1.86560261249542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88413023948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265810489655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562598705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417710781097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555562496185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396602153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9311625957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95681619644165</t>
+    <t xml:space="preserve">1.8841301202774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265786647797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555526733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396590232849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116235733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95681583881378</t>
   </si>
   <si>
     <t xml:space="preserve">1.9439891576767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87842953205109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700414657593</t>
+    <t xml:space="preserve">1.87842929363251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700438499451</t>
   </si>
   <si>
     <t xml:space="preserve">1.85990166664124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90978407859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410674571991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130355834961</t>
+    <t xml:space="preserve">1.90978419780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8941068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130331993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524972915649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89268147945404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543791770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00954866409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111548900604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971395492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532032966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279930591583</t>
+    <t xml:space="preserve">1.89268136024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819435596466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532044887543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8171454668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279918670654</t>
   </si>
   <si>
     <t xml:space="preserve">1.83139729499817</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">1.97106838226318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669836997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672162532806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957227706909</t>
+    <t xml:space="preserve">2.04517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669884681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0309271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672174453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9995721578598</t>
   </si>
   <si>
     <t xml:space="preserve">2.09648680686951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09363627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06655764579773</t>
+    <t xml:space="preserve">2.09363651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06655740737915</t>
   </si>
   <si>
     <t xml:space="preserve">2.07368350028992</t>
@@ -2186,76 +2186,76 @@
     <t xml:space="preserve">2.0622820854187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96394205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831194400787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123295783997</t>
+    <t xml:space="preserve">1.96394217014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831218242645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123307704926</t>
   </si>
   <si>
     <t xml:space="preserve">1.89695727825165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92973709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263449192047</t>
+    <t xml:space="preserve">1.92973685264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91690969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263461112976</t>
   </si>
   <si>
     <t xml:space="preserve">1.89125657081604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90835881233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9971706867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94334995746613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425776481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96371471881866</t>
+    <t xml:space="preserve">1.90835893154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99717009067535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94335031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425812244415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96371483802795</t>
   </si>
   <si>
     <t xml:space="preserve">1.97389674186707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95062327384949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989446640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462264537811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8968026638031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8895298242569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916844367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880427837372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953296661377</t>
+    <t xml:space="preserve">1.95062291622162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989410877228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462252616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952970504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9491685628891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880403995514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953272819519</t>
   </si>
   <si>
     <t xml:space="preserve">2.02044439315796</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">2.01026177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98553347587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00880718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02189898490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02917194366455</t>
+    <t xml:space="preserve">1.98553371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00880765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02189874649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02917146682739</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062629699707</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">2.05099081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10044693946838</t>
+    <t xml:space="preserve">2.10044741630554</t>
   </si>
   <si>
     <t xml:space="preserve">2.09608364105225</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">2.16881394386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08444666862488</t>
+    <t xml:space="preserve">2.0844464302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.09753775596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08008241653442</t>
+    <t xml:space="preserve">2.08008289337158</t>
   </si>
   <si>
     <t xml:space="preserve">2.09462881088257</t>
@@ -2312,64 +2312,64 @@
     <t xml:space="preserve">2.23863458633423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18917751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1659038066864</t>
+    <t xml:space="preserve">2.24736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1891782283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16590452194214</t>
   </si>
   <si>
     <t xml:space="preserve">2.09899258613586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06844615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07717347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07280969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.128084897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14553999900818</t>
+    <t xml:space="preserve">2.06844592094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07717370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07280993461609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12808465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499309539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1455397605896</t>
   </si>
   <si>
     <t xml:space="preserve">2.14699482917786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13099384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0829918384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07426404953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05826354026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808115959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02335381507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0640823841095</t>
+    <t xml:space="preserve">2.13390350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13099408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08299231529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05826330184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771687507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06408214569092</t>
   </si>
   <si>
     <t xml:space="preserve">2.04226303100586</t>
@@ -2393,136 +2393,136 @@
     <t xml:space="preserve">2.00589823722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9986252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935070514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826063632965</t>
+    <t xml:space="preserve">1.99862492084503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95935034751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826075553894</t>
   </si>
   <si>
     <t xml:space="preserve">1.96080541610718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99280667304993</t>
+    <t xml:space="preserve">1.99280655384064</t>
   </si>
   <si>
     <t xml:space="preserve">2.06117272377014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06990075111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04080843925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03353571891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96807813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9113484621048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553033351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370819568634</t>
+    <t xml:space="preserve">2.06990051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04080820083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03353548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96807861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91134893894196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643802165985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.890984416008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553069114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370795726776</t>
   </si>
   <si>
     <t xml:space="preserve">1.79352593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079865455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.819708943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152746200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8255273103714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83279991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898339748383</t>
+    <t xml:space="preserve">1.80079925060272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81970882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552742958069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516266822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83280026912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898280143738</t>
   </si>
   <si>
     <t xml:space="preserve">1.85171020030975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84298229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752820968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83570957183838</t>
+    <t xml:space="preserve">1.84298276901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752880573273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83570945262909</t>
   </si>
   <si>
     <t xml:space="preserve">1.84880101680756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87061977386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460959911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860932826996</t>
+    <t xml:space="preserve">1.87062013149261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788982868195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460983753204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860920906067</t>
   </si>
   <si>
     <t xml:space="preserve">1.68152129650116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61751878261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351626873016</t>
+    <t xml:space="preserve">1.61751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351638793945</t>
   </si>
   <si>
     <t xml:space="preserve">1.56224405765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62770116329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5273334980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842344760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36441814899445</t>
+    <t xml:space="preserve">1.62770092487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52733337879181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278256893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36441791057587</t>
   </si>
   <si>
     <t xml:space="preserve">1.35569036006927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19277465343475</t>
+    <t xml:space="preserve">1.19277477264404</t>
   </si>
   <si>
     <t xml:space="preserve">1.21241188049316</t>
@@ -2531,85 +2531,85 @@
     <t xml:space="preserve">1.16150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15931880474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13386332988739</t>
+    <t xml:space="preserve">1.1593189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13386356830597</t>
   </si>
   <si>
     <t xml:space="preserve">1.10768043994904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11422634124756</t>
+    <t xml:space="preserve">1.11422622203827</t>
   </si>
   <si>
     <t xml:space="preserve">1.08440697193146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1804107427597</t>
+    <t xml:space="preserve">1.18041062355042</t>
   </si>
   <si>
     <t xml:space="preserve">1.17968332767487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19713842868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11204433441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550157546997</t>
+    <t xml:space="preserve">1.19713878631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11204421520233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877237796783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550169467926</t>
   </si>
   <si>
     <t xml:space="preserve">1.10549867153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09022521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0414959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07640635967255</t>
+    <t xml:space="preserve">1.09022533893585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04149615764618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07640647888184</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059451580048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24514055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641288280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077526569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22186660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24223124980927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36005413532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47351324558258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58939063549042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649650096893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331379413605</t>
+    <t xml:space="preserve">1.24514043331146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20077502727509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22186672687531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24223136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36005401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023814678192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47351336479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331367492676</t>
   </si>
   <si>
     <t xml:space="preserve">1.5624772310257</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">1.47500848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60284757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061188220978</t>
+    <t xml:space="preserve">1.60284733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5206116437912</t>
   </si>
   <si>
     <t xml:space="preserve">1.48397958278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192900180817</t>
+    <t xml:space="preserve">1.42192888259888</t>
   </si>
   <si>
     <t xml:space="preserve">1.40473449230194</t>
@@ -2648,178 +2648,178 @@
     <t xml:space="preserve">1.46005642414093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44884240627289</t>
+    <t xml:space="preserve">1.44884252548218</t>
   </si>
   <si>
     <t xml:space="preserve">1.43762850761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4951936006546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56546759605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733306407928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228500843048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64321792125702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498692035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807327747345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471328258514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479493618011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535726547241</t>
+    <t xml:space="preserve">1.49519348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56546783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228512763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64321780204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807339668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479469776154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535690784454</t>
   </si>
   <si>
     <t xml:space="preserve">1.67760717868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65069365501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490478992462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976109981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583794116974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62527549266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58340978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59238147735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135209560394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7105016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797740459442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7060159444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003509521484</t>
+    <t xml:space="preserve">1.65069377422333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5849050283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686684608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976098060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6312563419342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62527513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58340990543365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59238135814667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172255992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71050155162811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.717977643013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003485679626</t>
   </si>
   <si>
     <t xml:space="preserve">1.67013120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68956875801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788117408752</t>
+    <t xml:space="preserve">1.68956863880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7478814125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.72545349597931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7807754278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656369686127</t>
+    <t xml:space="preserve">1.78077554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656405448914</t>
   </si>
   <si>
     <t xml:space="preserve">1.80021286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78675651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85404002666473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871761798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310759067535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292946815491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881432533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161222934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104930400848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264113426208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609795570374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85852539539337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8929146528244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786683559418</t>
+    <t xml:space="preserve">1.78675627708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85403990745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8600207567215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871785640717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423260688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292922973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881396770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161187171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104990005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264125347137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85852563381195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291512966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786719322205</t>
   </si>
   <si>
     <t xml:space="preserve">1.90039110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89141988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992500305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487658977509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543903827667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83011710643768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912415266037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8555349111557</t>
+    <t xml:space="preserve">1.8914201259613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8899245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487682819366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543915748596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011662960052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124188423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553514957428</t>
   </si>
   <si>
     <t xml:space="preserve">1.81666016578674</t>
@@ -2828,130 +2828,130 @@
     <t xml:space="preserve">1.8076890707016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77928042411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8346027135849</t>
+    <t xml:space="preserve">1.77928066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460247516632</t>
   </si>
   <si>
     <t xml:space="preserve">1.80170834064484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8480589389801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8450688123703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646806240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058320522308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83908820152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82862186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114589214325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900619029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7134917974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508315086365</t>
+    <t xml:space="preserve">1.84805929660797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84506869316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646818161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058308601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83908808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82862150669098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114601135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947276592255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900642871857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71349191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508291244507</t>
   </si>
   <si>
     <t xml:space="preserve">1.68059766292572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73442435264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395801544189</t>
+    <t xml:space="preserve">1.73442459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395837306976</t>
   </si>
   <si>
     <t xml:space="preserve">1.87497234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.782271027565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582384109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685226917267</t>
+    <t xml:space="preserve">1.84207844734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227055072784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7658234834671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638593196869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685238838196</t>
   </si>
   <si>
     <t xml:space="preserve">1.72246289253235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63424670696259</t>
+    <t xml:space="preserve">1.6342465877533</t>
   </si>
   <si>
     <t xml:space="preserve">1.51762139797211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59836173057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74937629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75984287261963</t>
+    <t xml:space="preserve">1.59836184978485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74937641620636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.72694838047028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75386190414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469834804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80918407440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301112174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235256195068</t>
+    <t xml:space="preserve">1.753861784935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8046989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80918419361115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81965053081512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301136016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235268115997</t>
   </si>
   <si>
     <t xml:space="preserve">1.93926620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96617960929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159812927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056886672974</t>
+    <t xml:space="preserve">1.96617949008942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159777164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9721599817276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056934356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345610618591</t>
@@ -2960,25 +2960,25 @@
     <t xml:space="preserve">2.014972448349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074692726135</t>
+    <t xml:space="preserve">2.04074716567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710175514221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316640853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677836894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00890803337097</t>
+    <t xml:space="preserve">2.03316617012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677872657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00890779495239</t>
   </si>
   <si>
     <t xml:space="preserve">2.00132703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99981093406677</t>
+    <t xml:space="preserve">1.9998105764389</t>
   </si>
   <si>
     <t xml:space="preserve">2.03165030479431</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">2.01800465583801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00435924530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01042413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03013372421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03468251228333</t>
+    <t xml:space="preserve">2.00435948371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0104238986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03013443946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03468298912048</t>
   </si>
   <si>
     <t xml:space="preserve">2.04681205749512</t>
@@ -3005,58 +3005,58 @@
     <t xml:space="preserve">2.05136013031006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04377937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07561874389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06803798675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442614555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12261939048767</t>
+    <t xml:space="preserve">2.04377913475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07561850547791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06803774833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442566871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287599563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12261962890625</t>
   </si>
   <si>
     <t xml:space="preserve">2.21358942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19084644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16203927993774</t>
+    <t xml:space="preserve">2.19084715843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1332323551178</t>
+    <t xml:space="preserve">2.13323283195496</t>
   </si>
   <si>
     <t xml:space="preserve">2.15597534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023371696472</t>
+    <t xml:space="preserve">2.18023347854614</t>
   </si>
   <si>
     <t xml:space="preserve">2.20145988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27120304107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26362204551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24846076965332</t>
+    <t xml:space="preserve">2.27120327949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933081626892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26362252235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484610080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.21510529518127</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">2.29546165466309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30000996589661</t>
+    <t xml:space="preserve">2.30000972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.32275223731995</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">2.31062340736389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34246230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35762405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34852719306946</t>
+    <t xml:space="preserve">2.34246253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576238155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34852695465088</t>
   </si>
   <si>
     <t xml:space="preserve">2.35914015769958</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">2.36368846893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39249563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639788627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491463661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36520481109619</t>
+    <t xml:space="preserve">2.39249539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36520457267761</t>
   </si>
   <si>
     <t xml:space="preserve">2.36823701858521</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32426857948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35459184646606</t>
+    <t xml:space="preserve">2.32426834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35459160804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.34549474716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38036632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44101214408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36065626144409</t>
+    <t xml:space="preserve">2.38036680221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410126209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36065602302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.3727855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.318204164505</t>
+    <t xml:space="preserve">2.31820392608643</t>
   </si>
   <si>
     <t xml:space="preserve">2.40007615089417</t>
@@ -3143,46 +3143,46 @@
     <t xml:space="preserve">2.40765714645386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41523766517639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49407815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4349479675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41827011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614128112793</t>
+    <t xml:space="preserve">2.41523790359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978621482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4940779209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43494772911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41827034950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42888307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614104270935</t>
   </si>
   <si>
     <t xml:space="preserve">2.3075909614563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32730078697205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34397888183594</t>
+    <t xml:space="preserve">2.32730031013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34397864341736</t>
   </si>
   <si>
     <t xml:space="preserve">2.35610795021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45314168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51682043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48649716377258</t>
+    <t xml:space="preserve">2.45314192771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51681995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48649740219116</t>
   </si>
   <si>
     <t xml:space="preserve">2.49862670898438</t>
@@ -3197,31 +3197,31 @@
     <t xml:space="preserve">2.54714345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58959627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56685328483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266133308411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327429771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355996131897</t>
+    <t xml:space="preserve">2.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56685352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266157150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327477455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355924606323</t>
   </si>
   <si>
     <t xml:space="preserve">2.52038192749023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50052404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51579928398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51427173614502</t>
+    <t xml:space="preserve">2.50052428245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5157995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427149772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.49899673461914</t>
@@ -3230,28 +3230,28 @@
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286736488342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386408805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553399085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761178016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4806661605835</t>
+    <t xml:space="preserve">2.53412938117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286664962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109417915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942379951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761130332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48066639900208</t>
   </si>
   <si>
     <t xml:space="preserve">2.41192889213562</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">2.42262125015259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4669189453125</t>
+    <t xml:space="preserve">2.46691870689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.45775413513184</t>
@@ -3272,46 +3272,46 @@
     <t xml:space="preserve">2.43025898933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45928120613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706153869629</t>
+    <t xml:space="preserve">2.45928144454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706106185913</t>
   </si>
   <si>
     <t xml:space="preserve">2.43331384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45622682571411</t>
+    <t xml:space="preserve">2.45622658729553</t>
   </si>
   <si>
     <t xml:space="preserve">2.48372173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50816178321838</t>
+    <t xml:space="preserve">2.50816130638123</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023909568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65938425064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64869213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63799929618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67618703842163</t>
+    <t xml:space="preserve">2.65938472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6486918926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63799953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67618727684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6181423664093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60439467430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65632939338684</t>
+    <t xml:space="preserve">2.60439443588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65632963180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.68382453918457</t>
@@ -3320,70 +3320,70 @@
     <t xml:space="preserve">2.73575973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6884069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63952708244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61966943740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5937020778656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54634952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53565669059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482197761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260135650635</t>
+    <t xml:space="preserve">2.68840765953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63952684402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61966967582703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59370160102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5463490486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53565645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885437965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260159492493</t>
   </si>
   <si>
     <t xml:space="preserve">2.50663423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54329395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997404098511</t>
+    <t xml:space="preserve">2.58148241043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54329442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997380256653</t>
   </si>
   <si>
     <t xml:space="preserve">2.49135899543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48830413818359</t>
+    <t xml:space="preserve">2.48830389976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.48219442367554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40734624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4104015827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38290619850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48524928092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44247889518738</t>
+    <t xml:space="preserve">2.40734648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526869773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41040110588074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38290643692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48524904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44247913360596</t>
   </si>
   <si>
     <t xml:space="preserve">2.47455644607544</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">2.52801895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4898316860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52649164199829</t>
+    <t xml:space="preserve">2.48983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52649188041687</t>
   </si>
   <si>
     <t xml:space="preserve">2.52496409416199</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">2.55856919288635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55398678779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54787659645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56162405014038</t>
+    <t xml:space="preserve">2.5539870262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54787683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56162452697754</t>
   </si>
   <si>
     <t xml:space="preserve">2.5295467376709</t>
@@ -3422,28 +3422,28 @@
     <t xml:space="preserve">2.4516441822052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42873120307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42414927482605</t>
+    <t xml:space="preserve">2.4287314414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42414903640747</t>
   </si>
   <si>
     <t xml:space="preserve">2.42567658424377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45011639595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4272038936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40581870079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5051064491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39818120002747</t>
+    <t xml:space="preserve">2.4501166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42720413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40581893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510668754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39818167686462</t>
   </si>
   <si>
     <t xml:space="preserve">2.38596129417419</t>
@@ -3455,37 +3455,37 @@
     <t xml:space="preserve">2.37221384048462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40887403488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37355303764343</t>
+    <t xml:space="preserve">2.40887379646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37355327606201</t>
   </si>
   <si>
     <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42535662651062</t>
+    <t xml:space="preserve">2.4253568649292</t>
   </si>
   <si>
     <t xml:space="preserve">2.43791532516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40965867042542</t>
+    <t xml:space="preserve">2.42378687858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40965843200684</t>
   </si>
   <si>
     <t xml:space="preserve">2.35157585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35000610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34372663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34058737754822</t>
+    <t xml:space="preserve">2.35000538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34372687339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34058713912964</t>
   </si>
   <si>
     <t xml:space="preserve">2.33116841316223</t>
@@ -3494,37 +3494,37 @@
     <t xml:space="preserve">2.35471534729004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34686636924744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39396095275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593813896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4473340511322</t>
+    <t xml:space="preserve">2.34686613082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39396071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44733428955078</t>
   </si>
   <si>
     <t xml:space="preserve">2.43948531150818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4740207195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105505943298</t>
+    <t xml:space="preserve">2.47402095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410548210144</t>
   </si>
   <si>
     <t xml:space="preserve">2.45675325393677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46931147575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4677414894104</t>
+    <t xml:space="preserve">2.46931123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46774172782898</t>
   </si>
   <si>
     <t xml:space="preserve">2.48814940452576</t>
@@ -3536,31 +3536,31 @@
     <t xml:space="preserve">2.45047378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27622509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25581765174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31547021865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29977202415466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29192328453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27151560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36256408691406</t>
+    <t xml:space="preserve">2.27622485160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837611198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25581741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2573869228363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31546998023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29977250099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29192304611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27151584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3625648021698</t>
   </si>
   <si>
     <t xml:space="preserve">2.31076097488403</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">2.32017946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26994562149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22913026809692</t>
+    <t xml:space="preserve">2.2699453830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2291305065155</t>
   </si>
   <si>
     <t xml:space="preserve">2.22442102432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24639868736267</t>
+    <t xml:space="preserve">2.24639844894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244359970093</t>
@@ -3593,46 +3593,46 @@
     <t xml:space="preserve">2.14122128486633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20401358604431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19773435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16319870948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732644081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1867458820343</t>
+    <t xml:space="preserve">2.20401406288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19773459434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16319894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732667922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18674564361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.18203616142273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16633796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15534949302673</t>
+    <t xml:space="preserve">2.1663384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15534925460815</t>
   </si>
   <si>
     <t xml:space="preserve">2.14750051498413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1584894657135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21186304092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23070001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21657204627991</t>
+    <t xml:space="preserve">2.15848898887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21186256408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23070049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21657180786133</t>
   </si>
   <si>
     <t xml:space="preserve">2.22756099700928</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">2.2636661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31860995292664</t>
+    <t xml:space="preserve">2.31860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">2.29349279403687</t>
@@ -3650,43 +3650,43 @@
     <t xml:space="preserve">2.24796843528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23540997505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24011945724487</t>
+    <t xml:space="preserve">2.2354097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24011921882629</t>
   </si>
   <si>
     <t xml:space="preserve">2.24482846260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26052713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529685974121</t>
+    <t xml:space="preserve">2.26052689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291152000427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529662132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407382965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11924409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20087385177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18831562995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2212815284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23227024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23697948455811</t>
+    <t xml:space="preserve">2.11924386024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20087361335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18831539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22128129005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23697972297668</t>
   </si>
   <si>
     <t xml:space="preserve">2.19930386543274</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">2.22599101066589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27936434745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16476821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03447389602661</t>
+    <t xml:space="preserve">2.27936458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16476845741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03447437286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.09255695343018</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">1.97953069210052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95441389083862</t>
+    <t xml:space="preserve">1.95441401004791</t>
   </si>
   <si>
     <t xml:space="preserve">2.01092720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92615723609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766662120819</t>
+    <t xml:space="preserve">1.92615699768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766674041748</t>
   </si>
   <si>
     <t xml:space="preserve">1.80057215690613</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">1.82254981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86807429790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202902793884</t>
+    <t xml:space="preserve">1.86807453632355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045928001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202914714813</t>
   </si>
   <si>
     <t xml:space="preserve">2.00935697555542</t>
@@ -3749,25 +3749,25 @@
     <t xml:space="preserve">1.99365890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97796070575714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877593994141</t>
+    <t xml:space="preserve">1.97796094417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877617835999</t>
   </si>
   <si>
     <t xml:space="preserve">2.0172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99208962917328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98894953727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9967987537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959153175354</t>
+    <t xml:space="preserve">1.9920893907547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894941806793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99679851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959105491638</t>
   </si>
   <si>
     <t xml:space="preserve">2.01249670982361</t>
@@ -3776,25 +3776,25 @@
     <t xml:space="preserve">2.01406645774841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96854186058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639095783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220274448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650431156158</t>
+    <t xml:space="preserve">1.96854174137115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639107704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220238685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650466918945</t>
   </si>
   <si>
     <t xml:space="preserve">1.91516864299774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92301762104034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790070056915</t>
+    <t xml:space="preserve">1.92301750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790058135986</t>
   </si>
   <si>
     <t xml:space="preserve">1.89947044849396</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">2.01642274856567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01158380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.969642162323</t>
+    <t xml:space="preserve">2.01158356666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964204311371</t>
   </si>
   <si>
     <t xml:space="preserve">1.93092668056488</t>
@@ -3824,73 +3824,73 @@
     <t xml:space="preserve">1.87607991695404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92770040035248</t>
+    <t xml:space="preserve">1.92770051956177</t>
   </si>
   <si>
     <t xml:space="preserve">1.91156876087189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90189051628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221131801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704339504242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77122604846954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7970358133316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81316733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801421642303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672957897186</t>
+    <t xml:space="preserve">1.90189027786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221107959747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607281208038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77122581005096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79703629016876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81316769123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801397800446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672969818115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94383192062378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91963481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382445812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802167892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9325395822525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479516029358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318936347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254728317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02932810783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609460353851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448892593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480984687805</t>
+    <t xml:space="preserve">1.91963505744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382410049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802179813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253982067108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479504108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9631894826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254716396332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02932834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609448432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448868751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">1.97448134422302</t>
@@ -3899,103 +3899,103 @@
     <t xml:space="preserve">1.97770762443542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99061298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415284156799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124049663544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82929873466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285363674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88898479938507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86317491531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85833549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8438173532486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672223567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88253283500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87769341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486567735672</t>
+    <t xml:space="preserve">1.99061262607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9341527223587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124037742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82929861545563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285375595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88898527622223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86317455768585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85833537578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381723403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88253247737885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87769317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865641593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187559127808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81155431270599</t>
+    <t xml:space="preserve">1.81155455112457</t>
   </si>
   <si>
     <t xml:space="preserve">1.75993394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78574419021606</t>
+    <t xml:space="preserve">1.78574395179749</t>
   </si>
   <si>
     <t xml:space="preserve">1.8180068731308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86962735652924</t>
+    <t xml:space="preserve">1.86962747573853</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575165271759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82768583297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350317955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9389922618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95189726352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383902549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802890300751</t>
+    <t xml:space="preserve">1.82768571376801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350329875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93899250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9518975019455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802878379822</t>
   </si>
   <si>
     <t xml:space="preserve">1.99222576618195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06643056869507</t>
+    <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
     <t xml:space="preserve">2.0744960308075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05029892921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0519118309021</t>
+    <t xml:space="preserve">2.05029916763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05191206932068</t>
   </si>
   <si>
     <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01319646835327</t>
+    <t xml:space="preserve">2.01319718360901</t>
   </si>
   <si>
     <t xml:space="preserve">2.07288289070129</t>
@@ -4016,25 +4016,25 @@
     <t xml:space="preserve">2.00835752487183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98899972438812</t>
+    <t xml:space="preserve">1.98899984359741</t>
   </si>
   <si>
     <t xml:space="preserve">1.95512366294861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97932088375092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866399765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91318190097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9293133020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286832332611</t>
+    <t xml:space="preserve">1.97932064533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866387844086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91318213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931354045868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286808490753</t>
   </si>
   <si>
     <t xml:space="preserve">1.96480286121368</t>
@@ -4043,22 +4043,22 @@
     <t xml:space="preserve">1.94544470310211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83736479282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025626659393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81474304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78290569782257</t>
+    <t xml:space="preserve">1.8373646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025602817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495889186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474316120148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78290557861328</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845813035965</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">1.79128396511078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.776202917099</t>
+    <t xml:space="preserve">1.77620267868042</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73933827877045</t>
+    <t xml:space="preserve">1.73933839797974</t>
   </si>
   <si>
     <t xml:space="preserve">1.74604117870331</t>
@@ -4085,64 +4085,64 @@
     <t xml:space="preserve">1.79966223239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86333751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83820259571075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8566347360611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86166155338287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87674307823181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517498016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9136073589325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203961849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685094356537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355336666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879603385925</t>
+    <t xml:space="preserve">1.86333739757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83820235729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85663485527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86166167259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87674283981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517533779144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360747814178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8968505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355348587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879627227783</t>
   </si>
   <si>
     <t xml:space="preserve">1.94376921653748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09625506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836213111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19176745414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18506455421448</t>
+    <t xml:space="preserve">2.09625482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1783618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19176697731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1616051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18506503105164</t>
   </si>
   <si>
     <t xml:space="preserve">2.29900979995728</t>
@@ -4151,34 +4151,34 @@
     <t xml:space="preserve">2.29230737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28895592689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3258204460144</t>
+    <t xml:space="preserve">2.28895616531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32582068443298</t>
   </si>
   <si>
     <t xml:space="preserve">2.33419895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34257698059082</t>
+    <t xml:space="preserve">2.3425772190094</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917165756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25711846351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29398274421692</t>
+    <t xml:space="preserve">2.25711822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2939829826355</t>
   </si>
   <si>
     <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30068564414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31576657295227</t>
+    <t xml:space="preserve">2.3006854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31576633453369</t>
   </si>
   <si>
     <t xml:space="preserve">2.29733443260193</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">2.33754992485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42636013031006</t>
+    <t xml:space="preserve">2.42636036872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981980323792</t>
@@ -4220,13 +4220,13 @@
     <t xml:space="preserve">2.40122532844543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40290093421936</t>
+    <t xml:space="preserve">2.40290117263794</t>
   </si>
   <si>
     <t xml:space="preserve">2.37609052658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38279318809509</t>
+    <t xml:space="preserve">2.38279294967651</t>
   </si>
   <si>
     <t xml:space="preserve">2.41295504570007</t>
@@ -4235,40 +4235,40 @@
     <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36938762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37776589393616</t>
+    <t xml:space="preserve">2.36938786506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37776637077332</t>
   </si>
   <si>
     <t xml:space="preserve">2.36100959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3492796421051</t>
+    <t xml:space="preserve">2.34927940368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.37944149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38781976699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49171113967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45987367630005</t>
+    <t xml:space="preserve">2.38782000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49171090126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45987343788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776392936707</t>
+    <t xml:space="preserve">2.68776369094849</t>
   </si>
   <si>
     <t xml:space="preserve">2.6492235660553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77824974060059</t>
+    <t xml:space="preserve">2.77824926376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.80170893669128</t>
@@ -4277,94 +4277,94 @@
     <t xml:space="preserve">2.77322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78160095214844</t>
+    <t xml:space="preserve">2.78160071372986</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019518852234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93073511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92905926704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90224838256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9642481803894</t>
+    <t xml:space="preserve">2.93073487281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92905950546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90224862098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96424841880798</t>
   </si>
   <si>
     <t xml:space="preserve">3.03295040130615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06311202049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1184093952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1502468585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16030097007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20554375648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20219254493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1435444355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20889472961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18878698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19213843345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19884085655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17705750465393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2926778793335</t>
+    <t xml:space="preserve">3.06311249732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11840915679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15024662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16030073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20219206809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14354419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20889496803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18878722190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19213819503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1988410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17705726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29267811775208</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33792114257812</t>
+    <t xml:space="preserve">3.33792090415955</t>
   </si>
   <si>
     <t xml:space="preserve">3.35132622718811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40494799613953</t>
+    <t xml:space="preserve">3.40494775772095</t>
   </si>
   <si>
     <t xml:space="preserve">3.25581336021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34797501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3178129196167</t>
+    <t xml:space="preserve">3.34797525405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781315803528</t>
   </si>
   <si>
     <t xml:space="preserve">3.39321827888489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3647313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3546781539917</t>
+    <t xml:space="preserve">3.36473155021667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35467791557312</t>
   </si>
   <si>
     <t xml:space="preserve">3.18543601036072</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">3.13851714134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23235416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13349008560181</t>
+    <t xml:space="preserve">3.23235440254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13348984718323</t>
   </si>
   <si>
     <t xml:space="preserve">3.1904628276825</t>
@@ -4391,28 +4391,28 @@
     <t xml:space="preserve">3.24575972557068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2390570640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21559762954712</t>
+    <t xml:space="preserve">3.23905682563782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2155978679657</t>
   </si>
   <si>
     <t xml:space="preserve">3.26419186592102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29770517349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435396194458</t>
+    <t xml:space="preserve">3.29770541191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.294353723526</t>
   </si>
   <si>
     <t xml:space="preserve">3.34294819831848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43510913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30105662345886</t>
+    <t xml:space="preserve">3.43510937690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30105686187744</t>
   </si>
   <si>
     <t xml:space="preserve">3.40159606933594</t>
@@ -4421,16 +4421,16 @@
     <t xml:space="preserve">3.38986659049988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3848397731781</t>
+    <t xml:space="preserve">3.38483953475952</t>
   </si>
   <si>
     <t xml:space="preserve">3.37981271743774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3664071559906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37143445014954</t>
+    <t xml:space="preserve">3.36640739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37143421173096</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619142532349</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">3.21789693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22305393218994</t>
+    <t xml:space="preserve">3.22305417060852</t>
   </si>
   <si>
     <t xml:space="preserve">3.20414519309998</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">3.12335419654846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05975222587585</t>
+    <t xml:space="preserve">3.05975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">3.09413146972656</t>
@@ -4487,28 +4487,28 @@
     <t xml:space="preserve">3.13194894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18867421150208</t>
+    <t xml:space="preserve">3.18867444992065</t>
   </si>
   <si>
     <t xml:space="preserve">3.22649145126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26602792739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24024319648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09928870201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16117119789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19383144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15257596969604</t>
+    <t xml:space="preserve">3.2660276889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24024343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09928846359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16117095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19383120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15257620811462</t>
   </si>
   <si>
     <t xml:space="preserve">3.11991596221924</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">3.1542956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14741945266724</t>
+    <t xml:space="preserve">3.14741921424866</t>
   </si>
   <si>
     <t xml:space="preserve">3.10960221290588</t>
@@ -4538,25 +4538,25 @@
     <t xml:space="preserve">3.17664194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398169517517</t>
+    <t xml:space="preserve">3.14398145675659</t>
   </si>
   <si>
     <t xml:space="preserve">3.27462244033813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24196243286133</t>
+    <t xml:space="preserve">3.24196219444275</t>
   </si>
   <si>
     <t xml:space="preserve">3.19039344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19898796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15601396560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26258993148804</t>
+    <t xml:space="preserve">3.19898819923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15601420402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26258969306946</t>
   </si>
   <si>
     <t xml:space="preserve">3.27290368080139</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">3.13538670539856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10272622108459</t>
+    <t xml:space="preserve">3.10272598266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.08209872245789</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">3.04084396362305</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04771971702576</t>
+    <t xml:space="preserve">3.04771947860718</t>
   </si>
   <si>
     <t xml:space="preserve">3.05631446838379</t>
@@ -4592,13 +4592,13 @@
     <t xml:space="preserve">3.01162147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03396773338318</t>
+    <t xml:space="preserve">3.0339674949646</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583698272705</t>
+    <t xml:space="preserve">2.98583674430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.07350420951843</t>
@@ -4613,19 +4613,19 @@
     <t xml:space="preserve">2.97552299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94458198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93083047866821</t>
+    <t xml:space="preserve">2.94458222389221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93083024024963</t>
   </si>
   <si>
     <t xml:space="preserve">2.92051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87582325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87754225730896</t>
+    <t xml:space="preserve">2.87582349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87754249572754</t>
   </si>
   <si>
     <t xml:space="preserve">2.88785600662231</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">2.99786949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0511577129364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03053021430969</t>
+    <t xml:space="preserve">3.05115747451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03052997589111</t>
   </si>
   <si>
     <t xml:space="preserve">3.0494384765625</t>
@@ -4661,10 +4661,10 @@
     <t xml:space="preserve">3.05459547042847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08725547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04256272315979</t>
+    <t xml:space="preserve">3.08725571632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04256296157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.02021622657776</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">2.99615073204041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03912448883057</t>
+    <t xml:space="preserve">3.03912472724915</t>
   </si>
   <si>
     <t xml:space="preserve">3.06490921974182</t>
@@ -5991,6 +5991,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.98199999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01200008392334</t>
   </si>
 </sst>
 </file>
@@ -71147,7 +71150,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6495949074</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>1335652</v>
@@ -71168,6 +71171,32 @@
         <v>1987</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.649375</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>2832517</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>2.01600003242493</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>1.99800002574921</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>2.01200008392334</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="1996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.3917795419693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3601485490799</t>
+    <t xml:space="preserve">1.36014819145203</t>
   </si>
   <si>
     <t xml:space="preserve">1.30827283859253</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">1.23931646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21401143074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676342964172</t>
+    <t xml:space="preserve">1.21401131153107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676354885101</t>
   </si>
   <si>
     <t xml:space="preserve">1.23425531387329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20831775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009362697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18680822849274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11595416069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09191417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1747887134552</t>
+    <t xml:space="preserve">1.20831799507141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2000937461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18680846691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11595404148102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09191405773163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478835582733</t>
   </si>
   <si>
     <t xml:space="preserve">1.15644228458405</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22097015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087067127228</t>
+    <t xml:space="preserve">1.22097027301788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087055206299</t>
   </si>
   <si>
     <t xml:space="preserve">1.10646462440491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1172194480896</t>
+    <t xml:space="preserve">1.11721932888031</t>
   </si>
   <si>
     <t xml:space="preserve">1.12164771556854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04699766635895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826295375824</t>
+    <t xml:space="preserve">1.04699790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826307296753</t>
   </si>
   <si>
     <t xml:space="preserve">1.1184846162796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11089301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366782665253</t>
+    <t xml:space="preserve">1.11089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366794586182</t>
   </si>
   <si>
     <t xml:space="preserve">1.17795157432556</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">1.16213595867157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20578730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17921698093414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13872885704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770745277405</t>
+    <t xml:space="preserve">1.20578706264496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17921674251556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13872873783112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1317697763443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770757198334</t>
   </si>
   <si>
     <t xml:space="preserve">1.24311232566833</t>
@@ -164,112 +164,112 @@
     <t xml:space="preserve">1.29688549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29182457923889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29941582679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598626613617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525437831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27917194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25892806053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199155807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413325309753</t>
+    <t xml:space="preserve">1.2918244600296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598638534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2652542591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27917206287384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25892782211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199167728424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413349151611</t>
   </si>
   <si>
     <t xml:space="preserve">1.20135891437531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19376695156097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18237996101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464407444</t>
+    <t xml:space="preserve">1.19376730918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18238008022308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20452201366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464383602142</t>
   </si>
   <si>
     <t xml:space="preserve">1.19186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18554294109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264666080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123661518097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17984962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17162537574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11152577400208</t>
+    <t xml:space="preserve">1.18554317951202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264642238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123685359955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1798495054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17162525653839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11152589321136</t>
   </si>
   <si>
     <t xml:space="preserve">1.09571015834808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07546603679657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709738731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417829036713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062654972076</t>
+    <t xml:space="preserve">1.07546615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062643051147</t>
   </si>
   <si>
     <t xml:space="preserve">1.16719710826874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1545444726944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227051734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405784130096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2482088804245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406289100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812969684601</t>
+    <t xml:space="preserve">1.15454435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227039813995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24820876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406301021576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812945842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.26837289333344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28918695449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138184547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27682852745056</t>
+    <t xml:space="preserve">1.289186835289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27682876586914</t>
   </si>
   <si>
     <t xml:space="preserve">1.25731515884399</t>
@@ -278,190 +278,190 @@
     <t xml:space="preserve">1.24495661258698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19031894207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19096970558167</t>
+    <t xml:space="preserve">1.1903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096946716309</t>
   </si>
   <si>
     <t xml:space="preserve">1.17796051502228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12527441978455</t>
+    <t xml:space="preserve">1.12527418136597</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495144367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17340755462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18056237697601</t>
+    <t xml:space="preserve">1.17080557346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755330562592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495156288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17340731620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056225776672</t>
   </si>
   <si>
     <t xml:space="preserve">1.15389394760132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1630003452301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649569034576</t>
+    <t xml:space="preserve">1.16300022602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649592876434</t>
   </si>
   <si>
     <t xml:space="preserve">1.16169917583466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17730987071991</t>
+    <t xml:space="preserve">1.17731022834778</t>
   </si>
   <si>
     <t xml:space="preserve">1.18901801109314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14283621311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12852644920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1103138923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09665465354919</t>
+    <t xml:space="preserve">1.14283657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11031401157379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0966545343399</t>
   </si>
   <si>
     <t xml:space="preserve">1.10641121864319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055720806122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11486721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250866413116</t>
+    <t xml:space="preserve">1.10055732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11486732959747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250854492188</t>
   </si>
   <si>
     <t xml:space="preserve">1.05112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05372488498688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04656994342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04526925086975</t>
+    <t xml:space="preserve">1.05372524261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04657018184662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04526937007904</t>
   </si>
   <si>
     <t xml:space="preserve">1.10185825824738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13177871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120761394501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1291766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05307459831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255368232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485412120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99518495798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640616893768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01339745521545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982826292514801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321935653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968516409397125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97762256860733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671231746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0036404132843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950954258441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166874885559</t>
+    <t xml:space="preserve">1.13177859783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120797157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917685508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0530743598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255070209503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485650539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640640735626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01339709758759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982826411724091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321816444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968516290187836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977622807025909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671350955963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00364065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9808748960495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166934490204</t>
   </si>
   <si>
     <t xml:space="preserve">0.971118211746216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965914666652679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759844303131</t>
+    <t xml:space="preserve">0.965914487838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958759665489197</t>
   </si>
   <si>
     <t xml:space="preserve">1.05437552928925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05957901477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0660834312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974314689636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892848968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283104419708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340226650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06022942066193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08559691905975</t>
+    <t xml:space="preserve">1.05957913398743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06608355045319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974302768707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892884731293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283128261566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673395633698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340214729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06022965908051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08559703826904</t>
   </si>
   <si>
     <t xml:space="preserve">1.09275186061859</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.11421656608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09795558452606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07779157161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0738890171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10901296138763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746907234192</t>
+    <t xml:space="preserve">1.09795546531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07779169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07388889789581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10901308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746919155121</t>
   </si>
   <si>
     <t xml:space="preserve">1.14348673820496</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">1.1187698841095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13828301429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14543831348419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14023470878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278760433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218604564667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15129208564758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16234982013702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299517631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315907001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600412845612</t>
+    <t xml:space="preserve">1.13828337192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543795585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14023458957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12787580490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218592643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15129220485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16234970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803993701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0829952955246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600436687469</t>
   </si>
   <si>
     <t xml:space="preserve">1.08169424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09210169315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1051105260849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11356616020203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08949983119965</t>
+    <t xml:space="preserve">1.09990668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511028766632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11356604099274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08949971199036</t>
   </si>
   <si>
     <t xml:space="preserve">1.07584035396576</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">1.08234477043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09925639629364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429634571075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07518994808197</t>
+    <t xml:space="preserve">1.09925651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429610729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07518982887268</t>
   </si>
   <si>
     <t xml:space="preserve">1.0875483751297</t>
@@ -566,154 +566,154 @@
     <t xml:space="preserve">1.07453942298889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05827796459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07323861122131</t>
+    <t xml:space="preserve">1.05827832221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762779712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07323825359344</t>
   </si>
   <si>
     <t xml:space="preserve">1.06933581829071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05697727203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04722058773041</t>
+    <t xml:space="preserve">1.0569771528244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0472207069397</t>
   </si>
   <si>
     <t xml:space="preserve">1.05047297477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06348192691803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03421151638031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95680844783783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392286300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440889835358</t>
+    <t xml:space="preserve">1.06348168849945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0342116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144587993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982175767421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95680820941925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392107486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440830230713</t>
   </si>
   <si>
     <t xml:space="preserve">0.936644434928894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.949653446674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953556180000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9626624584198</t>
+    <t xml:space="preserve">0.949653387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95355623960495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96266233921051</t>
   </si>
   <si>
     <t xml:space="preserve">0.956158041954041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957458913326263</t>
+    <t xml:space="preserve">0.957458853721619</t>
   </si>
   <si>
     <t xml:space="preserve">0.955507397651672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.986728847026825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965264141559601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940547168254852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078798770905</t>
+    <t xml:space="preserve">0.986728966236115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96526426076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940547049045563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98607861995697</t>
   </si>
   <si>
     <t xml:space="preserve">0.995835244655609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00429105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315402030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03030896186829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03681337833405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02380442619324</t>
+    <t xml:space="preserve">1.00429093837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315390110016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.030308842659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03681349754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02380430698395</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120268344879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04201698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770698070526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852151870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356111049652</t>
+    <t xml:space="preserve">1.04201722145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917168617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852139949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0335613489151</t>
   </si>
   <si>
     <t xml:space="preserve">1.03095936775208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03160977363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567634105682</t>
+    <t xml:space="preserve">1.03160965442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567646026611</t>
   </si>
   <si>
     <t xml:space="preserve">1.05502605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03291058540344</t>
+    <t xml:space="preserve">1.03291094303131</t>
   </si>
   <si>
     <t xml:space="preserve">1.03551256656647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01860117912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999087572097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991932392120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00494146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0251053571701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999737977981567</t>
+    <t xml:space="preserve">1.01860094070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999087512493134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925146579742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932332515717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00494134426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02510523796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737858772278</t>
   </si>
   <si>
     <t xml:space="preserve">0.989981055259705</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">0.994534552097321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988029956817627</t>
+    <t xml:space="preserve">0.988029837608337</t>
   </si>
   <si>
     <t xml:space="preserve">0.946401178836823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952905893325806</t>
+    <t xml:space="preserve">0.952905595302582</t>
   </si>
   <si>
     <t xml:space="preserve">1.0166494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01404786109924</t>
+    <t xml:space="preserve">1.01404762268066</t>
   </si>
   <si>
     <t xml:space="preserve">1.04136657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02965867519379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991281986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00949466228485</t>
+    <t xml:space="preserve">1.0296585559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991282284259796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00949454307556</t>
   </si>
   <si>
     <t xml:space="preserve">1.01795053482056</t>
@@ -758,55 +758,55 @@
     <t xml:space="preserve">1.03226017951965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07063663005829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06218087673187</t>
+    <t xml:space="preserve">1.07063674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06218111515045</t>
   </si>
   <si>
     <t xml:space="preserve">1.09470331668854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14478766918182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18251347541809</t>
+    <t xml:space="preserve">1.14478778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18251395225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.23585057258606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845207691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633684635162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21438562870026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21308493614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20072615146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893870830536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381440639496</t>
+    <t xml:space="preserve">1.23845219612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21633672714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983254909515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21438550949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755847454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2130845785141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20072603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023952007294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527946949005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381464481354</t>
   </si>
   <si>
     <t xml:space="preserve">1.20267748832703</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">1.16430115699768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17600893974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999967098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194684505463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268414497375</t>
+    <t xml:space="preserve">1.17600929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268378734589</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482917785645</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">1.28777754306793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26697432994843</t>
+    <t xml:space="preserve">1.26697421073914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2401317358017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24348700046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24415814876556</t>
+    <t xml:space="preserve">1.24013161659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24348711967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24415826797485</t>
   </si>
   <si>
     <t xml:space="preserve">1.22738134860992</t>
@@ -860,40 +860,40 @@
     <t xml:space="preserve">1.24818444252014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25422394275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27368497848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24147403240204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006570339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831638813019</t>
+    <t xml:space="preserve">1.25422406196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2736850976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24147391319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006546497345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831662654877</t>
   </si>
   <si>
     <t xml:space="preserve">1.26294803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31462001800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30992269515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3105936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200181484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30455422401428</t>
+    <t xml:space="preserve">1.31462013721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30992257595062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059372425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200193405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146285057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
     <t xml:space="preserve">1.35555517673492</t>
@@ -905,88 +905,88 @@
     <t xml:space="preserve">1.35689735412598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34481823444366</t>
+    <t xml:space="preserve">1.3448178768158</t>
   </si>
   <si>
     <t xml:space="preserve">1.34079170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32669937610626</t>
+    <t xml:space="preserve">1.32669949531555</t>
   </si>
   <si>
     <t xml:space="preserve">1.32602822780609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30388295650482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925166606903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29650139808655</t>
+    <t xml:space="preserve">1.30388307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925154685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29650115966797</t>
   </si>
   <si>
     <t xml:space="preserve">1.34213387966156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32871246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864666938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031865119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239777088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37434506416321</t>
+    <t xml:space="preserve">1.32871282100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031853199005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239789009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434494495392</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010961055756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43876731395721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45084643363953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.448162317276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48976862430573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46158397197723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4602415561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50721645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540146350861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51929545402527</t>
+    <t xml:space="preserve">1.43876755237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4508467912674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44816243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48976874351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46158385276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46024167537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50721633434296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540122509003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51929569244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.50050568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5058741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829450130463</t>
+    <t xml:space="preserve">1.50587403774261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829426288605</t>
   </si>
   <si>
     <t xml:space="preserve">1.45755732059479</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">1.48037362098694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44547820091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950473308563</t>
+    <t xml:space="preserve">1.44547832012177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950461387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.45621514320374</t>
@@ -1007,124 +1007,124 @@
     <t xml:space="preserve">1.45889961719513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44279408454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290414333344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640229701996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042859077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727118492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411437511444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60787606239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61458706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713923931122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995577812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277172088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350902080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398171424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069295883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.723299741745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7098788022995</t>
+    <t xml:space="preserve">1.44279384613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566523551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290402412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129759788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640205860138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042870998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411413669586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60787653923035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61458694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277184009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350878238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398207187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6306928396225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72330009937286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987856388092</t>
   </si>
   <si>
     <t xml:space="preserve">1.66558814048767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70853650569916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048356056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719397068024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732615470886</t>
+    <t xml:space="preserve">1.70853638648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048308372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732627391815</t>
   </si>
   <si>
     <t xml:space="preserve">1.69108879566193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6857203245163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66693019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66424572467804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632496356964</t>
+    <t xml:space="preserve">1.68572020530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6669305562973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66424584388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632520198822</t>
   </si>
   <si>
     <t xml:space="preserve">1.65753543376923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63740336894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64679801464081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67364084720612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490604877472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7743011713028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75819516181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74880015850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7380633354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624822616577</t>
+    <t xml:space="preserve">1.63740348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64679825305939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67364108562469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490616798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77430105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75819551944733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74880027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73806321620941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624798774719</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174864292145</t>
@@ -1133,52 +1133,52 @@
     <t xml:space="preserve">1.77832746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77161705493927</t>
+    <t xml:space="preserve">1.77161681652069</t>
   </si>
   <si>
     <t xml:space="preserve">1.75416898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77564311027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074757099152</t>
+    <t xml:space="preserve">1.77564322948456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208950996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074792861938</t>
   </si>
   <si>
     <t xml:space="preserve">1.73537886142731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73940551280975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7595374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503823280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772222995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101170063019</t>
+    <t xml:space="preserve">1.73940515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953733921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503835201263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101205825806</t>
   </si>
   <si>
     <t xml:space="preserve">1.81188070774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261765003204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248594284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8306702375412</t>
+    <t xml:space="preserve">1.79845929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261741161346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248582363129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067083358765</t>
   </si>
   <si>
     <t xml:space="preserve">1.88435590267181</t>
@@ -1190,106 +1190,106 @@
     <t xml:space="preserve">1.88704025745392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88569808006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8454338312149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79577505588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598421573639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793127059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001039028168</t>
+    <t xml:space="preserve">1.88569831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543406963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79577529430389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598433494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793115139008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001062870026</t>
   </si>
   <si>
     <t xml:space="preserve">1.76893222332001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77698528766632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222169399261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316791534424</t>
+    <t xml:space="preserve">1.77698540687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222145557404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356375217438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316779613495</t>
   </si>
   <si>
     <t xml:space="preserve">1.69645750522614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6803514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69511532783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243061542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766749858856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874518871307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653436183929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921859741211</t>
+    <t xml:space="preserve">1.68035161495209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69511473178864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69243085384369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6776670217514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874542713165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814066886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653412342072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921847820282</t>
   </si>
   <si>
     <t xml:space="preserve">1.5702965259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57432281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57969152927399</t>
+    <t xml:space="preserve">1.57432293891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5796914100647</t>
   </si>
   <si>
     <t xml:space="preserve">1.55687522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54345381259918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51392722129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63203489780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229902744293</t>
+    <t xml:space="preserve">1.54345393180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51392710208893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63203501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229890823364</t>
   </si>
   <si>
     <t xml:space="preserve">1.66827273368835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75148439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611604213715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71390509605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72195768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658933162689</t>
+    <t xml:space="preserve">1.75148463249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611639976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390473842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72195792198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7165892124176</t>
   </si>
   <si>
     <t xml:space="preserve">1.63606107234955</t>
@@ -1304,31 +1304,31 @@
     <t xml:space="preserve">1.53674328327179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52197957038879</t>
+    <t xml:space="preserve">1.52197968959808</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613816738129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54882252216339</t>
+    <t xml:space="preserve">1.54882264137268</t>
   </si>
   <si>
     <t xml:space="preserve">1.54748034477234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53271663188934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076957702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211211204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869057655334</t>
+    <t xml:space="preserve">1.53271687030792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895458698273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076969623566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211175441742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869069576263</t>
   </si>
   <si>
     <t xml:space="preserve">1.5676121711731</t>
@@ -1337,205 +1337,205 @@
     <t xml:space="preserve">1.55955934524536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52600634098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190259456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519194602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6132447719574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56627011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661133766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50318992137909</t>
+    <t xml:space="preserve">1.52600622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774435520172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190235614777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56627035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782156944275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5031898021698</t>
   </si>
   <si>
     <t xml:space="preserve">1.49647927284241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50990045070648</t>
+    <t xml:space="preserve">1.50990068912506</t>
   </si>
   <si>
     <t xml:space="preserve">1.42266178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48171532154083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46695232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305809497833</t>
+    <t xml:space="preserve">1.4817156791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46292567253113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46695268154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305785655975</t>
   </si>
   <si>
     <t xml:space="preserve">1.48440003395081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52332174777985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405892848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662487030029</t>
+    <t xml:space="preserve">1.52332186698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405928611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662498950958</t>
   </si>
   <si>
     <t xml:space="preserve">1.56837046146393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53947961330414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884281635284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5160915851593</t>
+    <t xml:space="preserve">1.53947937488556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884293556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51609146595001</t>
   </si>
   <si>
     <t xml:space="preserve">1.49958217144012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56286764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57387387752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5518616437912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52159452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50233376026154</t>
+    <t xml:space="preserve">1.56286776065826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57387375831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55186152458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52159464359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095808506012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5023341178894</t>
   </si>
   <si>
     <t xml:space="preserve">1.49820673465729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47619450092316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042468070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4665641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42804265022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43767309188843</t>
+    <t xml:space="preserve">1.47619438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042432308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656394004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42804276943207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43767285346985</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391538619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46518850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42116367816925</t>
+    <t xml:space="preserve">1.46518814563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106112003326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42116403579712</t>
   </si>
   <si>
     <t xml:space="preserve">1.37370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40327894687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814568519592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280635356903</t>
+    <t xml:space="preserve">1.40327858924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814532756805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280647277832</t>
   </si>
   <si>
     <t xml:space="preserve">1.44180023670197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43629729747772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45143055915833</t>
+    <t xml:space="preserve">1.4362975358963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143067836761</t>
   </si>
   <si>
     <t xml:space="preserve">1.41566073894501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45555782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904900550842</t>
+    <t xml:space="preserve">1.45555794239044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904876708984</t>
   </si>
   <si>
     <t xml:space="preserve">1.42941868305206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41841244697571</t>
+    <t xml:space="preserve">1.41841220855713</t>
   </si>
   <si>
     <t xml:space="preserve">1.39640009403229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36613345146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4142849445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5339766740799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46793985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48032140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48169732093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069132328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48720037937164</t>
+    <t xml:space="preserve">1.3661333322525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41428518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53397655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4679399728775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48032164573669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48169755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069144248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48720061779022</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50508558750153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54085540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5312248468399</t>
+    <t xml:space="preserve">1.50508522987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54085516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53122472763062</t>
   </si>
   <si>
     <t xml:space="preserve">1.54223108291626</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">1.5491099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5477340221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53260099887848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900701999664</t>
+    <t xml:space="preserve">1.54773426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5326007604599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900713920593</t>
   </si>
   <si>
     <t xml:space="preserve">1.57112205028534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56561899185181</t>
+    <t xml:space="preserve">1.5656191110611</t>
   </si>
   <si>
     <t xml:space="preserve">1.51746726036072</t>
@@ -1565,103 +1565,103 @@
     <t xml:space="preserve">1.52984929084778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53810369968414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672802448273</t>
+    <t xml:space="preserve">1.53810381889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461323261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672826290131</t>
   </si>
   <si>
     <t xml:space="preserve">1.45830941200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.417036652565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38539409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851536273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576377391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36406981945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364862442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40190327167511</t>
+    <t xml:space="preserve">1.41703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878188610077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3785148859024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576365470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364874362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40190315246582</t>
   </si>
   <si>
     <t xml:space="preserve">1.36888480186462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32073318958282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26570272445679</t>
+    <t xml:space="preserve">1.32073330879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26570248603821</t>
   </si>
   <si>
     <t xml:space="preserve">1.2828996181488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28909063339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2966570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33724236488342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34343314170837</t>
+    <t xml:space="preserve">1.28909051418304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29665720462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33724224567413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34343326091766</t>
   </si>
   <si>
     <t xml:space="preserve">1.33105134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36200618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37989091873169</t>
+    <t xml:space="preserve">1.36200630664825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37989103794098</t>
   </si>
   <si>
     <t xml:space="preserve">1.3826425075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39089679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978788375854</t>
+    <t xml:space="preserve">1.39089703559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978800296783</t>
   </si>
   <si>
     <t xml:space="preserve">1.42666697502136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4321700334549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079423904419</t>
+    <t xml:space="preserve">1.43217015266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4307941198349</t>
   </si>
   <si>
     <t xml:space="preserve">1.43492162227631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41153347492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37301206588745</t>
+    <t xml:space="preserve">1.41153359413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581505298615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37301230430603</t>
   </si>
   <si>
     <t xml:space="preserve">1.35719096660614</t>
@@ -1682,58 +1682,58 @@
     <t xml:space="preserve">1.24506604671478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924482822418</t>
+    <t xml:space="preserve">1.22924470901489</t>
   </si>
   <si>
     <t xml:space="preserve">1.25951170921326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22786915302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130857944489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18315696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1955384016037</t>
+    <t xml:space="preserve">1.22786891460419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130834102631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1831568479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19553875923157</t>
   </si>
   <si>
     <t xml:space="preserve">1.19003570079803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24025106430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380281925201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30009651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29940867424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496313095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30078458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252994060516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2677663564682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28221154212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088738441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051770687103</t>
+    <t xml:space="preserve">1.24025094509125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338029384613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3000967502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994087934494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28496325016022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3007847070694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29252982139587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26776611804962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28221166133881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051758766174</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818719387054</t>
@@ -1745,70 +1745,70 @@
     <t xml:space="preserve">1.26363885402679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23268413543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22030234336853</t>
+    <t xml:space="preserve">1.23268437385559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22030258178711</t>
   </si>
   <si>
     <t xml:space="preserve">1.21204793453217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.214111328125</t>
+    <t xml:space="preserve">1.21411144733429</t>
   </si>
   <si>
     <t xml:space="preserve">1.18522047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18797183036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20172953605652</t>
+    <t xml:space="preserve">1.18797194957733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20172965526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.19347500801086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19966578483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104169845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808451652527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28083622455597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2815238237381</t>
+    <t xml:space="preserve">1.1996659040451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20104193687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2808358669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28152370452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.25676012039185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23612368106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273553371429</t>
+    <t xml:space="preserve">1.23612356185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792078971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273565292358</t>
   </si>
   <si>
     <t xml:space="preserve">1.20379328727722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19209921360016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.215487241745</t>
+    <t xml:space="preserve">1.19209945201874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548700332642</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046618938446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27946031093597</t>
+    <t xml:space="preserve">1.27946019172668</t>
   </si>
   <si>
     <t xml:space="preserve">1.2505692243576</t>
@@ -1826,52 +1826,52 @@
     <t xml:space="preserve">1.30353617668152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32417249679565</t>
+    <t xml:space="preserve">1.32417237758636</t>
   </si>
   <si>
     <t xml:space="preserve">1.32554841041565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33930587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34756028652191</t>
+    <t xml:space="preserve">1.33930611610413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34756052494049</t>
   </si>
   <si>
     <t xml:space="preserve">1.3317391872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31110262870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31522989273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34893643856049</t>
+    <t xml:space="preserve">1.31110286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523001194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3489363193512</t>
   </si>
   <si>
     <t xml:space="preserve">1.36063039302826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38126647472382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38401818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480881690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687256813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512721538544</t>
+    <t xml:space="preserve">1.38126659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38401830196381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422377586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623636722565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34687268733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512733459473</t>
   </si>
   <si>
     <t xml:space="preserve">1.36957275867462</t>
@@ -1883,238 +1883,238 @@
     <t xml:space="preserve">1.33793020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44455170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4830733537674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323719978333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958856344223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128625392914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59038269519806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.598637342453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57937657833099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424343585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52572202682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921261310577</t>
+    <t xml:space="preserve">1.44455182552338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323731899261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59038293361664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59863722324371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57937669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52572166919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921273231506</t>
   </si>
   <si>
     <t xml:space="preserve">1.51333999633789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51058864593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49545502662659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59726178646088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60001301765442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340104579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007418632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77611088752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79949867725372</t>
+    <t xml:space="preserve">1.51058840751648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49545526504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59726190567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.600013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340092658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007454395294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77611112594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7994989156723</t>
   </si>
   <si>
     <t xml:space="preserve">1.78436577320099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85847675800323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438879013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726293563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75301098823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728642940521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025454998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595549583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420107841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403614521027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89553165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572020053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018371105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597887039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73733329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73590838909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579080104828</t>
+    <t xml:space="preserve">1.85847640037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77438926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151500225067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719221591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726317405701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301086902618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153873443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728666782379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595525741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420072078705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403626441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89553225040436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81571972370148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298725605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018406867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597875118256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7373331785202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7359082698822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579068183899</t>
   </si>
   <si>
     <t xml:space="preserve">1.76013660430908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80004286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79006612300873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422469139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137415885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723944187164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016033649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73020768165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310484409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564936161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282256126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78293991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001925468445</t>
+    <t xml:space="preserve">1.80004274845123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7900664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8442245721817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723956108093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016057491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73020732402802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310496330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588477611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289304256439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8456494808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282268047333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294062614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146849155426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001949310303</t>
   </si>
   <si>
     <t xml:space="preserve">1.82854700088501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83994853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87415361404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560261249542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413035869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265786647797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562598705292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417722702026</t>
+    <t xml:space="preserve">1.83994889259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87415409088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265834331512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8556262254715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417758464813</t>
   </si>
   <si>
     <t xml:space="preserve">1.88555538654327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95396566390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116235733032</t>
+    <t xml:space="preserve">1.9539657831192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116211891174</t>
   </si>
   <si>
     <t xml:space="preserve">1.95681607723236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94398939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8784294128418</t>
+    <t xml:space="preserve">1.94398903846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87842917442322</t>
   </si>
   <si>
     <t xml:space="preserve">1.87700426578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990130901337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978443622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410710334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130308151245</t>
+    <t xml:space="preserve">1.85990166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978372097015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410674571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130343914032</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524972915649</t>
@@ -2123,193 +2123,193 @@
     <t xml:space="preserve">1.89268159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93543815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00954937934875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971359729767</t>
+    <t xml:space="preserve">1.93543791770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0095489025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111501216888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971335887909</t>
   </si>
   <si>
     <t xml:space="preserve">1.97819435596466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98532044887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714522838593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279906749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139765262604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94969034194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9710681438446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669836997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0309271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672186374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648680686951</t>
+    <t xml:space="preserve">1.98532021045685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81714534759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279942512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969022274017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106826305389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517865180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672210216522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9995721578598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648656845093</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655764579773</t>
+    <t xml:space="preserve">2.06655716896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.07368350028992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06228160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831182479858</t>
+    <t xml:space="preserve">2.06228184700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394217014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831194400787</t>
   </si>
   <si>
     <t xml:space="preserve">1.90123295783997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89695739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973697185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263437271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89125633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9971706867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94335007667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425812244415</t>
+    <t xml:space="preserve">1.89695703983307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9169100522995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263461112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89125657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835893154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99717032909393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9433501958847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425788402557</t>
   </si>
   <si>
     <t xml:space="preserve">1.97971498966217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96371483802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389662265778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95062327384949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989410877228</t>
+    <t xml:space="preserve">1.96371459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389698028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95062291622162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989434719086</t>
   </si>
   <si>
     <t xml:space="preserve">1.89389371871948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93462240695953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952958583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94916868209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880415916443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953332424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02044439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00735235214233</t>
+    <t xml:space="preserve">1.9346227645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680254459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952994346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880403995514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0204439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00735282897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.01026177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98553335666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00880718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02189874649048</t>
+    <t xml:space="preserve">1.98553395271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00880765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0218985080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.02917194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03062653541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208088874817</t>
+    <t xml:space="preserve">2.03062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208065032959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10044741630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608340263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08444690704346</t>
+    <t xml:space="preserve">2.10044693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608316421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881394386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0844464302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.09753823280334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.080082654953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863434791565</t>
+    <t xml:space="preserve">2.08008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462904930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863458633423</t>
   </si>
   <si>
     <t xml:space="preserve">2.24736189842224</t>
@@ -2318,34 +2318,34 @@
     <t xml:space="preserve">2.1891782283783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16590452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899234771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06844592094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07717347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07280993461609</t>
+    <t xml:space="preserve">2.16590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899282455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06844568252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07717370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07281017303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.12808465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11499309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1455397605896</t>
+    <t xml:space="preserve">2.11499381065369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14553999900818</t>
   </si>
   <si>
     <t xml:space="preserve">2.1469943523407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13390350341797</t>
+    <t xml:space="preserve">2.13390326499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.13099408149719</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">2.0829918384552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07426404953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05826377868652</t>
+    <t xml:space="preserve">2.07426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05826330184937</t>
   </si>
   <si>
     <t xml:space="preserve">2.04808163642883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335286140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771711349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06408214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04226326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99426114559174</t>
+    <t xml:space="preserve">2.023353099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771735191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0640823841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04226303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99426138401031</t>
   </si>
   <si>
     <t xml:space="preserve">2.03789973258972</t>
@@ -2384,22 +2384,22 @@
     <t xml:space="preserve">2.03644466400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517221450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02626252174377</t>
+    <t xml:space="preserve">2.04517245292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262622833252</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589799880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99862468242645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935070514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826051712036</t>
+    <t xml:space="preserve">1.99862539768219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826075553894</t>
   </si>
   <si>
     <t xml:space="preserve">1.96080553531647</t>
@@ -2411,97 +2411,97 @@
     <t xml:space="preserve">2.0611732006073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06990075111389</t>
+    <t xml:space="preserve">2.06990051269531</t>
   </si>
   <si>
     <t xml:space="preserve">2.04080843925476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03353571891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96807861328125</t>
+    <t xml:space="preserve">2.03353548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96807849407196</t>
   </si>
   <si>
     <t xml:space="preserve">1.91134881973267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553021430969</t>
+    <t xml:space="preserve">1.87643837928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.890984416008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553033351898</t>
   </si>
   <si>
     <t xml:space="preserve">1.80370819568634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79352581501007</t>
+    <t xml:space="preserve">1.79352617263794</t>
   </si>
   <si>
     <t xml:space="preserve">1.80079889297485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81970870494843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152781963348</t>
+    <t xml:space="preserve">1.81970918178558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152805805206</t>
   </si>
   <si>
     <t xml:space="preserve">1.82552719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80516290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83280038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898315906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298264980316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752844810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83570957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880113601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061965465546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788935184479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460995674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152165412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751878261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388114929199</t>
+    <t xml:space="preserve">1.80516242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8328001499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898292064667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171020030975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298253059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752809047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8357093334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880101680756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061989307404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788959026337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61461007595062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860908985138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152153491974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738810300827</t>
   </si>
   <si>
     <t xml:space="preserve">1.55351638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56224405765533</t>
+    <t xml:space="preserve">1.56224417686462</t>
   </si>
   <si>
     <t xml:space="preserve">1.62770116329193</t>
@@ -2510,43 +2510,43 @@
     <t xml:space="preserve">1.52733361721039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278256893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36441814899445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35569036006927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19277477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21241188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16150069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1593189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13386332988739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10768032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11422598361969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18041062355042</t>
+    <t xml:space="preserve">1.50842368602753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278280735016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36441791057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3556901216507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19277489185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21241176128387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16150081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15931904315948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1338632106781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10768055915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11422622203827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08440697193146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18041050434113</t>
   </si>
   <si>
     <t xml:space="preserve">1.17968332767487</t>
@@ -2558,76 +2558,76 @@
     <t xml:space="preserve">1.11204433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12877225875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550169467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1054984331131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09022533893585</t>
+    <t xml:space="preserve">1.12877213954926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550145626068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10549879074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09022510051727</t>
   </si>
   <si>
     <t xml:space="preserve">1.0414959192276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07640671730042</t>
+    <t xml:space="preserve">1.07640659809113</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059451580048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24514055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641276359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077502727509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22186684608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24223124980927</t>
+    <t xml:space="preserve">1.24514031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20077514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22186672687531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24223136901855</t>
   </si>
   <si>
     <t xml:space="preserve">1.36005413532257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41023778915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.473513007164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58939075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649650096893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331391334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56247735023499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967920780182</t>
+    <t xml:space="preserve">1.41023802757263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47351324558258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939063549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649673938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331379413605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5624772310257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967908859253</t>
   </si>
   <si>
     <t xml:space="preserve">1.4608039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47575604915619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284757614136</t>
+    <t xml:space="preserve">1.47575616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500860691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284745693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.52061176300049</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">1.48397970199585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192912101746</t>
+    <t xml:space="preserve">1.42192924022675</t>
   </si>
   <si>
     <t xml:space="preserve">1.40473425388336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37931597232819</t>
+    <t xml:space="preserve">1.37931609153748</t>
   </si>
   <si>
     <t xml:space="preserve">1.46005654335022</t>
@@ -2657,28 +2657,28 @@
     <t xml:space="preserve">1.49519348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56546795368195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228512763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64321768283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498668193817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807375431061</t>
+    <t xml:space="preserve">1.56546771526337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733306407928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228500843048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64321732521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807351589203</t>
   </si>
   <si>
     <t xml:space="preserve">1.6447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77479517459869</t>
+    <t xml:space="preserve">1.77479493618011</t>
   </si>
   <si>
     <t xml:space="preserve">1.75535702705383</t>
@@ -2687,73 +2687,73 @@
     <t xml:space="preserve">1.67760741710663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65069341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490526676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976098060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125598430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583794116974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62527549266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59238111972809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135221481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050155162811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797728538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7060159444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013108730316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956875801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788117408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72545337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077578544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656393527985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80021321773529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78675627708435</t>
+    <t xml:space="preserve">1.65069353580475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58490514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686672687531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976109981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583806037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62527513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58341002464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59238123893738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135209560394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172255992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71050179004669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003521442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013132572174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956887722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74788129329681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545349597931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7807754278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656417369843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80021274089813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78675639629364</t>
   </si>
   <si>
     <t xml:space="preserve">1.85403990745544</t>
@@ -2762,91 +2762,91 @@
     <t xml:space="preserve">1.86002051830292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79871785640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310723304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292934894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881372928619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104966163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264077663422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609783649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85852539539337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291501045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786707401276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141964912415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992488384247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9048764705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543903827667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83011674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79124188423157</t>
+    <t xml:space="preserve">1.79871773719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8331071138382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423248767853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292922973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881384849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161222934723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264113426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609747886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85852551460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291512966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039098262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141976833344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992476463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543915748596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011698722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124176502228</t>
   </si>
   <si>
     <t xml:space="preserve">1.85553526878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81666028499603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80768895149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928054332733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8346027135849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170834064484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8480589389801</t>
+    <t xml:space="preserve">1.81666004657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8076890707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928030490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460247516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84805905818939</t>
   </si>
   <si>
     <t xml:space="preserve">1.84506893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87646782398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058320522308</t>
+    <t xml:space="preserve">1.87646806240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8405829668045</t>
   </si>
   <si>
     <t xml:space="preserve">1.83908808231354</t>
@@ -2858,37 +2858,37 @@
     <t xml:space="preserve">1.82114577293396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77778518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900642871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349155902863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508303165436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059742450714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442411422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7239578962326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497293949127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227090835571</t>
+    <t xml:space="preserve">1.77778506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947252750397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7090060710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7134917974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508315086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442471027374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395813465118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497270107269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207832813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227078914642</t>
   </si>
   <si>
     <t xml:space="preserve">1.76582372188568</t>
@@ -2897,37 +2897,37 @@
     <t xml:space="preserve">1.74638617038727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75685214996338</t>
+    <t xml:space="preserve">1.75685238838196</t>
   </si>
   <si>
     <t xml:space="preserve">1.72246301174164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63424670696259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51762127876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836173057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74937629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75984275341034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72694849967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386202335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469858646393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80918431282043</t>
+    <t xml:space="preserve">1.63424646854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5176215171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74937653541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75984299182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72694826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80469846725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80918407440186</t>
   </si>
   <si>
     <t xml:space="preserve">1.81965053081512</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">1.91235268115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93926572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617949008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159753322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216022014618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056910514832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01345634460449</t>
+    <t xml:space="preserve">1.93926596641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.966179728508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159789085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216010093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056958198547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01345610618591</t>
   </si>
   <si>
     <t xml:space="preserve">2.014972448349</t>
@@ -2966,28 +2966,28 @@
     <t xml:space="preserve">2.02710199356079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677860736847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00890803337097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00132703781128</t>
+    <t xml:space="preserve">2.03316640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677872657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00890779495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00132727622986</t>
   </si>
   <si>
     <t xml:space="preserve">1.99981069564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03165030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800513267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435948371887</t>
+    <t xml:space="preserve">2.03165054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435924530029</t>
   </si>
   <si>
     <t xml:space="preserve">2.01042366027832</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">2.03013396263123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0346827507019</t>
+    <t xml:space="preserve">2.03468227386475</t>
   </si>
   <si>
     <t xml:space="preserve">2.04681181907654</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">2.05136013031006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04377937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07561850547791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06803822517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442566871643</t>
+    <t xml:space="preserve">2.04377961158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07561874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06803798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442590713501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05287647247314</t>
@@ -3023,22 +3023,22 @@
     <t xml:space="preserve">2.12261962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21358895301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084644317627</t>
+    <t xml:space="preserve">2.21358919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084692001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.16203951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14687776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13323283195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15597534179688</t>
+    <t xml:space="preserve">2.14687824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13323259353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1559751033783</t>
   </si>
   <si>
     <t xml:space="preserve">2.18023347854614</t>
@@ -3047,25 +3047,25 @@
     <t xml:space="preserve">2.20145988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27120327949524</t>
+    <t xml:space="preserve">2.27120304107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.18933057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26362204551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24846076965332</t>
+    <t xml:space="preserve">2.26362228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484610080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.21510529518127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21662163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546141624451</t>
+    <t xml:space="preserve">2.21662139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546165466309</t>
   </si>
   <si>
     <t xml:space="preserve">2.30000972747803</t>
@@ -3074,52 +3074,52 @@
     <t xml:space="preserve">2.32275223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35762357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34852719306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35914015769958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38794708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36368894577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39249563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639788627625</t>
+    <t xml:space="preserve">2.31062293052673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576238155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34852695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35913991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38794732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36368870735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39249539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639764785767</t>
   </si>
   <si>
     <t xml:space="preserve">2.38491439819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36520457267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823725700378</t>
+    <t xml:space="preserve">2.36520433425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823701858521</t>
   </si>
   <si>
     <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32426881790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35459184646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549498558044</t>
+    <t xml:space="preserve">2.32426834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35459160804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549474716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.38036632537842</t>
@@ -3128,28 +3128,28 @@
     <t xml:space="preserve">2.4410126209259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36065626144409</t>
+    <t xml:space="preserve">2.36065602302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.3727855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31820392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40765690803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41523838043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49407815933228</t>
+    <t xml:space="preserve">2.318204164505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40007662773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40765714645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41523790359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978621482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4940779209137</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349479675293</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">2.41827011108398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614104270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30759048461914</t>
+    <t xml:space="preserve">2.42888307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759072303772</t>
   </si>
   <si>
     <t xml:space="preserve">2.32730078697205</t>
@@ -3179,118 +3179,118 @@
     <t xml:space="preserve">2.45314192771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51682019233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48649740219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49862670898438</t>
+    <t xml:space="preserve">2.51682043075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.486496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4986264705658</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043274879456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4485936164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54714369773865</t>
+    <t xml:space="preserve">2.44859313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54714322090149</t>
   </si>
   <si>
     <t xml:space="preserve">2.58959603309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685352325439</t>
+    <t xml:space="preserve">2.56685376167297</t>
   </si>
   <si>
     <t xml:space="preserve">2.64266157150269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355924606323</t>
+    <t xml:space="preserve">2.65327429771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355972290039</t>
   </si>
   <si>
     <t xml:space="preserve">2.52038168907166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50052428245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51579928398132</t>
+    <t xml:space="preserve">2.50052380561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5157995223999</t>
   </si>
   <si>
     <t xml:space="preserve">2.51427149772644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49899673461914</t>
+    <t xml:space="preserve">2.49899649620056</t>
   </si>
   <si>
     <t xml:space="preserve">2.52343678474426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412938117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286688804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109417915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553351402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942427635193</t>
+    <t xml:space="preserve">2.53412890434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286664962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386408805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942379951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.47761178016663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48066639900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41192865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443398475647</t>
+    <t xml:space="preserve">2.48066663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4119291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443422317505</t>
   </si>
   <si>
     <t xml:space="preserve">2.42262125015259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46691942214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43025898933411</t>
+    <t xml:space="preserve">2.46691918373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43025922775269</t>
   </si>
   <si>
     <t xml:space="preserve">2.45928144454956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44706106185913</t>
+    <t xml:space="preserve">2.44706130027771</t>
   </si>
   <si>
     <t xml:space="preserve">2.43331408500671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45622682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023909568787</t>
+    <t xml:space="preserve">2.45622658729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4837212562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50816130638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023957252502</t>
   </si>
   <si>
     <t xml:space="preserve">2.65938472747803</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">2.6486918926239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63799929618835</t>
+    <t xml:space="preserve">2.63799977302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.67618703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6181423664093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60439467430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65632963180542</t>
+    <t xml:space="preserve">2.61814188957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60439443588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65632939338684</t>
   </si>
   <si>
     <t xml:space="preserve">2.68382453918457</t>
@@ -3320,103 +3320,103 @@
     <t xml:space="preserve">2.73575973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840718269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63952708244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61966967582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5937020778656</t>
+    <t xml:space="preserve">2.68840742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63952684402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61966943740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59370160102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.54634928703308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53565645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482197761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260183334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50663423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58148217201233</t>
+    <t xml:space="preserve">2.53565692901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885437965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260159492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50663447380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.54329419136047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46997356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4913592338562</t>
+    <t xml:space="preserve">2.46997380256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49135947227478</t>
   </si>
   <si>
     <t xml:space="preserve">2.48830389976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48219442367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40734624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526869773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41040134429932</t>
+    <t xml:space="preserve">2.48219418525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40734648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41040110588074</t>
   </si>
   <si>
     <t xml:space="preserve">2.38290619850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48524880409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44247913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47455668449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48983144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52649188041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52496409416199</t>
+    <t xml:space="preserve">2.48524904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44247889518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47455620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48983192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52649164199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52496433258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.55856919288635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5539870262146</t>
+    <t xml:space="preserve">2.55398678779602</t>
   </si>
   <si>
     <t xml:space="preserve">2.54787659645081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56162452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52954649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732683181763</t>
+    <t xml:space="preserve">2.56162428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732659339905</t>
   </si>
   <si>
     <t xml:space="preserve">2.4516441822052</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">2.4287314414978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42414879798889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42567682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4501166343689</t>
+    <t xml:space="preserve">2.42414927482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4256763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45011639595032</t>
   </si>
   <si>
     <t xml:space="preserve">2.4272038936615</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">2.3890163898468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40887403488159</t>
+    <t xml:space="preserve">2.37221360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40887379646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.37355303764343</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">2.42535710334778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43791532516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40965890884399</t>
+    <t xml:space="preserve">2.43791556358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42378759384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40965843200684</t>
   </si>
   <si>
     <t xml:space="preserve">2.35157608985901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35000586509705</t>
+    <t xml:space="preserve">2.35000610351562</t>
   </si>
   <si>
     <t xml:space="preserve">2.34372663497925</t>
@@ -3491,19 +3491,19 @@
     <t xml:space="preserve">2.33116817474365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35471510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34686613082886</t>
+    <t xml:space="preserve">2.35471534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34686636924744</t>
   </si>
   <si>
     <t xml:space="preserve">2.39396071434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41593813896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44733428955078</t>
+    <t xml:space="preserve">2.41593790054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44733452796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.43948531150818</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">2.47402095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45361351966858</t>
+    <t xml:space="preserve">2.45361328125</t>
   </si>
   <si>
     <t xml:space="preserve">2.4410548210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45675325393677</t>
+    <t xml:space="preserve">2.45675277709961</t>
   </si>
   <si>
     <t xml:space="preserve">2.46931147575378</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">2.50384712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45047378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25581741333008</t>
+    <t xml:space="preserve">2.45047354698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837611198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25581765174866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738716125488</t>
@@ -3551,67 +3551,67 @@
     <t xml:space="preserve">2.31547021865845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29977202415466</t>
+    <t xml:space="preserve">2.29977226257324</t>
   </si>
   <si>
     <t xml:space="preserve">2.29192328453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27151584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36256432533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31076073646545</t>
+    <t xml:space="preserve">2.27151536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36256456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31076049804688</t>
   </si>
   <si>
     <t xml:space="preserve">2.32017946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2699453830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2291305065155</t>
+    <t xml:space="preserve">2.26994562149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22913074493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.22442102432251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24639892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20244407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15064001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14122128486633</t>
+    <t xml:space="preserve">2.24639821052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20244359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15063953399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005921363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14122080802917</t>
   </si>
   <si>
     <t xml:space="preserve">2.20401382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16319847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732691764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18674564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18203592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16633820533752</t>
+    <t xml:space="preserve">2.19773411750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16319823265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732667922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18674516677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18203616142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16633796691895</t>
   </si>
   <si>
     <t xml:space="preserve">2.15534949302673</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">2.21186256408691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23070025444031</t>
+    <t xml:space="preserve">2.23070049285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.21657204627991</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">2.26366639137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31860971450806</t>
+    <t xml:space="preserve">2.31860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">2.29349303245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24796867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23540997505188</t>
+    <t xml:space="preserve">2.2479681968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2354097366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.24011921882629</t>
@@ -3659,40 +3659,40 @@
     <t xml:space="preserve">2.24482870101929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26052713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529662132263</t>
+    <t xml:space="preserve">2.26052689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529614448547</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407382965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11924386024475</t>
+    <t xml:space="preserve">2.11924409866333</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087385177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831562995911</t>
+    <t xml:space="preserve">2.18831539154053</t>
   </si>
   <si>
     <t xml:space="preserve">2.2212815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23227024078369</t>
+    <t xml:space="preserve">2.23227047920227</t>
   </si>
   <si>
     <t xml:space="preserve">2.23697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19930410385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22599077224731</t>
+    <t xml:space="preserve">2.19930386543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22599053382874</t>
   </si>
   <si>
     <t xml:space="preserve">2.27936458587646</t>
@@ -3704,67 +3704,67 @@
     <t xml:space="preserve">2.03447437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09255695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953033447266</t>
+    <t xml:space="preserve">2.0925567150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05802130699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953104972839</t>
   </si>
   <si>
     <t xml:space="preserve">1.95441377162933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0109269618988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92615723609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766638278961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592303752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.822549700737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807429790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202914714813</t>
+    <t xml:space="preserve">2.01092720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92615711688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8476665019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592339515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254946231842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045916080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202890872955</t>
   </si>
   <si>
     <t xml:space="preserve">2.009357213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9936591386795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796082496643</t>
+    <t xml:space="preserve">1.99365878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9779611825943</t>
   </si>
   <si>
     <t xml:space="preserve">2.01877593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01720643043518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920893907547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9889497756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99679827690125</t>
+    <t xml:space="preserve">2.01720571517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99208950996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894965648651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99679863452911</t>
   </si>
   <si>
     <t xml:space="preserve">2.05959105491638</t>
@@ -3773,76 +3773,76 @@
     <t xml:space="preserve">2.01249647140503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01406645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854174137115</t>
+    <t xml:space="preserve">2.01406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854209899902</t>
   </si>
   <si>
     <t xml:space="preserve">1.97639119625092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88220238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650454998016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301738262177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92124783992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01642274856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01158356666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96964156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543747901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87607979774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770040035248</t>
+    <t xml:space="preserve">1.88220226764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516864299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790070056915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947044849396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92124772071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576610088348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01642298698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01158308982849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964180469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543771743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87607991695404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770051956177</t>
   </si>
   <si>
     <t xml:space="preserve">1.91156888008118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90189039707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221107959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704315662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77122581005096</t>
+    <t xml:space="preserve">1.90189015865326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221119880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607293128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77122592926025</t>
   </si>
   <si>
     <t xml:space="preserve">1.79703617095947</t>
@@ -3851,91 +3851,91 @@
     <t xml:space="preserve">1.81316757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86801409721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672981739044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94383203983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382433891296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802179813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9325395822525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318924427032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9825474023819</t>
+    <t xml:space="preserve">1.86801397800446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672957897186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383192062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963493824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802155971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253970146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479527950287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9631894826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254704475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9760947227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448868751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448122501373</t>
+    <t xml:space="preserve">1.97609448432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448098659515</t>
   </si>
   <si>
     <t xml:space="preserve">1.97770738601685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99061298370361</t>
+    <t xml:space="preserve">1.99061274528503</t>
   </si>
   <si>
     <t xml:space="preserve">1.9341527223587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87124061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8292989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285363674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88898503780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86317467689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85833525657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8438173532486</t>
+    <t xml:space="preserve">1.87124025821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82929909229279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285339832306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88898515701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86317479610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85833537578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381723403931</t>
   </si>
   <si>
     <t xml:space="preserve">1.85672235488892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88253271579742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87769329547882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486567735672</t>
+    <t xml:space="preserve">1.88253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87769305706024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187571048737</t>
@@ -3947,19 +3947,19 @@
     <t xml:space="preserve">1.75993406772614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78574419021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81800675392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86962747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575177192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768595218658</t>
+    <t xml:space="preserve">1.78574407100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81800699234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86962735652924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575141429901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768607139587</t>
   </si>
   <si>
     <t xml:space="preserve">1.90350317955017</t>
@@ -3968,19 +3968,19 @@
     <t xml:space="preserve">1.93899238109589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95189774036407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383914470673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802878379822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222576618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06643033027649</t>
+    <t xml:space="preserve">1.9518975019455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383902549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99222612380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06643056869507</t>
   </si>
   <si>
     <t xml:space="preserve">2.07449579238892</t>
@@ -3989,31 +3989,31 @@
     <t xml:space="preserve">2.05029892921448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0519118309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03416752815247</t>
+    <t xml:space="preserve">2.05191206932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03416776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.01319670677185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07288289070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09546661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07933568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0761091709137</t>
+    <t xml:space="preserve">2.07288241386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09546709060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0793354511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07610893249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.00351786613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00835704803467</t>
+    <t xml:space="preserve">2.00835728645325</t>
   </si>
   <si>
     <t xml:space="preserve">1.98899984359741</t>
@@ -4025,109 +4025,109 @@
     <t xml:space="preserve">1.97932076454163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89866399765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91318237781525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286832332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480274200439</t>
+    <t xml:space="preserve">1.89866375923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91318202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931342124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9728684425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9648026227951</t>
   </si>
   <si>
     <t xml:space="preserve">1.9454448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83736479282379</t>
+    <t xml:space="preserve">1.8373646736145</t>
   </si>
   <si>
     <t xml:space="preserve">1.91025602817535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82647299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8147429227829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78290569782257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845813035965</t>
+    <t xml:space="preserve">1.82647287845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474328041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78290581703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78458154201508</t>
   </si>
   <si>
     <t xml:space="preserve">1.79128408432007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77620279788971</t>
+    <t xml:space="preserve">1.776202917099</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73933839797974</t>
+    <t xml:space="preserve">1.73933827877045</t>
   </si>
   <si>
     <t xml:space="preserve">1.74604117870331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79798650741577</t>
+    <t xml:space="preserve">1.79798674583435</t>
   </si>
   <si>
     <t xml:space="preserve">1.79966223239899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86333727836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83820247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85663497447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86166167259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87674295902252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171590328217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517509937286</t>
+    <t xml:space="preserve">1.86333763599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83820235729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8566347360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86166179180145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87674272060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517521858215</t>
   </si>
   <si>
     <t xml:space="preserve">1.91360747814178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93203973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8968505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355336666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879603385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94376933574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09625506401062</t>
+    <t xml:space="preserve">1.93203949928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685094356537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355348587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879615306854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9437689781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09625458717346</t>
   </si>
   <si>
     <t xml:space="preserve">2.17836213111877</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">2.19176745414734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14820027351379</t>
+    <t xml:space="preserve">2.14820003509521</t>
   </si>
   <si>
     <t xml:space="preserve">2.16160535812378</t>
@@ -4145,19 +4145,19 @@
     <t xml:space="preserve">2.18506479263306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29901003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29230737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28895616531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32582068443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33419919013977</t>
+    <t xml:space="preserve">2.29900979995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29230713844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28895592689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3258204460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33419871330261</t>
   </si>
   <si>
     <t xml:space="preserve">2.3425772190094</t>
@@ -4169,31 +4169,31 @@
     <t xml:space="preserve">2.25711822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2939829826355</t>
+    <t xml:space="preserve">2.29398274421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.30906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3006854057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31576633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29733467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31409072875977</t>
+    <t xml:space="preserve">2.30068564414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31576657295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31409096717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33755040168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42636013031006</t>
+    <t xml:space="preserve">2.33755016326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42636036872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981956481934</t>
@@ -4202,49 +4202,49 @@
     <t xml:space="preserve">2.46657609939575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46490049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4799816608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46322464942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38614416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40122532844543</t>
+    <t xml:space="preserve">2.46490025520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47998142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4632248878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306279182434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38614439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40122509002686</t>
   </si>
   <si>
     <t xml:space="preserve">2.40290069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609052658081</t>
+    <t xml:space="preserve">2.37609028816223</t>
   </si>
   <si>
     <t xml:space="preserve">2.38279318809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35430669784546</t>
+    <t xml:space="preserve">2.41295504570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35430693626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.36938786506653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37776637077332</t>
+    <t xml:space="preserve">2.37776613235474</t>
   </si>
   <si>
     <t xml:space="preserve">2.36100935935974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34927940368652</t>
+    <t xml:space="preserve">2.34927988052368</t>
   </si>
   <si>
     <t xml:space="preserve">2.37944173812866</t>
@@ -4256,19 +4256,19 @@
     <t xml:space="preserve">2.49171113967896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45987367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371069908142</t>
+    <t xml:space="preserve">2.45987391471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5537109375</t>
   </si>
   <si>
     <t xml:space="preserve">2.68776369094849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6492235660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77824926376343</t>
+    <t xml:space="preserve">2.64922332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77824950218201</t>
   </si>
   <si>
     <t xml:space="preserve">2.80170893669128</t>
@@ -4277,28 +4277,28 @@
     <t xml:space="preserve">2.77322268486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78160047531128</t>
+    <t xml:space="preserve">2.78160095214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93073487281799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92905926704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90224862098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9642481803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03295063972473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06311225891113</t>
+    <t xml:space="preserve">2.93073511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92905950546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90224885940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96424841880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03294992446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06311178207397</t>
   </si>
   <si>
     <t xml:space="preserve">3.11840891838074</t>
@@ -4307,22 +4307,22 @@
     <t xml:space="preserve">3.1502468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16030097007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20554351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20219206809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1435444355011</t>
+    <t xml:space="preserve">3.16030073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554375648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20219254493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14354395866394</t>
   </si>
   <si>
     <t xml:space="preserve">3.20889496803284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18878698348999</t>
+    <t xml:space="preserve">3.18878722190857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19213843345642</t>
@@ -4331,64 +4331,64 @@
     <t xml:space="preserve">3.1988410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17705726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29267811775208</t>
+    <t xml:space="preserve">3.17705750465393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29267859458923</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33792114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132622718811</t>
+    <t xml:space="preserve">3.33792090415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132598876953</t>
   </si>
   <si>
     <t xml:space="preserve">3.40494751930237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25581336021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34797501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3178129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39321804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36473155021667</t>
+    <t xml:space="preserve">3.25581383705139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34797477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781315803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39321780204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3647313117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.35467767715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18543577194214</t>
+    <t xml:space="preserve">3.18543553352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24240827560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13851714134216</t>
+    <t xml:space="preserve">3.13851737976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.23235416412354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13349008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19046306610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23403024673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24575996398926</t>
+    <t xml:space="preserve">3.13349032402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1904628276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23402976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24575972557068</t>
   </si>
   <si>
     <t xml:space="preserve">3.2390570640564</t>
@@ -4397,40 +4397,40 @@
     <t xml:space="preserve">3.2155978679657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26419186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29770517349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34294819831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510937690735</t>
+    <t xml:space="preserve">3.2641921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29770541191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435420036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34294772148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510961532593</t>
   </si>
   <si>
     <t xml:space="preserve">3.30105638504028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40159630775452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38986682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38484001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981271743774</t>
+    <t xml:space="preserve">3.40159606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3898663520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38483929634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981224060059</t>
   </si>
   <si>
     <t xml:space="preserve">3.36640739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37143421173096</t>
+    <t xml:space="preserve">3.37143445014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619142532349</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">3.23508644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2178966999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22305393218994</t>
+    <t xml:space="preserve">3.21789693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22305369377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.20414519309998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21445894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19555044174194</t>
+    <t xml:space="preserve">3.21445918083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19555020332336</t>
   </si>
   <si>
     <t xml:space="preserve">3.16976571083069</t>
@@ -4466,10 +4466,10 @@
     <t xml:space="preserve">3.20070719718933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12335419654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05975198745728</t>
+    <t xml:space="preserve">3.12335395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">3.09413146972656</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">3.13366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194894790649</t>
+    <t xml:space="preserve">3.13194870948792</t>
   </si>
   <si>
     <t xml:space="preserve">3.18867468833923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22649145126343</t>
+    <t xml:space="preserve">3.22649168968201</t>
   </si>
   <si>
     <t xml:space="preserve">3.2660276889801</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15257596969604</t>
+    <t xml:space="preserve">3.15257620811462</t>
   </si>
   <si>
     <t xml:space="preserve">3.11991596221924</t>
@@ -4517,55 +4517,55 @@
     <t xml:space="preserve">3.09756946563721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06834721565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14741921424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12507271766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18695569038391</t>
+    <t xml:space="preserve">3.06834697723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429520606995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14741945266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10960221290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12507295608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">3.17664194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398145675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27462244033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24196267127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1903932094574</t>
+    <t xml:space="preserve">3.14398121833801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24196219444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19039344787598</t>
   </si>
   <si>
     <t xml:space="preserve">3.19898796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15601420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26258969306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27290368080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538694381714</t>
+    <t xml:space="preserve">3.15601396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26258993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27290391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12851119041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538670539856</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
@@ -4574,58 +4574,58 @@
     <t xml:space="preserve">3.08209896087646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04084372520447</t>
+    <t xml:space="preserve">3.04084396362305</t>
   </si>
   <si>
     <t xml:space="preserve">3.04771947860718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05631422996521</t>
+    <t xml:space="preserve">3.05631446838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.01677846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00818371772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01162147521973</t>
+    <t xml:space="preserve">3.0081832408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01162123680115</t>
   </si>
   <si>
     <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98755598068237</t>
+    <t xml:space="preserve">2.98755621910095</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07350420951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07006621360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05287647247314</t>
+    <t xml:space="preserve">3.07350373268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07006597518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05287671089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.9755232334137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94458198547363</t>
+    <t xml:space="preserve">2.94458222389221</t>
   </si>
   <si>
     <t xml:space="preserve">2.93083024024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92051649093628</t>
+    <t xml:space="preserve">2.9205162525177</t>
   </si>
   <si>
     <t xml:space="preserve">2.87582325935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87754225730896</t>
+    <t xml:space="preserve">2.87754249572754</t>
   </si>
   <si>
     <t xml:space="preserve">2.88785600662231</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">2.95661473274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98411774635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005272865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286274909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786949157715</t>
+    <t xml:space="preserve">2.98411798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786925315857</t>
   </si>
   <si>
     <t xml:space="preserve">3.05115747451782</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">3.03052997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0494384765625</t>
+    <t xml:space="preserve">3.04943871498108</t>
   </si>
   <si>
     <t xml:space="preserve">3.05459547042847</t>
@@ -4664,19 +4664,19 @@
     <t xml:space="preserve">3.08725571632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04256248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02021646499634</t>
+    <t xml:space="preserve">3.04256296157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02021622657776</t>
   </si>
   <si>
     <t xml:space="preserve">2.99615049362183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03912496566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06490921974182</t>
+    <t xml:space="preserve">3.03912472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06490898132324</t>
   </si>
   <si>
     <t xml:space="preserve">2.9749481678009</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729724884033</t>
+    <t xml:space="preserve">3.03729748725891</t>
   </si>
   <si>
     <t xml:space="preserve">2.99276232719421</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">2.79858899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6721088886261</t>
+    <t xml:space="preserve">2.67210912704468</t>
   </si>
   <si>
     <t xml:space="preserve">2.67923450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69526743888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67032766342163</t>
+    <t xml:space="preserve">2.69526720046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67032742500305</t>
   </si>
   <si>
     <t xml:space="preserve">2.60797834396362</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">2.59372711181641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62579226493835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58125734329224</t>
+    <t xml:space="preserve">2.62579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58125758171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.64538788795471</t>
@@ -4739,22 +4739,22 @@
     <t xml:space="preserve">2.47971725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31939077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36570715904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32473492622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28554391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33720445632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392593383789</t>
+    <t xml:space="preserve">2.31939101219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36570739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32473468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2855441570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720517158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392569541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.26060438156128</t>
@@ -4763,25 +4763,25 @@
     <t xml:space="preserve">2.27663683891296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29445123672485</t>
+    <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
     <t xml:space="preserve">2.38708424568176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32829761505127</t>
+    <t xml:space="preserve">2.32829785346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.32117199897766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36927032470703</t>
+    <t xml:space="preserve">2.36927008628845</t>
   </si>
   <si>
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323715209961</t>
+    <t xml:space="preserve">2.35323762893677</t>
   </si>
   <si>
     <t xml:space="preserve">2.35145616531372</t>
@@ -4790,22 +4790,22 @@
     <t xml:space="preserve">2.43161916732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40667939186096</t>
+    <t xml:space="preserve">2.40667963027954</t>
   </si>
   <si>
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955401420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42449355125427</t>
+    <t xml:space="preserve">2.39955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449378967285</t>
   </si>
   <si>
     <t xml:space="preserve">2.34254908561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39242839813232</t>
+    <t xml:space="preserve">2.39242815971375</t>
   </si>
   <si>
     <t xml:space="preserve">2.39599132537842</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">2.3603630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41380524635315</t>
+    <t xml:space="preserve">2.41380500793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.51534509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49931287765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56522488594055</t>
+    <t xml:space="preserve">2.49931263923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56522464752197</t>
   </si>
   <si>
     <t xml:space="preserve">2.53494071960449</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.4975311756134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50287532806396</t>
+    <t xml:space="preserve">2.50287556648254</t>
   </si>
   <si>
     <t xml:space="preserve">2.57056879997253</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">2.60085296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303904533386</t>
+    <t xml:space="preserve">2.5830385684967</t>
   </si>
   <si>
     <t xml:space="preserve">2.64360666275024</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">2.65785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65073251724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67567205429077</t>
+    <t xml:space="preserve">2.65073227882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67567181587219</t>
   </si>
   <si>
     <t xml:space="preserve">2.65963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65251350402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291811943054</t>
+    <t xml:space="preserve">2.6525137424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291835784912</t>
   </si>
   <si>
     <t xml:space="preserve">2.55453634262085</t>
@@ -4886,31 +4886,31 @@
     <t xml:space="preserve">2.60441565513611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60619711875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59550857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74336528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7166440486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68992328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70773720741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66676497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77721214294434</t>
+    <t xml:space="preserve">2.60619735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59550881385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74336504936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71664428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68992304801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70773696899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66676473617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73445820808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77721190452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.76830506324768</t>
@@ -4940,31 +4940,31 @@
     <t xml:space="preserve">2.78968191146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8235285282135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.848468542099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77008628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81284022331238</t>
+    <t xml:space="preserve">2.82352876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84846830368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77008652687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8128399848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.80927729606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80749583244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81996560096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81105875968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78790068626404</t>
+    <t xml:space="preserve">2.80749607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81996583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81105852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78790044784546</t>
   </si>
   <si>
     <t xml:space="preserve">2.83065414428711</t>
@@ -4976,43 +4976,43 @@
     <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63469934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5527548789978</t>
+    <t xml:space="preserve">2.63469958305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55275464057922</t>
   </si>
   <si>
     <t xml:space="preserve">2.54741072654724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5313777923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5420663356781</t>
+    <t xml:space="preserve">2.53137803077698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54206657409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.55809903144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57947587966919</t>
+    <t xml:space="preserve">2.57947611808777</t>
   </si>
   <si>
     <t xml:space="preserve">2.52781534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51178240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50821995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60263419151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61154127120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988073348999</t>
+    <t xml:space="preserve">2.5117826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50821971893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60263395309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61154103279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988049507141</t>
   </si>
   <si>
     <t xml:space="preserve">2.58482027053833</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">2.57769465446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56878757476807</t>
+    <t xml:space="preserve">2.56878733634949</t>
   </si>
   <si>
     <t xml:space="preserve">2.5866014957428</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">2.56700611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51890826225281</t>
+    <t xml:space="preserve">2.51890802383423</t>
   </si>
   <si>
     <t xml:space="preserve">2.46724724769592</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">2.48867678642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49051070213318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47400522232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43916010856628</t>
+    <t xml:space="preserve">2.49051094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47400498390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43915987014771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49417877197266</t>
@@ -5063,19 +5063,19 @@
     <t xml:space="preserve">2.51618599891663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52718997001648</t>
+    <t xml:space="preserve">2.5271897315979</t>
   </si>
   <si>
     <t xml:space="preserve">2.54002737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58587622642517</t>
+    <t xml:space="preserve">2.58587646484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.59871411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61521983146667</t>
+    <t xml:space="preserve">2.6152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">2.62438941001892</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">2.61888742446899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62255549430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63172507286072</t>
+    <t xml:space="preserve">2.62255525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6317253112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.60971760749817</t>
@@ -5099,25 +5099,25 @@
     <t xml:space="preserve">2.57303857803345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5510311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60604953765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58404231071472</t>
+    <t xml:space="preserve">2.55103135108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60605001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5840425491333</t>
   </si>
   <si>
     <t xml:space="preserve">2.5675368309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57487273216248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60054802894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63355922698975</t>
+    <t xml:space="preserve">2.5748724937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6005482673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63355898857117</t>
   </si>
   <si>
     <t xml:space="preserve">2.61705350875854</t>
@@ -5129,43 +5129,43 @@
     <t xml:space="preserve">2.6115517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5308575630188</t>
+    <t xml:space="preserve">2.53085780143738</t>
   </si>
   <si>
     <t xml:space="preserve">2.54736351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57670640945435</t>
+    <t xml:space="preserve">2.57670664787292</t>
   </si>
   <si>
     <t xml:space="preserve">2.51802015304565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48500895500183</t>
+    <t xml:space="preserve">2.48500871658325</t>
   </si>
   <si>
     <t xml:space="preserve">2.51251816749573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53269147872925</t>
+    <t xml:space="preserve">2.53269171714783</t>
   </si>
   <si>
     <t xml:space="preserve">2.58037447929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59321236610413</t>
+    <t xml:space="preserve">2.59321212768555</t>
   </si>
   <si>
     <t xml:space="preserve">2.64089512825012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60238218307495</t>
+    <t xml:space="preserve">2.60238194465637</t>
   </si>
   <si>
     <t xml:space="preserve">2.56386876106262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5602011680603</t>
+    <t xml:space="preserve">2.56020092964172</t>
   </si>
   <si>
     <t xml:space="preserve">2.54552936553955</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">2.56937074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5877103805542</t>
+    <t xml:space="preserve">2.58771014213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.61338567733765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47583889961243</t>
+    <t xml:space="preserve">2.47583913803101</t>
   </si>
   <si>
     <t xml:space="preserve">2.4868426322937</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.5033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767281532288</t>
+    <t xml:space="preserve">2.47767305374146</t>
   </si>
   <si>
     <t xml:space="preserve">2.49234461784363</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">2.46116757392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40798282623291</t>
+    <t xml:space="preserve">2.40798258781433</t>
   </si>
   <si>
     <t xml:space="preserve">2.34196043014526</t>
@@ -5219,19 +5219,19 @@
     <t xml:space="preserve">2.33462452888489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33645844459534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31261682510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31078314781189</t>
+    <t xml:space="preserve">2.33645868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31261706352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31078338623047</t>
   </si>
   <si>
     <t xml:space="preserve">2.27777194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29611134529114</t>
+    <t xml:space="preserve">2.29611158370972</t>
   </si>
   <si>
     <t xml:space="preserve">2.28694176673889</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">2.30344724655151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32728886604309</t>
+    <t xml:space="preserve">2.32728862762451</t>
   </si>
   <si>
     <t xml:space="preserve">2.34746217727661</t>
@@ -5261,16 +5261,16 @@
     <t xml:space="preserve">2.35113000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39881300926208</t>
+    <t xml:space="preserve">2.39881277084351</t>
   </si>
   <si>
     <t xml:space="preserve">2.40248084068298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41898655891418</t>
+    <t xml:space="preserve">2.40981650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41898632049561</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732595443726</t>
@@ -5279,7 +5279,7 @@
     <t xml:space="preserve">2.46666932106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42815637588501</t>
+    <t xml:space="preserve">2.42815613746643</t>
   </si>
   <si>
     <t xml:space="preserve">2.41531872749329</t>
@@ -5291,31 +5291,31 @@
     <t xml:space="preserve">2.39697909355164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39514517784119</t>
+    <t xml:space="preserve">2.39514493942261</t>
   </si>
   <si>
     <t xml:space="preserve">2.37863945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38780951499939</t>
+    <t xml:space="preserve">2.38780927658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.44099402427673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43182396888733</t>
+    <t xml:space="preserve">2.43182420730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.44466161727905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4428277015686</t>
+    <t xml:space="preserve">2.44282793998718</t>
   </si>
   <si>
     <t xml:space="preserve">2.31064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30297493934631</t>
+    <t xml:space="preserve">2.30297470092773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37008905410767</t>
@@ -5336,22 +5336,22 @@
     <t xml:space="preserve">2.43720316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38926458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43145036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46021366119385</t>
+    <t xml:space="preserve">2.38926482200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43145060539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46021389961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.41994524002075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41227531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40460467338562</t>
+    <t xml:space="preserve">2.41227507591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4046049118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.42569804191589</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">2.3643364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29722213745117</t>
+    <t xml:space="preserve">2.29722189903259</t>
   </si>
   <si>
     <t xml:space="preserve">2.197509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18408703804016</t>
+    <t xml:space="preserve">2.16491150856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18408679962158</t>
   </si>
   <si>
     <t xml:space="preserve">2.18792200088501</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">2.13806581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12272524833679</t>
+    <t xml:space="preserve">2.12272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">2.09012699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09971499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10354971885681</t>
+    <t xml:space="preserve">2.09971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10354995727539</t>
   </si>
   <si>
     <t xml:space="preserve">2.08053946495056</t>
@@ -5441,10 +5441,10 @@
     <t xml:space="preserve">2.00767254829407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95781636238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424970149994</t>
+    <t xml:space="preserve">1.95781624317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424946308136</t>
   </si>
   <si>
     <t xml:space="preserve">1.99808490276337</t>
@@ -5474,31 +5474,31 @@
     <t xml:space="preserve">2.07095170021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08820939064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07862186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04410600662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0306830406189</t>
+    <t xml:space="preserve">2.08820962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07862162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04410576820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03068327903748</t>
   </si>
   <si>
     <t xml:space="preserve">1.97315657138824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01534271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06903386116028</t>
+    <t xml:space="preserve">2.01534247398376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06903409957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.05561113357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10546731948853</t>
+    <t xml:space="preserve">2.1054675579071</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930252075195</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">2.05369353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752873420715</t>
+    <t xml:space="preserve">2.05752849578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.06136393547058</t>
@@ -5531,22 +5531,22 @@
     <t xml:space="preserve">2.03835320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02301287651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05177617073059</t>
+    <t xml:space="preserve">2.02301263809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05177640914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.05944633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643584251404</t>
+    <t xml:space="preserve">2.03643560409546</t>
   </si>
   <si>
     <t xml:space="preserve">2.07286906242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03260040283203</t>
+    <t xml:space="preserve">2.03260064125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.02876543998718</t>
@@ -5561,16 +5561,16 @@
     <t xml:space="preserve">2.09587979316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14573574066162</t>
+    <t xml:space="preserve">2.1457359790802</t>
   </si>
   <si>
     <t xml:space="preserve">2.11889028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12080788612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09204459190369</t>
+    <t xml:space="preserve">2.12080764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09204435348511</t>
   </si>
   <si>
     <t xml:space="preserve">1.85906255245209</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">1.9271354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94439351558685</t>
+    <t xml:space="preserve">1.94439363479614</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165144443512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93672323226929</t>
+    <t xml:space="preserve">1.93672311306</t>
   </si>
   <si>
     <t xml:space="preserve">1.92905306816101</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">1.87823808193207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87919688224792</t>
+    <t xml:space="preserve">1.87919676303864</t>
   </si>
   <si>
     <t xml:space="preserve">1.83029937744141</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">1.71812283992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73825693130493</t>
+    <t xml:space="preserve">1.73825705051422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75167989730835</t>
@@ -6000,6 +6000,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.0239999294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98699998855591</t>
   </si>
 </sst>
 </file>
@@ -71234,7 +71237,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494791667</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>472932</v>
@@ -71255,6 +71258,32 @@
         <v>1995</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6911921296</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1083758</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>2.03600001335144</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>1.98199999332428</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>1.98699998855591</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,97 +38,97 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847168445587</t>
+    <t xml:space="preserve">1.42847180366516</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39177966117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36014831066132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30827283859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2715802192688</t>
+    <t xml:space="preserve">1.3917795419693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36014842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30827271938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158045768738</t>
   </si>
   <si>
     <t xml:space="preserve">1.23931646347046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21401143074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676319122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425555229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831763744354</t>
+    <t xml:space="preserve">1.21401107311249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676354885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.234255194664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831751823425</t>
   </si>
   <si>
     <t xml:space="preserve">1.20009350776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18680834770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11595404148102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09191405773163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478859424591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15644228458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19439995288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23299014568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2064197063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22096991539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437761306763</t>
+    <t xml:space="preserve">1.18680846691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11595416069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09191417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15644252300262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.232990026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20641982555389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2209700345993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437737464905</t>
   </si>
   <si>
     <t xml:space="preserve">1.16087067127228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1064647436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1172194480896</t>
+    <t xml:space="preserve">1.10646462440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11721956729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.12164783477783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04699766635895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826319217682</t>
+    <t xml:space="preserve">1.04699778556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826295375824</t>
   </si>
   <si>
     <t xml:space="preserve">1.11848473548889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11089301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366758823395</t>
+    <t xml:space="preserve">1.11089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366770744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.17795157432556</t>
@@ -137,61 +137,61 @@
     <t xml:space="preserve">1.19819569587708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21337878704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213619709015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578718185425</t>
+    <t xml:space="preserve">1.21337866783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213572025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578706264496</t>
   </si>
   <si>
     <t xml:space="preserve">1.17921674251556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13872873783112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13176965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770757198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311232566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688537120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29182469844818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29941594600677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598638534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525413990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27917182445526</t>
+    <t xml:space="preserve">1.13872849941254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1317697763443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770769119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311220645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29182422161102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2994157075882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598662376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27917194366455</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892782211304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20199131965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135867595673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376707077026</t>
+    <t xml:space="preserve">1.20199167728424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413349151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135891437531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376730918884</t>
   </si>
   <si>
     <t xml:space="preserve">1.18238008022308</t>
@@ -200,130 +200,130 @@
     <t xml:space="preserve">1.20452201366425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464383602142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19186949729919</t>
+    <t xml:space="preserve">1.21464407444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19186925888062</t>
   </si>
   <si>
     <t xml:space="preserve">1.18554294109344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15264666080475</t>
+    <t xml:space="preserve">1.15264654159546</t>
   </si>
   <si>
     <t xml:space="preserve">1.19123685359955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17984962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17162537574768</t>
+    <t xml:space="preserve">1.1798495054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17162549495697</t>
   </si>
   <si>
     <t xml:space="preserve">1.11152589321136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09570980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546591758728</t>
+    <t xml:space="preserve">1.09571003913879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546627521515</t>
   </si>
   <si>
     <t xml:space="preserve">1.10709726810455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12417829036713</t>
+    <t xml:space="preserve">1.12417817115784</t>
   </si>
   <si>
     <t xml:space="preserve">1.14062654972076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16719675064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454423427582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405772209167</t>
+    <t xml:space="preserve">1.16719686985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15454435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227039813995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405784130096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24820864200592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25406312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26837253570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918707370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138184547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27682864665985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2573150396347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495661258698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1903190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19096946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796051502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527418136597</t>
+    <t xml:space="preserve">1.25406277179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812945842743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26837265491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918719291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138172626495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27682852745056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25731515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495685100555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031894207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1909693479538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527430057526</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690289974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080569267273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755330562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17340743541718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1805624961853</t>
+    <t xml:space="preserve">1.17080557346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495144367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17340731620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056213855743</t>
   </si>
   <si>
     <t xml:space="preserve">1.15389406681061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16300046443939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649569034576</t>
+    <t xml:space="preserve">1.16300022602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950476169586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649580955505</t>
   </si>
   <si>
     <t xml:space="preserve">1.16169941425323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17731010913849</t>
+    <t xml:space="preserve">1.1773099899292</t>
   </si>
   <si>
     <t xml:space="preserve">1.18901813030243</t>
@@ -332,85 +332,85 @@
     <t xml:space="preserve">1.14283621311188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12852668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11031401157379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0966545343399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10641145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10055720806122</t>
+    <t xml:space="preserve">1.12852644920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1103138923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09665417671204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10641121864319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10055732727051</t>
   </si>
   <si>
     <t xml:space="preserve">1.11486732959747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10250854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372512340546</t>
+    <t xml:space="preserve">1.10250890254974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372476577759</t>
   </si>
   <si>
     <t xml:space="preserve">1.04657006263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10185813903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177859783173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120761394501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12917697429657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05307471752167</t>
+    <t xml:space="preserve">1.04526913166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185837745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120785236359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917709350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05307447910309</t>
   </si>
   <si>
     <t xml:space="preserve">0.952255189418793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996485829353333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184719562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640628814697</t>
+    <t xml:space="preserve">0.996485531330109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184779167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640604972839</t>
   </si>
   <si>
     <t xml:space="preserve">1.01339745521545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982826411724091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321876049042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97762268781662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671172142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00364077091217</t>
+    <t xml:space="preserve">0.982826292514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968516290187836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977622747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00364065170288</t>
   </si>
   <si>
     <t xml:space="preserve">0.950954258441925</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">0.970467805862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969166874885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118032932281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96591454744339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437552928925</t>
+    <t xml:space="preserve">0.96916663646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118330955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965914666652679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958759665489197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437541007996</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957901477814</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">1.06608355045319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07974290847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892860889435</t>
+    <t xml:space="preserve">1.07974302768707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892872810364</t>
   </si>
   <si>
     <t xml:space="preserve">1.06283116340637</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">1.09340238571167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06022965908051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08559679985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09275197982788</t>
+    <t xml:space="preserve">1.06022953987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08559691905975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09275186061859</t>
   </si>
   <si>
     <t xml:space="preserve">1.11421680450439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09795558452606</t>
+    <t xml:space="preserve">1.09795546531677</t>
   </si>
   <si>
     <t xml:space="preserve">1.07779145240784</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">1.07388889789581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10901296138763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746907234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348673820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1187698841095</t>
+    <t xml:space="preserve">1.10901284217834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11876976490021</t>
   </si>
   <si>
     <t xml:space="preserve">1.13828313350677</t>
@@ -497,31 +497,31 @@
     <t xml:space="preserve">1.1454381942749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1402348279953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12787592411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218580722809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15129232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16235017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803969860077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0829952955246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315883159637</t>
+    <t xml:space="preserve">1.14023458957672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1278760433197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218628406525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15129208564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16234982013702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803993701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438045978546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299541473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315871238708</t>
   </si>
   <si>
     <t xml:space="preserve">1.09600424766541</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">1.08169424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990680217743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09210133552551</t>
+    <t xml:space="preserve">1.09990692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210157394409</t>
   </si>
   <si>
     <t xml:space="preserve">1.10511040687561</t>
@@ -542,112 +542,112 @@
     <t xml:space="preserve">1.11356627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949959278107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584023475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234465122223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429598808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07518970966339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08754849433899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07453918457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07323849201202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06933581829071</t>
+    <t xml:space="preserve">1.08949983119965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584035396576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234453201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925639629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429610729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07518994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0875483751297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0745393037796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827832221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762791633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07323861122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06933569908142</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697739124298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04722046852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047285556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348156929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0342116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982175648212433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956808388233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392226696014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931441009044647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644375324249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653565883636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95355612039566</t>
+    <t xml:space="preserve">1.0472207069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047297477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348168849945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03421139717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144587993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982176005840302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95680832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392345905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644613742828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953556299209595</t>
   </si>
   <si>
     <t xml:space="preserve">0.9626624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956158041954041</t>
+    <t xml:space="preserve">0.956157863140106</t>
   </si>
   <si>
     <t xml:space="preserve">0.957458853721619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955507516860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98672890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965264081954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940547227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078381538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429117679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315402030945</t>
+    <t xml:space="preserve">0.955507695674896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986728847026825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965264141559601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940547287464142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078441143036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835244655609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429093837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315390110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
@@ -659,82 +659,82 @@
     <t xml:space="preserve">1.02380454540253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02120244503021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04201698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917216300964</t>
+    <t xml:space="preserve">1.02120268344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04201686382294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917192459106</t>
   </si>
   <si>
     <t xml:space="preserve">1.02770709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04852151870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356111049652</t>
+    <t xml:space="preserve">1.04852139949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03356122970581</t>
   </si>
   <si>
     <t xml:space="preserve">1.03095960617065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03160977363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567634105682</t>
+    <t xml:space="preserve">1.03160989284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567646026611</t>
   </si>
   <si>
     <t xml:space="preserve">1.05502581596375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03291082382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03551256656647</t>
+    <t xml:space="preserve">1.03291070461273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03551232814789</t>
   </si>
   <si>
     <t xml:space="preserve">1.01860094070435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999087512493134</t>
+    <t xml:space="preserve">0.999087631702423</t>
   </si>
   <si>
     <t xml:space="preserve">1.01925134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991932392120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00494146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0251053571701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999737799167633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981234073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534194469452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988030016422272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401238441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905595302582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01664960384369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404786109924</t>
+    <t xml:space="preserve">0.991932511329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00494158267975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02510547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737918376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534134864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029897212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401178836823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0166494846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404798030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.04136645793915</t>
@@ -746,67 +746,67 @@
     <t xml:space="preserve">0.991282105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00949466228485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01795041561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01469838619232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226029872894</t>
+    <t xml:space="preserve">1.00949454307556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01795053482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01469814777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226053714752</t>
   </si>
   <si>
     <t xml:space="preserve">1.07063674926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06218087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09470331668854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14478778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18251347541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23585045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845219612122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633672714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983254909515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21438562870026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755847454071</t>
+    <t xml:space="preserve">1.06218099594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09470319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1447879076004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18251359462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23585021495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845231533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21633696556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983231067657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21438550949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755835533142</t>
   </si>
   <si>
     <t xml:space="preserve">1.21308469772339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20072627067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893882751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023987770081</t>
+    <t xml:space="preserve">1.20072615146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893870830536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023963928223</t>
   </si>
   <si>
     <t xml:space="preserve">1.20527946949005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18381476402283</t>
+    <t xml:space="preserve">1.18381464481354</t>
   </si>
   <si>
     <t xml:space="preserve">1.20267748832703</t>
@@ -827,100 +827,100 @@
     <t xml:space="preserve">1.21194684505463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22268414497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482905864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502739429474</t>
+    <t xml:space="preserve">1.22268378734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482882022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502727508545</t>
   </si>
   <si>
     <t xml:space="preserve">1.28777754306793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26697432994843</t>
+    <t xml:space="preserve">1.26697421073914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2401317358017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24348711967468</t>
+    <t xml:space="preserve">1.24013161659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24348700046539</t>
   </si>
   <si>
     <t xml:space="preserve">1.24415814876556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22738146781921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818456172943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422394275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2736850976944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24147379398346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006558418274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831650733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26294803619385</t>
+    <t xml:space="preserve">1.2273815870285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818432331085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422406196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27368497848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24147391319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006570339203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831638813019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26294779777527</t>
   </si>
   <si>
     <t xml:space="preserve">1.31462025642395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30992269515991</t>
+    <t xml:space="preserve">1.3099228143692</t>
   </si>
   <si>
     <t xml:space="preserve">1.31059372425079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3220020532608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146296977997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3045539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35555529594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018682479858</t>
+    <t xml:space="preserve">1.32200193405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146285057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30455410480499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35555517673492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018670558929</t>
   </si>
   <si>
     <t xml:space="preserve">1.35689735412598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34481823444366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3407918214798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32669937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32602834701538</t>
+    <t xml:space="preserve">1.34481799602509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34079146385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32669949531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32602822780609</t>
   </si>
   <si>
     <t xml:space="preserve">1.30388307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30925166606903</t>
+    <t xml:space="preserve">1.30925142765045</t>
   </si>
   <si>
     <t xml:space="preserve">1.29650139808655</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">1.3287125825882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31864631175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031900882721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239789009094</t>
+    <t xml:space="preserve">1.31864643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031888961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239765167236</t>
   </si>
   <si>
     <t xml:space="preserve">1.3743451833725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44010984897614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43876767158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4508467912674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.448162317276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48976862430573</t>
+    <t xml:space="preserve">1.44010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43876755237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45084667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44816243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48976898193359</t>
   </si>
   <si>
     <t xml:space="preserve">1.46158385276794</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">1.4602415561676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50721633434296</t>
+    <t xml:space="preserve">1.50721621513367</t>
   </si>
   <si>
     <t xml:space="preserve">1.50453221797943</t>
@@ -977,136 +977,136 @@
     <t xml:space="preserve">1.53540110588074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51929521560669</t>
+    <t xml:space="preserve">1.51929533481598</t>
   </si>
   <si>
     <t xml:space="preserve">1.50050556659698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50587427616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45755732059479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48037362098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44547820091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950473308563</t>
+    <t xml:space="preserve">1.5058741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829438209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4575572013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48037350177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4454779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950461387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.45621538162231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45889973640442</t>
+    <t xml:space="preserve">1.45889949798584</t>
   </si>
   <si>
     <t xml:space="preserve">1.44279408454895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57566499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290402412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129735946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727118492126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411401748657</t>
+    <t xml:space="preserve">1.57566511631012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290354728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129759788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640229701996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042870998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727130413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411425590515</t>
   </si>
   <si>
     <t xml:space="preserve">1.60787630081177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61458683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713900089264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995530128479</t>
+    <t xml:space="preserve">1.61458706855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713959693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995601654053</t>
   </si>
   <si>
     <t xml:space="preserve">1.64277172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6535085439682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398207187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069260120392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72329950332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558802127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853614807129</t>
+    <t xml:space="preserve">1.65350902080536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398219108582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64143002033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069272041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72330009937286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987856388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853638648987</t>
   </si>
   <si>
     <t xml:space="preserve">1.70048344135284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70719408988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732615470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108819961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68572044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66693007946014</t>
+    <t xml:space="preserve">1.7071944475174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732603549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108891487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68572008609772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66693031787872</t>
   </si>
   <si>
     <t xml:space="preserve">1.66424584388733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67632508277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753543376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740336894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64679789543152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67364072799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490581035614</t>
+    <t xml:space="preserve">1.67632484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64679801464081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67364060878754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490604877472</t>
   </si>
   <si>
     <t xml:space="preserve">1.77430105209351</t>
@@ -1115,115 +1115,115 @@
     <t xml:space="preserve">1.75819528102875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74880027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73806345462799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624810695648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174864292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832734584808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161657810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564287185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7420893907547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7407478094101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7353789806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7595374584198</t>
+    <t xml:space="preserve">1.74880003929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7380633354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624798774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174888134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832758426666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161645889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416934490204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564334869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074757099152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73537909984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940587043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953722000122</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503787517548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.787721991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101181983948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188070774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79845905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261776924133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248558521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067059516907</t>
+    <t xml:space="preserve">1.78772246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101170063019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188058853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.798459649086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261788845062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248606204987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067083358765</t>
   </si>
   <si>
     <t xml:space="preserve">1.88435614109039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88703989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569760322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84543430805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79577541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598433494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793138980865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73001050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893246173859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698576450348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76222145557404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76356422901154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316767692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645738601685</t>
+    <t xml:space="preserve">1.89911925792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8870404958725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569843769073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7957751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7259840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793162822723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73001062870026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7689323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698504924774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76222169399261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76356375217438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645726680756</t>
   </si>
   <si>
     <t xml:space="preserve">1.68035161495209</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">1.6951150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69243085384369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766737937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874542713165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814078807831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653424263</t>
+    <t xml:space="preserve">1.69243133068085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67766749858856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874518871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814054965973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653412342072</t>
   </si>
   <si>
     <t xml:space="preserve">1.60921859741211</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">1.5702965259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57432341575623</t>
+    <t xml:space="preserve">1.57432281970978</t>
   </si>
   <si>
     <t xml:space="preserve">1.57969152927399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55687510967255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345381259918</t>
+    <t xml:space="preserve">1.55687522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345393180847</t>
   </si>
   <si>
     <t xml:space="preserve">1.51392710208893</t>
@@ -1274,184 +1274,184 @@
     <t xml:space="preserve">1.67229878902435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6682722568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148463249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611604213715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71390473842621</t>
+    <t xml:space="preserve">1.66827261447906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148451328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611639976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390497684479</t>
   </si>
   <si>
     <t xml:space="preserve">1.72195756435394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71658909320831</t>
+    <t xml:space="preserve">1.71658933162689</t>
   </si>
   <si>
     <t xml:space="preserve">1.63606107234955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6038498878479</t>
+    <t xml:space="preserve">1.60385024547577</t>
   </si>
   <si>
     <t xml:space="preserve">1.58371782302856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197992801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54613816738129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5488224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54748046398163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53271675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895470619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076957702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.542111992836</t>
+    <t xml:space="preserve">1.53674352169037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197968959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54613828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54882252216339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54748022556305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53271687030792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895422935486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076969623566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211187362671</t>
   </si>
   <si>
     <t xml:space="preserve">1.52869057655334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5676121711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955970287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600622177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774411678314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190247535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519206523895</t>
+    <t xml:space="preserve">1.56761252880096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600610256195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774435520172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190283298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519182682037</t>
   </si>
   <si>
     <t xml:space="preserve">1.61324489116669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56627023220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782156944275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661109924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5031898021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990056991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266154289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48171579837799</t>
+    <t xml:space="preserve">1.56627011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782168865204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661133766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50319015979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49647927284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990080833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48171555995941</t>
   </si>
   <si>
     <t xml:space="preserve">1.46292591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46695256233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48440003395081</t>
+    <t xml:space="preserve">1.46695232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305821418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439991474152</t>
   </si>
   <si>
     <t xml:space="preserve">1.52332210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53405892848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662522792816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5683708190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947949409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884317398071</t>
+    <t xml:space="preserve">1.53405916690826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662498950958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56837069988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947961330414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884281635284</t>
   </si>
   <si>
     <t xml:space="preserve">1.5160915851593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49958276748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56286752223969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57387375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55186128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52159464359283</t>
+    <t xml:space="preserve">1.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56286764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57387351989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55186152458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52159440517426</t>
   </si>
   <si>
     <t xml:space="preserve">1.50095820426941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5023341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49820649623871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619462013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042456150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656382083893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42804265022278</t>
+    <t xml:space="preserve">1.50233399868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498206615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619450092316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042479991913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656405925751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42804276943207</t>
   </si>
   <si>
     <t xml:space="preserve">1.43767297267914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42391526699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46518838405609</t>
+    <t xml:space="preserve">1.42391538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4651882648468</t>
   </si>
   <si>
     <t xml:space="preserve">1.46931552886963</t>
@@ -1466,52 +1466,52 @@
     <t xml:space="preserve">1.37370002269745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40327894687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814556598663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280635356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180023670197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629729747772</t>
+    <t xml:space="preserve">1.40327882766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814580440521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180035591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629741668701</t>
   </si>
   <si>
     <t xml:space="preserve">1.45143055915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41566109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.418412566185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.396399974823</t>
+    <t xml:space="preserve">1.4156608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555794239044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904864788055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941868305206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41841220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39640009403229</t>
   </si>
   <si>
     <t xml:space="preserve">1.36613321304321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41428518295288</t>
+    <t xml:space="preserve">1.4142849445343</t>
   </si>
   <si>
     <t xml:space="preserve">1.53397643566132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4679399728775</t>
+    <t xml:space="preserve">1.46793985366821</t>
   </si>
   <si>
     <t xml:space="preserve">1.48032164573669</t>
@@ -1520,58 +1520,58 @@
     <t xml:space="preserve">1.48169732093811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47069156169891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48720061779022</t>
+    <t xml:space="preserve">1.47069132328033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48720049858093</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683082103729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50508546829224</t>
+    <t xml:space="preserve">1.50508522987366</t>
   </si>
   <si>
     <t xml:space="preserve">1.54085528850555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53122496604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223120212555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5491099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54773414134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5326007604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900701999664</t>
+    <t xml:space="preserve">1.53122508525848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223108291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54910981655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54773426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53260087966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900690078735</t>
   </si>
   <si>
     <t xml:space="preserve">1.57112205028534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56561899185181</t>
+    <t xml:space="preserve">1.56561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">1.51746726036072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52984917163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810369968414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461275577545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672814369202</t>
+    <t xml:space="preserve">1.5298490524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810358047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461299419403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672802448273</t>
   </si>
   <si>
     <t xml:space="preserve">1.45830929279327</t>
@@ -1583,70 +1583,70 @@
     <t xml:space="preserve">1.40878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38539397716522</t>
+    <t xml:space="preserve">1.38539409637451</t>
   </si>
   <si>
     <t xml:space="preserve">1.37851524353027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37576377391815</t>
+    <t xml:space="preserve">1.37576365470886</t>
   </si>
   <si>
     <t xml:space="preserve">1.36406970024109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39364862442017</t>
+    <t xml:space="preserve">1.39364850521088</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36888492107391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26570248603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28289973735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909063339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2966570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33724224567413</t>
+    <t xml:space="preserve">1.3688850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073318958282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2657026052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2828996181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909051418304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29665720462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33724236488342</t>
   </si>
   <si>
     <t xml:space="preserve">1.34343314170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33105146884918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36200618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37989091873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38264226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089715480804</t>
+    <t xml:space="preserve">1.33105134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36200606822968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37989115715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38264238834381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089691638947</t>
   </si>
   <si>
     <t xml:space="preserve">1.41978812217712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42666697502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43216979503632</t>
+    <t xml:space="preserve">1.42666685581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4321700334549</t>
   </si>
   <si>
     <t xml:space="preserve">1.43079423904419</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">1.43492150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41153359413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581517219543</t>
+    <t xml:space="preserve">1.41153347492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581529140472</t>
   </si>
   <si>
     <t xml:space="preserve">1.37301206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35719084739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692396640778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565108776093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771483898163</t>
+    <t xml:space="preserve">1.35719096660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692408561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565096855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528152942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771471977234</t>
   </si>
   <si>
     <t xml:space="preserve">1.24506604671478</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">1.22924494743347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25951147079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2278687953949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130834102631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18315660953522</t>
+    <t xml:space="preserve">1.25951159000397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22786915302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2313084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18315672874451</t>
   </si>
   <si>
     <t xml:space="preserve">1.19553864002228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19003534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025094509125</t>
+    <t xml:space="preserve">1.19003558158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025070667267</t>
   </si>
   <si>
     <t xml:space="preserve">1.3338029384613</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">1.30009651184082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29940891265869</t>
+    <t xml:space="preserve">1.2994087934494</t>
   </si>
   <si>
     <t xml:space="preserve">1.28496325016022</t>
@@ -1721,25 +1721,25 @@
     <t xml:space="preserve">1.3007847070694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29253005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26776611804962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28221166133881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051770687103</t>
+    <t xml:space="preserve">1.29252994060516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2677663564682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088738441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051782608032</t>
   </si>
   <si>
     <t xml:space="preserve">1.23818719387054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25882375240326</t>
+    <t xml:space="preserve">1.25882351398468</t>
   </si>
   <si>
     <t xml:space="preserve">1.26363897323608</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">1.21204769611359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21411156654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18522024154663</t>
+    <t xml:space="preserve">1.21411144733429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1852205991745</t>
   </si>
   <si>
     <t xml:space="preserve">1.18797183036804</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">1.20172953605652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19347512722015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19966602325439</t>
+    <t xml:space="preserve">1.19347488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19966566562653</t>
   </si>
   <si>
     <t xml:space="preserve">1.20104169845581</t>
@@ -1778,106 +1778,106 @@
     <t xml:space="preserve">1.27808439731598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28083574771881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28152394294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676000118256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23612368106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792043209076</t>
+    <t xml:space="preserve">1.28083598613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2815238237381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676035881042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792055130005</t>
   </si>
   <si>
     <t xml:space="preserve">1.21273565292358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20379304885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19209921360016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.215487241745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29046642780304</t>
+    <t xml:space="preserve">1.20379340648651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19209933280945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548700332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29046630859375</t>
   </si>
   <si>
     <t xml:space="preserve">1.2794600725174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25056910514832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326941490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136950969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3021605014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32417237758636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32554817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33930611610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34756052494049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33173930644989</t>
+    <t xml:space="preserve">1.2505692243576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326929569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30216038227081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32417261600494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32554829120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3475604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33173894882202</t>
   </si>
   <si>
     <t xml:space="preserve">1.31110274791718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31523001194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3489363193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063039302826</t>
+    <t xml:space="preserve">1.31523013114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34893620014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063027381897</t>
   </si>
   <si>
     <t xml:space="preserve">1.3812667131424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38401830196381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422377586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480893611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34687280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35512745380402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787868499756</t>
+    <t xml:space="preserve">1.38401818275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623589038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480881690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34687256813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35512733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957275867462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787856578827</t>
   </si>
   <si>
     <t xml:space="preserve">1.33793008327484</t>
@@ -1889,46 +1889,46 @@
     <t xml:space="preserve">1.48307311534882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55323708057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958856344223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128565788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59038293361664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276484489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59863746166229</t>
+    <t xml:space="preserve">1.55323719978333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59588587284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128613471985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276460647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.598637342453</t>
   </si>
   <si>
     <t xml:space="preserve">1.57937669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56424331665039</t>
+    <t xml:space="preserve">1.56424307823181</t>
   </si>
   <si>
     <t xml:space="preserve">1.52572178840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50921261310577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51334011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058864593506</t>
+    <t xml:space="preserve">1.50921273231506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334023475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058840751648</t>
   </si>
   <si>
     <t xml:space="preserve">1.49545514583588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59726166725159</t>
+    <t xml:space="preserve">1.59726178646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.600013256073</t>
@@ -1937,187 +1937,187 @@
     <t xml:space="preserve">1.62340104579926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71007418632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77611088752747</t>
+    <t xml:space="preserve">1.71007430553436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77611112594604</t>
   </si>
   <si>
     <t xml:space="preserve">1.79949867725372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78436553478241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151476383209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719257354736</t>
+    <t xml:space="preserve">1.78436529636383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847675800323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7743889093399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151524066925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719269275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.76726269721985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75301074981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728631019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420048236847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403638362885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8955317735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572008132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434168338776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018371105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597875118256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7373331785202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73590803146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579068183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013672351837</t>
+    <t xml:space="preserve">1.75301051139832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153861522675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7572865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595573425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420107841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403602600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89553213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572031974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7629873752594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018347263336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597863197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73733365535736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7359082698822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7857905626297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7601363658905</t>
   </si>
   <si>
     <t xml:space="preserve">1.80004286766052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79006659984589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422433376312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137380123138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723944187164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73020732402802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310460567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588513374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289304256439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564960002899</t>
+    <t xml:space="preserve">1.7900664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422445297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137392044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723932266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016045570374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73020768165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289328098297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564971923828</t>
   </si>
   <si>
     <t xml:space="preserve">1.83282268047333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78294026851654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8014680147171</t>
+    <t xml:space="preserve">1.78294050693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146813392639</t>
   </si>
   <si>
     <t xml:space="preserve">1.81001925468445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82854700088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83994877338409</t>
+    <t xml:space="preserve">1.82854676246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83994889259338</t>
   </si>
   <si>
     <t xml:space="preserve">1.87415361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413035869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265762805939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562586784363</t>
+    <t xml:space="preserve">1.86560237407684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88413047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265786647797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562610626221</t>
   </si>
   <si>
     <t xml:space="preserve">1.86417710781097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88555538654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9539657831192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95681595802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94398891925812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87842929363251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700390815735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990190505981</t>
+    <t xml:space="preserve">1.88555574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396554470062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116247653961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95681607723236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94398939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8784294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700426578522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990142822266</t>
   </si>
   <si>
     <t xml:space="preserve">1.90978407859802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8941068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130320072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524972915649</t>
+    <t xml:space="preserve">1.89410722255707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87130343914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524996757507</t>
   </si>
   <si>
     <t xml:space="preserve">1.89268159866333</t>
@@ -2129,151 +2129,151 @@
     <t xml:space="preserve">2.00954866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95111525058746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971335887909</t>
+    <t xml:space="preserve">1.95111536979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9397132396698</t>
   </si>
   <si>
     <t xml:space="preserve">1.97819411754608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98532032966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714510917664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279894828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83139741420746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94968974590302</t>
+    <t xml:space="preserve">1.9853208065033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81714534759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279918670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83139717578888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969022274017</t>
   </si>
   <si>
     <t xml:space="preserve">1.97106826305389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517889022827</t>
+    <t xml:space="preserve">2.04517936706543</t>
   </si>
   <si>
     <t xml:space="preserve">2.00669836997986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672174453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957239627838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648656845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09363627433777</t>
+    <t xml:space="preserve">2.0309271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672186374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09363651275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.06655764579773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0736837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06228184700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394217014313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831170558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9012326002121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695703983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973673343658</t>
+    <t xml:space="preserve">2.07368350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06228137016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394228935242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831206321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123283863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695727825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973732948303</t>
   </si>
   <si>
     <t xml:space="preserve">1.91691017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91263473033905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89125645160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835881233215</t>
+    <t xml:space="preserve">1.91263449192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89125657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.99717044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94335007667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971487045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96371471881866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389650344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95062279701233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9098938703537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389359951019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462228775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680278301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952994346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9491685628891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953296661377</t>
+    <t xml:space="preserve">1.9433501958847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971475124359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9637143611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389686107635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95062303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989422798157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389371871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462264537811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680302143097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952970504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916868209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880427837372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953320503235</t>
   </si>
   <si>
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735259056091</t>
+    <t xml:space="preserve">2.00735235214233</t>
   </si>
   <si>
     <t xml:space="preserve">2.01026153564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98553371429443</t>
+    <t xml:space="preserve">1.98553359508514</t>
   </si>
   <si>
     <t xml:space="preserve">2.00880718231201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02189874649048</t>
+    <t xml:space="preserve">2.02189826965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.02917170524597</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">2.03062605857849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208088874817</t>
+    <t xml:space="preserve">2.03208065032959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">2.10044741630554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09608316421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881370544434</t>
+    <t xml:space="preserve">2.09608364105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881394386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.08444666862488</t>
@@ -2303,52 +2303,52 @@
     <t xml:space="preserve">2.09753799438477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08008241653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863458633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24736189842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18917798995972</t>
+    <t xml:space="preserve">2.08008313179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462904930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863482475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1891782283783</t>
   </si>
   <si>
     <t xml:space="preserve">2.16590428352356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09899234771729</t>
+    <t xml:space="preserve">2.09899258613586</t>
   </si>
   <si>
     <t xml:space="preserve">2.06844615936279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07717347145081</t>
+    <t xml:space="preserve">2.07717370986938</t>
   </si>
   <si>
     <t xml:space="preserve">2.07280969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12808465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499309539795</t>
+    <t xml:space="preserve">2.128084897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499357223511</t>
   </si>
   <si>
     <t xml:space="preserve">2.14553999900818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1469943523407</t>
+    <t xml:space="preserve">2.14699459075928</t>
   </si>
   <si>
     <t xml:space="preserve">2.13390302658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13099408149719</t>
+    <t xml:space="preserve">2.13099384307861</t>
   </si>
   <si>
     <t xml:space="preserve">2.08299207687378</t>
@@ -2357,112 +2357,112 @@
     <t xml:space="preserve">2.07426428794861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0582640171051</t>
+    <t xml:space="preserve">2.05826330184937</t>
   </si>
   <si>
     <t xml:space="preserve">2.04808115959167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335333824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771711349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06408214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04226326942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99426162242889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789877891541</t>
+    <t xml:space="preserve">2.02335286140442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771735191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0640823841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04226350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99426102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789925575256</t>
   </si>
   <si>
     <t xml:space="preserve">2.03644466400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517197608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589776039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862492084503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935070514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080553531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280619621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0611732006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06990027427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04080843925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03353571891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96807813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134893894196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098465442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553033351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79352581501007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079877376556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81970870494843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552707195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516254901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8328001499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898315906525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8517097234726</t>
+    <t xml:space="preserve">2.04517245292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02626276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826039791107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080565452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280631542206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06117296218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06990051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04080867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03353548049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96807837486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91134858131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643826007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.890984416008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553021430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370795726776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79352617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079901218414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81970918178558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152817726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8255273103714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516302585602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83280050754547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898292064667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85170996189117</t>
   </si>
   <si>
     <t xml:space="preserve">1.84298241138458</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">1.85752844810486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83570921421051</t>
+    <t xml:space="preserve">1.8357093334198</t>
   </si>
   <si>
     <t xml:space="preserve">1.84880077838898</t>
@@ -2480,79 +2480,79 @@
     <t xml:space="preserve">1.87061989307404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79788947105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460983753204</t>
+    <t xml:space="preserve">1.79788959026337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460995674133</t>
   </si>
   <si>
     <t xml:space="preserve">1.59860897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68152177333832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751902103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388079166412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351626873016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56224405765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62770092487335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733337879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842368602753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278268814087</t>
+    <t xml:space="preserve">1.68152117729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56224381923676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62770116329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52733361721039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278280735016</t>
   </si>
   <si>
     <t xml:space="preserve">1.36441802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35569024085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19277477264404</t>
+    <t xml:space="preserve">1.35569036006927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19277465343475</t>
   </si>
   <si>
     <t xml:space="preserve">1.21241188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16150069236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15931880474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13386332988739</t>
+    <t xml:space="preserve">1.16150093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1593189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13386344909668</t>
   </si>
   <si>
     <t xml:space="preserve">1.10768032073975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11422634124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18041062355042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968308925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19713830947876</t>
+    <t xml:space="preserve">1.11422610282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08440697193146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1804107427597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968344688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19713866710663</t>
   </si>
   <si>
     <t xml:space="preserve">1.11204421520233</t>
@@ -2564,28 +2564,28 @@
     <t xml:space="preserve">1.18550181388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10549855232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09022533893585</t>
+    <t xml:space="preserve">1.10549867153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09022498130798</t>
   </si>
   <si>
     <t xml:space="preserve">1.04149603843689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07640647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24514055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641312122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077502727509</t>
+    <t xml:space="preserve">1.07640659809113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059451580048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24514067173004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20077526569366</t>
   </si>
   <si>
     <t xml:space="preserve">1.22186672687531</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">1.24223113059998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36005425453186</t>
+    <t xml:space="preserve">1.36005413532257</t>
   </si>
   <si>
     <t xml:space="preserve">1.41023802757263</t>
@@ -2603,127 +2603,127 @@
     <t xml:space="preserve">1.47351312637329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58939063549042</t>
+    <t xml:space="preserve">1.589390873909</t>
   </si>
   <si>
     <t xml:space="preserve">1.55649638175964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61331379413605</t>
+    <t xml:space="preserve">1.61331355571747</t>
   </si>
   <si>
     <t xml:space="preserve">1.5624772310257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49967908859253</t>
+    <t xml:space="preserve">1.49967896938324</t>
   </si>
   <si>
     <t xml:space="preserve">1.4608039855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4757559299469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500836849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284745693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5206116437912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48397970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473413467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931597232819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46005642414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44884252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49519348144531</t>
+    <t xml:space="preserve">1.47575616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500860691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284757614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48397958278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192912101746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473437309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931609153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46005630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44884264469147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762850761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4951936006546</t>
   </si>
   <si>
     <t xml:space="preserve">1.56546771526337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60733330249786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228500843048</t>
+    <t xml:space="preserve">1.60733318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228488922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.64321768283844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71498703956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807339668274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471316337585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479493618011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535702705383</t>
+    <t xml:space="preserve">1.71498680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807363510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7747950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535726547241</t>
   </si>
   <si>
     <t xml:space="preserve">1.67760717868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65069353580475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5849050283432</t>
+    <t xml:space="preserve">1.65069329738617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58490490913391</t>
   </si>
   <si>
     <t xml:space="preserve">1.59686660766602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62976121902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125622272491</t>
+    <t xml:space="preserve">1.62976098060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125598430634</t>
   </si>
   <si>
     <t xml:space="preserve">1.60583782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62527549266815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58341002464294</t>
+    <t xml:space="preserve">1.62527537345886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58340990543365</t>
   </si>
   <si>
     <t xml:space="preserve">1.59238123893738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60135197639465</t>
+    <t xml:space="preserve">1.60135209560394</t>
   </si>
   <si>
     <t xml:space="preserve">1.64172267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71050143241882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797740459442</t>
+    <t xml:space="preserve">1.71050155162811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.717977643013</t>
   </si>
   <si>
     <t xml:space="preserve">1.7060159444809</t>
@@ -2732,304 +2732,304 @@
     <t xml:space="preserve">1.70003497600555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67013120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956851959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788129329681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72545349597931</t>
+    <t xml:space="preserve">1.67013096809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956863880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74788105487823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545337677002</t>
   </si>
   <si>
     <t xml:space="preserve">1.7807754278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84656417369843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800213098526</t>
+    <t xml:space="preserve">1.84656393527985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80021297931671</t>
   </si>
   <si>
     <t xml:space="preserve">1.78675639629364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85404026508331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002087593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871785640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310687541962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423224925995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292946815491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7688136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161222934723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104978084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609783649445</t>
+    <t xml:space="preserve">1.85403978824615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002051830292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871797561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310735225677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423213005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292934894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161234855652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104954242706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264053821564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609759807587</t>
   </si>
   <si>
     <t xml:space="preserve">1.85852563381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89291501045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786731243134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039122104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141952991486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992488384247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487635135651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543903827667</t>
+    <t xml:space="preserve">1.89291524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786719322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039086341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89142000675201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992476463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487694740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543915748596</t>
   </si>
   <si>
     <t xml:space="preserve">1.83011698722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79124176502228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553514957428</t>
+    <t xml:space="preserve">1.79124200344086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553503036499</t>
   </si>
   <si>
     <t xml:space="preserve">1.81666028499603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8076890707016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928018569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460223674774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170857906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84805881977081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84506893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646758556366</t>
+    <t xml:space="preserve">1.80768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460247516632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170845985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84805929660797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84506869316101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646818161011</t>
   </si>
   <si>
     <t xml:space="preserve">1.84058320522308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83908784389496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82862186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778506278992</t>
+    <t xml:space="preserve">1.83908808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82862174510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778518199921</t>
   </si>
   <si>
     <t xml:space="preserve">1.71947252750397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7090060710907</t>
+    <t xml:space="preserve">1.70900619029999</t>
   </si>
   <si>
     <t xml:space="preserve">1.71349203586578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68508303165436</t>
+    <t xml:space="preserve">1.68508315086365</t>
   </si>
   <si>
     <t xml:space="preserve">1.68059754371643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73442423343658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395825386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8749725818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207832813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.782271027565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582360267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638605117798</t>
+    <t xml:space="preserve">1.73442447185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395777702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227078914642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638617038727</t>
   </si>
   <si>
     <t xml:space="preserve">1.75685238838196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72246289253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63424682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5176215171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836184978485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74937653541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75984287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72694849967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469834804535</t>
+    <t xml:space="preserve">1.72246277332306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6342465877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51762139797211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836220741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74937665462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75984299182892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72694838047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386202335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80469846725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.80918431282043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81965053081512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301124095917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235268115997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93926632404327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617949008942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159789085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216045856476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01345658302307</t>
+    <t xml:space="preserve">1.8196507692337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301100254059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93926584720612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159777164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216010093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056910514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01345634460449</t>
   </si>
   <si>
     <t xml:space="preserve">2.014972448349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074716567993</t>
+    <t xml:space="preserve">2.04074668884277</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710175514221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00890779495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0013267993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800465583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435924530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0104238986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03013372421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03468251228333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05136036872864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0437798500061</t>
+    <t xml:space="preserve">2.03316617012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677860736847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00890803337097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00132727622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981093406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435948371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01042366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0301342010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0346827507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681158065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05136013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04377961158752</t>
   </si>
   <si>
     <t xml:space="preserve">2.07561850547791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06803774833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05287623405457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12261962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21358919143677</t>
+    <t xml:space="preserve">2.06803822517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442566871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05287647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12261986732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21358895301819</t>
   </si>
   <si>
     <t xml:space="preserve">2.19084692001343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1620397567749</t>
+    <t xml:space="preserve">2.16203951835632</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">2.13323259353638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15597534179688</t>
+    <t xml:space="preserve">2.1559751033783</t>
   </si>
   <si>
     <t xml:space="preserve">2.18023324012756</t>
@@ -3047,25 +3047,25 @@
     <t xml:space="preserve">2.20145964622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27120280265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26362228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2484610080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21510529518127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2166211605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546117782593</t>
+    <t xml:space="preserve">2.27120327949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933081626892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26362204551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24846076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2151050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21662139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546165466309</t>
   </si>
   <si>
     <t xml:space="preserve">2.30000996589661</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">2.32275247573853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31062293052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35762405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34852743148804</t>
+    <t xml:space="preserve">2.31062316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246206283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35762357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3485267162323</t>
   </si>
   <si>
     <t xml:space="preserve">2.35913991928101</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">2.38794708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36368870735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39249563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639788627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491487503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36520457267761</t>
+    <t xml:space="preserve">2.36368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39249539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639812469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491463661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36520481109619</t>
   </si>
   <si>
     <t xml:space="preserve">2.36823701858521</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32426810264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35459136962891</t>
+    <t xml:space="preserve">2.32426857948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35459160804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.34549474716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38036608695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44101238250732</t>
+    <t xml:space="preserve">2.380366563797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410126209259</t>
   </si>
   <si>
     <t xml:space="preserve">2.36065626144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37278580665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31820368766785</t>
+    <t xml:space="preserve">2.37278604507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31820392608643</t>
   </si>
   <si>
     <t xml:space="preserve">2.40007638931274</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">2.41523790359497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41978669166565</t>
+    <t xml:space="preserve">2.41978621482849</t>
   </si>
   <si>
     <t xml:space="preserve">2.49407815933228</t>
@@ -3155,34 +3155,34 @@
     <t xml:space="preserve">2.4349479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41826987266541</t>
+    <t xml:space="preserve">2.41827011108398</t>
   </si>
   <si>
     <t xml:space="preserve">2.42888355255127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40614104270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3075909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32730054855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35610818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45314168930054</t>
+    <t xml:space="preserve">2.40614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32730102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34397840499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35610771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45314192771912</t>
   </si>
   <si>
     <t xml:space="preserve">2.51682019233704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48649764060974</t>
+    <t xml:space="preserve">2.48649740219116</t>
   </si>
   <si>
     <t xml:space="preserve">2.49862670898438</t>
@@ -3197,31 +3197,31 @@
     <t xml:space="preserve">2.54714345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56685352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327429771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61355924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52038192749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50052404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51579904556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51427173614502</t>
+    <t xml:space="preserve">2.58959603309631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56685328483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266133308411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61355900764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52038168907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50052380561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51579928398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427149772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.49899649620056</t>
@@ -3230,49 +3230,49 @@
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286688804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109417915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553399085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48066639900208</t>
+    <t xml:space="preserve">2.53412890434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386408805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109441757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553422927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942427635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761178016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4806661605835</t>
   </si>
   <si>
     <t xml:space="preserve">2.4119291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38443374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262101173401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46691918373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43025875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928144454956</t>
+    <t xml:space="preserve">2.38443350791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262148857117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46691942214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775389671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43025898933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928168296814</t>
   </si>
   <si>
     <t xml:space="preserve">2.44706177711487</t>
@@ -3281,31 +3281,31 @@
     <t xml:space="preserve">2.43331408500671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45622682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50816178321838</t>
+    <t xml:space="preserve">2.45622658729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48372149467468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50816130638123</t>
   </si>
   <si>
     <t xml:space="preserve">2.54023933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65938472747803</t>
+    <t xml:space="preserve">2.65938520431519</t>
   </si>
   <si>
     <t xml:space="preserve">2.64869213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63799905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67618727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61814212799072</t>
+    <t xml:space="preserve">2.63799953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67618703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61814188957214</t>
   </si>
   <si>
     <t xml:space="preserve">2.60439491271973</t>
@@ -3326,25 +3326,25 @@
     <t xml:space="preserve">2.63952708244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61966943740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59370136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54634952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53565645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885461807251</t>
+    <t xml:space="preserve">2.61966967582703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59370183944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54634928703308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53565669059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885414123535</t>
   </si>
   <si>
     <t xml:space="preserve">2.54482173919678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53260183334351</t>
+    <t xml:space="preserve">2.53260159492493</t>
   </si>
   <si>
     <t xml:space="preserve">2.50663423538208</t>
@@ -3353,28 +3353,28 @@
     <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54329371452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997404098511</t>
+    <t xml:space="preserve">2.54329419136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997380256653</t>
   </si>
   <si>
     <t xml:space="preserve">2.4913592338562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48830389976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48219418525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40734624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4104015827179</t>
+    <t xml:space="preserve">2.48830413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40734648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41040134429932</t>
   </si>
   <si>
     <t xml:space="preserve">2.38290619850159</t>
@@ -3383,22 +3383,22 @@
     <t xml:space="preserve">2.48524880409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4424786567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47455668449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801918983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48983192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52649211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52496409416199</t>
+    <t xml:space="preserve">2.44247889518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47455644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4898316860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52649188041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52496433258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.55856895446777</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">2.54787683486938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56162476539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52954626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732683181763</t>
+    <t xml:space="preserve">2.56162452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52954649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732659339905</t>
   </si>
   <si>
     <t xml:space="preserve">2.4516441822052</t>
@@ -3434,22 +3434,22 @@
     <t xml:space="preserve">2.4501166343689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42720365524292</t>
+    <t xml:space="preserve">2.4272038936615</t>
   </si>
   <si>
     <t xml:space="preserve">2.40581893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39818120002747</t>
+    <t xml:space="preserve">2.50510668754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
     <t xml:space="preserve">2.38596129417419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901591300964</t>
+    <t xml:space="preserve">2.38901615142822</t>
   </si>
   <si>
     <t xml:space="preserve">2.37221360206604</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37355303764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36727404594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42535662651062</t>
+    <t xml:space="preserve">2.37355351448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36727380752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42535710334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.43791508674622</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">2.40965867042542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35157561302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35000610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34372687339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34058737754822</t>
+    <t xml:space="preserve">2.35157608985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35000586509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34372711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34058713912964</t>
   </si>
   <si>
     <t xml:space="preserve">2.33116817474365</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">2.35471510887146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34686613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39396047592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41593790054321</t>
+    <t xml:space="preserve">2.34686636924744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39396071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.44733428955078</t>
@@ -3509,37 +3509,37 @@
     <t xml:space="preserve">2.43948531150818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4740207195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105505943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45675349235535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46931171417236</t>
+    <t xml:space="preserve">2.47402119636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44105458259583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45675301551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46931195259094</t>
   </si>
   <si>
     <t xml:space="preserve">2.46774172782898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48814940452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50384712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45047378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27622532844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26837587356567</t>
+    <t xml:space="preserve">2.48814916610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50384759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45047354698181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27622485160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26837563514709</t>
   </si>
   <si>
     <t xml:space="preserve">2.25581741333008</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">2.25738716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31547045707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29977226257324</t>
+    <t xml:space="preserve">2.31546998023987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29977202415466</t>
   </si>
   <si>
     <t xml:space="preserve">2.29192328453064</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">2.27151560783386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36256432533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31076097488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32017970085144</t>
+    <t xml:space="preserve">2.36256456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31076073646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32017946243286</t>
   </si>
   <si>
     <t xml:space="preserve">2.26994585990906</t>
@@ -3575,16 +3575,16 @@
     <t xml:space="preserve">2.22913026809692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22442126274109</t>
+    <t xml:space="preserve">2.22442102432251</t>
   </si>
   <si>
     <t xml:space="preserve">2.24639844894409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15064001083374</t>
+    <t xml:space="preserve">2.20244383811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15064024925232</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005897521973</t>
@@ -3602,64 +3602,64 @@
     <t xml:space="preserve">2.16319847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17732667922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18674540519714</t>
+    <t xml:space="preserve">2.17732691764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18674564361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.18203639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1663384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15534949302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14750027656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584894657135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814179420471</t>
+    <t xml:space="preserve">2.16633796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15534925460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14750051498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15848922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814203262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.21186280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23070025444031</t>
+    <t xml:space="preserve">2.23070049285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.21657204627991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2275607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26366639137268</t>
+    <t xml:space="preserve">2.22756099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2636661529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.31860971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29349279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24796843528748</t>
+    <t xml:space="preserve">2.29349255561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24796867370605</t>
   </si>
   <si>
     <t xml:space="preserve">2.2354097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24011969566345</t>
+    <t xml:space="preserve">2.24011921882629</t>
   </si>
   <si>
     <t xml:space="preserve">2.24482846260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26052665710449</t>
+    <t xml:space="preserve">2.26052689552307</t>
   </si>
   <si>
     <t xml:space="preserve">2.30291152000427</t>
@@ -3668,76 +3668,76 @@
     <t xml:space="preserve">2.34529662132263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28407430648804</t>
+    <t xml:space="preserve">2.28407382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.11924386024475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087385177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18831562995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22128129005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23697924613953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19930386543274</t>
+    <t xml:space="preserve">2.2008740901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18831539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22128176689148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23227024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23697948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19930458068848</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599101066589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27936434745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16476845741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03447437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09255743026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05802130699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441377162933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01092720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92615711688995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057227611542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592339515686</t>
+    <t xml:space="preserve">2.27936410903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1647686958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03447389602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09255695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9795309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441365242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01092672348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92615723609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766697883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">1.82254981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86807405948639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045916080475</t>
+    <t xml:space="preserve">1.86807429790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045892238617</t>
   </si>
   <si>
     <t xml:space="preserve">1.91202878952026</t>
@@ -3746,73 +3746,73 @@
     <t xml:space="preserve">2.009357213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9936591386795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796082496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0172061920166</t>
+    <t xml:space="preserve">1.99365890026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9779611825943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877617835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01720643043518</t>
   </si>
   <si>
     <t xml:space="preserve">1.99208915233612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98894965648651</t>
+    <t xml:space="preserve">1.98894953727722</t>
   </si>
   <si>
     <t xml:space="preserve">1.9967987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05959105491638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406645774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854174137115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639119625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650431156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91516864299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92301785945892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790070056915</t>
+    <t xml:space="preserve">2.05959129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249670982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639095783234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220274448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650454998016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91516852378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92301762104034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790081977844</t>
   </si>
   <si>
     <t xml:space="preserve">1.89947044849396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92124783992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576598167419</t>
+    <t xml:space="preserve">1.92124760150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576610088348</t>
   </si>
   <si>
     <t xml:space="preserve">2.01642298698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96964204311371</t>
+    <t xml:space="preserve">2.01158356666565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964192390442</t>
   </si>
   <si>
     <t xml:space="preserve">1.93092668056488</t>
@@ -3821,172 +3821,172 @@
     <t xml:space="preserve">1.89543771743774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87608003616333</t>
+    <t xml:space="preserve">1.87607991695404</t>
   </si>
   <si>
     <t xml:space="preserve">1.92770040035248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91156899929047</t>
+    <t xml:space="preserve">1.91156888008118</t>
   </si>
   <si>
     <t xml:space="preserve">1.90189003944397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89221155643463</t>
+    <t xml:space="preserve">1.89221131801605</t>
   </si>
   <si>
     <t xml:space="preserve">1.84704327583313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82607233524323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77122604846954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79703617095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81316757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672981739044</t>
+    <t xml:space="preserve">1.82607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77122616767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79703593254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81316721439362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801409721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672934055328</t>
   </si>
   <si>
     <t xml:space="preserve">1.94383192062378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91963458061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382445812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802144050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93253993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479551792145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9631894826889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254692554474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02932834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9760947227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448122501373</t>
+    <t xml:space="preserve">1.91963469982147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802179813385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253970146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479527950287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96318960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254704475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02932810783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609436511993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448892593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448134422302</t>
   </si>
   <si>
     <t xml:space="preserve">1.97770738601685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99061274528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415296077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124025821686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8292989730835</t>
+    <t xml:space="preserve">1.99061298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93415319919586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124037742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82929873466492</t>
   </si>
   <si>
     <t xml:space="preserve">1.87285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86317455768585</t>
+    <t xml:space="preserve">1.88898503780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86317491531372</t>
   </si>
   <si>
     <t xml:space="preserve">1.85833537578583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84381711483002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672223567963</t>
+    <t xml:space="preserve">1.8438173532486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672235488892</t>
   </si>
   <si>
     <t xml:space="preserve">1.88253271579742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87769305706024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84865665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80187559127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81155467033386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78574419021606</t>
+    <t xml:space="preserve">1.87769329547882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84865641593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80187547206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81155443191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993371009827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78574407100677</t>
   </si>
   <si>
     <t xml:space="preserve">1.81800699234009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86962759494781</t>
+    <t xml:space="preserve">1.86962723731995</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575141429901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82768571376801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93899214267731</t>
+    <t xml:space="preserve">1.82768607139587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350317955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93899238109589</t>
   </si>
   <si>
     <t xml:space="preserve">1.95189762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99383866786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9680290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222600460052</t>
+    <t xml:space="preserve">1.99383878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99222576618195</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0744960308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05029892921448</t>
+    <t xml:space="preserve">2.07449650764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0502986907959</t>
   </si>
   <si>
     <t xml:space="preserve">2.05191206932068</t>
@@ -3995,10 +3995,10 @@
     <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01319646835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07288289070129</t>
+    <t xml:space="preserve">2.01319694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07288241386414</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546685218811</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">2.0793354511261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07610869407654</t>
+    <t xml:space="preserve">2.07610893249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.00351786613464</t>
@@ -4016,43 +4016,43 @@
     <t xml:space="preserve">2.00835728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98899984359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95512342453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932076454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89866387844086</t>
+    <t xml:space="preserve">1.98899960517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512413978577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932088375092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89866399765015</t>
   </si>
   <si>
     <t xml:space="preserve">1.91318225860596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92931342124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286832332611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480250358582</t>
+    <t xml:space="preserve">1.92931354045868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286856174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96480286121368</t>
   </si>
   <si>
     <t xml:space="preserve">1.94544494152069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83736479282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025602817535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495913028717</t>
+    <t xml:space="preserve">1.83736455440521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025614738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647287845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495901107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.81474316120148</t>
@@ -4061,31 +4061,31 @@
     <t xml:space="preserve">1.78290569782257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78458154201508</t>
+    <t xml:space="preserve">1.7845813035965</t>
   </si>
   <si>
     <t xml:space="preserve">1.79128384590149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77620267868042</t>
+    <t xml:space="preserve">1.77620303630829</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73933839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74604105949402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79798674583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966223239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333739757538</t>
+    <t xml:space="preserve">1.73933827877045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74604117870331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79798662662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966235160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
@@ -4094,88 +4094,88 @@
     <t xml:space="preserve">1.85663485527039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86166179180145</t>
+    <t xml:space="preserve">1.86166155338287</t>
   </si>
   <si>
     <t xml:space="preserve">1.87674283981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87171578407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517498016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360712051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203985691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685046672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355324745178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701256275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879639148712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9437689781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09625482559204</t>
+    <t xml:space="preserve">1.87171566486359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517521858215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360723972321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203949928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685070514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355336666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879651069641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94376921653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09625506401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.17836213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19176745414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18506503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29901003837585</t>
+    <t xml:space="preserve">2.19176721572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14819979667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16160559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18506455421448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29900979995728</t>
   </si>
   <si>
     <t xml:space="preserve">2.29230737686157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28895616531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3258204460144</t>
+    <t xml:space="preserve">2.28895592689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32582020759583</t>
   </si>
   <si>
     <t xml:space="preserve">2.33419871330261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34257745742798</t>
+    <t xml:space="preserve">2.34257698059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25711822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2939829826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30906391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3006854057312</t>
+    <t xml:space="preserve">2.25711846351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29398274421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30906414985657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30068564414978</t>
   </si>
   <si>
     <t xml:space="preserve">2.31576609611511</t>
@@ -4190,49 +4190,49 @@
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33755016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42636013031006</t>
+    <t xml:space="preserve">2.33754992485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42636036872864</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981956481934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46657633781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490025520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47998189926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4632248878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306279182434</t>
+    <t xml:space="preserve">2.46657609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4799816608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46322512626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306303024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.38614439964294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40122556686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40290069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609028816223</t>
+    <t xml:space="preserve">2.40122532844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40290117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609052658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.38279318809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295480728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35430645942688</t>
+    <t xml:space="preserve">2.41295504570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35430669784546</t>
   </si>
   <si>
     <t xml:space="preserve">2.36938786506653</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">2.36100959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3492796421051</t>
+    <t xml:space="preserve">2.34927988052368</t>
   </si>
   <si>
     <t xml:space="preserve">2.37944149971008</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">2.38782000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49171090126038</t>
+    <t xml:space="preserve">2.49171113967896</t>
   </si>
   <si>
     <t xml:space="preserve">2.45987367630005</t>
@@ -4262,22 +4262,22 @@
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776345252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64922308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77824926376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80170893669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77322268486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78160071372986</t>
+    <t xml:space="preserve">2.68776392936707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64922332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77824950218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80170869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78160095214844</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019495010376</t>
@@ -4286,16 +4286,16 @@
     <t xml:space="preserve">2.93073487281799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92905950546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90224862098694</t>
+    <t xml:space="preserve">2.92905926704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90224838256836</t>
   </si>
   <si>
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03295040130615</t>
+    <t xml:space="preserve">3.03295016288757</t>
   </si>
   <si>
     <t xml:space="preserve">3.06311202049255</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">3.1502468585968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16030073165894</t>
+    <t xml:space="preserve">3.16030097007751</t>
   </si>
   <si>
     <t xml:space="preserve">3.20554351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20219230651855</t>
+    <t xml:space="preserve">3.20219254493713</t>
   </si>
   <si>
     <t xml:space="preserve">3.1435444355011</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">3.20889472961426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18878698348999</t>
+    <t xml:space="preserve">3.18878674507141</t>
   </si>
   <si>
     <t xml:space="preserve">3.19213843345642</t>
@@ -4334,31 +4334,31 @@
     <t xml:space="preserve">3.17705750465393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29267835617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30608344078064</t>
+    <t xml:space="preserve">3.29267811775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
     <t xml:space="preserve">3.33792114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35132622718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40494751930237</t>
+    <t xml:space="preserve">3.35132646560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40494775772095</t>
   </si>
   <si>
     <t xml:space="preserve">3.25581336021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34797501564026</t>
+    <t xml:space="preserve">3.34797525405884</t>
   </si>
   <si>
     <t xml:space="preserve">3.31781315803528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39321804046631</t>
+    <t xml:space="preserve">3.39321780204773</t>
   </si>
   <si>
     <t xml:space="preserve">3.36473155021667</t>
@@ -4367,13 +4367,13 @@
     <t xml:space="preserve">3.35467767715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18543577194214</t>
+    <t xml:space="preserve">3.18543553352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24240827560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13851714134216</t>
+    <t xml:space="preserve">3.13851737976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.23235440254211</t>
@@ -4385,13 +4385,13 @@
     <t xml:space="preserve">3.1904628276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23403000831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24575996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23905682563782</t>
+    <t xml:space="preserve">3.23402976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24575924873352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2390570640564</t>
   </si>
   <si>
     <t xml:space="preserve">3.21559762954712</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">3.26419162750244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29770517349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34294819831848</t>
+    <t xml:space="preserve">3.29770541191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.294353723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3429479598999</t>
   </si>
   <si>
     <t xml:space="preserve">3.43510961532593</t>
@@ -4421,19 +4421,19 @@
     <t xml:space="preserve">3.38986682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38483953475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37143445014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619142532349</t>
+    <t xml:space="preserve">3.3848397731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981247901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36640763282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37143468856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619118690491</t>
   </si>
   <si>
     <t xml:space="preserve">3.31243968009949</t>
@@ -4445,31 +4445,31 @@
     <t xml:space="preserve">3.2178966999054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22305393218994</t>
+    <t xml:space="preserve">3.22305369377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.2041449546814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21445918083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19555044174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16976571083069</t>
+    <t xml:space="preserve">3.21445894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19555020332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16976618766785</t>
   </si>
   <si>
     <t xml:space="preserve">3.25571417808533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20070743560791</t>
+    <t xml:space="preserve">3.20070695877075</t>
   </si>
   <si>
     <t xml:space="preserve">3.12335395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05975198745728</t>
+    <t xml:space="preserve">3.05975222587585</t>
   </si>
   <si>
     <t xml:space="preserve">3.09413170814514</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">3.10616445541382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13366770744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13194870948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18867421150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22649168968201</t>
+    <t xml:space="preserve">3.13366746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13194894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18867444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22649145126343</t>
   </si>
   <si>
     <t xml:space="preserve">3.26602792739868</t>
@@ -4499,46 +4499,46 @@
     <t xml:space="preserve">3.24024343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09928822517395</t>
+    <t xml:space="preserve">3.09928870201111</t>
   </si>
   <si>
     <t xml:space="preserve">3.16117119789124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19383120536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15257620811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11991620063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09756922721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06834697723389</t>
+    <t xml:space="preserve">3.19383144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1525764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11991596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09756946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06834721565247</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14741921424866</t>
+    <t xml:space="preserve">3.14741945266724</t>
   </si>
   <si>
     <t xml:space="preserve">3.10960221290588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12507295608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18695569038391</t>
+    <t xml:space="preserve">3.12507271766663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">3.17664194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398145675659</t>
+    <t xml:space="preserve">3.14398169517517</t>
   </si>
   <si>
     <t xml:space="preserve">3.27462267875671</t>
@@ -4547,25 +4547,25 @@
     <t xml:space="preserve">3.24196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1903932094574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19898796081543</t>
+    <t xml:space="preserve">3.19039344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19898819923401</t>
   </si>
   <si>
     <t xml:space="preserve">3.15601420402527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26258993148804</t>
+    <t xml:space="preserve">3.26258969306946</t>
   </si>
   <si>
     <t xml:space="preserve">3.27290368080139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538694381714</t>
+    <t xml:space="preserve">3.12851071357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1353862285614</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
@@ -4577,37 +4577,37 @@
     <t xml:space="preserve">3.04084372520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04771947860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05631422996521</t>
+    <t xml:space="preserve">3.04771971702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05631446838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.01677823066711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0081832408905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01162147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03396797180176</t>
+    <t xml:space="preserve">3.00818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01162123680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583698272705</t>
+    <t xml:space="preserve">2.98583674430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.07350397109985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07006597518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05287671089172</t>
+    <t xml:space="preserve">3.07006621360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0528769493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.97552299499512</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">2.94458198547363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93083000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92051649093628</t>
+    <t xml:space="preserve">2.93083024024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9205162525177</t>
   </si>
   <si>
     <t xml:space="preserve">2.87582349777222</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">2.87754225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88785600662231</t>
+    <t xml:space="preserve">2.88785624504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.91020250320435</t>
@@ -4637,19 +4637,19 @@
     <t xml:space="preserve">2.95661473274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98411774635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286298751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05115723609924</t>
+    <t xml:space="preserve">2.98411798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005272865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286274909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786972999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05115747451782</t>
   </si>
   <si>
     <t xml:space="preserve">3.03053021430969</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">3.04943871498108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05459570884705</t>
+    <t xml:space="preserve">3.05459547042847</t>
   </si>
   <si>
     <t xml:space="preserve">3.08725571632385</t>
@@ -4670,40 +4670,40 @@
     <t xml:space="preserve">3.02021622657776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99615097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03912496566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06490898132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97494792938232</t>
+    <t xml:space="preserve">2.99615073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03912472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06490921974182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9749481678009</t>
   </si>
   <si>
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729724884033</t>
+    <t xml:space="preserve">3.03729748725891</t>
   </si>
   <si>
     <t xml:space="preserve">2.99276232719421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9535710811615</t>
+    <t xml:space="preserve">2.95357131958008</t>
   </si>
   <si>
     <t xml:space="preserve">2.79858899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6721088886261</t>
+    <t xml:space="preserve">2.67210936546326</t>
   </si>
   <si>
     <t xml:space="preserve">2.67923450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69526767730713</t>
+    <t xml:space="preserve">2.69526720046997</t>
   </si>
   <si>
     <t xml:space="preserve">2.67032766342163</t>
@@ -4715,16 +4715,16 @@
     <t xml:space="preserve">2.58838272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59372711181641</t>
+    <t xml:space="preserve">2.59372687339783</t>
   </si>
   <si>
     <t xml:space="preserve">2.62579250335693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58125758171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64538788795471</t>
+    <t xml:space="preserve">2.58125734329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64538812637329</t>
   </si>
   <si>
     <t xml:space="preserve">2.64004373550415</t>
@@ -4733,13 +4733,13 @@
     <t xml:space="preserve">2.60976004600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52247095108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47971701622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31939053535461</t>
+    <t xml:space="preserve">2.5224711894989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47971725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31939077377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.36570715904236</t>
@@ -4748,31 +4748,31 @@
     <t xml:space="preserve">2.32473492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28554391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33720469474792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26060438156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27663707733154</t>
+    <t xml:space="preserve">2.2855441570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3372049331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392569541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2606041431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27663683891296</t>
   </si>
   <si>
     <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38708424568176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32829761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32117223739624</t>
+    <t xml:space="preserve">2.38708400726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32829785346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32117199897766</t>
   </si>
   <si>
     <t xml:space="preserve">2.36927008628845</t>
@@ -4781,28 +4781,28 @@
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35145592689514</t>
+    <t xml:space="preserve">2.35323739051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35145616531372</t>
   </si>
   <si>
     <t xml:space="preserve">2.43161916732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40667939186096</t>
+    <t xml:space="preserve">2.40667963027954</t>
   </si>
   <si>
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955401420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42449378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34254884719849</t>
+    <t xml:space="preserve">2.39955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34254932403564</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242839813232</t>
@@ -4811,64 +4811,64 @@
     <t xml:space="preserve">2.39599108695984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37461423873901</t>
+    <t xml:space="preserve">2.37461400032043</t>
   </si>
   <si>
     <t xml:space="preserve">2.36036324501038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41380548477173</t>
+    <t xml:space="preserve">2.41380500793457</t>
   </si>
   <si>
     <t xml:space="preserve">2.51534509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49931287765503</t>
+    <t xml:space="preserve">2.49931263923645</t>
   </si>
   <si>
     <t xml:space="preserve">2.56522488594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53494095802307</t>
+    <t xml:space="preserve">2.53494071960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.52068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49753141403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50287532806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57056856155396</t>
+    <t xml:space="preserve">2.4975311756134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50287556648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57056903839111</t>
   </si>
   <si>
     <t xml:space="preserve">2.60085296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64360642433167</t>
+    <t xml:space="preserve">2.58303880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64360666275024</t>
   </si>
   <si>
     <t xml:space="preserve">2.64895081520081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65785789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65073227882385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67567205429077</t>
+    <t xml:space="preserve">2.65785813331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65073204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67567181587219</t>
   </si>
   <si>
     <t xml:space="preserve">2.65963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65251350402832</t>
+    <t xml:space="preserve">2.6525137424469</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291811943054</t>
@@ -4877,43 +4877,43 @@
     <t xml:space="preserve">2.55453634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61510419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65429472923279</t>
+    <t xml:space="preserve">2.61510443687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65429520606995</t>
   </si>
   <si>
     <t xml:space="preserve">2.60441565513611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60619711875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59550857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74336528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7166440486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68992304801941</t>
+    <t xml:space="preserve">2.60619735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59550881385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74336504936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71664428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68992328643799</t>
   </si>
   <si>
     <t xml:space="preserve">2.70773696899414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66676497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445820808411</t>
+    <t xml:space="preserve">2.66676473617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73445796966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.77721214294434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76830530166626</t>
+    <t xml:space="preserve">2.76830506324768</t>
   </si>
   <si>
     <t xml:space="preserve">2.7718677520752</t>
@@ -4925,16 +4925,16 @@
     <t xml:space="preserve">2.72911405563354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74692797660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020697593689</t>
+    <t xml:space="preserve">2.74692845344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020673751831</t>
   </si>
   <si>
     <t xml:space="preserve">2.75049114227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76117920875549</t>
+    <t xml:space="preserve">2.76117944717407</t>
   </si>
   <si>
     <t xml:space="preserve">2.78968191146851</t>
@@ -4946,16 +4946,16 @@
     <t xml:space="preserve">2.84846830368042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77008652687073</t>
+    <t xml:space="preserve">2.77008628845215</t>
   </si>
   <si>
     <t xml:space="preserve">2.81284022331238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80927753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80749583244324</t>
+    <t xml:space="preserve">2.80927729606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80749607086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.81996583938599</t>
@@ -4964,16 +4964,16 @@
     <t xml:space="preserve">2.81105852127075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78790068626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83065390586853</t>
+    <t xml:space="preserve">2.78790044784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83065414428711</t>
   </si>
   <si>
     <t xml:space="preserve">2.84312415122986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7576162815094</t>
+    <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
     <t xml:space="preserve">2.63469958305359</t>
@@ -4982,43 +4982,43 @@
     <t xml:space="preserve">2.5527548789978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54741072654724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53137803077698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54206657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55809926986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57947564125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52781534194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51178240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50821995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60263442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6115415096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988049507141</t>
+    <t xml:space="preserve">2.54741048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53137826919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5420663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55809903144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57947611808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52781510353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5117826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50821971893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60263395309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61154103279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988025665283</t>
   </si>
   <si>
     <t xml:space="preserve">2.58482027053833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5776948928833</t>
+    <t xml:space="preserve">2.57769465446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.56878757476807</t>
@@ -5027,166 +5027,166 @@
     <t xml:space="preserve">2.5866014957428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56700611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51890826225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4672474861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47081017494202</t>
+    <t xml:space="preserve">2.5670063495636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51890802383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46724724769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48684287071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48867678642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49051094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47400498390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43915987014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49417877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55469918251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51618599891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5271897315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54002737998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58587646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59871411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6152195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62438941001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67390608787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61888742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62255525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6317253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60971760749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57303857803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55103135108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60605001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5840425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5675368309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5748724937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6005482673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63355898857117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705350875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63722705841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6115517616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53085780143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54736351966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57670664787292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51802015304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48500871658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51251816749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53269171714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58037447929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59321212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64089512825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60238194465637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56386876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56020092964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54552936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56937074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58771014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61338567733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47583913803101</t>
   </si>
   <si>
     <t xml:space="preserve">2.4868426322937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48867678642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49051070213318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47400522232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43916010856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49417877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55469918251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51618599891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52718997001648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54002737998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58587622642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59871411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61521983146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6243896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67390608787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61888742446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62255525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63172507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60971760749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57303857803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5510311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60604977607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58404231071472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5675368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5748724937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60054802894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63355922698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705350875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63722705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6115517616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5308575630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54736351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57670664787292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51802015304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48500895500183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51251816749573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53269171714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58037447929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59321236610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64089488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60238218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56386876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5602011680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54552936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56937074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58771014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61338567733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47583889961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48684239387512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4795069694519</t>
+    <t xml:space="preserve">2.47950673103333</t>
   </si>
   <si>
     <t xml:space="preserve">2.45383167266846</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.5033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767281532288</t>
+    <t xml:space="preserve">2.47767305374146</t>
   </si>
   <si>
     <t xml:space="preserve">2.49234461784363</t>
@@ -5207,19 +5207,19 @@
     <t xml:space="preserve">2.46116757392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40798282623291</t>
+    <t xml:space="preserve">2.40798258781433</t>
   </si>
   <si>
     <t xml:space="preserve">2.34196043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34562802314758</t>
+    <t xml:space="preserve">2.34562826156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462452888489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33645844459534</t>
+    <t xml:space="preserve">2.33645868301392</t>
   </si>
   <si>
     <t xml:space="preserve">2.31261706352234</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">2.27777194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29611134529114</t>
+    <t xml:space="preserve">2.29611158370972</t>
   </si>
   <si>
     <t xml:space="preserve">2.28694176673889</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">2.33095669746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36763548851013</t>
+    <t xml:space="preserve">2.36763572692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.35113000869751</t>
@@ -5264,13 +5264,13 @@
     <t xml:space="preserve">2.39881277084351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4024806022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40981674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41898655891418</t>
+    <t xml:space="preserve">2.40248084068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40981650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41898632049561</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732595443726</t>
@@ -5282,7 +5282,7 @@
     <t xml:space="preserve">2.42815613746643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41531848907471</t>
+    <t xml:space="preserve">2.41531872749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.42448830604553</t>
@@ -5291,31 +5291,31 @@
     <t xml:space="preserve">2.39697909355164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39514517784119</t>
+    <t xml:space="preserve">2.39514493942261</t>
   </si>
   <si>
     <t xml:space="preserve">2.37863945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38780951499939</t>
+    <t xml:space="preserve">2.38780927658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.44099402427673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43182396888733</t>
+    <t xml:space="preserve">2.43182420730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.44466161727905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4428277015686</t>
+    <t xml:space="preserve">2.44282793998718</t>
   </si>
   <si>
     <t xml:space="preserve">2.31064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30297493934631</t>
+    <t xml:space="preserve">2.30297470092773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37008905410767</t>
@@ -5336,22 +5336,22 @@
     <t xml:space="preserve">2.43720316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38926458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43145036697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46021366119385</t>
+    <t xml:space="preserve">2.38926482200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43145060539246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46021389961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.41994524002075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41227531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40460467338562</t>
+    <t xml:space="preserve">2.41227507591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4046049118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.42569804191589</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">2.3643364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29722213745117</t>
+    <t xml:space="preserve">2.29722189903259</t>
   </si>
   <si>
     <t xml:space="preserve">2.197509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18408703804016</t>
+    <t xml:space="preserve">2.16491150856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18408679962158</t>
   </si>
   <si>
     <t xml:space="preserve">2.18792200088501</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">2.13806581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12272524833679</t>
+    <t xml:space="preserve">2.12272548675537</t>
   </si>
   <si>
     <t xml:space="preserve">2.09012699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09971499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10354971885681</t>
+    <t xml:space="preserve">2.09971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10354995727539</t>
   </si>
   <si>
     <t xml:space="preserve">2.08053946495056</t>
@@ -5441,10 +5441,10 @@
     <t xml:space="preserve">2.00767254829407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95781636238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424970149994</t>
+    <t xml:space="preserve">1.95781624317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424946308136</t>
   </si>
   <si>
     <t xml:space="preserve">1.99808490276337</t>
@@ -5474,31 +5474,31 @@
     <t xml:space="preserve">2.07095170021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08820939064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07862186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04410600662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0306830406189</t>
+    <t xml:space="preserve">2.08820962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07862162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04410576820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03068327903748</t>
   </si>
   <si>
     <t xml:space="preserve">1.97315657138824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01534271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06903386116028</t>
+    <t xml:space="preserve">2.01534247398376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06903409957886</t>
   </si>
   <si>
     <t xml:space="preserve">2.05561113357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10546731948853</t>
+    <t xml:space="preserve">2.1054675579071</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930252075195</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">2.05369353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752873420715</t>
+    <t xml:space="preserve">2.05752849578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.06136393547058</t>
@@ -5531,22 +5531,22 @@
     <t xml:space="preserve">2.03835320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02301287651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05177617073059</t>
+    <t xml:space="preserve">2.02301263809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05177640914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.05944633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643584251404</t>
+    <t xml:space="preserve">2.03643560409546</t>
   </si>
   <si>
     <t xml:space="preserve">2.07286906242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03260040283203</t>
+    <t xml:space="preserve">2.03260064125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.02876543998718</t>
@@ -5561,16 +5561,16 @@
     <t xml:space="preserve">2.09587979316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14573574066162</t>
+    <t xml:space="preserve">2.1457359790802</t>
   </si>
   <si>
     <t xml:space="preserve">2.11889028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12080788612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09204459190369</t>
+    <t xml:space="preserve">2.12080764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09204435348511</t>
   </si>
   <si>
     <t xml:space="preserve">1.85906255245209</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">1.9271354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94439351558685</t>
+    <t xml:space="preserve">1.94439363479614</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165144443512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93672323226929</t>
+    <t xml:space="preserve">1.93672311306</t>
   </si>
   <si>
     <t xml:space="preserve">1.92905306816101</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">1.87823808193207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87919688224792</t>
+    <t xml:space="preserve">1.87919676303864</t>
   </si>
   <si>
     <t xml:space="preserve">1.83029937744141</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">1.71812283992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73825693130493</t>
+    <t xml:space="preserve">1.73825705051422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75167989730835</t>
@@ -6006,6 +6006,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.98099994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96399998664856</t>
   </si>
 </sst>
 </file>
@@ -71318,7 +71321,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6912268518</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>457561</v>
@@ -71339,6 +71342,32 @@
         <v>1997</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6910648148</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>976289</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>1.98599994182587</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>1.942999958992</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>1.97800004482269</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>1.96399998664856</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="2000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847180366516</t>
+    <t xml:space="preserve">1.42847192287445</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">1.3917795419693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36014842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30827271938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158045768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23931646347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21401107311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676354885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.234255194664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831751823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009350776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18680846691132</t>
+    <t xml:space="preserve">1.36014807224274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30827283859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27158033847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23931634426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21401154994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676331043243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831763744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009338855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18680822849274</t>
   </si>
   <si>
     <t xml:space="preserve">1.11595416069031</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">1.17478847503662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15644252300262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1943998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.232990026474</t>
+    <t xml:space="preserve">1.15644216537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19439995288849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23299026489258</t>
   </si>
   <si>
     <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2209700345993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437737464905</t>
+    <t xml:space="preserve">1.22097015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437749385834</t>
   </si>
   <si>
     <t xml:space="preserve">1.16087067127228</t>
@@ -119,97 +119,97 @@
     <t xml:space="preserve">1.04699778556824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04826295375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848473548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11089324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366770744324</t>
+    <t xml:space="preserve">1.04826307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1184846162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11089301109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366782665253</t>
   </si>
   <si>
     <t xml:space="preserve">1.17795157432556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19819569587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21337866783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213572025299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578706264496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17921674251556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13872849941254</t>
+    <t xml:space="preserve">1.1981954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21337878704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17921686172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13872861862183</t>
   </si>
   <si>
     <t xml:space="preserve">1.1317697763443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15770769119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29182422161102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2994157075882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598662376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525402069092</t>
+    <t xml:space="preserve">1.15770757198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311208724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688560962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2918244600296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598626613617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525413990021</t>
   </si>
   <si>
     <t xml:space="preserve">1.27917194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25892782211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20199167728424</t>
+    <t xml:space="preserve">1.25892794132233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20199120044708</t>
   </si>
   <si>
     <t xml:space="preserve">1.22413349151611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20135891437531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19376730918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18238008022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20452201366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21464407444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554294109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264654159546</t>
+    <t xml:space="preserve">1.20135903358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19376718997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18237996101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20452189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21464383602142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19186961650848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554317951202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264666080475</t>
   </si>
   <si>
     <t xml:space="preserve">1.19123685359955</t>
@@ -227,184 +227,184 @@
     <t xml:space="preserve">1.09571003913879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07546627521515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10709726810455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12417817115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062654972076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16719686985016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15454435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227039813995</t>
+    <t xml:space="preserve">1.07546603679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10709738731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12417829036713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062666893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16719698905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15454459190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227015972137</t>
   </si>
   <si>
     <t xml:space="preserve">1.17405784130096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24820864200592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406277179718</t>
+    <t xml:space="preserve">1.24820911884308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406301021576</t>
   </si>
   <si>
     <t xml:space="preserve">1.27812945842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26837265491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918719291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138172626495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27682852745056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25731515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495685100555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031894207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1909693479538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527430057526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16690289974213</t>
+    <t xml:space="preserve">1.26837277412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918731212616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138148784637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27682876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2573150396347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031918048859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096958637238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796063423157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527441978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16690301895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.17080557346344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16755342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495144367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17340731620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18056213855743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15389406681061</t>
+    <t xml:space="preserve">1.16755330562592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495168209076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17340743541718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18056225776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15389394760132</t>
   </si>
   <si>
     <t xml:space="preserve">1.16300022602081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16950476169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649580955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16169941425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1773099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901813030243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14283621311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12852644920349</t>
+    <t xml:space="preserve">1.16950464248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649592876434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16169929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17731022834778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18901801109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14283645153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1285263299942</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103138923645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09665417671204</t>
+    <t xml:space="preserve">1.09665465354919</t>
   </si>
   <si>
     <t xml:space="preserve">1.10641121864319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11486732959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10250890254974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372476577759</t>
+    <t xml:space="preserve">1.10055756568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11486721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10250866413116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372512340546</t>
   </si>
   <si>
     <t xml:space="preserve">1.04657006263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526913166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10185837745667</t>
+    <t xml:space="preserve">1.04526925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185825824738</t>
   </si>
   <si>
     <t xml:space="preserve">1.13177871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10120785236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12917709350586</t>
+    <t xml:space="preserve">1.1012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12917697429657</t>
   </si>
   <si>
     <t xml:space="preserve">1.05307447910309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.952255189418793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485531330109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184779167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640604972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01339745521545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982826292514801</t>
+    <t xml:space="preserve">0.952255249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485650539398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01339709758759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982826173305511</t>
   </si>
   <si>
     <t xml:space="preserve">0.976321935653687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968516290187836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977622747421265</t>
+    <t xml:space="preserve">0.96851658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977622807025909</t>
   </si>
   <si>
     <t xml:space="preserve">0.975671410560608</t>
@@ -413,52 +413,52 @@
     <t xml:space="preserve">1.00364065170288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950954258441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96916663646698</t>
+    <t xml:space="preserve">0.95095431804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980874955654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467686653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166934490204</t>
   </si>
   <si>
     <t xml:space="preserve">0.971118330955505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965914666652679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.958759665489197</t>
+    <t xml:space="preserve">0.96591454744339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958760023117065</t>
   </si>
   <si>
     <t xml:space="preserve">1.05437541007996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05957901477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06608355045319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974302768707</t>
+    <t xml:space="preserve">1.05957889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06608378887177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974278926849</t>
   </si>
   <si>
     <t xml:space="preserve">1.05892872810364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06283116340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673395633698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340238571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06022953987122</t>
+    <t xml:space="preserve">1.06283152103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673407554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340250492096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06022942066193</t>
   </si>
   <si>
     <t xml:space="preserve">1.08559691905975</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">1.09275186061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11421680450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09795546531677</t>
+    <t xml:space="preserve">1.11421692371368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09795522689819</t>
   </si>
   <si>
     <t xml:space="preserve">1.07779145240784</t>
@@ -479,61 +479,61 @@
     <t xml:space="preserve">1.07388889789581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10901284217834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11746883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11876976490021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13828313350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1454381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14023458957672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1278760433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218628406525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15129208564758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16234982013702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14803993701935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438045978546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315871238708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600424766541</t>
+    <t xml:space="preserve">1.10901308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11746895313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348685741425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1187698841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13828337192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14543831348419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14023470878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12787616252899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218592643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15129220485687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16234970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14803981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299505710602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315907001495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600389003754</t>
   </si>
   <si>
     <t xml:space="preserve">1.08169424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09210157394409</t>
+    <t xml:space="preserve">1.09990680217743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210133552551</t>
   </si>
   <si>
     <t xml:space="preserve">1.10511040687561</t>
@@ -542,79 +542,79 @@
     <t xml:space="preserve">1.11356627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949983119965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584035396576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234453201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925639629364</t>
+    <t xml:space="preserve">1.08949971199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584023475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234488964081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925627708435</t>
   </si>
   <si>
     <t xml:space="preserve">1.08429610729218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07518994808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0875483751297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0745393037796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827832221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05762791633606</t>
+    <t xml:space="preserve">1.07518982887268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08754849433899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05762779712677</t>
   </si>
   <si>
     <t xml:space="preserve">1.07323861122131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933569908142</t>
+    <t xml:space="preserve">1.06933557987213</t>
   </si>
   <si>
     <t xml:space="preserve">1.05697739124298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0472207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348168849945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03421139717102</t>
+    <t xml:space="preserve">1.04722046852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03421175479889</t>
   </si>
   <si>
     <t xml:space="preserve">1.01144587993622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982176005840302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95680832862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392345905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644613742828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953556299209595</t>
+    <t xml:space="preserve">0.982175767421722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95680844783783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392286300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440949440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644375324249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95355612039566</t>
   </si>
   <si>
     <t xml:space="preserve">0.9626624584198</t>
@@ -623,31 +623,31 @@
     <t xml:space="preserve">0.956157863140106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.957458853721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507695674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986728847026825</t>
+    <t xml:space="preserve">0.957459032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507636070251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98672878742218</t>
   </si>
   <si>
     <t xml:space="preserve">0.965264141559601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940547287464142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078441143036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995835244655609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315390110016</t>
+    <t xml:space="preserve">0.940547168254852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078560352325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995835304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429105758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315402030945</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
@@ -656,46 +656,46 @@
     <t xml:space="preserve">1.03681325912476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02380454540253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02120268344879</t>
+    <t xml:space="preserve">1.02380418777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02120280265808</t>
   </si>
   <si>
     <t xml:space="preserve">1.04201686382294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04917192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770709991455</t>
+    <t xml:space="preserve">1.04917180538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770733833313</t>
   </si>
   <si>
     <t xml:space="preserve">1.04852139949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03356122970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03095960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03160989284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05502581596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03291070461273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03551232814789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01860094070435</t>
+    <t xml:space="preserve">1.03356111049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03095948696136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03161013126373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567634105682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05502593517303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03291046619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03551268577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01860105991364</t>
   </si>
   <si>
     <t xml:space="preserve">0.999087631702423</t>
@@ -713,40 +713,40 @@
     <t xml:space="preserve">1.02510547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999737918376923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534134864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029897212982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401178836823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0166494846344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404798030853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136645793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0296585559845</t>
+    <t xml:space="preserve">0.999738037586212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029837608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905714511871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01664936542511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404786109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136669635773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02965843677521</t>
   </si>
   <si>
     <t xml:space="preserve">0.991282105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00949454307556</t>
+    <t xml:space="preserve">1.00949466228485</t>
   </si>
   <si>
     <t xml:space="preserve">1.01795053482056</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">1.01469814777374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03226053714752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07063674926758</t>
+    <t xml:space="preserve">1.03226029872894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07063663005829</t>
   </si>
   <si>
     <t xml:space="preserve">1.06218099594116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09470319747925</t>
+    <t xml:space="preserve">1.09470331668854</t>
   </si>
   <si>
     <t xml:space="preserve">1.1447879076004</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">1.18251359462738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23585021495819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845231533051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633696556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983231067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21438550949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755835533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21308469772339</t>
+    <t xml:space="preserve">1.23585033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845219612122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21633684635162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983242988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21438539028168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21308493614197</t>
   </si>
   <si>
     <t xml:space="preserve">1.20072615146637</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">1.21893870830536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22023963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527946949005</t>
+    <t xml:space="preserve">1.22023952007294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527935028076</t>
   </si>
   <si>
     <t xml:space="preserve">1.18381464481354</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">1.20267748832703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18446493148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16430115699768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17600917816162</t>
+    <t xml:space="preserve">1.18446505069733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16430127620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17600905895233</t>
   </si>
   <si>
     <t xml:space="preserve">1.21999967098236</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">1.21194684505463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22268378734589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482882022858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27502727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28777754306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26697421073914</t>
+    <t xml:space="preserve">1.22268402576447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482929706573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27502715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28777766227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26697444915771</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">1.24348700046539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24415814876556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2273815870285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818432331085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422406196594</t>
+    <t xml:space="preserve">1.24415802955627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22738134860992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818444252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422394275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.27368497848511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24147391319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23006570339203</t>
+    <t xml:space="preserve">1.24147379398346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23006546497345</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831638813019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26294779777527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31462025642395</t>
+    <t xml:space="preserve">1.26294791698456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31462001800537</t>
   </si>
   <si>
     <t xml:space="preserve">1.3099228143692</t>
@@ -887,61 +887,61 @@
     <t xml:space="preserve">1.31059372425079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32200193405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146285057068</t>
+    <t xml:space="preserve">1.32200169563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146273136139</t>
   </si>
   <si>
     <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35555517673492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018670558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481799602509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34079146385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32669949531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32602822780609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30388307571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925142765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29650139808655</t>
+    <t xml:space="preserve">1.35555505752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689723491669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34079170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32669937610626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32602834701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3038831949234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29650127887726</t>
   </si>
   <si>
     <t xml:space="preserve">1.34213387966156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3287125825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300288677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031888961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239765167236</t>
+    <t xml:space="preserve">1.32871246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864655017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031865119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.3743451833725</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">1.44816243648529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48976898193359</t>
+    <t xml:space="preserve">1.48976838588715</t>
   </si>
   <si>
     <t xml:space="preserve">1.46158385276794</t>
@@ -968,232 +968,232 @@
     <t xml:space="preserve">1.4602415561676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50721621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50453221797943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540110588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51929533481598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50050556659698</t>
+    <t xml:space="preserve">1.50721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50453186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51929545402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50050580501556</t>
   </si>
   <si>
     <t xml:space="preserve">1.5058741569519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46829438209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4575572013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48037350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4454779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950461387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45621538162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45889949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279408454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566511631012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290354728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129759788513</t>
+    <t xml:space="preserve">1.46829462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45755743980408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48037374019623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44547808170319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950497150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45621514320374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45889973640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279396533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566523551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290390491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129783630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.58640229701996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59042870998383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727130413055</t>
+    <t xml:space="preserve">1.59042847156525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727142333984</t>
   </si>
   <si>
     <t xml:space="preserve">1.64411425590515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60787630081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61458706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713959693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277172088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350902080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398219108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64143002033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63069272041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72330009937286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987856388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853638648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048344135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7071944475174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732603549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108891487122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68572008609772</t>
+    <t xml:space="preserve">1.60787642002106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61458694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5971394777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995565891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350866317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6306928396225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72329998016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987832546234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558802127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853626728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70719432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732627391815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108843803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6857203245163</t>
   </si>
   <si>
     <t xml:space="preserve">1.66693031787872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66424584388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740348815918</t>
+    <t xml:space="preserve">1.66424608230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632520198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753495693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740336894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.64679801464081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67364060878754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490604877472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77430105209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75819528102875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74880003929138</t>
+    <t xml:space="preserve">1.67364096641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76490592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77430140972137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75819540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74880039691925</t>
   </si>
   <si>
     <t xml:space="preserve">1.7380633354187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72866868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624798774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174888134003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832758426666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416934490204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074757099152</t>
+    <t xml:space="preserve">1.7286684513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624810695648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174876213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832734584808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416910648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564287185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74209010601044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074804782867</t>
   </si>
   <si>
     <t xml:space="preserve">1.73537909984589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73940587043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503787517548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772246837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78101170063019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188058853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.798459649086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261788845062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248606204987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067083358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435614109039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89911925792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8870404958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569843769073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84543418884277</t>
+    <t xml:space="preserve">1.73940539360046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953757762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772222995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7810115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188070774078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261776924133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248582363129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8843560218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89911949634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88703978061676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569819927216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543430805206</t>
   </si>
   <si>
     <t xml:space="preserve">1.7957751750946</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">1.7259840965271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71793162822723</t>
+    <t xml:space="preserve">1.71793127059937</t>
   </si>
   <si>
     <t xml:space="preserve">1.73001062870026</t>
@@ -1217,91 +1217,91 @@
     <t xml:space="preserve">1.76222169399261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76356375217438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316791534424</t>
+    <t xml:space="preserve">1.76356363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316803455353</t>
   </si>
   <si>
     <t xml:space="preserve">1.69645726680756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68035161495209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6951150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69243133068085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766749858856</t>
+    <t xml:space="preserve">1.68035113811493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69511520862579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6924307346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67766761779785</t>
   </si>
   <si>
     <t xml:space="preserve">1.63874518871307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64814054965973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653412342072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921859741211</t>
+    <t xml:space="preserve">1.64814066886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653424263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921847820282</t>
   </si>
   <si>
     <t xml:space="preserve">1.5702965259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57432281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57969152927399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54345393180847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51392710208893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63203454017639</t>
+    <t xml:space="preserve">1.57432293891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57969176769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687510967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54345405101776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51392698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6320344209671</t>
   </si>
   <si>
     <t xml:space="preserve">1.67229878902435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66827261447906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148451328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611639976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71390497684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72195756435394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658933162689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606107234955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60385024547577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371782302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674352169037</t>
+    <t xml:space="preserve">1.66827237606049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148463249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611628055573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7139048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72195780277252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71658885478973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6038498878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371794223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53674364089966</t>
   </si>
   <si>
     <t xml:space="preserve">1.52197968959808</t>
@@ -1313,133 +1313,133 @@
     <t xml:space="preserve">1.54882252216339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54748022556305</t>
+    <t xml:space="preserve">1.54748010635376</t>
   </si>
   <si>
     <t xml:space="preserve">1.53271687030792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56895422935486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076969623566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211187362671</t>
+    <t xml:space="preserve">1.56895446777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076933860779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211175441742</t>
   </si>
   <si>
     <t xml:space="preserve">1.52869057655334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56761252880096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955934524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600610256195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774435520172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190283298492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519182682037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324489116669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56627011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782168865204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51661133766174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50319015979767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647927284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990080833435</t>
+    <t xml:space="preserve">1.5676121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955922603607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600598335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774447441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190259456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519194602966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56627023220062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51661109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50319004058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49647903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990056991577</t>
   </si>
   <si>
     <t xml:space="preserve">1.42266178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48171555995941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292591094971</t>
+    <t xml:space="preserve">1.48171579837799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.462926030159</t>
   </si>
   <si>
     <t xml:space="preserve">1.46695232391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48305821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48439991474152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405916690826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662498950958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56837069988251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947961330414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51884281635284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5160915851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49958229064941</t>
+    <t xml:space="preserve">1.48305797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48440003395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332186698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405869007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662510871887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56837034225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947949409485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51884305477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51609146595001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4995824098587</t>
   </si>
   <si>
     <t xml:space="preserve">1.56286764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57387351989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55186152458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52159440517426</t>
+    <t xml:space="preserve">1.57387399673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55186128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52159452438354</t>
   </si>
   <si>
     <t xml:space="preserve">1.50095820426941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50233399868011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619450092316</t>
+    <t xml:space="preserve">1.50233364105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49820685386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619426250458</t>
   </si>
   <si>
     <t xml:space="preserve">1.44042479991913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46656405925751</t>
+    <t xml:space="preserve">1.46656429767609</t>
   </si>
   <si>
     <t xml:space="preserve">1.42804276943207</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">1.43767297267914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42391538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4651882648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106123924255</t>
+    <t xml:space="preserve">1.42391526699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46518838405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931540966034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106100082397</t>
   </si>
   <si>
     <t xml:space="preserve">1.42116379737854</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">1.37370002269745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40327882766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814580440521</t>
+    <t xml:space="preserve">1.40327906608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814544677734</t>
   </si>
   <si>
     <t xml:space="preserve">1.45280647277832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44180035591125</t>
+    <t xml:space="preserve">1.44180023670197</t>
   </si>
   <si>
     <t xml:space="preserve">1.43629741668701</t>
@@ -1484,64 +1484,64 @@
     <t xml:space="preserve">1.45143055915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4156608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555794239044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904864788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42941868305206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41841220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39640009403229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36613321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4142849445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53397643566132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46793985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48032164573669</t>
+    <t xml:space="preserve">1.41566073894501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555770397186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904852867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42941856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41841232776642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39640021324158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36613345146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41428518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53397631645203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46793973445892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48032176494598</t>
   </si>
   <si>
     <t xml:space="preserve">1.48169732093811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47069132328033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48720049858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50508522987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54085528850555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53122508525848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223108291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54910981655121</t>
+    <t xml:space="preserve">1.47069144248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48720037937164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683105945587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50508546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54085540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53122496604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223120212555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5491099357605</t>
   </si>
   <si>
     <t xml:space="preserve">1.54773426055908</t>
@@ -1553,70 +1553,70 @@
     <t xml:space="preserve">1.58900690078735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57112205028534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56561923027039</t>
+    <t xml:space="preserve">1.57112216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5656191110611</t>
   </si>
   <si>
     <t xml:space="preserve">1.51746726036072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5298490524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810358047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461299419403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672802448273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45830929279327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41703641414642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878200531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38539409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37851524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37576365470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36406970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364850521088</t>
+    <t xml:space="preserve">1.52984929084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810381889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461287498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672778606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45830941200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878212451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37851512432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37576389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3640695810318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364838600159</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3688850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073318958282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2657026052475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2828996181488</t>
+    <t xml:space="preserve">1.36888492107391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073307037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26570248603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28289973735809</t>
   </si>
   <si>
     <t xml:space="preserve">1.28909051418304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29665720462799</t>
+    <t xml:space="preserve">1.29665732383728</t>
   </si>
   <si>
     <t xml:space="preserve">1.33724236488342</t>
@@ -1628,43 +1628,43 @@
     <t xml:space="preserve">1.33105134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36200606822968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37989115715027</t>
+    <t xml:space="preserve">1.36200594902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37989103794098</t>
   </si>
   <si>
     <t xml:space="preserve">1.38264238834381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39089691638947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978812217712</t>
+    <t xml:space="preserve">1.39089703559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978788375854</t>
   </si>
   <si>
     <t xml:space="preserve">1.42666685581207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4321700334549</t>
+    <t xml:space="preserve">1.43217015266418</t>
   </si>
   <si>
     <t xml:space="preserve">1.43079423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43492150306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41153347492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581529140472</t>
+    <t xml:space="preserve">1.43492138385773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41153335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581493377686</t>
   </si>
   <si>
     <t xml:space="preserve">1.37301206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35719096660614</t>
+    <t xml:space="preserve">1.35719084739685</t>
   </si>
   <si>
     <t xml:space="preserve">1.32692408561707</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">1.28565096855164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528152942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771471977234</t>
+    <t xml:space="preserve">1.29528141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771483898163</t>
   </si>
   <si>
     <t xml:space="preserve">1.24506604671478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25951159000397</t>
+    <t xml:space="preserve">1.22924470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25951170921326</t>
   </si>
   <si>
     <t xml:space="preserve">1.22786915302277</t>
@@ -1697,28 +1697,28 @@
     <t xml:space="preserve">1.18315672874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19553864002228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19003558158875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025070667267</t>
+    <t xml:space="preserve">1.19553852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19003570079803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025094509125</t>
   </si>
   <si>
     <t xml:space="preserve">1.3338029384613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30009651184082</t>
+    <t xml:space="preserve">1.30009663105011</t>
   </si>
   <si>
     <t xml:space="preserve">1.2994087934494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28496325016022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3007847070694</t>
+    <t xml:space="preserve">1.28496313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30078446865082</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252994060516</t>
@@ -1730,49 +1730,49 @@
     <t xml:space="preserve">1.2822117805481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088738441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818719387054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25882351398468</t>
+    <t xml:space="preserve">1.26088726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051770687103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818743228912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25882387161255</t>
   </si>
   <si>
     <t xml:space="preserve">1.26363897323608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2326842546463</t>
+    <t xml:space="preserve">1.23268437385559</t>
   </si>
   <si>
     <t xml:space="preserve">1.22030234336853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21204769611359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21411144733429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1852205991745</t>
+    <t xml:space="preserve">1.21204793453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.214111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18522036075592</t>
   </si>
   <si>
     <t xml:space="preserve">1.18797183036804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20172953605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19347488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19966566562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104169845581</t>
+    <t xml:space="preserve">1.20172965526581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19347512722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19966578483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2010418176651</t>
   </si>
   <si>
     <t xml:space="preserve">1.27808439731598</t>
@@ -1781,88 +1781,88 @@
     <t xml:space="preserve">1.28083598613739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2815238237381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676035881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23612380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792055130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273565292358</t>
+    <t xml:space="preserve">1.28152358531952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676000118256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23612368106842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792043209076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273577213287</t>
   </si>
   <si>
     <t xml:space="preserve">1.20379340648651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19209933280945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21548700332642</t>
+    <t xml:space="preserve">1.19209921360016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21548712253571</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2794600725174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2505692243576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326929569244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136962890625</t>
+    <t xml:space="preserve">1.27946031093597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25056898593903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326905727386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136950969696</t>
   </si>
   <si>
     <t xml:space="preserve">1.30216038227081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30353605747223</t>
+    <t xml:space="preserve">1.30353629589081</t>
   </si>
   <si>
     <t xml:space="preserve">1.32417261600494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32554829120636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33930587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3475604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33173894882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110274791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523013114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34893620014191</t>
+    <t xml:space="preserve">1.32554817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33930575847626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34756052494049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33173930644989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110262870789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523001194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3489363193512</t>
   </si>
   <si>
     <t xml:space="preserve">1.36063027381897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3812667131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38401818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623589038849</t>
+    <t xml:space="preserve">1.38126647472382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3840184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422389507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623636722565</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480881690979</t>
@@ -1871,31 +1871,31 @@
     <t xml:space="preserve">1.34687256813049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957275867462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787856578827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33793008327484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44455194473267</t>
+    <t xml:space="preserve">1.35512709617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787880420685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33793020248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44455182552338</t>
   </si>
   <si>
     <t xml:space="preserve">1.48307311534882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55323719978333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59588587284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128613471985</t>
+    <t xml:space="preserve">1.55323708057404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128601551056</t>
   </si>
   <si>
     <t xml:space="preserve">1.59038257598877</t>
@@ -1907,124 +1907,124 @@
     <t xml:space="preserve">1.598637342453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57937669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424307823181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52572178840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921273231506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51334023475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058840751648</t>
+    <t xml:space="preserve">1.57937681674957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52572190761566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921285152435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5133398771286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058888435364</t>
   </si>
   <si>
     <t xml:space="preserve">1.49545514583588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59726178646088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.600013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62340104579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007430553436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77611112594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79949867725372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78436529636383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847675800323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7743889093399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151524066925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719269275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726269721985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75301051139832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153861522675</t>
+    <t xml:space="preserve">1.59726166725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60001313686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62340116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007418632507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77611064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79949879646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78436577320099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847651958466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77438879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151512145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719221591949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726305484772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301086902618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153849601746</t>
   </si>
   <si>
     <t xml:space="preserve">1.7572865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595573425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420107841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403602600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89553213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81572031974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7629873752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018347263336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70597863197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73733365535736</t>
+    <t xml:space="preserve">1.71025431156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595513820648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420095920563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403650283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8955317735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81571996212006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434180259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298725605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70597875118256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73733353614807</t>
   </si>
   <si>
     <t xml:space="preserve">1.7359082698822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7857905626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7601363658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7900664806366</t>
+    <t xml:space="preserve">1.78579044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004274845123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79006636142731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84422445297241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84137392044067</t>
+    <t xml:space="preserve">1.84137356281281</t>
   </si>
   <si>
     <t xml:space="preserve">1.77723932266235</t>
@@ -2036,82 +2036,82 @@
     <t xml:space="preserve">1.73020768165588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71310484409332</t>
+    <t xml:space="preserve">1.71310472488403</t>
   </si>
   <si>
     <t xml:space="preserve">1.74588489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80289328098297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282268047333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78294050693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146813392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001925468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82854676246643</t>
+    <t xml:space="preserve">1.80289316177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564960002899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282244205475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146825313568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8285471200943</t>
   </si>
   <si>
     <t xml:space="preserve">1.83994889259338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87415361404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560237407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88413047790527</t>
+    <t xml:space="preserve">1.87415397167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560261249542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8841301202774</t>
   </si>
   <si>
     <t xml:space="preserve">1.90265786647797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85562610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417710781097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396554470062</t>
+    <t xml:space="preserve">1.85562574863434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555550575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396590232849</t>
   </si>
   <si>
     <t xml:space="preserve">1.93116247653961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95681607723236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94398939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8784294128418</t>
+    <t xml:space="preserve">1.95681643486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94398903846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87842965126038</t>
   </si>
   <si>
     <t xml:space="preserve">1.87700426578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978407859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410722255707</t>
+    <t xml:space="preserve">1.85990178585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9097843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410662651062</t>
   </si>
   <si>
     <t xml:space="preserve">1.87130343914032</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">2.01524996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89268159866333</t>
+    <t xml:space="preserve">1.89268136024475</t>
   </si>
   <si>
     <t xml:space="preserve">1.93543803691864</t>
@@ -2129,118 +2129,118 @@
     <t xml:space="preserve">2.00954866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95111536979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9397132396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819411754608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9853208065033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714534759521</t>
+    <t xml:space="preserve">1.95111513137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971371650696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819435596466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532092571259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8171454668045</t>
   </si>
   <si>
     <t xml:space="preserve">1.84279918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83139717578888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94969022274017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106826305389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669836997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0309271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672186374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957263469696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648704528809</t>
+    <t xml:space="preserve">1.83139741420746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94969010353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517889022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669884681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672210216522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957251548767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06655764579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07368350028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06228137016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394228935242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831206321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123283863068</t>
+    <t xml:space="preserve">2.06655788421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0736837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0622820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394181251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831170558929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123295783997</t>
   </si>
   <si>
     <t xml:space="preserve">1.89695727825165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92973732948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263449192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89125657081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99717044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9433501958847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425776481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971475124359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9637143611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389686107635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95062303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989422798157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389371871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462264537811</t>
+    <t xml:space="preserve">1.92973697185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91691040992737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263473033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8912558555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835881233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9971706867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94334971904755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425764560699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96371459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389674186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9506231546402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989398956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8938934803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462240695953</t>
   </si>
   <si>
     <t xml:space="preserve">1.89680302143097</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">1.88952970504761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94916868209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880427837372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953320503235</t>
+    <t xml:space="preserve">1.9491685628891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880392074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953308582306</t>
   </si>
   <si>
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735235214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01026153564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98553359508514</t>
+    <t xml:space="preserve">2.00735259056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01026177406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98553335666656</t>
   </si>
   <si>
     <t xml:space="preserve">2.00880718231201</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">2.02189826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02917170524597</t>
+    <t xml:space="preserve">2.02917194366455</t>
   </si>
   <si>
     <t xml:space="preserve">2.03062605857849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208065032959</t>
+    <t xml:space="preserve">2.03208088874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099058151245</t>
@@ -2291,94 +2291,94 @@
     <t xml:space="preserve">2.10044741630554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09608364105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881394386292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08444666862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09753799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008313179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462904930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23863482475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1891782283783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16590428352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899258613586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06844615936279</t>
+    <t xml:space="preserve">2.09608340263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881346702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08444690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09753823280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462881088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23863458633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2473623752594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18917798995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16590452194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899282455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06844592094421</t>
   </si>
   <si>
     <t xml:space="preserve">2.07717370986938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07280969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.128084897995</t>
+    <t xml:space="preserve">2.07280945777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12808465957642</t>
   </si>
   <si>
     <t xml:space="preserve">2.11499357223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14553999900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14699459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13099384307861</t>
+    <t xml:space="preserve">2.14554023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1469943523407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13099408149719</t>
   </si>
   <si>
     <t xml:space="preserve">2.08299207687378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07426428794861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05826330184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808115959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02335286140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771735191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0640823841095</t>
+    <t xml:space="preserve">2.07426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0582640171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808187484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.023353099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771711349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06408214569092</t>
   </si>
   <si>
     <t xml:space="preserve">2.04226350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99426102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789925575256</t>
+    <t xml:space="preserve">1.99426114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789949417114</t>
   </si>
   <si>
     <t xml:space="preserve">2.03644466400146</t>
@@ -2387,55 +2387,55 @@
     <t xml:space="preserve">2.04517245292664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02626276016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862480163574</t>
+    <t xml:space="preserve">2.02626252174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589823722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862468242645</t>
   </si>
   <si>
     <t xml:space="preserve">1.9593505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97826039791107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080565452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280631542206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06117296218872</t>
+    <t xml:space="preserve">1.97826027870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280691146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06117343902588</t>
   </si>
   <si>
     <t xml:space="preserve">2.06990051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04080867767334</t>
+    <t xml:space="preserve">2.04080843925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96807837486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134858131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.890984416008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370795726776</t>
+    <t xml:space="preserve">1.96807861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91134893894196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90552997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370831489563</t>
   </si>
   <si>
     <t xml:space="preserve">1.79352617263794</t>
@@ -2444,64 +2444,64 @@
     <t xml:space="preserve">1.80079901218414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81970918178558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152817726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8255273103714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516302585602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83280050754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898292064667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85170996189117</t>
+    <t xml:space="preserve">1.819708943367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152781963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552742958069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516266822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83280026912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171031951904</t>
   </si>
   <si>
     <t xml:space="preserve">1.84298241138458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85752844810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8357093334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880077838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061989307404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788959026337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460995674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152117729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751866340637</t>
+    <t xml:space="preserve">1.85752809047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83570957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880089759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061977386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460959911346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5986088514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152141571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751878261566</t>
   </si>
   <si>
     <t xml:space="preserve">1.57388091087341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55351638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56224381923676</t>
+    <t xml:space="preserve">1.55351614952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56224405765533</t>
   </si>
   <si>
     <t xml:space="preserve">1.62770116329193</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">1.52733361721039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50842356681824</t>
+    <t xml:space="preserve">1.50842344760895</t>
   </si>
   <si>
     <t xml:space="preserve">1.39278280735016</t>
@@ -2522,37 +2522,37 @@
     <t xml:space="preserve">1.35569036006927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19277465343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21241188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16150093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1593189239502</t>
+    <t xml:space="preserve">1.19277489185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21241199970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16150081157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15931880474091</t>
   </si>
   <si>
     <t xml:space="preserve">1.13386344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10768032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11422610282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08440697193146</t>
+    <t xml:space="preserve">1.10768043994904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11422622203827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08440673351288</t>
   </si>
   <si>
     <t xml:space="preserve">1.1804107427597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17968344688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19713866710663</t>
+    <t xml:space="preserve">1.17968332767487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19713854789734</t>
   </si>
   <si>
     <t xml:space="preserve">1.11204421520233</t>
@@ -2564,28 +2564,28 @@
     <t xml:space="preserve">1.18550181388855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10549867153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09022498130798</t>
+    <t xml:space="preserve">1.1054984331131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09022521972656</t>
   </si>
   <si>
     <t xml:space="preserve">1.04149603843689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07640659809113</t>
+    <t xml:space="preserve">1.07640647888184</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059451580048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24514067173004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077526569366</t>
+    <t xml:space="preserve">1.24514055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20077502727509</t>
   </si>
   <si>
     <t xml:space="preserve">1.22186672687531</t>
@@ -2594,121 +2594,121 @@
     <t xml:space="preserve">1.24223113059998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36005413532257</t>
+    <t xml:space="preserve">1.36005425453186</t>
   </si>
   <si>
     <t xml:space="preserve">1.41023802757263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47351312637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.589390873909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649638175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331355571747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5624772310257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967896938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4608039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47575616836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500860691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061176300049</t>
+    <t xml:space="preserve">1.47351324558258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331379413605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56247711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967920780182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46080410480499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4757559299469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284769535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061188220978</t>
   </si>
   <si>
     <t xml:space="preserve">1.48397958278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42192912101746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473437309265</t>
+    <t xml:space="preserve">1.42192900180817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473425388336</t>
   </si>
   <si>
     <t xml:space="preserve">1.37931609153748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46005630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44884264469147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762850761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4951936006546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56546771526337</t>
+    <t xml:space="preserve">1.46005666255951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44884252548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762838840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49519371986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56546807289124</t>
   </si>
   <si>
     <t xml:space="preserve">1.60733318328857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64321768283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807363510132</t>
+    <t xml:space="preserve">1.62228512763977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64321756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498692035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807351589203</t>
   </si>
   <si>
     <t xml:space="preserve">1.64471292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7747950553894</t>
+    <t xml:space="preserve">1.77479481697083</t>
   </si>
   <si>
     <t xml:space="preserve">1.75535726547241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67760717868805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65069329738617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58490490913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976098060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125598430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583782196045</t>
+    <t xml:space="preserve">1.67760741710663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65069365501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5849050283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686648845673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976109981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583794116974</t>
   </si>
   <si>
     <t xml:space="preserve">1.62527537345886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58340990543365</t>
+    <t xml:space="preserve">1.58341002464294</t>
   </si>
   <si>
     <t xml:space="preserve">1.59238123893738</t>
@@ -2717,121 +2717,121 @@
     <t xml:space="preserve">1.60135209560394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64172267913818</t>
+    <t xml:space="preserve">1.64172279834747</t>
   </si>
   <si>
     <t xml:space="preserve">1.71050155162811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.717977643013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7060159444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70003497600555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013096809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956863880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788105487823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72545337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7807754278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656393527985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80021297931671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78675639629364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85403978824615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002051830292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871797561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310735225677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423213005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292934894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161234855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104954242706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264053821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609759807587</t>
+    <t xml:space="preserve">1.71797752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70601570606232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70003509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013132572174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956875801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7478814125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7254536151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78077530860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656405448914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.800213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78675651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85404002666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002111434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871773719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310723304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292911052704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881396770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161246776581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104978084564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264089584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609795570374</t>
   </si>
   <si>
     <t xml:space="preserve">1.85852563381195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89291524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786719322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039086341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89142000675201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992476463318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487694740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543915748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83011698722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79124200344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666028499603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80768871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460247516632</t>
+    <t xml:space="preserve">1.89291501045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039098262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992464542389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487635135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543903827667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8301168680191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7912415266037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553514957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666016578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8076890707016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928030490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460235595703</t>
   </si>
   <si>
     <t xml:space="preserve">1.80170845985413</t>
@@ -2840,127 +2840,127 @@
     <t xml:space="preserve">1.84805929660797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84506869316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646818161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058320522308</t>
+    <t xml:space="preserve">1.84506893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646794319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058344364166</t>
   </si>
   <si>
     <t xml:space="preserve">1.83908808231354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82862174510956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947252750397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900619029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349203586578</t>
+    <t xml:space="preserve">1.82862162590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114565372467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778542041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947228908539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900595188141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7134917974472</t>
   </si>
   <si>
     <t xml:space="preserve">1.68508315086365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68059754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442447185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395777702332</t>
+    <t xml:space="preserve">1.68059718608856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395801544189</t>
   </si>
   <si>
     <t xml:space="preserve">1.87497282028198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84207820892334</t>
+    <t xml:space="preserve">1.84207808971405</t>
   </si>
   <si>
     <t xml:space="preserve">1.78227078914642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76582384109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638617038727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685238838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246277332306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6342465877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51762139797211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836220741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74937665462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75984299182892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72694838047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386202335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80469846725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80918431282043</t>
+    <t xml:space="preserve">1.76582360267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7463858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685226917267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63424670696259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5176215171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836184978485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74937629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75984275341034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72694885730743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386214256287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80469858646393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80918395519257</t>
   </si>
   <si>
     <t xml:space="preserve">1.8196507692337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86301100254059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91235256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93926584720612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159777164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216010093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056910514832</t>
+    <t xml:space="preserve">1.86301147937775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91235268115997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93926644325256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.966179728508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159801006317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216045856476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056934356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.014972448349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04074668884277</t>
+    <t xml:space="preserve">2.01497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04074692726135</t>
   </si>
   <si>
     <t xml:space="preserve">2.02710175514221</t>
@@ -2972,46 +2972,46 @@
     <t xml:space="preserve">1.99677860736847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00890803337097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00132727622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981093406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03165054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800489425659</t>
+    <t xml:space="preserve">2.00890779495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00132703781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03164982795715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800465583801</t>
   </si>
   <si>
     <t xml:space="preserve">2.00435948371887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01042366027832</t>
+    <t xml:space="preserve">2.01042413711548</t>
   </si>
   <si>
     <t xml:space="preserve">2.0301342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0346827507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681158065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05136013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04377961158752</t>
+    <t xml:space="preserve">2.03468251228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681181907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05136036872864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04377937316895</t>
   </si>
   <si>
     <t xml:space="preserve">2.07561850547791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06803822517395</t>
+    <t xml:space="preserve">2.06803774833679</t>
   </si>
   <si>
     <t xml:space="preserve">2.10442566871643</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">2.12261986732483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21358895301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19084692001343</t>
+    <t xml:space="preserve">2.21358919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19084668159485</t>
   </si>
   <si>
     <t xml:space="preserve">2.16203951835632</t>
@@ -3041,31 +3041,31 @@
     <t xml:space="preserve">2.1559751033783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023324012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20145964622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27120327949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18933081626892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26362204551697</t>
+    <t xml:space="preserve">2.18023347854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20145988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27120304107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18933057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26362228393555</t>
   </si>
   <si>
     <t xml:space="preserve">2.24846076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2151050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21662139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546165466309</t>
+    <t xml:space="preserve">2.21510481834412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21662163734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.30000996589661</t>
@@ -3077,28 +3077,28 @@
     <t xml:space="preserve">2.31062316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34246206283569</t>
+    <t xml:space="preserve">2.34246230125427</t>
   </si>
   <si>
     <t xml:space="preserve">2.35762357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3485267162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35913991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38794708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36368846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39249539375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639812469482</t>
+    <t xml:space="preserve">2.34852695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35914015769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38794732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36368870735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39249587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639764785767</t>
   </si>
   <si>
     <t xml:space="preserve">2.38491463661194</t>
@@ -3113,34 +3113,34 @@
     <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32426857948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35459160804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549474716187</t>
+    <t xml:space="preserve">2.32426834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35459136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549498558044</t>
   </si>
   <si>
     <t xml:space="preserve">2.380366563797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4410126209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36065626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37278604507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31820392608643</t>
+    <t xml:space="preserve">2.44101238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36065649986267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3727855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.318204164505</t>
   </si>
   <si>
     <t xml:space="preserve">2.40007638931274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40765738487244</t>
+    <t xml:space="preserve">2.40765714645386</t>
   </si>
   <si>
     <t xml:space="preserve">2.41523790359497</t>
@@ -3149,49 +3149,49 @@
     <t xml:space="preserve">2.41978621482849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49407815933228</t>
+    <t xml:space="preserve">2.4940779209137</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42888355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30759048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32730102539062</t>
+    <t xml:space="preserve">2.41827034950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42888331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614104270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759119987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32730054855347</t>
   </si>
   <si>
     <t xml:space="preserve">2.34397840499878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35610771179199</t>
+    <t xml:space="preserve">2.35610795021057</t>
   </si>
   <si>
     <t xml:space="preserve">2.45314192771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51682019233704</t>
+    <t xml:space="preserve">2.51682066917419</t>
   </si>
   <si>
     <t xml:space="preserve">2.48649740219116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49862670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44859337806702</t>
+    <t xml:space="preserve">2.49862694740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043274879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44859313964844</t>
   </si>
   <si>
     <t xml:space="preserve">2.54714345932007</t>
@@ -3200,85 +3200,85 @@
     <t xml:space="preserve">2.58959603309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685328483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266133308411</t>
+    <t xml:space="preserve">2.56685352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266157150269</t>
   </si>
   <si>
     <t xml:space="preserve">2.65327453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61355900764465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52038168907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50052380561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51579928398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51427149772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49899649620056</t>
+    <t xml:space="preserve">2.61355948448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52038192749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50052428245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5157995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51427173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49899673461914</t>
   </si>
   <si>
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412890434265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60286712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46386408805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109441757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43942427635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761178016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4806661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4119291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443350791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262148857117</t>
+    <t xml:space="preserve">2.53412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60286688804626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46386432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43942379951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761154174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48066663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41192865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443398475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262125015259</t>
   </si>
   <si>
     <t xml:space="preserve">2.46691942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45775389671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43025898933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706177711487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43331408500671</t>
+    <t xml:space="preserve">2.45775413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43025875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43331432342529</t>
   </si>
   <si>
     <t xml:space="preserve">2.45622658729553</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">2.48372149467468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50816130638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65938520431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64869213104248</t>
+    <t xml:space="preserve">2.5081615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023909568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65938472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6486918926239</t>
   </si>
   <si>
     <t xml:space="preserve">2.63799953460693</t>
@@ -3305,28 +3305,28 @@
     <t xml:space="preserve">2.67618703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61814188957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60439491271973</t>
+    <t xml:space="preserve">2.61814212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60439443588257</t>
   </si>
   <si>
     <t xml:space="preserve">2.65632963180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68382453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73575973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68840742111206</t>
+    <t xml:space="preserve">2.68382430076599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.735759973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.63952708244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61966967582703</t>
+    <t xml:space="preserve">2.61966943740845</t>
   </si>
   <si>
     <t xml:space="preserve">2.59370183944702</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">2.51885414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54482173919678</t>
+    <t xml:space="preserve">2.54482197761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.53260159492493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50663423538208</t>
+    <t xml:space="preserve">2.5066339969635</t>
   </si>
   <si>
     <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54329419136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997380256653</t>
+    <t xml:space="preserve">2.54329395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997427940369</t>
   </si>
   <si>
     <t xml:space="preserve">2.4913592338562</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">2.48219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40734648704529</t>
+    <t xml:space="preserve">2.40734624862671</t>
   </si>
   <si>
     <t xml:space="preserve">2.37526845932007</t>
@@ -3377,61 +3377,61 @@
     <t xml:space="preserve">2.41040134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38290619850159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48524880409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44247889518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47455644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801895141602</t>
+    <t xml:space="preserve">2.38290643692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48524928092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4424786567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47455668449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801942825317</t>
   </si>
   <si>
     <t xml:space="preserve">2.4898316860199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52649188041687</t>
+    <t xml:space="preserve">2.52649164199829</t>
   </si>
   <si>
     <t xml:space="preserve">2.52496433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55856895446777</t>
+    <t xml:space="preserve">2.55856943130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.5539870262146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54787683486938</t>
+    <t xml:space="preserve">2.54787659645081</t>
   </si>
   <si>
     <t xml:space="preserve">2.56162452697754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52954649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732659339905</t>
+    <t xml:space="preserve">2.5295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732683181763</t>
   </si>
   <si>
     <t xml:space="preserve">2.4516441822052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4287314414978</t>
+    <t xml:space="preserve">2.42873167991638</t>
   </si>
   <si>
     <t xml:space="preserve">2.42414903640747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42567682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4501166343689</t>
+    <t xml:space="preserve">2.42567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45011639595032</t>
   </si>
   <si>
     <t xml:space="preserve">2.4272038936615</t>
@@ -3440,88 +3440,88 @@
     <t xml:space="preserve">2.40581893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510668754578</t>
+    <t xml:space="preserve">2.50510621070862</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596129417419</t>
+    <t xml:space="preserve">2.38596177101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901615142822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37221360206604</t>
+    <t xml:space="preserve">2.37221336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.40887403488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37355351448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36727380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42535710334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791508674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42378711700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40965867042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35157608985901</t>
+    <t xml:space="preserve">2.37355303764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36727356910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4253568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42378687858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40965890884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35157561302185</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000586509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34372711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34058713912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33116817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35471510887146</t>
+    <t xml:space="preserve">2.34372663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34058737754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33116841316223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35471534729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.34686636924744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39396071434021</t>
+    <t xml:space="preserve">2.39396047592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44733428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43948531150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47402119636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44105458259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45675301551819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46931195259094</t>
+    <t xml:space="preserve">2.4473340511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4394850730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47402095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45361351966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410548210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45675325393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46931171417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.46774172782898</t>
@@ -3530,25 +3530,25 @@
     <t xml:space="preserve">2.48814916610718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50384759902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45047354698181</t>
+    <t xml:space="preserve">2.50384712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45047378540039</t>
   </si>
   <si>
     <t xml:space="preserve">2.27622485160828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26837563514709</t>
+    <t xml:space="preserve">2.26837587356567</t>
   </si>
   <si>
     <t xml:space="preserve">2.25581741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31546998023987</t>
+    <t xml:space="preserve">2.2573869228363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31547045707703</t>
   </si>
   <si>
     <t xml:space="preserve">2.29977202415466</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">2.29192328453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27151560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36256456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31076073646545</t>
+    <t xml:space="preserve">2.27151584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36256432533264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31076097488403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32017946243286</t>
@@ -3572,25 +3572,25 @@
     <t xml:space="preserve">2.26994585990906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22913026809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22442102432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24639844894409</t>
+    <t xml:space="preserve">2.2291305065155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22442150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244383811951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15064024925232</t>
+    <t xml:space="preserve">2.15063977241516</t>
   </si>
   <si>
     <t xml:space="preserve">2.16005897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14122104644775</t>
+    <t xml:space="preserve">2.14122152328491</t>
   </si>
   <si>
     <t xml:space="preserve">2.20401382446289</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">2.19773435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16319847106934</t>
+    <t xml:space="preserve">2.16319823265076</t>
   </si>
   <si>
     <t xml:space="preserve">2.17732691764832</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">2.18674564361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18203639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16633796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15534925460815</t>
+    <t xml:space="preserve">2.18203616142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16633820533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15534973144531</t>
   </si>
   <si>
     <t xml:space="preserve">2.14750051498413</t>
@@ -3623,13 +3623,13 @@
     <t xml:space="preserve">2.15848922729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21814203262329</t>
+    <t xml:space="preserve">2.21814179420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.21186280250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23070049285889</t>
+    <t xml:space="preserve">2.23070025444031</t>
   </si>
   <si>
     <t xml:space="preserve">2.21657204627991</t>
@@ -3638,46 +3638,46 @@
     <t xml:space="preserve">2.22756099700928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2636661529541</t>
+    <t xml:space="preserve">2.26366639137268</t>
   </si>
   <si>
     <t xml:space="preserve">2.31860971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29349255561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24796867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2354097366333</t>
+    <t xml:space="preserve">2.29349279403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24796843528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23540997505188</t>
   </si>
   <si>
     <t xml:space="preserve">2.24011921882629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24482846260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052689552307</t>
+    <t xml:space="preserve">2.24482893943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052713394165</t>
   </si>
   <si>
     <t xml:space="preserve">2.30291152000427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34529662132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407382965088</t>
+    <t xml:space="preserve">2.34529638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407406806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.11924386024475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2008740901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18831539154053</t>
+    <t xml:space="preserve">2.20087432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18831562995911</t>
   </si>
   <si>
     <t xml:space="preserve">2.22128176689148</t>
@@ -3689,100 +3689,100 @@
     <t xml:space="preserve">2.23697948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19930458068848</t>
+    <t xml:space="preserve">2.19930410385132</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599101066589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27936410903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1647686958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03447389602661</t>
+    <t xml:space="preserve">2.27936458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16476821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03447413444519</t>
   </si>
   <si>
     <t xml:space="preserve">2.09255695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9795309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441365242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01092672348022</t>
+    <t xml:space="preserve">2.05802130699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441377162933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0109269618988</t>
   </si>
   <si>
     <t xml:space="preserve">1.92615723609924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84766697883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057239532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82254981994629</t>
+    <t xml:space="preserve">1.84766685962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057227611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592327594757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254958152771</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807429790497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91045892238617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.009357213974</t>
+    <t xml:space="preserve">1.91045904159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202867031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00935697555542</t>
   </si>
   <si>
     <t xml:space="preserve">1.99365890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9779611825943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877617835999</t>
+    <t xml:space="preserve">1.97796082496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877593994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.01720643043518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99208915233612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98894953727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9967987537384</t>
+    <t xml:space="preserve">1.9920893907547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9889497756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99679851531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.05959129333496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01249670982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96854186058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639095783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220274448395</t>
+    <t xml:space="preserve">2.01249647140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406645774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96854197978973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639119625092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220262527466</t>
   </si>
   <si>
     <t xml:space="preserve">1.86650454998016</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">1.91516852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92301762104034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790081977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947044849396</t>
+    <t xml:space="preserve">1.92301738262177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947056770325</t>
   </si>
   <si>
     <t xml:space="preserve">1.92124760150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93576610088348</t>
+    <t xml:space="preserve">1.93576598167419</t>
   </si>
   <si>
     <t xml:space="preserve">2.01642298698425</t>
@@ -3812,112 +3812,112 @@
     <t xml:space="preserve">2.01158356666565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96964192390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092668056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543771743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87607991695404</t>
+    <t xml:space="preserve">1.96964204311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092656135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543747901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87608003616333</t>
   </si>
   <si>
     <t xml:space="preserve">1.92770040035248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91156888008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221131801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704327583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77122616767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79703593254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81316721439362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801409721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672934055328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94383192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963469982147</t>
+    <t xml:space="preserve">1.91156911849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189015865326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221155643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704339504242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8260725736618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77122604846954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79703617095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81316757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801433563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672993659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383180141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963458061218</t>
   </si>
   <si>
     <t xml:space="preserve">1.89382457733154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91802179813385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93253970146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91479527950287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96318960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254704475403</t>
+    <t xml:space="preserve">1.91802155971527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9325395822525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91479516029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9631894826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254692554474</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932810783386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609436511993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448892593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448134422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97770738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99061298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415319919586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124037742615</t>
+    <t xml:space="preserve">1.97609448432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448868751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480984687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97770762443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99061274528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93415296077728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124061584473</t>
   </si>
   <si>
     <t xml:space="preserve">1.82929873466492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87285375595093</t>
+    <t xml:space="preserve">1.87285363674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.88898503780365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86317491531372</t>
+    <t xml:space="preserve">1.86317467689514</t>
   </si>
   <si>
     <t xml:space="preserve">1.85833537578583</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">1.8438173532486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85672235488892</t>
+    <t xml:space="preserve">1.85672211647034</t>
   </si>
   <si>
     <t xml:space="preserve">1.88253271579742</t>
@@ -3935,58 +3935,58 @@
     <t xml:space="preserve">1.87769329547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84865641593933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80187547206879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81155443191528</t>
+    <t xml:space="preserve">1.8486567735672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8018753528595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81155467033386</t>
   </si>
   <si>
     <t xml:space="preserve">1.75993371009827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78574407100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81800699234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86962723731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575141429901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82768607139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350317955017</t>
+    <t xml:space="preserve">1.78574419021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8180068731308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86962747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8357515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82768583297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">1.93899238109589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95189762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802890300751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222576618195</t>
+    <t xml:space="preserve">1.95189774036407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383914470673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802854537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99222600460052</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07449650764465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0502986907959</t>
+    <t xml:space="preserve">2.07449579238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05029916763306</t>
   </si>
   <si>
     <t xml:space="preserve">2.05191206932068</t>
@@ -3995,22 +3995,22 @@
     <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07288241386414</t>
+    <t xml:space="preserve">2.01319646835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07288289070129</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0793354511261</t>
+    <t xml:space="preserve">2.07933568954468</t>
   </si>
   <si>
     <t xml:space="preserve">2.07610893249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00351786613464</t>
+    <t xml:space="preserve">2.00351762771606</t>
   </si>
   <si>
     <t xml:space="preserve">2.00835728645325</t>
@@ -4019,55 +4019,55 @@
     <t xml:space="preserve">1.98899960517883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95512413978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97932088375092</t>
+    <t xml:space="preserve">1.9551237821579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97932076454163</t>
   </si>
   <si>
     <t xml:space="preserve">1.89866399765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91318225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931354045868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286856174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96480286121368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94544494152069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83736455440521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025614738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647287845612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495901107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81474316120148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78290569782257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845813035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79128384590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77620303630829</t>
+    <t xml:space="preserve">1.91318237781525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97286832332611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96480274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9454448223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83736479282379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025602817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647299766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78290557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78458142280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79128408432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77620279788971</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
@@ -4079,40 +4079,40 @@
     <t xml:space="preserve">1.74604117870331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79798662662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966235160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333751678467</t>
+    <t xml:space="preserve">1.79798650741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966223239899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333727836609</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85663485527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86166155338287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87674283981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171566486359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517521858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360723972321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685070514679</t>
+    <t xml:space="preserve">1.85663497447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86166167259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87674295902252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171590328217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517509937286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360747814178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685082435608</t>
   </si>
   <si>
     <t xml:space="preserve">1.90355336666107</t>
@@ -4121,31 +4121,31 @@
     <t xml:space="preserve">1.92701268196106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94879651069641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94376921653748</t>
+    <t xml:space="preserve">1.94879627227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94376933574677</t>
   </si>
   <si>
     <t xml:space="preserve">2.09625506401062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17836213111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19176721572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14819979667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16160559654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18506455421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29900979995728</t>
+    <t xml:space="preserve">2.1783618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19176745414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820027351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1616051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18506479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29901003837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.29230737686157</t>
@@ -4154,73 +4154,73 @@
     <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32582020759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33419871330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34257698059082</t>
+    <t xml:space="preserve">2.3258204460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33419919013977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3425772190094</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25711846351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29398274421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30906414985657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30068564414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31576609611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29733443260193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31409096717834</t>
+    <t xml:space="preserve">2.25711822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2939829826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30906391143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3006854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31576633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31409072875977</t>
   </si>
   <si>
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33754992485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42636036872864</t>
+    <t xml:space="preserve">2.33755040168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42636013031006</t>
   </si>
   <si>
     <t xml:space="preserve">2.44981956481934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46657609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490073204041</t>
+    <t xml:space="preserve">2.46657633781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490025520325</t>
   </si>
   <si>
     <t xml:space="preserve">2.4799816608429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46322512626648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43306303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38614439964294</t>
+    <t xml:space="preserve">2.4632248878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4330632686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38614416122437</t>
   </si>
   <si>
     <t xml:space="preserve">2.40122532844543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40290117263794</t>
+    <t xml:space="preserve">2.40290069580078</t>
   </si>
   <si>
     <t xml:space="preserve">2.37609052658081</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.38279318809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295504570007</t>
+    <t xml:space="preserve">2.41295528411865</t>
   </si>
   <si>
     <t xml:space="preserve">2.35430669784546</t>
@@ -4241,19 +4241,19 @@
     <t xml:space="preserve">2.37776613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36100959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34927988052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37944149971008</t>
+    <t xml:space="preserve">2.36100935935974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3492796421051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37944173812866</t>
   </si>
   <si>
     <t xml:space="preserve">2.38782000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49171113967896</t>
+    <t xml:space="preserve">2.49171137809753</t>
   </si>
   <si>
     <t xml:space="preserve">2.45987367630005</t>
@@ -4262,22 +4262,22 @@
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776392936707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64922332763672</t>
+    <t xml:space="preserve">2.68776369094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6492235660553</t>
   </si>
   <si>
     <t xml:space="preserve">2.77824950218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80170869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78160095214844</t>
+    <t xml:space="preserve">2.80170893669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77322268486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78160047531128</t>
   </si>
   <si>
     <t xml:space="preserve">2.83019495010376</t>
@@ -4289,19 +4289,19 @@
     <t xml:space="preserve">2.92905926704407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224838256836</t>
+    <t xml:space="preserve">2.90224862098694</t>
   </si>
   <si>
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03295016288757</t>
+    <t xml:space="preserve">3.03295040130615</t>
   </si>
   <si>
     <t xml:space="preserve">3.06311202049255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11840891838074</t>
+    <t xml:space="preserve">3.11840915679932</t>
   </si>
   <si>
     <t xml:space="preserve">3.1502468585968</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">3.20554351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20219254493713</t>
+    <t xml:space="preserve">3.20219206809998</t>
   </si>
   <si>
     <t xml:space="preserve">3.1435444355011</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">3.20889472961426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18878674507141</t>
+    <t xml:space="preserve">3.18878698348999</t>
   </si>
   <si>
     <t xml:space="preserve">3.19213843345642</t>
@@ -4331,16 +4331,16 @@
     <t xml:space="preserve">3.1988410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17705750465393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29267811775208</t>
+    <t xml:space="preserve">3.17705726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29267835617065</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33792114257812</t>
+    <t xml:space="preserve">3.3379213809967</t>
   </si>
   <si>
     <t xml:space="preserve">3.35132646560669</t>
@@ -4352,22 +4352,22 @@
     <t xml:space="preserve">3.25581336021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34797525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31781315803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39321780204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36473155021667</t>
+    <t xml:space="preserve">3.34797501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3178129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39321804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3647313117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.35467767715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18543553352356</t>
+    <t xml:space="preserve">3.18543577194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.24240827560425</t>
@@ -4376,40 +4376,40 @@
     <t xml:space="preserve">3.13851737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23235440254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13349032402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1904628276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23402976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24575924873352</t>
+    <t xml:space="preserve">3.23235416412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13348984718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19046306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23403024673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24575972557068</t>
   </si>
   <si>
     <t xml:space="preserve">3.2390570640564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21559762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26419162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29770541191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.294353723526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3429479598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510961532593</t>
+    <t xml:space="preserve">3.2155978679657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26419186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29770517349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29435396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34294819831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510913848877</t>
   </si>
   <si>
     <t xml:space="preserve">3.30105662345886</t>
@@ -4421,22 +4421,22 @@
     <t xml:space="preserve">3.38986682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3848397731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981247901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640763282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37143468856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619118690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31243968009949</t>
+    <t xml:space="preserve">3.38484001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36640739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37143445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619166374207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31243991851807</t>
   </si>
   <si>
     <t xml:space="preserve">3.23508644104004</t>
@@ -4445,40 +4445,40 @@
     <t xml:space="preserve">3.2178966999054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22305369377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2041449546814</t>
+    <t xml:space="preserve">3.22305393218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414519309998</t>
   </si>
   <si>
     <t xml:space="preserve">3.21445894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19555020332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16976618766785</t>
+    <t xml:space="preserve">3.19555044174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16976571083069</t>
   </si>
   <si>
     <t xml:space="preserve">3.25571417808533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20070695877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12335395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05975222587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09413170814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08897471427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10616445541382</t>
+    <t xml:space="preserve">3.20070719718933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12335419654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05975198745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09413146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08897495269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10616421699524</t>
   </si>
   <si>
     <t xml:space="preserve">3.13366746902466</t>
@@ -4487,19 +4487,19 @@
     <t xml:space="preserve">3.13194894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18867444992065</t>
+    <t xml:space="preserve">3.18867468833923</t>
   </si>
   <si>
     <t xml:space="preserve">3.22649145126343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26602792739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24024343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09928870201111</t>
+    <t xml:space="preserve">3.2660276889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24024319648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09928846359253</t>
   </si>
   <si>
     <t xml:space="preserve">3.16117119789124</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1525764465332</t>
+    <t xml:space="preserve">3.15257596969604</t>
   </si>
   <si>
     <t xml:space="preserve">3.11991596221924</t>
@@ -4523,34 +4523,34 @@
     <t xml:space="preserve">3.15429544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14741945266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10960221290588</t>
+    <t xml:space="preserve">3.14741921424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1096019744873</t>
   </si>
   <si>
     <t xml:space="preserve">3.12507271766663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18695545196533</t>
+    <t xml:space="preserve">3.18695569038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.17664194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398169517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27462267875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24196243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19039344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19898819923401</t>
+    <t xml:space="preserve">3.14398145675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27462244033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24196267127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1903932094574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19898796081543</t>
   </si>
   <si>
     <t xml:space="preserve">3.15601420402527</t>
@@ -4562,55 +4562,55 @@
     <t xml:space="preserve">3.27290368080139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12851071357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1353862285614</t>
+    <t xml:space="preserve">3.12851095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538694381714</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08209872245789</t>
+    <t xml:space="preserve">3.08209896087646</t>
   </si>
   <si>
     <t xml:space="preserve">3.04084372520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04771971702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05631446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01677823066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01162123680115</t>
+    <t xml:space="preserve">3.04771947860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05631422996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01677846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00818371772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01162147521973</t>
   </si>
   <si>
     <t xml:space="preserve">3.03396773338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98755621910095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583674430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07350397109985</t>
+    <t xml:space="preserve">2.98755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07350420951843</t>
   </si>
   <si>
     <t xml:space="preserve">3.07006621360779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0528769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97552299499512</t>
+    <t xml:space="preserve">3.05287647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9755232334137</t>
   </si>
   <si>
     <t xml:space="preserve">2.94458198547363</t>
@@ -4619,16 +4619,16 @@
     <t xml:space="preserve">2.93083024024963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9205162525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87582349777222</t>
+    <t xml:space="preserve">2.92051649093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87582325935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.87754225730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88785624504089</t>
+    <t xml:space="preserve">2.88785600662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.91020250320435</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">2.95661473274231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98411798477173</t>
+    <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005272865295</t>
@@ -4646,16 +4646,16 @@
     <t xml:space="preserve">2.94286274909973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99786972999573</t>
+    <t xml:space="preserve">2.99786949157715</t>
   </si>
   <si>
     <t xml:space="preserve">3.05115747451782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03053021430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04943871498108</t>
+    <t xml:space="preserve">3.03052997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">3.05459547042847</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">3.04256248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02021622657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99615073204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03912472724915</t>
+    <t xml:space="preserve">3.02021646499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99615049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03912496566772</t>
   </si>
   <si>
     <t xml:space="preserve">3.06490921974182</t>
@@ -4685,25 +4685,25 @@
     <t xml:space="preserve">3.00523209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03729748725891</t>
+    <t xml:space="preserve">3.03729724884033</t>
   </si>
   <si>
     <t xml:space="preserve">2.99276232719421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95357131958008</t>
+    <t xml:space="preserve">2.9535710811615</t>
   </si>
   <si>
     <t xml:space="preserve">2.79858899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67210936546326</t>
+    <t xml:space="preserve">2.6721088886261</t>
   </si>
   <si>
     <t xml:space="preserve">2.67923450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69526720046997</t>
+    <t xml:space="preserve">2.69526743888855</t>
   </si>
   <si>
     <t xml:space="preserve">2.67032766342163</t>
@@ -4715,16 +4715,16 @@
     <t xml:space="preserve">2.58838272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59372687339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62579250335693</t>
+    <t xml:space="preserve">2.59372711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62579226493835</t>
   </si>
   <si>
     <t xml:space="preserve">2.58125734329224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64538812637329</t>
+    <t xml:space="preserve">2.64538788795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.64004373550415</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">2.60976004600525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5224711894989</t>
+    <t xml:space="preserve">2.52247095108032</t>
   </si>
   <si>
     <t xml:space="preserve">2.47971725463867</t>
@@ -4748,40 +4748,40 @@
     <t xml:space="preserve">2.32473492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2855441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3372049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392569541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2606041431427</t>
+    <t xml:space="preserve">2.28554391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720445632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392593383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26060438156128</t>
   </si>
   <si>
     <t xml:space="preserve">2.27663683891296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29445099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38708400726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32829785346985</t>
+    <t xml:space="preserve">2.29445123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38708424568176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32829761505127</t>
   </si>
   <si>
     <t xml:space="preserve">2.32117199897766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36927008628845</t>
+    <t xml:space="preserve">2.36927032470703</t>
   </si>
   <si>
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323739051819</t>
+    <t xml:space="preserve">2.35323715209961</t>
   </si>
   <si>
     <t xml:space="preserve">2.35145616531372</t>
@@ -4790,40 +4790,40 @@
     <t xml:space="preserve">2.43161916732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40667963027954</t>
+    <t xml:space="preserve">2.40667939186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955425262451</t>
+    <t xml:space="preserve">2.39955401420593</t>
   </si>
   <si>
     <t xml:space="preserve">2.42449355125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34254932403564</t>
+    <t xml:space="preserve">2.34254908561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.39242839813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39599108695984</t>
+    <t xml:space="preserve">2.39599132537842</t>
   </si>
   <si>
     <t xml:space="preserve">2.37461400032043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36036324501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41380500793457</t>
+    <t xml:space="preserve">2.3603630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41380524635315</t>
   </si>
   <si>
     <t xml:space="preserve">2.51534509658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49931263923645</t>
+    <t xml:space="preserve">2.49931287765503</t>
   </si>
   <si>
     <t xml:space="preserve">2.56522488594055</t>
@@ -4838,16 +4838,16 @@
     <t xml:space="preserve">2.4975311756134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50287556648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57056903839111</t>
+    <t xml:space="preserve">2.50287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57056879997253</t>
   </si>
   <si>
     <t xml:space="preserve">2.60085296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303880691528</t>
+    <t xml:space="preserve">2.58303904533386</t>
   </si>
   <si>
     <t xml:space="preserve">2.64360666275024</t>
@@ -4856,19 +4856,19 @@
     <t xml:space="preserve">2.64895081520081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65785813331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65073204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67567181587219</t>
+    <t xml:space="preserve">2.65785789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65073251724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67567205429077</t>
   </si>
   <si>
     <t xml:space="preserve">2.65963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6525137424469</t>
+    <t xml:space="preserve">2.65251350402832</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291811943054</t>
@@ -4877,37 +4877,37 @@
     <t xml:space="preserve">2.55453634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61510443687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65429520606995</t>
+    <t xml:space="preserve">2.61510419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65429496765137</t>
   </si>
   <si>
     <t xml:space="preserve">2.60441565513611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60619735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59550881385803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74336504936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71664428710938</t>
+    <t xml:space="preserve">2.60619711875916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59550857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74336528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7166440486908</t>
   </si>
   <si>
     <t xml:space="preserve">2.68992328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70773696899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66676473617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445796966553</t>
+    <t xml:space="preserve">2.70773720741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66676497459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73445844650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.77721214294434</t>
@@ -4919,16 +4919,16 @@
     <t xml:space="preserve">2.7718677520752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76474213600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72911405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74692845344543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72020673751831</t>
+    <t xml:space="preserve">2.76474237442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72911381721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74692821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72020697593689</t>
   </si>
   <si>
     <t xml:space="preserve">2.75049114227295</t>
@@ -4943,7 +4943,7 @@
     <t xml:space="preserve">2.8235285282135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84846830368042</t>
+    <t xml:space="preserve">2.848468542099</t>
   </si>
   <si>
     <t xml:space="preserve">2.77008628845215</t>
@@ -4955,16 +4955,16 @@
     <t xml:space="preserve">2.80927729606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80749607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81996583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81105852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78790044784546</t>
+    <t xml:space="preserve">2.80749583244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81996560096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81105875968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78790068626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.83065414428711</t>
@@ -4976,16 +4976,16 @@
     <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63469958305359</t>
+    <t xml:space="preserve">2.63469934463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.5527548789978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54741048812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53137826919556</t>
+    <t xml:space="preserve">2.54741072654724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5313777923584</t>
   </si>
   <si>
     <t xml:space="preserve">2.5420663356781</t>
@@ -4994,25 +4994,25 @@
     <t xml:space="preserve">2.55809903144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57947611808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52781510353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5117826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50821971893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60263395309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61154103279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988025665283</t>
+    <t xml:space="preserve">2.57947587966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52781534194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51178240776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50821995735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60263419151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61154127120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988073348999</t>
   </si>
   <si>
     <t xml:space="preserve">2.58482027053833</t>
@@ -5027,16 +5027,16 @@
     <t xml:space="preserve">2.5866014957428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5670063495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51890802383423</t>
+    <t xml:space="preserve">2.56700611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51890826225281</t>
   </si>
   <si>
     <t xml:space="preserve">2.46724724769592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47080993652344</t>
+    <t xml:space="preserve">2.47081017494202</t>
   </si>
   <si>
     <t xml:space="preserve">2.48684287071228</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">2.48867678642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49051094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47400498390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43915987014771</t>
+    <t xml:space="preserve">2.49051070213318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47400522232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43916010856628</t>
   </si>
   <si>
     <t xml:space="preserve">2.49417877197266</t>
@@ -5063,19 +5063,19 @@
     <t xml:space="preserve">2.51618599891663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5271897315979</t>
+    <t xml:space="preserve">2.52718997001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.54002737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58587646484375</t>
+    <t xml:space="preserve">2.58587622642517</t>
   </si>
   <si>
     <t xml:space="preserve">2.59871411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6152195930481</t>
+    <t xml:space="preserve">2.61521983146667</t>
   </si>
   <si>
     <t xml:space="preserve">2.62438941001892</t>
@@ -5087,10 +5087,10 @@
     <t xml:space="preserve">2.61888742446899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62255525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6317253112793</t>
+    <t xml:space="preserve">2.62255549430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63172507286072</t>
   </si>
   <si>
     <t xml:space="preserve">2.60971760749817</t>
@@ -5099,25 +5099,25 @@
     <t xml:space="preserve">2.57303857803345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55103135108948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60605001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5840425491333</t>
+    <t xml:space="preserve">2.5510311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60604953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58404231071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.5675368309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5748724937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6005482673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63355898857117</t>
+    <t xml:space="preserve">2.57487273216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60054802894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63355922698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.61705350875854</t>
@@ -5129,43 +5129,43 @@
     <t xml:space="preserve">2.6115517616272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53085780143738</t>
+    <t xml:space="preserve">2.5308575630188</t>
   </si>
   <si>
     <t xml:space="preserve">2.54736351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57670664787292</t>
+    <t xml:space="preserve">2.57670640945435</t>
   </si>
   <si>
     <t xml:space="preserve">2.51802015304565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48500871658325</t>
+    <t xml:space="preserve">2.48500895500183</t>
   </si>
   <si>
     <t xml:space="preserve">2.51251816749573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53269171714783</t>
+    <t xml:space="preserve">2.53269147872925</t>
   </si>
   <si>
     <t xml:space="preserve">2.58037447929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59321212768555</t>
+    <t xml:space="preserve">2.59321236610413</t>
   </si>
   <si>
     <t xml:space="preserve">2.64089512825012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60238194465637</t>
+    <t xml:space="preserve">2.60238218307495</t>
   </si>
   <si>
     <t xml:space="preserve">2.56386876106262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56020092964172</t>
+    <t xml:space="preserve">2.5602011680603</t>
   </si>
   <si>
     <t xml:space="preserve">2.54552936553955</t>
@@ -5174,13 +5174,13 @@
     <t xml:space="preserve">2.56937074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58771014213562</t>
+    <t xml:space="preserve">2.5877103805542</t>
   </si>
   <si>
     <t xml:space="preserve">2.61338567733765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47583913803101</t>
+    <t xml:space="preserve">2.47583889961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.4868426322937</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">2.5033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767305374146</t>
+    <t xml:space="preserve">2.47767281532288</t>
   </si>
   <si>
     <t xml:space="preserve">2.49234461784363</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">2.46116757392883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40798258781433</t>
+    <t xml:space="preserve">2.40798282623291</t>
   </si>
   <si>
     <t xml:space="preserve">2.34196043014526</t>
@@ -5219,19 +5219,19 @@
     <t xml:space="preserve">2.33462452888489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33645868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31261706352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31078338623047</t>
+    <t xml:space="preserve">2.33645844459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31261682510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31078314781189</t>
   </si>
   <si>
     <t xml:space="preserve">2.27777194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29611158370972</t>
+    <t xml:space="preserve">2.29611134529114</t>
   </si>
   <si>
     <t xml:space="preserve">2.28694176673889</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">2.30344724655151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32728862762451</t>
+    <t xml:space="preserve">2.32728886604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.34746217727661</t>
@@ -5261,16 +5261,16 @@
     <t xml:space="preserve">2.35113000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39881277084351</t>
+    <t xml:space="preserve">2.39881300926208</t>
   </si>
   <si>
     <t xml:space="preserve">2.40248084068298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40981650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41898632049561</t>
+    <t xml:space="preserve">2.40981674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41898655891418</t>
   </si>
   <si>
     <t xml:space="preserve">2.43732595443726</t>
@@ -5279,7 +5279,7 @@
     <t xml:space="preserve">2.46666932106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42815613746643</t>
+    <t xml:space="preserve">2.42815637588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.41531872749329</t>
@@ -5291,31 +5291,31 @@
     <t xml:space="preserve">2.39697909355164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39514493942261</t>
+    <t xml:space="preserve">2.39514517784119</t>
   </si>
   <si>
     <t xml:space="preserve">2.37863945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38780927658081</t>
+    <t xml:space="preserve">2.38780951499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.44099402427673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43182420730591</t>
+    <t xml:space="preserve">2.43182396888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.44466161727905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44282793998718</t>
+    <t xml:space="preserve">2.4428277015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.31064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30297470092773</t>
+    <t xml:space="preserve">2.30297493934631</t>
   </si>
   <si>
     <t xml:space="preserve">2.37008905410767</t>
@@ -5336,22 +5336,22 @@
     <t xml:space="preserve">2.43720316886902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38926482200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43145060539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46021389961243</t>
+    <t xml:space="preserve">2.38926458358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43145036697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46021366119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.41994524002075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41227507591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4046049118042</t>
+    <t xml:space="preserve">2.41227531433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40460467338562</t>
   </si>
   <si>
     <t xml:space="preserve">2.42569804191589</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">2.3643364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29722189903259</t>
+    <t xml:space="preserve">2.29722213745117</t>
   </si>
   <si>
     <t xml:space="preserve">2.197509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16491150856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18408679962158</t>
+    <t xml:space="preserve">2.1649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18408703804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.18792200088501</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">2.13806581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12272548675537</t>
+    <t xml:space="preserve">2.12272524833679</t>
   </si>
   <si>
     <t xml:space="preserve">2.09012699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09971475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10354995727539</t>
+    <t xml:space="preserve">2.09971499443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10354971885681</t>
   </si>
   <si>
     <t xml:space="preserve">2.08053946495056</t>
@@ -5441,10 +5441,10 @@
     <t xml:space="preserve">2.00767254829407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95781624317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99424946308136</t>
+    <t xml:space="preserve">1.95781636238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99424970149994</t>
   </si>
   <si>
     <t xml:space="preserve">1.99808490276337</t>
@@ -5474,31 +5474,31 @@
     <t xml:space="preserve">2.07095170021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08820962905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07862162590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04410576820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03068327903748</t>
+    <t xml:space="preserve">2.08820939064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07862186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04410600662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0306830406189</t>
   </si>
   <si>
     <t xml:space="preserve">1.97315657138824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01534247398376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06903409957886</t>
+    <t xml:space="preserve">2.01534271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06903386116028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05561113357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1054675579071</t>
+    <t xml:space="preserve">2.10546731948853</t>
   </si>
   <si>
     <t xml:space="preserve">2.10930252075195</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">2.05369353294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05752849578857</t>
+    <t xml:space="preserve">2.05752873420715</t>
   </si>
   <si>
     <t xml:space="preserve">2.06136393547058</t>
@@ -5531,22 +5531,22 @@
     <t xml:space="preserve">2.03835320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02301263809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05177640914917</t>
+    <t xml:space="preserve">2.02301287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05177617073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.05944633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643560409546</t>
+    <t xml:space="preserve">2.03643584251404</t>
   </si>
   <si>
     <t xml:space="preserve">2.07286906242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03260064125061</t>
+    <t xml:space="preserve">2.03260040283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.02876543998718</t>
@@ -5561,16 +5561,16 @@
     <t xml:space="preserve">2.09587979316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1457359790802</t>
+    <t xml:space="preserve">2.14573574066162</t>
   </si>
   <si>
     <t xml:space="preserve">2.11889028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12080764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09204435348511</t>
+    <t xml:space="preserve">2.12080788612366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09204459190369</t>
   </si>
   <si>
     <t xml:space="preserve">1.85906255245209</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">1.9271354675293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94439363479614</t>
+    <t xml:space="preserve">1.94439351558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.96165144443512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93672311306</t>
+    <t xml:space="preserve">1.93672323226929</t>
   </si>
   <si>
     <t xml:space="preserve">1.92905306816101</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">1.87823808193207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87919676303864</t>
+    <t xml:space="preserve">1.87919688224792</t>
   </si>
   <si>
     <t xml:space="preserve">1.83029937744141</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">1.71812283992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73825705051422</t>
+    <t xml:space="preserve">1.73825693130493</t>
   </si>
   <si>
     <t xml:space="preserve">1.75167989730835</t>
@@ -6009,6 +6009,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.96399998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97300004959106</t>
   </si>
 </sst>
 </file>
@@ -71347,7 +71350,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910648148</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>976289</v>
@@ -71368,6 +71371,32 @@
         <v>1998</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911342593</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>554474</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>1.98399996757507</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>1.96099996566772</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>1.96700000762939</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>1.97300004959106</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="2001">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42847192287445</t>
+    <t xml:space="preserve">1.42847180366516</t>
   </si>
   <si>
     <t xml:space="preserve">PIA.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">1.3917795419693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36014807224274</t>
+    <t xml:space="preserve">1.36014819145203</t>
   </si>
   <si>
     <t xml:space="preserve">1.30827283859253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27158033847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23931634426117</t>
+    <t xml:space="preserve">1.27158045768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23931646347046</t>
   </si>
   <si>
     <t xml:space="preserve">1.21401154994965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28676331043243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831763744354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20009338855743</t>
+    <t xml:space="preserve">1.28676319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425543308258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20009350776672</t>
   </si>
   <si>
     <t xml:space="preserve">1.18680822849274</t>
@@ -80,73 +80,73 @@
     <t xml:space="preserve">1.11595416069031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09191417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15644216537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19439995288849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23299026489258</t>
+    <t xml:space="preserve">1.09191405773163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478859424591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15644228458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19440007209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.232990026474</t>
   </si>
   <si>
     <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22097015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24437749385834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16087067127228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10646462440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11721956729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12164783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04699778556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1184846162796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11089301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13366782665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17795157432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1981954574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21337878704071</t>
+    <t xml:space="preserve">1.22097027301788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24437737464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16087031364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10646498203278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1172194480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12164759635925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04699790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826283454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11848473548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11089313030243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13366770744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17795169353485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19819593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21337854862213</t>
   </si>
   <si>
     <t xml:space="preserve">1.16213595867157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20578730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17921686172485</t>
+    <t xml:space="preserve">1.20578718185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17921662330627</t>
   </si>
   <si>
     <t xml:space="preserve">1.13872861862183</t>
@@ -155,85 +155,85 @@
     <t xml:space="preserve">1.1317697763443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15770757198334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311208724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688560962677</t>
+    <t xml:space="preserve">1.15770769119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311220645905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.2918244600296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29941606521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598626613617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525413990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27917194366455</t>
+    <t xml:space="preserve">1.2994157075882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598602771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27917206287384</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892794132233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20199120044708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413349151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20135903358459</t>
+    <t xml:space="preserve">1.20199143886566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20135879516602</t>
   </si>
   <si>
     <t xml:space="preserve">1.19376718997955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18237996101379</t>
+    <t xml:space="preserve">1.18238008022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.20452189445496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21464383602142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19186961650848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554317951202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15264666080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19123685359955</t>
+    <t xml:space="preserve">1.21464395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1918693780899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554329872131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15264654159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19123649597168</t>
   </si>
   <si>
     <t xml:space="preserve">1.1798495054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17162549495697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11152589321136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09571003913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546603679657</t>
+    <t xml:space="preserve">1.17162525653839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11152565479279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09571015834808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546615600586</t>
   </si>
   <si>
     <t xml:space="preserve">1.10709738731384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12417829036713</t>
+    <t xml:space="preserve">1.12417817115784</t>
   </si>
   <si>
     <t xml:space="preserve">1.14062666893005</t>
@@ -242,109 +242,109 @@
     <t xml:space="preserve">1.16719698905945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15454459190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227015972137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405784130096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24820911884308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406301021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812945842743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26837277412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918731212616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28138148784637</t>
+    <t xml:space="preserve">1.15454435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227039813995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405807971954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24820899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406277179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26837289333344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918707370758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28138172626495</t>
   </si>
   <si>
     <t xml:space="preserve">1.27682876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2573150396347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031918048859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19096958637238</t>
+    <t xml:space="preserve">1.25731527805328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2449563741684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19031894207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096946716309</t>
   </si>
   <si>
     <t xml:space="preserve">1.17796063423157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12527441978455</t>
+    <t xml:space="preserve">1.12527418136597</t>
   </si>
   <si>
     <t xml:space="preserve">1.16690301895142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17080557346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755330562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495168209076</t>
+    <t xml:space="preserve">1.17080545425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755318641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495156288147</t>
   </si>
   <si>
     <t xml:space="preserve">1.17340743541718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18056225776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15389394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16300022602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15649592876434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16169929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17731022834778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901801109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14283645153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1285263299942</t>
+    <t xml:space="preserve">1.18056237697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15389406681061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1630003452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950488090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15649580955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16169953346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1773099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18901813030243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14283621311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12852644920349</t>
   </si>
   <si>
     <t xml:space="preserve">1.1103138923645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09665465354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10641121864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10055756568909</t>
+    <t xml:space="preserve">1.0966545343399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10641133785248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10055732727051</t>
   </si>
   <si>
     <t xml:space="preserve">1.11486721038818</t>
@@ -353,127 +353,127 @@
     <t xml:space="preserve">1.10250866413116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05112314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05372512340546</t>
+    <t xml:space="preserve">1.05112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05372524261475</t>
   </si>
   <si>
     <t xml:space="preserve">1.04657006263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04526925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10185825824738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13177871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1012077331543</t>
+    <t xml:space="preserve">1.04526937007904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10185813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177859783173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120761394501</t>
   </si>
   <si>
     <t xml:space="preserve">1.12917697429657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05307447910309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485650539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995184659957886</t>
+    <t xml:space="preserve">1.05307459831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255070209503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485590934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99518483877182</t>
   </si>
   <si>
     <t xml:space="preserve">1.02640628814697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01339709758759</t>
+    <t xml:space="preserve">1.01339733600616</t>
   </si>
   <si>
     <t xml:space="preserve">0.982826173305511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976321935653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977622807025909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671410560608</t>
+    <t xml:space="preserve">0.976321876049042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97762268781662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671648979187</t>
   </si>
   <si>
     <t xml:space="preserve">1.00364065170288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95095431804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980874955654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970467686653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166934490204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971118330955505</t>
+    <t xml:space="preserve">0.95095419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.980875015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970467567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971118152141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.96591454744339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958760023117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437541007996</t>
+    <t xml:space="preserve">0.958759605884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437552928925</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06608378887177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892872810364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06283152103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06673407554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340250492096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06022942066193</t>
+    <t xml:space="preserve">1.0660834312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974290847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892825126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06283116340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06673395633698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340226650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06022953987122</t>
   </si>
   <si>
     <t xml:space="preserve">1.08559691905975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09275186061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11421692371368</t>
+    <t xml:space="preserve">1.09275197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1142166852951</t>
   </si>
   <si>
     <t xml:space="preserve">1.09795522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07779145240784</t>
+    <t xml:space="preserve">1.07779157161713</t>
   </si>
   <si>
     <t xml:space="preserve">1.07388889789581</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">1.10901308059692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11746895313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14348685741425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1187698841095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13828337192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14543831348419</t>
+    <t xml:space="preserve">1.11746907234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14348673820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11877000331879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13828325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1454381942749</t>
   </si>
   <si>
     <t xml:space="preserve">1.14023470878601</t>
@@ -503,64 +503,64 @@
     <t xml:space="preserve">1.12787616252899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14218592643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15129220485687</t>
+    <t xml:space="preserve">1.14218604564667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15129208564758</t>
   </si>
   <si>
     <t xml:space="preserve">1.16234970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14803981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299505710602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315907001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09600389003754</t>
+    <t xml:space="preserve">1.14803993701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09600400924683</t>
   </si>
   <si>
     <t xml:space="preserve">1.08169424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09990680217743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09210133552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511040687561</t>
+    <t xml:space="preserve">1.09990704059601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09210169315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10511064529419</t>
   </si>
   <si>
     <t xml:space="preserve">1.11356627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949971199036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584023475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234488964081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09925627708435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08429610729218</t>
+    <t xml:space="preserve">1.08949983119965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234477043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09925639629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08429622650146</t>
   </si>
   <si>
     <t xml:space="preserve">1.07518982887268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08754849433899</t>
+    <t xml:space="preserve">1.0875483751297</t>
   </si>
   <si>
     <t xml:space="preserve">1.07453918457031</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">1.07323861122131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06933557987213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05697739124298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04722046852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05047273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06348156929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03421175479889</t>
+    <t xml:space="preserve">1.0693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05697751045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04722058773041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05047297477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06348180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0342116355896</t>
   </si>
   <si>
     <t xml:space="preserve">1.01144587993622</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">0.95680844783783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933392286300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440949440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644375324249</t>
+    <t xml:space="preserve">0.933392345905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440770626068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644494533539</t>
   </si>
   <si>
     <t xml:space="preserve">0.949653506278992</t>
@@ -617,28 +617,28 @@
     <t xml:space="preserve">0.95355612039566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9626624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956157863140106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957459032535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507636070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98672878742218</t>
+    <t xml:space="preserve">0.962662518024445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956158041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458734512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507397651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98672890663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.965264141559601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.940547168254852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986078560352325</t>
+    <t xml:space="preserve">0.940547108650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986078500747681</t>
   </si>
   <si>
     <t xml:space="preserve">0.995835304260254</t>
@@ -647,157 +647,157 @@
     <t xml:space="preserve">1.00429105758667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02315402030945</t>
+    <t xml:space="preserve">1.02315390110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03681325912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02380418777466</t>
+    <t xml:space="preserve">1.03681337833405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02380430698395</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120280265808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04201686382294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04917180538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02770733833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04852139949799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03356111049652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03095948696136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03161013126373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567634105682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05502593517303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03291046619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03551268577576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01860105991364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999087631702423</t>
+    <t xml:space="preserve">1.04201710224152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04917204380035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02770721912384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0485212802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0335613489151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03095960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03160965442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567622184753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05502605438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03291094303131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03551244735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01860094070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999087393283844</t>
   </si>
   <si>
     <t xml:space="preserve">1.01925134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991932511329651</t>
+    <t xml:space="preserve">0.99193274974823</t>
   </si>
   <si>
     <t xml:space="preserve">1.00494158267975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02510547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999738037586212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989981412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534492492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988029837608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905714511871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01664936542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01404786109924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136669635773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02965843677521</t>
+    <t xml:space="preserve">1.02510511875153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999737918376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989981114864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534313678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988030016422272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401357650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905833721161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0166494846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01404762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136645793915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0296585559845</t>
   </si>
   <si>
     <t xml:space="preserve">0.991282105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00949466228485</t>
+    <t xml:space="preserve">1.00949454307556</t>
   </si>
   <si>
     <t xml:space="preserve">1.01795053482056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01469814777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226029872894</t>
+    <t xml:space="preserve">1.01469826698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226041793823</t>
   </si>
   <si>
     <t xml:space="preserve">1.07063663005829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06218099594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09470331668854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1447879076004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18251359462738</t>
+    <t xml:space="preserve">1.06218087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09470319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14478766918182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18251347541809</t>
   </si>
   <si>
     <t xml:space="preserve">1.23585033416748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23845219612122</t>
+    <t xml:space="preserve">1.23845207691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.21633684635162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20983242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21438539028168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21308493614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20072615146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893870830536</t>
+    <t xml:space="preserve">1.20983231067657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21438550949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24755835533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2130845785141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20072638988495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893894672394</t>
   </si>
   <si>
     <t xml:space="preserve">1.22023952007294</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">1.20267748832703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18446505069733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16430127620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17600905895233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999967098236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194684505463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268402576447</t>
+    <t xml:space="preserve">1.18446516990662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16430115699768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17600917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999955177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194672584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268414497375</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482929706573</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">1.27502715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28777766227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26697444915771</t>
+    <t xml:space="preserve">1.28777754306793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.266974568367</t>
   </si>
   <si>
     <t xml:space="preserve">1.27435612678528</t>
@@ -851,25 +851,25 @@
     <t xml:space="preserve">1.24348700046539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24415802955627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22738134860992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24818444252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25422394275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27368497848511</t>
+    <t xml:space="preserve">1.24415791034698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22738122940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24818432331085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25422418117523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27368521690369</t>
   </si>
   <si>
     <t xml:space="preserve">1.24147379398346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23006546497345</t>
+    <t xml:space="preserve">1.23006570339203</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831638813019</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">1.3099228143692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31059372425079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200169563293</t>
+    <t xml:space="preserve">1.3105936050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200193405151</t>
   </si>
   <si>
     <t xml:space="preserve">1.34146273136139</t>
@@ -896,19 +896,19 @@
     <t xml:space="preserve">1.30455410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35555505752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35018682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689723491669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34079170227051</t>
+    <t xml:space="preserve">1.35555517673492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35018670558929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689759254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481799602509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3407918214798</t>
   </si>
   <si>
     <t xml:space="preserve">1.32669937610626</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">1.32602834701538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3038831949234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30925178527832</t>
+    <t xml:space="preserve">1.30388295650482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30925154685974</t>
   </si>
   <si>
     <t xml:space="preserve">1.29650127887726</t>
@@ -929,49 +929,49 @@
     <t xml:space="preserve">1.34213387966156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32871246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864655017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300300598145</t>
+    <t xml:space="preserve">1.3287125825882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864666938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300288677216</t>
   </si>
   <si>
     <t xml:space="preserve">1.37031865119934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38239789009094</t>
+    <t xml:space="preserve">1.38239777088165</t>
   </si>
   <si>
     <t xml:space="preserve">1.3743451833725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44010972976685</t>
+    <t xml:space="preserve">1.44010961055756</t>
   </si>
   <si>
     <t xml:space="preserve">1.43876755237579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45084667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44816243648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48976838588715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46158385276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4602415561676</t>
+    <t xml:space="preserve">1.45084655284882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44816255569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4897688627243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46158373355865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46024179458618</t>
   </si>
   <si>
     <t xml:space="preserve">1.50721645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50453186035156</t>
+    <t xml:space="preserve">1.50453209877014</t>
   </si>
   <si>
     <t xml:space="preserve">1.53540134429932</t>
@@ -986,130 +986,130 @@
     <t xml:space="preserve">1.5058741569519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46829462051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45755743980408</t>
+    <t xml:space="preserve">1.46829450130463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45755732059479</t>
   </si>
   <si>
     <t xml:space="preserve">1.48037374019623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44547808170319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44950497150421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45621514320374</t>
+    <t xml:space="preserve">1.44547832012177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44950473308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45621526241302</t>
   </si>
   <si>
     <t xml:space="preserve">1.45889973640442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44279396533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566523551941</t>
+    <t xml:space="preserve">1.44279384613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566487789154</t>
   </si>
   <si>
     <t xml:space="preserve">1.66290390491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58640229701996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59042847156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411425590515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60787642002106</t>
+    <t xml:space="preserve">1.62129771709442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58640241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59042859077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727154254913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411389827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60787618160248</t>
   </si>
   <si>
     <t xml:space="preserve">1.61458694934845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5971394777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995565891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277195930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6306928396225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72329998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70987832546234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558802127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853626728058</t>
+    <t xml:space="preserve">1.59713935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995577812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277184009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350925922394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398207187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63069272041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72330009937286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70987868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558825969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853638648987</t>
   </si>
   <si>
     <t xml:space="preserve">1.70048332214355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70719432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72732627391815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69108843803406</t>
+    <t xml:space="preserve">1.70719408988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72732603549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69108891487122</t>
   </si>
   <si>
     <t xml:space="preserve">1.6857203245163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66693031787872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66424608230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632520198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753495693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63740336894989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64679801464081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67364096641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76490592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77430140972137</t>
+    <t xml:space="preserve">1.66692996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66424596309662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632508277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753519535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6374032497406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64679825305939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67364084720612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7649062871933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77430093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75819540023804</t>
@@ -1118,100 +1118,100 @@
     <t xml:space="preserve">1.74880039691925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7380633354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7286684513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624810695648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79174876213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77832734584808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77161693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564287185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74209010601044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074804782867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73537909984589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73940539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75953757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78772222995758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7810115814209</t>
+    <t xml:space="preserve">1.73806309700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72866821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624822616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79174888134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77832746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77161681652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416874885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77564311027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208998680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73940551280975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75953722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503835201263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78772246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78101170063019</t>
   </si>
   <si>
     <t xml:space="preserve">1.81188070774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79845952987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261776924133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80248582363129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8843560218811</t>
+    <t xml:space="preserve">1.79845941066742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261765003204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802485704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067059516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435578346252</t>
   </si>
   <si>
     <t xml:space="preserve">1.89911949634552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88703978061676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569819927216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84543430805206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7957751750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7259840965271</t>
+    <t xml:space="preserve">1.88704073429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569808006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84543406963348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79577493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598421573639</t>
   </si>
   <si>
     <t xml:space="preserve">1.71793127059937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001062870026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7689323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698504924774</t>
+    <t xml:space="preserve">1.73001074790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893258094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77698516845703</t>
   </si>
   <si>
     <t xml:space="preserve">1.76222169399261</t>
@@ -1220,43 +1220,43 @@
     <t xml:space="preserve">1.76356363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70316803455353</t>
+    <t xml:space="preserve">1.70316779613495</t>
   </si>
   <si>
     <t xml:space="preserve">1.69645726680756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68035113811493</t>
+    <t xml:space="preserve">1.68035161495209</t>
   </si>
   <si>
     <t xml:space="preserve">1.69511520862579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6924307346344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67766761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874518871307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814066886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653424263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60921847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5702965259552</t>
+    <t xml:space="preserve">1.69243085384369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67766726016998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814043045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653436183929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6092187166214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57029664516449</t>
   </si>
   <si>
     <t xml:space="preserve">1.57432293891907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57969176769257</t>
+    <t xml:space="preserve">1.57969164848328</t>
   </si>
   <si>
     <t xml:space="preserve">1.55687510967255</t>
@@ -1268,43 +1268,43 @@
     <t xml:space="preserve">1.51392698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6320344209671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229878902435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827237606049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75148463249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74611628055573</t>
+    <t xml:space="preserve">1.63203465938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229866981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827249526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75148451328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74611616134644</t>
   </si>
   <si>
     <t xml:space="preserve">1.7139048576355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72195780277252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71658885478973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606119155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6038498878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58371794223785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53674364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197968959808</t>
+    <t xml:space="preserve">1.72195756435394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71658945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606095314026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60384976863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58371806144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5367431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197992801666</t>
   </si>
   <si>
     <t xml:space="preserve">1.54613828659058</t>
@@ -1313,94 +1313,94 @@
     <t xml:space="preserve">1.54882252216339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54748010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53271687030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54076933860779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211175441742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869057655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5676121711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55955922603607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52600598335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774447441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190259456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519194602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56627023220062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49782133102417</t>
+    <t xml:space="preserve">1.54748034477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53271675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895458698273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54076957702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54211187362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869045734406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56761229038239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55955958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52600586414337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774411678314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190283298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5662704706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49782156944275</t>
   </si>
   <si>
     <t xml:space="preserve">1.51661109924316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50319004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49647903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990056991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266178131104</t>
+    <t xml:space="preserve">1.50318992137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49647927284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990068912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266166210175</t>
   </si>
   <si>
     <t xml:space="preserve">1.48171579837799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.462926030159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46695232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48440003395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52332186698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405869007111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662510871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56837034225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53947949409485</t>
+    <t xml:space="preserve">1.46292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46695256233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305773735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405892848969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662546634674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5683708190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53947961330414</t>
   </si>
   <si>
     <t xml:space="preserve">1.51884305477142</t>
@@ -1409,61 +1409,61 @@
     <t xml:space="preserve">1.51609146595001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4995824098587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56286764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57387399673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55186128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52159452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095820426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50233364105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49820685386658</t>
+    <t xml:space="preserve">1.49958252906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5628674030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57387375831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5518616437912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52159464359283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233387947083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498206615448</t>
   </si>
   <si>
     <t xml:space="preserve">1.47619426250458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44042479991913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656429767609</t>
+    <t xml:space="preserve">1.44042456150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656405925751</t>
   </si>
   <si>
     <t xml:space="preserve">1.42804276943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43767297267914</t>
+    <t xml:space="preserve">1.43767309188843</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46518838405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931540966034</t>
+    <t xml:space="preserve">1.46518850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931552886963</t>
   </si>
   <si>
     <t xml:space="preserve">1.46106100082397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42116379737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37370002269745</t>
+    <t xml:space="preserve">1.42116391658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37369990348816</t>
   </si>
   <si>
     <t xml:space="preserve">1.40327906608582</t>
@@ -1472,31 +1472,31 @@
     <t xml:space="preserve">1.38814544677734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45280647277832</t>
+    <t xml:space="preserve">1.45280635356903</t>
   </si>
   <si>
     <t xml:space="preserve">1.44180023670197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43629741668701</t>
+    <t xml:space="preserve">1.43629705905914</t>
   </si>
   <si>
     <t xml:space="preserve">1.45143055915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41566073894501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45555770397186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43904852867126</t>
+    <t xml:space="preserve">1.41566109657288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45555782318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43904900550842</t>
   </si>
   <si>
     <t xml:space="preserve">1.42941856384277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41841232776642</t>
+    <t xml:space="preserve">1.41841244697571</t>
   </si>
   <si>
     <t xml:space="preserve">1.39640021324158</t>
@@ -1505,73 +1505,73 @@
     <t xml:space="preserve">1.36613345146179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41428518295288</t>
+    <t xml:space="preserve">1.41428506374359</t>
   </si>
   <si>
     <t xml:space="preserve">1.53397631645203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46793973445892</t>
+    <t xml:space="preserve">1.4679399728775</t>
   </si>
   <si>
     <t xml:space="preserve">1.48032176494598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48169732093811</t>
+    <t xml:space="preserve">1.48169720172882</t>
   </si>
   <si>
     <t xml:space="preserve">1.47069144248962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48720037937164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683105945587</t>
+    <t xml:space="preserve">1.48720073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683082103729</t>
   </si>
   <si>
     <t xml:space="preserve">1.50508546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54085540771484</t>
+    <t xml:space="preserve">1.54085516929626</t>
   </si>
   <si>
     <t xml:space="preserve">1.53122496604919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54223120212555</t>
+    <t xml:space="preserve">1.54223108291626</t>
   </si>
   <si>
     <t xml:space="preserve">1.5491099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54773426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53260087966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58900690078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57112216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5656191110611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746726036072</t>
+    <t xml:space="preserve">1.54773437976837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53260052204132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58900701999664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57112193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56561887264252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746737957001</t>
   </si>
   <si>
     <t xml:space="preserve">1.52984929084778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53810381889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461287498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672778606415</t>
+    <t xml:space="preserve">1.53810369968414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461275577545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672790527344</t>
   </si>
   <si>
     <t xml:space="preserve">1.45830941200256</t>
@@ -1583,28 +1583,28 @@
     <t xml:space="preserve">1.40878212451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38539397716522</t>
+    <t xml:space="preserve">1.38539385795593</t>
   </si>
   <si>
     <t xml:space="preserve">1.37851512432098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37576389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3640695810318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39364838600159</t>
+    <t xml:space="preserve">1.37576377391815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39364850521088</t>
   </si>
   <si>
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36888492107391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073307037354</t>
+    <t xml:space="preserve">1.36888480186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073318958282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26570248603821</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">1.28909051418304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29665732383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33724236488342</t>
+    <t xml:space="preserve">1.29665720462799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33724224567413</t>
   </si>
   <si>
     <t xml:space="preserve">1.34343314170837</t>
@@ -1631,67 +1631,67 @@
     <t xml:space="preserve">1.36200594902039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37989103794098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38264238834381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089703559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978788375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42666685581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43217015266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43079423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43492138385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41153335571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37301206588745</t>
+    <t xml:space="preserve">1.37989091873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38264262676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089715480804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978776454926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4266664981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43216991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4307941198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43492150306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41153347492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581505298615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37301230430603</t>
   </si>
   <si>
     <t xml:space="preserve">1.35719084739685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32692408561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28565096855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29528141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28771483898163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24506604671478</t>
+    <t xml:space="preserve">1.32692396640778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28565108776093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29528152942657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28771471977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24506616592407</t>
   </si>
   <si>
     <t xml:space="preserve">1.22924470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25951170921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22786915302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2313084602356</t>
+    <t xml:space="preserve">1.25951159000397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22786903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130822181702</t>
   </si>
   <si>
     <t xml:space="preserve">1.18315672874451</t>
@@ -1700,43 +1700,43 @@
     <t xml:space="preserve">1.19553852081299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19003570079803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025094509125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3338029384613</t>
+    <t xml:space="preserve">1.19003558158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025070667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33380281925201</t>
   </si>
   <si>
     <t xml:space="preserve">1.30009663105011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2994087934494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496313095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30078446865082</t>
+    <t xml:space="preserve">1.29940903186798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28496325016022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30078458786011</t>
   </si>
   <si>
     <t xml:space="preserve">1.29252994060516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2677663564682</t>
+    <t xml:space="preserve">1.26776623725891</t>
   </si>
   <si>
     <t xml:space="preserve">1.2822117805481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051770687103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818743228912</t>
+    <t xml:space="preserve">1.26088738441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818719387054</t>
   </si>
   <si>
     <t xml:space="preserve">1.25882387161255</t>
@@ -1748,55 +1748,55 @@
     <t xml:space="preserve">1.23268437385559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22030234336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21204793453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.214111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18522036075592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18797183036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20172965526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19347512722015</t>
+    <t xml:space="preserve">1.22030258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21204769611359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21411156654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18797206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20172953605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19347488880157</t>
   </si>
   <si>
     <t xml:space="preserve">1.19966578483582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2010418176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27808439731598</t>
+    <t xml:space="preserve">1.20104193687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27808463573456</t>
   </si>
   <si>
     <t xml:space="preserve">1.28083598613739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28152358531952</t>
+    <t xml:space="preserve">1.28152370452881</t>
   </si>
   <si>
     <t xml:space="preserve">1.25676000118256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23612368106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20792043209076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21273577213287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20379340648651</t>
+    <t xml:space="preserve">1.23612380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20792055130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21273565292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20379316806793</t>
   </si>
   <si>
     <t xml:space="preserve">1.19209921360016</t>
@@ -1808,289 +1808,289 @@
     <t xml:space="preserve">1.29046630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27946031093597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25056898593903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326905727386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136950969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30216038227081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30353629589081</t>
+    <t xml:space="preserve">1.27946019172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2505692243576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326941490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30216026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30353605747223</t>
   </si>
   <si>
     <t xml:space="preserve">1.32417261600494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32554817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33930575847626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34756052494049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33173930644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31110262870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31523001194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3489363193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36063027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38126647472382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3840184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30422389507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623636722565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34480881690979</t>
+    <t xml:space="preserve">1.32554841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33930599689484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3475604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3317391872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31110286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31523013114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34893620014191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36063039302826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38126659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38401818275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30422401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623612880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34480893611908</t>
   </si>
   <si>
     <t xml:space="preserve">1.34687256813049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35512709617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36957263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35787880420685</t>
+    <t xml:space="preserve">1.35512721538544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36957275867462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35787856578827</t>
   </si>
   <si>
     <t xml:space="preserve">1.33793020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44455182552338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48307311534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323708057404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59588575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128601551056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60276460647583</t>
+    <t xml:space="preserve">1.44455170631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5958856344223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128577709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59038293361664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60276472568512</t>
   </si>
   <si>
     <t xml:space="preserve">1.598637342453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57937681674957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56424331665039</t>
+    <t xml:space="preserve">1.57937669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5642431974411</t>
   </si>
   <si>
     <t xml:space="preserve">1.52572190761566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50921285152435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5133398771286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51058888435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49545514583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59726166725159</t>
+    <t xml:space="preserve">1.50921273231506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51334011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51058864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49545526504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5972615480423</t>
   </si>
   <si>
     <t xml:space="preserve">1.60001313686371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62340116500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007418632507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77611064910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79949879646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78436577320099</t>
+    <t xml:space="preserve">1.62340104579926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007406711578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77611100673676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7994989156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7843656539917</t>
   </si>
   <si>
     <t xml:space="preserve">1.85847651958466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77438879013062</t>
+    <t xml:space="preserve">1.77438926696777</t>
   </si>
   <si>
     <t xml:space="preserve">1.78151512145996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79719221591949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76726305484772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75301086902618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77153849601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7572865486145</t>
+    <t xml:space="preserve">1.79719257354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7672632932663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301110744476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77153837680817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728642940521</t>
   </si>
   <si>
     <t xml:space="preserve">1.71025431156158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71595513820648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420095920563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403650283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8955317735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81571996212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018383026123</t>
+    <t xml:space="preserve">1.71595525741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420083999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403638362885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89553225040436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81572008132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298749446869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018406867981</t>
   </si>
   <si>
     <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73733353614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7359082698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78579044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80004274845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79006636142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422445297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137356281281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723932266235</t>
+    <t xml:space="preserve">1.73733329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73590838909149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78579080104828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80004262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79006624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422409534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137368202209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723944187164</t>
   </si>
   <si>
     <t xml:space="preserve">1.75016045570374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73020768165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71310472488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564960002899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282244205475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78294038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146825313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81001949310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8285471200943</t>
+    <t xml:space="preserve">1.73020732402802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7131050825119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588465690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289304256439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564936161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282291889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78294026851654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146813392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81001913547516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82854700088501</t>
   </si>
   <si>
     <t xml:space="preserve">1.83994889259338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87415397167206</t>
+    <t xml:space="preserve">1.87415385246277</t>
   </si>
   <si>
     <t xml:space="preserve">1.86560261249542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8841301202774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90265786647797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562574863434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555550575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396590232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93116247653961</t>
+    <t xml:space="preserve">1.88413023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90265834331512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85562610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417734622955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555598258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396542549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9311625957489</t>
   </si>
   <si>
     <t xml:space="preserve">1.95681643486023</t>
@@ -2099,49 +2099,49 @@
     <t xml:space="preserve">1.94398903846741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87842965126038</t>
+    <t xml:space="preserve">1.87842953205109</t>
   </si>
   <si>
     <t xml:space="preserve">1.87700426578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990178585052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89410662651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87130343914032</t>
+    <t xml:space="preserve">1.85990166664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90978443622589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89410674571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8713036775589</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89268136024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93543803691864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00954866409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95111513137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971371650696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819435596466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532092571259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8171454668045</t>
+    <t xml:space="preserve">1.89268147945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93543815612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00954914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95111525058746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971335887909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819459438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532068729401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81714534759521</t>
   </si>
   <si>
     <t xml:space="preserve">1.84279918670654</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">1.83139741420746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94969010353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97106838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00669884681702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672210216522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99957251548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09648680686951</t>
+    <t xml:space="preserve">1.94968998432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97106862068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04517912864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00669836997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99672198295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.09363651275635</t>
@@ -2183,130 +2183,130 @@
     <t xml:space="preserve">2.0736837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0622820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96394181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92831170558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90123295783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89695727825165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92973697185516</t>
+    <t xml:space="preserve">2.06228160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96394217014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92831182479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90123248100281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89695715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92973685264587</t>
   </si>
   <si>
     <t xml:space="preserve">1.91691040992737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91263473033905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8912558555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835881233215</t>
+    <t xml:space="preserve">1.91263461112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89125657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835905075073</t>
   </si>
   <si>
     <t xml:space="preserve">1.9971706867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94334971904755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425764560699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971522808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96371459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97389674186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9506231546402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989398956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8938934803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93462240695953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680302143097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88952970504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9491685628891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92880392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96953308582306</t>
+    <t xml:space="preserve">1.94335055351257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971498966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96371471881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97389650344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95062303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989446640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9346227645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89680278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88953006267548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94916880130768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92880403995514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96953272819519</t>
   </si>
   <si>
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735259056091</t>
+    <t xml:space="preserve">2.00735282897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.01026177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98553335666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00880718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02189826965332</t>
+    <t xml:space="preserve">1.98553347587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00880742073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02189898490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.02917194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03062605857849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208088874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05099058151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10044741630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608340263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881346702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08444690704346</t>
+    <t xml:space="preserve">2.03062653541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208065032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05099081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10044717788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608364105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08444666862488</t>
   </si>
   <si>
     <t xml:space="preserve">2.09753823280334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462881088257</t>
+    <t xml:space="preserve">2.08008241653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462904930115</t>
   </si>
   <si>
     <t xml:space="preserve">2.23863458633423</t>
@@ -2318,34 +2318,34 @@
     <t xml:space="preserve">2.18917798995972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16590452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09899282455444</t>
+    <t xml:space="preserve">2.16590428352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09899306297302</t>
   </si>
   <si>
     <t xml:space="preserve">2.06844592094421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07717370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07280945777893</t>
+    <t xml:space="preserve">2.07717394828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07280969619751</t>
   </si>
   <si>
     <t xml:space="preserve">2.12808465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11499357223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1469943523407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390350341797</t>
+    <t xml:space="preserve">2.11499309539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14553999900818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14699482917786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390302658081</t>
   </si>
   <si>
     <t xml:space="preserve">2.13099408149719</t>
@@ -2357,166 +2357,166 @@
     <t xml:space="preserve">2.07426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0582640171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808187484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.023353099823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771711349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06408214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04226350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99426114559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789949417114</t>
+    <t xml:space="preserve">2.05826425552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808139801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771687507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0640823841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04226326942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99426090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789925575256</t>
   </si>
   <si>
     <t xml:space="preserve">2.03644466400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517245292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00589823722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99862468242645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826027870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080541610718</t>
+    <t xml:space="preserve">2.04517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02626276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00589799880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99862492084503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95935046672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080505847931</t>
   </si>
   <si>
     <t xml:space="preserve">1.99280691146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06117343902588</t>
+    <t xml:space="preserve">2.06117296218872</t>
   </si>
   <si>
     <t xml:space="preserve">2.06990051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04080843925476</t>
+    <t xml:space="preserve">2.04080867767334</t>
   </si>
   <si>
     <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96807861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134893894196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90552997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370831489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79352617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079901218414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.819708943367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84152781963348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552742958069</t>
+    <t xml:space="preserve">1.96807825565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91134905815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643826007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098429679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553057193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370855331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79352593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079889297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81970882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84152746200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552719116211</t>
   </si>
   <si>
     <t xml:space="preserve">1.80516266822815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83280026912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85898303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85171031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298241138458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752809047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83570957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880089759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061977386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788970947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460959911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5986088514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152141571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751878261566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388091087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351614952087</t>
+    <t xml:space="preserve">1.83279991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85898327827454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85171008110046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752856731415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83570945262909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880113601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87062013149261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788959026337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460971832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152165412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751902103424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388079166412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351638793945</t>
   </si>
   <si>
     <t xml:space="preserve">1.56224405765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62770116329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733361721039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842344760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39278280735016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36441802978516</t>
+    <t xml:space="preserve">1.62770128250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52733337879181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39278268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36441791057587</t>
   </si>
   <si>
     <t xml:space="preserve">1.35569036006927</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">1.16150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15931880474091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13386344909668</t>
+    <t xml:space="preserve">1.1593189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13386332988739</t>
   </si>
   <si>
     <t xml:space="preserve">1.10768043994904</t>
@@ -2543,28 +2543,28 @@
     <t xml:space="preserve">1.11422622203827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08440673351288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1804107427597</t>
+    <t xml:space="preserve">1.08440685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18041086196899</t>
   </si>
   <si>
     <t xml:space="preserve">1.17968332767487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19713854789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11204421520233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12877213954926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550181388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1054984331131</t>
+    <t xml:space="preserve">1.19713842868805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11204433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12877225875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550205230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10549855232239</t>
   </si>
   <si>
     <t xml:space="preserve">1.09022521972656</t>
@@ -2573,106 +2573,106 @@
     <t xml:space="preserve">1.04149603843689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07640647888184</t>
+    <t xml:space="preserve">1.07640659809113</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059451580048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24514055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641276359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077502727509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22186672687531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24223113059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023802757263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47351324558258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58939075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55649662017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331379413605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56247711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49967920780182</t>
+    <t xml:space="preserve">1.24514031410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20077514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22186684608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24223124980927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36005413532257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023778915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47351312637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58939051628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55649626255035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331391334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5624772310257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49967908859253</t>
   </si>
   <si>
     <t xml:space="preserve">1.46080410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4757559299469</t>
+    <t xml:space="preserve">1.47575604915619</t>
   </si>
   <si>
     <t xml:space="preserve">1.47500848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60284769535065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52061188220978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48397958278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42192900180817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40473425388336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46005666255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44884252548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43762838840485</t>
+    <t xml:space="preserve">1.60284733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5206116437912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48397970199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42192912101746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40473437309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46005642414093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44884240627289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43762850761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.49519371986389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56546807289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733318328857</t>
+    <t xml:space="preserve">1.56546771526337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733306407928</t>
   </si>
   <si>
     <t xml:space="preserve">1.62228512763977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64321756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71498692035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68807351589203</t>
+    <t xml:space="preserve">1.64321768283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71498715877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68807339668274</t>
   </si>
   <si>
     <t xml:space="preserve">1.64471292495728</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">1.77479481697083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75535726547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67760741710663</t>
+    <t xml:space="preserve">1.75535690784454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67760717868805</t>
   </si>
   <si>
     <t xml:space="preserve">1.65069365501404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5849050283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59686648845673</t>
+    <t xml:space="preserve">1.58490514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59686684608459</t>
   </si>
   <si>
     <t xml:space="preserve">1.62976109981537</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">1.58341002464294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59238123893738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135209560394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172279834747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050155162811</t>
+    <t xml:space="preserve">1.59238135814667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71050143241882</t>
   </si>
   <si>
     <t xml:space="preserve">1.71797752380371</t>
@@ -2729,178 +2729,178 @@
     <t xml:space="preserve">1.70601570606232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70003509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013132572174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956875801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7478814125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7254536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077530860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656405448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78675651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85404002666473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002111434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871773719788</t>
+    <t xml:space="preserve">1.70003521442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956863880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74788153171539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545349597931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78077566623688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80021286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78675639629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85404014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002039909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871785640717</t>
   </si>
   <si>
     <t xml:space="preserve">1.83310723304749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73292911052704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76881396770477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83161246776581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85104978084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609795570374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85852563381195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89291501045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90786695480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90039098262787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88992464542389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90487635135651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543903827667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301168680191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7912415266037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85553514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81666016578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8076890707016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928030490875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80170845985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84805929660797</t>
+    <t xml:space="preserve">1.79423213005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73292934894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83161211013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85104966163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264053821564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609747886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85852551460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89291477203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90786707401276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90039110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141964912415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88992476463318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90487670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011698722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124176502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85553526878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81666052341461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80768883228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928006649017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460259437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80170834064484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84805917739868</t>
   </si>
   <si>
     <t xml:space="preserve">1.84506893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87646794319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058344364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83908808231354</t>
+    <t xml:space="preserve">1.87646806240082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058356285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83908832073212</t>
   </si>
   <si>
     <t xml:space="preserve">1.82862162590027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82114565372467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778542041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947228908539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70900595188141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7134917974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508315086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059718608856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497282028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207808971405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78227078914642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76582360267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7463858127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75685226917267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72246313095093</t>
+    <t xml:space="preserve">1.82114601135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778518199921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947264671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7090060710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71349203586578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508303165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059754371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442435264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395813465118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497270107269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.782271027565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7658234834671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75685238838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72246301174164</t>
   </si>
   <si>
     <t xml:space="preserve">1.63424670696259</t>
@@ -2912,94 +2912,94 @@
     <t xml:space="preserve">1.59836184978485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74937629699707</t>
+    <t xml:space="preserve">1.74937653541565</t>
   </si>
   <si>
     <t xml:space="preserve">1.75984275341034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72694885730743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75386214256287</t>
+    <t xml:space="preserve">1.72694849967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75386190414429</t>
   </si>
   <si>
     <t xml:space="preserve">1.80469858646393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80918395519257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8196507692337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86301147937775</t>
+    <t xml:space="preserve">1.80918431282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">1.91235268115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93926644325256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.966179728508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99159801006317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216045856476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00056934356689</t>
+    <t xml:space="preserve">1.93926620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617937088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9915976524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216010093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00056910514832</t>
   </si>
   <si>
     <t xml:space="preserve">2.01345634460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01497268676758</t>
+    <t xml:space="preserve">2.014972448349</t>
   </si>
   <si>
     <t xml:space="preserve">2.04074692726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02710175514221</t>
+    <t xml:space="preserve">2.02710151672363</t>
   </si>
   <si>
     <t xml:space="preserve">2.03316617012024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99677860736847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00890779495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00132703781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03164982795715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01800465583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00435948371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01042413711548</t>
+    <t xml:space="preserve">1.99677848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00890755653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00132727622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981069564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03165006637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01800441741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00435924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0104238986969</t>
   </si>
   <si>
     <t xml:space="preserve">2.0301342010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468251228333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681181907654</t>
+    <t xml:space="preserve">2.03468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681205749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.05136036872864</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">2.04377937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07561850547791</t>
+    <t xml:space="preserve">2.07561874389648</t>
   </si>
   <si>
     <t xml:space="preserve">2.06803774833679</t>
@@ -3017,19 +3017,19 @@
     <t xml:space="preserve">2.10442566871643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05287647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12261986732483</t>
+    <t xml:space="preserve">2.05287623405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12261962890625</t>
   </si>
   <si>
     <t xml:space="preserve">2.21358919143677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19084668159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16203951835632</t>
+    <t xml:space="preserve">2.19084692001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16203999519348</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
@@ -3038,22 +3038,22 @@
     <t xml:space="preserve">2.13323259353638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1559751033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18023347854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20145988464355</t>
+    <t xml:space="preserve">2.15597534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18023324012756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20145964622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.27120304107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18933057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26362228393555</t>
+    <t xml:space="preserve">2.18933033943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26362180709839</t>
   </si>
   <si>
     <t xml:space="preserve">2.24846076965332</t>
@@ -3062,58 +3062,58 @@
     <t xml:space="preserve">2.21510481834412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21662163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29546189308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30000996589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32275247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31062316894531</t>
+    <t xml:space="preserve">2.21662139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29546141624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30001020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3227527141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31062293052673</t>
   </si>
   <si>
     <t xml:space="preserve">2.34246230125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35762357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35914015769958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38794732093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36368870735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39249587059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639764785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491463661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36520481109619</t>
+    <t xml:space="preserve">2.35762405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34852719306946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35913991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38794708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39249563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639788627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36520457267761</t>
   </si>
   <si>
     <t xml:space="preserve">2.36823701858521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32426834106445</t>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32426857948303</t>
   </si>
   <si>
     <t xml:space="preserve">2.35459136962891</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">2.34549498558044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.380366563797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44101238250732</t>
+    <t xml:space="preserve">2.38036632537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4410126209259</t>
   </si>
   <si>
     <t xml:space="preserve">2.36065649986267</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">2.3727855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.318204164505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40007638931274</t>
+    <t xml:space="preserve">2.31820392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40007615089417</t>
   </si>
   <si>
     <t xml:space="preserve">2.40765714645386</t>
@@ -3149,49 +3149,49 @@
     <t xml:space="preserve">2.41978621482849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4940779209137</t>
+    <t xml:space="preserve">2.49407815933228</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827034950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614104270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30759119987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32730054855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34397840499878</t>
+    <t xml:space="preserve">2.41827011108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42888307571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3075909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32730078697205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3439781665802</t>
   </si>
   <si>
     <t xml:space="preserve">2.35610795021057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45314192771912</t>
+    <t xml:space="preserve">2.45314168930054</t>
   </si>
   <si>
     <t xml:space="preserve">2.51682066917419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48649740219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49862694740295</t>
+    <t xml:space="preserve">2.48649764060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49862623214722</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043274879456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44859313964844</t>
+    <t xml:space="preserve">2.44859337806702</t>
   </si>
   <si>
     <t xml:space="preserve">2.54714345932007</t>
@@ -3200,19 +3200,19 @@
     <t xml:space="preserve">2.58959603309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56685352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266157150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65327453613281</t>
+    <t xml:space="preserve">2.56685376167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266180992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65327429771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.61355948448181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52038192749023</t>
+    <t xml:space="preserve">2.52038168907166</t>
   </si>
   <si>
     <t xml:space="preserve">2.50052428245544</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">2.5157995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51427173614502</t>
+    <t xml:space="preserve">2.51427149772644</t>
   </si>
   <si>
     <t xml:space="preserve">2.49899673461914</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412914276123</t>
+    <t xml:space="preserve">2.53412938117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.60286688804626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46386432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44553375244141</t>
+    <t xml:space="preserve">2.46386408805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42109370231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44553399085999</t>
   </si>
   <si>
     <t xml:space="preserve">2.43942379951477</t>
@@ -3254,34 +3254,34 @@
     <t xml:space="preserve">2.48066663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41192865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38443398475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42262125015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46691942214966</t>
+    <t xml:space="preserve">2.41192889213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38443374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42262148857117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46691918373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.45775413513184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43025875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45928120613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43331432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45622658729553</t>
+    <t xml:space="preserve">2.43025898933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45928168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706130027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43331408500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45622634887695</t>
   </si>
   <si>
     <t xml:space="preserve">2.48372149467468</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">2.5081615447998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54023909568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65938472747803</t>
+    <t xml:space="preserve">2.54023933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65938448905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.6486918926239</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">2.65632963180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68382430076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.735759973526</t>
+    <t xml:space="preserve">2.68382453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73575973510742</t>
   </si>
   <si>
     <t xml:space="preserve">2.6884069442749</t>
@@ -3326,73 +3326,73 @@
     <t xml:space="preserve">2.63952708244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61966943740845</t>
+    <t xml:space="preserve">2.61966919898987</t>
   </si>
   <si>
     <t xml:space="preserve">2.59370183944702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54634928703308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53565669059753</t>
+    <t xml:space="preserve">2.54634952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53565692901611</t>
   </si>
   <si>
     <t xml:space="preserve">2.51885414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54482197761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260159492493</t>
+    <t xml:space="preserve">2.54482173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260135650635</t>
   </si>
   <si>
     <t xml:space="preserve">2.5066339969635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54329395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46997427940369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4913592338562</t>
+    <t xml:space="preserve">2.58148217201233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54329419136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46997404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49135899543762</t>
   </si>
   <si>
     <t xml:space="preserve">2.48830413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48219394683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40734624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41040134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38290643692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48524928092957</t>
+    <t xml:space="preserve">2.48219418525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40734601020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4104015827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38290619850159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.4424786567688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47455668449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52801942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4898316860199</t>
+    <t xml:space="preserve">2.47455644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52801918983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48983192443848</t>
   </si>
   <si>
     <t xml:space="preserve">2.52649164199829</t>
@@ -3401,31 +3401,31 @@
     <t xml:space="preserve">2.52496433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55856943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5539870262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54787659645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56162452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5295467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51732683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4516441822052</t>
+    <t xml:space="preserve">2.55856919288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55398678779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54787683486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56162428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52954697608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51732635498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45164394378662</t>
   </si>
   <si>
     <t xml:space="preserve">2.42873167991638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42414903640747</t>
+    <t xml:space="preserve">2.42414927482605</t>
   </si>
   <si>
     <t xml:space="preserve">2.42567658424377</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">2.40581893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510621070862</t>
+    <t xml:space="preserve">2.50510692596436</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221336364746</t>
+    <t xml:space="preserve">2.38596129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221360206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.40887403488159</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">2.37355303764343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36727356910706</t>
+    <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
     <t xml:space="preserve">2.4253568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43791484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42378687858582</t>
+    <t xml:space="preserve">2.43791508674622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42378711700439</t>
   </si>
   <si>
     <t xml:space="preserve">2.40965890884399</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">2.35157561302185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35000586509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34372663497925</t>
+    <t xml:space="preserve">2.35000610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34372639656067</t>
   </si>
   <si>
     <t xml:space="preserve">2.34058737754822</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">2.33116841316223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35471534729004</t>
+    <t xml:space="preserve">2.35471510887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.34686636924744</t>
@@ -3506,37 +3506,37 @@
     <t xml:space="preserve">2.4473340511322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4394850730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47402095794678</t>
+    <t xml:space="preserve">2.43948531150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47402048110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.45361351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4410548210144</t>
+    <t xml:space="preserve">2.44105505943298</t>
   </si>
   <si>
     <t xml:space="preserve">2.45675325393677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46931171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46774172782898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48814916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50384712219238</t>
+    <t xml:space="preserve">2.46931147575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4677414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4881489276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50384736061096</t>
   </si>
   <si>
     <t xml:space="preserve">2.45047378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27622485160828</t>
+    <t xml:space="preserve">2.27622509002686</t>
   </si>
   <si>
     <t xml:space="preserve">2.26837587356567</t>
@@ -3548,67 +3548,67 @@
     <t xml:space="preserve">2.2573869228363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31547045707703</t>
+    <t xml:space="preserve">2.31547021865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.29977202415466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29192328453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27151584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36256432533264</t>
+    <t xml:space="preserve">2.29192304611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27151536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36256408691406</t>
   </si>
   <si>
     <t xml:space="preserve">2.31076097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32017946243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26994585990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2291305065155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22442150115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24639868736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20244383811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15063977241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14122152328491</t>
+    <t xml:space="preserve">2.32017970085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26994562149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22913074493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22442102432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24639844894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20244359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15064024925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005921363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14122104644775</t>
   </si>
   <si>
     <t xml:space="preserve">2.20401382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773435592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16319823265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17732691764832</t>
+    <t xml:space="preserve">2.19773411750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16319847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17732644081116</t>
   </si>
   <si>
     <t xml:space="preserve">2.18674564361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18203616142273</t>
+    <t xml:space="preserve">2.18203639984131</t>
   </si>
   <si>
     <t xml:space="preserve">2.16633820533752</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">2.15534973144531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14750051498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15848922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21814179420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21186280250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23070025444031</t>
+    <t xml:space="preserve">2.14750027656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15848898887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21814203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21186304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23070049285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.21657204627991</t>
@@ -3638,46 +3638,46 @@
     <t xml:space="preserve">2.22756099700928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26366639137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860971450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29349279403687</t>
+    <t xml:space="preserve">2.26366662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860947608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29349231719971</t>
   </si>
   <si>
     <t xml:space="preserve">2.24796843528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23540997505188</t>
+    <t xml:space="preserve">2.2354097366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.24011921882629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24482893943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291152000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34529638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11924386024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20087432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18831562995911</t>
+    <t xml:space="preserve">2.24482846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291128158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34529662132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11924409866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20087361335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18831539154053</t>
   </si>
   <si>
     <t xml:space="preserve">2.22128176689148</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">2.23227024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23697948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19930410385132</t>
+    <t xml:space="preserve">2.23697972297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19930386543274</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599101066589</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">2.09255695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05802130699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441377162933</t>
+    <t xml:space="preserve">2.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953104972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441389083862</t>
   </si>
   <si>
     <t xml:space="preserve">2.0109269618988</t>
@@ -3722,25 +3722,25 @@
     <t xml:space="preserve">1.92615723609924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84766685962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80057227611542</t>
+    <t xml:space="preserve">1.84766662120819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.800572514534</t>
   </si>
   <si>
     <t xml:space="preserve">1.87592327594757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82254958152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807429790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91202867031097</t>
+    <t xml:space="preserve">1.822549700737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807405948639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045916080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91202914714813</t>
   </si>
   <si>
     <t xml:space="preserve">2.00935697555542</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">1.99365890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97796082496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01720643043518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9920893907547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9889497756958</t>
+    <t xml:space="preserve">1.97796070575714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877617835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0172061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99208915233612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894953727722</t>
   </si>
   <si>
     <t xml:space="preserve">1.99679851531982</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">2.05959129333496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01249647140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01406645774841</t>
+    <t xml:space="preserve">2.01249670982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01406669616699</t>
   </si>
   <si>
     <t xml:space="preserve">1.96854197978973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97639119625092</t>
+    <t xml:space="preserve">1.97639095783234</t>
   </si>
   <si>
     <t xml:space="preserve">1.88220262527466</t>
@@ -3791,16 +3791,16 @@
     <t xml:space="preserve">1.91516852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92301738262177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790058135986</t>
+    <t xml:space="preserve">1.92301750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790034294128</t>
   </si>
   <si>
     <t xml:space="preserve">1.89947056770325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92124760150909</t>
+    <t xml:space="preserve">1.92124783992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.93576598167419</t>
@@ -3812,106 +3812,106 @@
     <t xml:space="preserve">2.01158356666565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96964204311371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543747901917</t>
+    <t xml:space="preserve">1.96964180469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092691898346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543771743774</t>
   </si>
   <si>
     <t xml:space="preserve">1.87608003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92770040035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91156911849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189015865326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221155643463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84704339504242</t>
+    <t xml:space="preserve">1.92770028114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91156888008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189003944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221119880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.847043633461</t>
   </si>
   <si>
     <t xml:space="preserve">1.8260725736618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77122604846954</t>
+    <t xml:space="preserve">1.77122616767883</t>
   </si>
   <si>
     <t xml:space="preserve">1.79703617095947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81316757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90672993659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94383180141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963458061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89382457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91802155971527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9325395822525</t>
+    <t xml:space="preserve">1.81316733360291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801421642303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90672957897186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94383203983307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963469982147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89382445812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91802167892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93253970146179</t>
   </si>
   <si>
     <t xml:space="preserve">1.91479516029358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9631894826889</t>
+    <t xml:space="preserve">1.96318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">1.98254692554474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02932810783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609448432922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448868751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01480984687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97770762443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99061274528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415296077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82929873466492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285363674164</t>
+    <t xml:space="preserve">2.02932834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609484195709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01481008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448122501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97770738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99061262607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93415307998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124049663544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8292989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285387516022</t>
   </si>
   <si>
     <t xml:space="preserve">1.88898503780365</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">1.86317467689514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85833537578583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8438173532486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672211647034</t>
+    <t xml:space="preserve">1.85833513736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381699562073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85672223567963</t>
   </si>
   <si>
     <t xml:space="preserve">1.88253271579742</t>
@@ -3935,22 +3935,22 @@
     <t xml:space="preserve">1.87769329547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8486567735672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8018753528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81155467033386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993371009827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78574419021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8180068731308</t>
+    <t xml:space="preserve">1.84865665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80187547206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81155455112457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78574407100677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81800675392151</t>
   </si>
   <si>
     <t xml:space="preserve">1.86962747573853</t>
@@ -3959,67 +3959,67 @@
     <t xml:space="preserve">1.8357515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82768583297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90350341796875</t>
+    <t xml:space="preserve">1.82768595218658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90350329875946</t>
   </si>
   <si>
     <t xml:space="preserve">1.93899238109589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95189774036407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383914470673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96802854537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99222600460052</t>
+    <t xml:space="preserve">1.9518975019455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96802890300751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9922262430191</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643033027649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07449579238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05029916763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05191206932068</t>
+    <t xml:space="preserve">2.0744960308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05029892921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0519118309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.03416752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01319646835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07288289070129</t>
+    <t xml:space="preserve">2.01319670677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07288265228271</t>
   </si>
   <si>
     <t xml:space="preserve">2.09546685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07933568954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07610893249512</t>
+    <t xml:space="preserve">2.07933521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0761091709137</t>
   </si>
   <si>
     <t xml:space="preserve">2.00351762771606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00835728645325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98899960517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9551237821579</t>
+    <t xml:space="preserve">2.00835704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9889999628067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512390136719</t>
   </si>
   <si>
     <t xml:space="preserve">1.97932076454163</t>
@@ -4031,91 +4031,91 @@
     <t xml:space="preserve">1.91318237781525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92931318283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97286832332611</t>
+    <t xml:space="preserve">1.92931354045868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9728684425354</t>
   </si>
   <si>
     <t xml:space="preserve">1.96480274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9454448223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83736479282379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91025602817535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82647299766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81474304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78290557861328</t>
+    <t xml:space="preserve">1.94544470310211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8373646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91025590896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82647287845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85495913028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81474316120148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78290569782257</t>
   </si>
   <si>
     <t xml:space="preserve">1.78458142280579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79128408432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77620279788971</t>
+    <t xml:space="preserve">1.79128384590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77620303630829</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73933827877045</t>
+    <t xml:space="preserve">1.73933839797974</t>
   </si>
   <si>
     <t xml:space="preserve">1.74604117870331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79798650741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79966223239899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333727836609</t>
+    <t xml:space="preserve">1.79798662662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7996621131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.83820247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85663497447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86166167259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87674295902252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87171590328217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89517509937286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360747814178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93203973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89685082435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355336666107</t>
+    <t xml:space="preserve">1.8566347360611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86166155338287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87674260139465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87171566486359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89517533779144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360723972321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93203949928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8968505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355348587036</t>
   </si>
   <si>
     <t xml:space="preserve">1.92701268196106</t>
@@ -4124,40 +4124,40 @@
     <t xml:space="preserve">1.94879627227783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94376933574677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09625506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1783618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19176745414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1616051197052</t>
+    <t xml:space="preserve">1.94376945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09625458717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836213111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19176721572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16160535812378</t>
   </si>
   <si>
     <t xml:space="preserve">2.18506479263306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29901003837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29230737686157</t>
+    <t xml:space="preserve">2.29900979995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29230713844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3258204460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33419919013977</t>
+    <t xml:space="preserve">2.32582068443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33419871330261</t>
   </si>
   <si>
     <t xml:space="preserve">2.3425772190094</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">2.32917189598083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25711822509766</t>
+    <t xml:space="preserve">2.25711846351624</t>
   </si>
   <si>
     <t xml:space="preserve">2.2939829826355</t>
@@ -4175,13 +4175,13 @@
     <t xml:space="preserve">2.30906391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3006854057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31576633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29733467102051</t>
+    <t xml:space="preserve">2.30068564414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31576657295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29733443260193</t>
   </si>
   <si>
     <t xml:space="preserve">2.31409072875977</t>
@@ -4190,46 +4190,46 @@
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33755040168762</t>
+    <t xml:space="preserve">2.33754992485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.42636013031006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46657633781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46490025520325</t>
+    <t xml:space="preserve">2.44981932640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46657609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46490049362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.4799816608429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4632248878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4330632686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38614416122437</t>
+    <t xml:space="preserve">2.46322512626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43306303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38614439964294</t>
   </si>
   <si>
     <t xml:space="preserve">2.40122532844543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40290069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609052658081</t>
+    <t xml:space="preserve">2.40290117263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609028816223</t>
   </si>
   <si>
     <t xml:space="preserve">2.38279318809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41295528411865</t>
+    <t xml:space="preserve">2.41295480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.35430669784546</t>
@@ -4253,22 +4253,22 @@
     <t xml:space="preserve">2.38782000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49171137809753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45987367630005</t>
+    <t xml:space="preserve">2.49171113967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45987391471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371069908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68776369094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6492235660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77824950218201</t>
+    <t xml:space="preserve">2.68776345252991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64922332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77824926376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.80170893669128</t>
@@ -4277,13 +4277,13 @@
     <t xml:space="preserve">2.77322268486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78160047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83019495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93073487281799</t>
+    <t xml:space="preserve">2.78160095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83019542694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93073511123657</t>
   </si>
   <si>
     <t xml:space="preserve">2.92905926704407</t>
@@ -4295,16 +4295,16 @@
     <t xml:space="preserve">2.9642481803894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03295040130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06311202049255</t>
+    <t xml:space="preserve">3.03295016288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06311225891113</t>
   </si>
   <si>
     <t xml:space="preserve">3.11840915679932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1502468585968</t>
+    <t xml:space="preserve">3.15024662017822</t>
   </si>
   <si>
     <t xml:space="preserve">3.16030097007751</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">3.20554351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20219206809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1435444355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20889472961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18878698348999</t>
+    <t xml:space="preserve">3.20219230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14354419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20889520645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18878722190857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19213843345642</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">3.1988410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17705726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29267835617065</t>
+    <t xml:space="preserve">3.17705750465393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2926778793335</t>
   </si>
   <si>
     <t xml:space="preserve">3.30608367919922</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">3.25581336021423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34797501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3178129196167</t>
+    <t xml:space="preserve">3.34797477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31781339645386</t>
   </si>
   <si>
     <t xml:space="preserve">3.39321804046631</t>
@@ -4364,10 +4364,10 @@
     <t xml:space="preserve">3.3647313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35467767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18543577194214</t>
+    <t xml:space="preserve">3.3546781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18543553352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24240827560425</t>
@@ -4376,40 +4376,40 @@
     <t xml:space="preserve">3.13851737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23235416412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13348984718323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19046306610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23403024673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24575972557068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2390570640564</t>
+    <t xml:space="preserve">3.23235440254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13349008560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1904628276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23402976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2457594871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23905682563782</t>
   </si>
   <si>
     <t xml:space="preserve">3.2155978679657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26419186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29770517349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29435396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34294819831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43510913848877</t>
+    <t xml:space="preserve">3.26419162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29770541191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.294353723526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34294772148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43510961532593</t>
   </si>
   <si>
     <t xml:space="preserve">3.30105662345886</t>
@@ -4418,34 +4418,34 @@
     <t xml:space="preserve">3.40159606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38986682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38484001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37981271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36640739440918</t>
+    <t xml:space="preserve">3.38986659049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38483929634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37981247901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36640763282776</t>
   </si>
   <si>
     <t xml:space="preserve">3.37143445014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32619166374207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31243991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23508644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2178966999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22305393218994</t>
+    <t xml:space="preserve">3.32619142532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31243968009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23508620262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21789693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22305369377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.20414519309998</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">3.21445894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19555044174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16976571083069</t>
+    <t xml:space="preserve">3.19554996490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16976594924927</t>
   </si>
   <si>
     <t xml:space="preserve">3.25571417808533</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">3.12335419654846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05975198745728</t>
+    <t xml:space="preserve">3.05975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">3.09413146972656</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">3.08897495269775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10616421699524</t>
+    <t xml:space="preserve">3.10616445541382</t>
   </si>
   <si>
     <t xml:space="preserve">3.13366746902466</t>
@@ -4490,16 +4490,16 @@
     <t xml:space="preserve">3.18867468833923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22649145126343</t>
+    <t xml:space="preserve">3.22649168968201</t>
   </si>
   <si>
     <t xml:space="preserve">3.2660276889801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24024319648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09928846359253</t>
+    <t xml:space="preserve">3.24024343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09928822517395</t>
   </si>
   <si>
     <t xml:space="preserve">3.16117119789124</t>
@@ -4508,31 +4508,31 @@
     <t xml:space="preserve">3.19383144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15257596969604</t>
+    <t xml:space="preserve">3.1525764465332</t>
   </si>
   <si>
     <t xml:space="preserve">3.11991596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09756946563721</t>
+    <t xml:space="preserve">3.09756970405579</t>
   </si>
   <si>
     <t xml:space="preserve">3.06834721565247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15429544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14741921424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12507271766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18695569038391</t>
+    <t xml:space="preserve">3.15429520606995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14741945266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10960245132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12507295608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">3.17664194107056</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">3.14398145675659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27462244033813</t>
+    <t xml:space="preserve">3.27462267875671</t>
   </si>
   <si>
     <t xml:space="preserve">3.24196267127991</t>
@@ -4550,46 +4550,46 @@
     <t xml:space="preserve">3.1903932094574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19898796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15601420402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26258969306946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27290368080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13538694381714</t>
+    <t xml:space="preserve">3.19898819923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15601396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26258993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12851071357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13538646697998</t>
   </si>
   <si>
     <t xml:space="preserve">3.10272622108459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08209896087646</t>
+    <t xml:space="preserve">3.08209872245789</t>
   </si>
   <si>
     <t xml:space="preserve">3.04084372520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04771947860718</t>
+    <t xml:space="preserve">3.04771971702576</t>
   </si>
   <si>
     <t xml:space="preserve">3.05631422996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01677846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00818371772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01162147521973</t>
+    <t xml:space="preserve">3.01677823066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0081832408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01162123680115</t>
   </si>
   <si>
     <t xml:space="preserve">3.03396773338318</t>
@@ -4598,37 +4598,37 @@
     <t xml:space="preserve">2.98755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07350420951843</t>
+    <t xml:space="preserve">2.98583674430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07350397109985</t>
   </si>
   <si>
     <t xml:space="preserve">3.07006621360779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05287647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9755232334137</t>
+    <t xml:space="preserve">3.05287671089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97552299499512</t>
   </si>
   <si>
     <t xml:space="preserve">2.94458198547363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93083024024963</t>
+    <t xml:space="preserve">2.93083000183105</t>
   </si>
   <si>
     <t xml:space="preserve">2.92051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87582325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87754225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88785600662231</t>
+    <t xml:space="preserve">2.87582349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87754249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88785624504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.91020250320435</t>
@@ -4640,40 +4640,40 @@
     <t xml:space="preserve">2.98411774635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005272865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94286274909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99786949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05115747451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03052997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05459547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08725571632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04256248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02021646499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99615049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03912496566772</t>
+    <t xml:space="preserve">2.96005249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94286298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99786996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0511577129364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03053021430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04943895339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05459523200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08725595474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04256272315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02021622657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99615073204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03912472724915</t>
   </si>
   <si>
     <t xml:space="preserve">3.06490921974182</t>
@@ -4748,22 +4748,22 @@
     <t xml:space="preserve">2.32473492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28554391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33720445632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36392593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26060438156128</t>
+    <t xml:space="preserve">2.2855441570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33720469474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36392569541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2606041431427</t>
   </si>
   <si>
     <t xml:space="preserve">2.27663683891296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29445123672485</t>
+    <t xml:space="preserve">2.29445099830627</t>
   </si>
   <si>
     <t xml:space="preserve">2.38708424568176</t>
@@ -4781,10 +4781,10 @@
     <t xml:space="preserve">2.3710515499115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35323715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35145616531372</t>
+    <t xml:space="preserve">2.35323739051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35145592689514</t>
   </si>
   <si>
     <t xml:space="preserve">2.43161916732788</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">2.38173985481262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39955401420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42449355125427</t>
+    <t xml:space="preserve">2.39955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42449378967285</t>
   </si>
   <si>
     <t xml:space="preserve">2.34254908561707</t>
@@ -4814,19 +4814,19 @@
     <t xml:space="preserve">2.37461400032043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3603630065918</t>
+    <t xml:space="preserve">2.36036324501038</t>
   </si>
   <si>
     <t xml:space="preserve">2.41380524635315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51534509658813</t>
+    <t xml:space="preserve">2.51534533500671</t>
   </si>
   <si>
     <t xml:space="preserve">2.49931287765503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56522488594055</t>
+    <t xml:space="preserve">2.56522464752197</t>
   </si>
   <si>
     <t xml:space="preserve">2.53494071960449</t>
@@ -4835,19 +4835,19 @@
     <t xml:space="preserve">2.52068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4975311756134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50287532806396</t>
+    <t xml:space="preserve">2.49753141403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50287556648254</t>
   </si>
   <si>
     <t xml:space="preserve">2.57056879997253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60085296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58303904533386</t>
+    <t xml:space="preserve">2.60085320472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58303880691528</t>
   </si>
   <si>
     <t xml:space="preserve">2.64360666275024</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">2.65785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65073251724243</t>
+    <t xml:space="preserve">2.65073227882385</t>
   </si>
   <si>
     <t xml:space="preserve">2.67567205429077</t>
@@ -4868,13 +4868,13 @@
     <t xml:space="preserve">2.65963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65251350402832</t>
+    <t xml:space="preserve">2.6525137424469</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291811943054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55453634262085</t>
+    <t xml:space="preserve">2.55453658103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.61510419845581</t>
@@ -4883,10 +4883,10 @@
     <t xml:space="preserve">2.65429496765137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60441565513611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60619711875916</t>
+    <t xml:space="preserve">2.60441541671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60619735717773</t>
   </si>
   <si>
     <t xml:space="preserve">2.59550857543945</t>
@@ -4895,10 +4895,10 @@
     <t xml:space="preserve">2.74336528778076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7166440486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68992328643799</t>
+    <t xml:space="preserve">2.71664428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68992304801941</t>
   </si>
   <si>
     <t xml:space="preserve">2.70773720741272</t>
@@ -4913,7 +4913,7 @@
     <t xml:space="preserve">2.77721214294434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76830506324768</t>
+    <t xml:space="preserve">2.76830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">2.7718677520752</t>
@@ -4922,16 +4922,16 @@
     <t xml:space="preserve">2.76474237442017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72911381721497</t>
+    <t xml:space="preserve">2.72911405563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.74692821502686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72020697593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75049114227295</t>
+    <t xml:space="preserve">2.72020673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75049138069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.76117944717407</t>
@@ -4943,22 +4943,22 @@
     <t xml:space="preserve">2.8235285282135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.848468542099</t>
+    <t xml:space="preserve">2.84846830368042</t>
   </si>
   <si>
     <t xml:space="preserve">2.77008628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81284022331238</t>
+    <t xml:space="preserve">2.8128399848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.80927729606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80749583244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81996560096741</t>
+    <t xml:space="preserve">2.80749607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81996583938599</t>
   </si>
   <si>
     <t xml:space="preserve">2.81105875968933</t>
@@ -4976,16 +4976,16 @@
     <t xml:space="preserve">2.75761651992798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63469934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5527548789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54741072654724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5313777923584</t>
+    <t xml:space="preserve">2.63469958305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55275464057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54741048812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53137803077698</t>
   </si>
   <si>
     <t xml:space="preserve">2.5420663356781</t>
@@ -5003,16 +5003,16 @@
     <t xml:space="preserve">2.51178240776062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50821995735168</t>
+    <t xml:space="preserve">2.50821971893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.60263419151306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61154127120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55988073348999</t>
+    <t xml:space="preserve">2.61154103279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55988049507141</t>
   </si>
   <si>
     <t xml:space="preserve">2.58482027053833</t>
@@ -5027,13 +5027,13 @@
     <t xml:space="preserve">2.5866014957428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56700611114502</t>
+    <t xml:space="preserve">2.5670063495636</t>
   </si>
   <si>
     <t xml:space="preserve">2.51890826225281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46724724769592</t>
+    <t xml:space="preserve">2.46724700927734</t>
   </si>
   <si>
     <t xml:space="preserve">2.47081017494202</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">2.61521983146667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62438941001892</t>
+    <t xml:space="preserve">2.6243896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.67390608787537</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">2.61888742446899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62255549430847</t>
+    <t xml:space="preserve">2.62255525588989</t>
   </si>
   <si>
     <t xml:space="preserve">2.63172507286072</t>
@@ -5102,7 +5102,7 @@
     <t xml:space="preserve">2.5510311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60604953765869</t>
+    <t xml:space="preserve">2.60604977607727</t>
   </si>
   <si>
     <t xml:space="preserve">2.58404231071472</t>
@@ -5111,7 +5111,7 @@
     <t xml:space="preserve">2.5675368309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57487273216248</t>
+    <t xml:space="preserve">2.5748724937439</t>
   </si>
   <si>
     <t xml:space="preserve">2.60054802894592</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">2.54736351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57670640945435</t>
+    <t xml:space="preserve">2.57670664787292</t>
   </si>
   <si>
     <t xml:space="preserve">2.51802015304565</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">2.51251816749573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53269147872925</t>
+    <t xml:space="preserve">2.53269171714783</t>
   </si>
   <si>
     <t xml:space="preserve">2.58037447929382</t>
@@ -5156,7 +5156,7 @@
     <t xml:space="preserve">2.59321236610413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64089512825012</t>
+    <t xml:space="preserve">2.64089488983154</t>
   </si>
   <si>
     <t xml:space="preserve">2.60238218307495</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">2.56937074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5877103805542</t>
+    <t xml:space="preserve">2.58771014213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.61338567733765</t>
@@ -5183,10 +5183,10 @@
     <t xml:space="preserve">2.47583889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4868426322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47950673103333</t>
+    <t xml:space="preserve">2.48684239387512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4795069694519</t>
   </si>
   <si>
     <t xml:space="preserve">2.45383167266846</t>
@@ -5213,7 +5213,7 @@
     <t xml:space="preserve">2.34196043014526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34562826156616</t>
+    <t xml:space="preserve">2.34562802314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462452888489</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">2.33645844459534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31261682510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31078314781189</t>
+    <t xml:space="preserve">2.31261706352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31078338623047</t>
   </si>
   <si>
     <t xml:space="preserve">2.27777194976807</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">2.30344724655151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32728886604309</t>
+    <t xml:space="preserve">2.32728862762451</t>
   </si>
   <si>
     <t xml:space="preserve">2.34746217727661</t>
@@ -5255,16 +5255,16 @@
     <t xml:space="preserve">2.33095669746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36763572692871</t>
+    <t xml:space="preserve">2.36763548851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.35113000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39881300926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40248084068298</t>
+    <t xml:space="preserve">2.39881277084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4024806022644</t>
   </si>
   <si>
     <t xml:space="preserve">2.40981674194336</t>
@@ -5279,10 +5279,10 @@
     <t xml:space="preserve">2.46666932106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42815637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41531872749329</t>
+    <t xml:space="preserve">2.42815613746643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41531848907471</t>
   </si>
   <si>
     <t xml:space="preserve">2.42448830604553</t>
@@ -6012,6 +6012,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.97300004959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93299996852875</t>
   </si>
 </sst>
 </file>
@@ -71376,7 +71379,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911342593</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>554474</v>
@@ -71397,6 +71400,32 @@
         <v>1999</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910300926</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>895922</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>1.98099994659424</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>1.932000041008</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>1.97699999809265</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>1.93299996852875</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIA.MI.xlsx
+++ b/data/PIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="2002">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,175 +44,175 @@
     <t xml:space="preserve">PIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3917795419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36014819145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30827283859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27158045768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23931646347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21401154994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28676319122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23425543308258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20831775665283</t>
+    <t xml:space="preserve">1.39177966117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36014842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30827295780182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2715802192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23931634426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21401143074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28676354885101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23425531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20831739902496</t>
   </si>
   <si>
     <t xml:space="preserve">1.20009350776672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18680822849274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11595416069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09191405773163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17478859424591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15644228458405</t>
+    <t xml:space="preserve">1.18680846691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11595392227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09191429615021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17478847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15644240379333</t>
   </si>
   <si>
     <t xml:space="preserve">1.19440007209778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.232990026474</t>
+    <t xml:space="preserve">1.23299014568329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20641982555389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22097027301788</t>
+    <t xml:space="preserve">1.2209700345993</t>
   </si>
   <si>
     <t xml:space="preserve">1.24437737464905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16087031364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10646498203278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1172194480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12164759635925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04699790477753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04826283454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11848473548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11089313030243</t>
+    <t xml:space="preserve">1.16087055206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1064647436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11721932888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12164771556854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04699778556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04826295375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1184846162796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11089336872101</t>
   </si>
   <si>
     <t xml:space="preserve">1.13366770744324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17795169353485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19819593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21337854862213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16213595867157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20578718185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17921662330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13872861862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1317697763443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15770769119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24311220645905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29688537120819</t>
+    <t xml:space="preserve">1.17795145511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19819569587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21337878704071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20578730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17921686172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13872873783112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13177013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15770757198334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24311244487762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29688560962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.2918244600296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2994157075882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32598602771759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26525402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27917206287384</t>
+    <t xml:space="preserve">1.29941606521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32598626613617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26525413990021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27917194366455</t>
   </si>
   <si>
     <t xml:space="preserve">1.25892794132233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20199143886566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22413337230682</t>
+    <t xml:space="preserve">1.20199131965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22413349151611</t>
   </si>
   <si>
     <t xml:space="preserve">1.20135879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19376718997955</t>
+    <t xml:space="preserve">1.19376742839813</t>
   </si>
   <si>
     <t xml:space="preserve">1.18238008022308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20452189445496</t>
+    <t xml:space="preserve">1.20452201366425</t>
   </si>
   <si>
     <t xml:space="preserve">1.21464395523071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1918693780899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18554329872131</t>
+    <t xml:space="preserve">1.19186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18554306030273</t>
   </si>
   <si>
     <t xml:space="preserve">1.15264654159546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19123649597168</t>
+    <t xml:space="preserve">1.19123661518097</t>
   </si>
   <si>
     <t xml:space="preserve">1.1798495054245</t>
@@ -224,46 +224,46 @@
     <t xml:space="preserve">1.11152565479279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09571015834808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07546615600586</t>
+    <t xml:space="preserve">1.09571003913879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07546603679657</t>
   </si>
   <si>
     <t xml:space="preserve">1.10709738731384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12417817115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14062666893005</t>
+    <t xml:space="preserve">1.12417840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14062643051147</t>
   </si>
   <si>
     <t xml:space="preserve">1.16719698905945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15454435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19227039813995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17405807971954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24820899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25406277179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27812957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26837289333344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28918707370758</t>
+    <t xml:space="preserve">1.15454423427582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19227051734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17405784130096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2482088804245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25406289100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27812969684601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26837265491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28918719291687</t>
   </si>
   <si>
     <t xml:space="preserve">1.28138172626495</t>
@@ -272,61 +272,61 @@
     <t xml:space="preserve">1.27682876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25731527805328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2449563741684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19031894207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19096946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17796063423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12527418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16690301895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17080545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16755318641663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16495156288147</t>
+    <t xml:space="preserve">1.25731515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19096958637238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17796051502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12527430057526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16690278053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17080557346344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16755342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16495180130005</t>
   </si>
   <si>
     <t xml:space="preserve">1.17340743541718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18056237697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15389406681061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1630003452301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16950488090515</t>
+    <t xml:space="preserve">1.1805624961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1538941860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16300010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16950452327728</t>
   </si>
   <si>
     <t xml:space="preserve">1.15649580955505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16169953346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1773099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18901813030243</t>
+    <t xml:space="preserve">1.16169941425323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17731034755707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1890184879303</t>
   </si>
   <si>
     <t xml:space="preserve">1.14283621311188</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">1.12852644920349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1103138923645</t>
+    <t xml:space="preserve">1.11031401157379</t>
   </si>
   <si>
     <t xml:space="preserve">1.0966545343399</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">1.10641133785248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10055732727051</t>
+    <t xml:space="preserve">1.1005574464798</t>
   </si>
   <si>
     <t xml:space="preserve">1.11486721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10250866413116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05112326145172</t>
+    <t xml:space="preserve">1.10250890254974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05112314224243</t>
   </si>
   <si>
     <t xml:space="preserve">1.05372524261475</t>
@@ -368,46 +368,46 @@
     <t xml:space="preserve">1.10185813903809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13177859783173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10120761394501</t>
+    <t xml:space="preserve">1.13177883625031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10120749473572</t>
   </si>
   <si>
     <t xml:space="preserve">1.12917697429657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05307459831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952255070209503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996485590934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99518483877182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02640628814697</t>
+    <t xml:space="preserve">1.05307447910309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952255189418793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996485769748688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995184659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02640640735626</t>
   </si>
   <si>
     <t xml:space="preserve">1.01339733600616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982826173305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976321876049042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96851634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97762268781662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975671648979187</t>
+    <t xml:space="preserve">0.982826292514801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976321637630463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96851646900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97762256860733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975671231746674</t>
   </si>
   <si>
     <t xml:space="preserve">1.00364065170288</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">0.980875015258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970467567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969166994094849</t>
+    <t xml:space="preserve">0.970467805862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969166874885559</t>
   </si>
   <si>
     <t xml:space="preserve">0.971118152141571</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">0.96591454744339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.958759605884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05437552928925</t>
+    <t xml:space="preserve">0.958759784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05437564849854</t>
   </si>
   <si>
     <t xml:space="preserve">1.05957889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0660834312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07974290847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05892825126648</t>
+    <t xml:space="preserve">1.06608366966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07974278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05892848968506</t>
   </si>
   <si>
     <t xml:space="preserve">1.06283116340637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06673395633698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09340226650238</t>
+    <t xml:space="preserve">1.06673407554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09340238571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.06022953987122</t>
@@ -464,190 +464,190 @@
     <t xml:space="preserve">1.08559691905975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09275197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1142166852951</t>
+    <t xml:space="preserve">1.09275186061859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11421680450439</t>
   </si>
   <si>
     <t xml:space="preserve">1.09795522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07779157161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07388889789581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10901308059692</t>
+    <t xml:space="preserve">1.07779169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0738890171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10901319980621</t>
   </si>
   <si>
     <t xml:space="preserve">1.11746907234192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14348673820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11877000331879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13828325271606</t>
+    <t xml:space="preserve">1.14348685741425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11876964569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13828313350677</t>
   </si>
   <si>
     <t xml:space="preserve">1.1454381942749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14023470878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12787616252899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14218604564667</t>
+    <t xml:space="preserve">1.14023435115814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12787580490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14218592643738</t>
   </si>
   <si>
     <t xml:space="preserve">1.15129208564758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16234970092773</t>
+    <t xml:space="preserve">1.16234982013702</t>
   </si>
   <si>
     <t xml:space="preserve">1.14803993701935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13438081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08299493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10315895080566</t>
+    <t xml:space="preserve">1.13438034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08299517631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10315907001495</t>
   </si>
   <si>
     <t xml:space="preserve">1.09600400924683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08169424533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09990704059601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09210169315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10511064529419</t>
+    <t xml:space="preserve">1.08169448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09990668296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0921014547348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1051105260849</t>
   </si>
   <si>
     <t xml:space="preserve">1.11356627941132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08949983119965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07584011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08234477043152</t>
+    <t xml:space="preserve">1.08949947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07584047317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08234488964081</t>
   </si>
   <si>
     <t xml:space="preserve">1.09925639629364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07518982887268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0875483751297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07453918457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05827808380127</t>
+    <t xml:space="preserve">1.08429610729218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07518970966339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08754825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0745393037796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05827820301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.05762779712677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07323861122131</t>
+    <t xml:space="preserve">1.07323837280273</t>
   </si>
   <si>
     <t xml:space="preserve">1.0693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05697751045227</t>
+    <t xml:space="preserve">1.05697727203369</t>
   </si>
   <si>
     <t xml:space="preserve">1.04722058773041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05047297477722</t>
+    <t xml:space="preserve">1.05047285556793</t>
   </si>
   <si>
     <t xml:space="preserve">1.06348180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0342116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01144587993622</t>
+    <t xml:space="preserve">1.03421175479889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01144599914551</t>
   </si>
   <si>
     <t xml:space="preserve">0.982175767421722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95680844783783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933392345905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931440770626068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936644494533539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949653506278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95355612039566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962662518024445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956158041954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957458734512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955507397651672</t>
+    <t xml:space="preserve">0.95680832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933392107486725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931440889835358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936644613742828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949653446674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.953555941581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962662398815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956157863140106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957458972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955507516860962</t>
   </si>
   <si>
     <t xml:space="preserve">0.98672890663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965264141559601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940547108650208</t>
+    <t xml:space="preserve">0.965264081954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940547168254852</t>
   </si>
   <si>
     <t xml:space="preserve">0.986078500747681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995835304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00429105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02315390110016</t>
+    <t xml:space="preserve">0.995835065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02315402030945</t>
   </si>
   <si>
     <t xml:space="preserve">1.03030896186829</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.03681337833405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02380430698395</t>
+    <t xml:space="preserve">1.02380442619324</t>
   </si>
   <si>
     <t xml:space="preserve">1.02120280265808</t>
@@ -668,94 +668,94 @@
     <t xml:space="preserve">1.04917204380035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02770721912384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0485212802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0335613489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03095960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03160965442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05567622184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05502605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03291094303131</t>
+    <t xml:space="preserve">1.02770709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04852139949799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03356111049652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03095936775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03160977363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05567634105682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05502593517303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03291070461273</t>
   </si>
   <si>
     <t xml:space="preserve">1.03551244735718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01860094070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999087393283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01925134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99193274974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00494158267975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02510511875153</t>
+    <t xml:space="preserve">1.01860082149506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999087333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01925146579742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991932511329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00494134426117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02510547637939</t>
   </si>
   <si>
     <t xml:space="preserve">0.999737918376923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989981114864349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994534313678741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988030016422272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946401357650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.952905833721161</t>
+    <t xml:space="preserve">0.989981174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994534432888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988029897212982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946401238441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952905714511871</t>
   </si>
   <si>
     <t xml:space="preserve">1.0166494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01404762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04136645793915</t>
+    <t xml:space="preserve">1.01404774188995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04136669635773</t>
   </si>
   <si>
     <t xml:space="preserve">1.0296585559845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991282105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00949454307556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01795053482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01469826698303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03226041793823</t>
+    <t xml:space="preserve">0.991282165050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00949478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01795041561127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01469814777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03226029872894</t>
   </si>
   <si>
     <t xml:space="preserve">1.07063663005829</t>
@@ -764,73 +764,73 @@
     <t xml:space="preserve">1.06218087673187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09470319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14478766918182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18251347541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23585033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23845207691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21633684635162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20983231067657</t>
+    <t xml:space="preserve">1.09470331668854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14478754997253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18251359462738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23585021495819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23845231533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21633696556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20983266830444</t>
   </si>
   <si>
     <t xml:space="preserve">1.21438550949097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24755835533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2130845785141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20072638988495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21893894672394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22023952007294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20527935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18381464481354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20267748832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18446516990662</t>
+    <t xml:space="preserve">1.24755847454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21308481693268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20072627067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21893882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22023963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20527923107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18381440639496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20267736911774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18446505069733</t>
   </si>
   <si>
     <t xml:space="preserve">1.16430115699768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17600917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21999955177307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22268414497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482929706573</t>
+    <t xml:space="preserve">1.17600929737091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21999967098236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22268390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482917785645</t>
   </si>
   <si>
     <t xml:space="preserve">1.27502715587616</t>
@@ -839,58 +839,58 @@
     <t xml:space="preserve">1.28777754306793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.266974568367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27435612678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24013161659241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24348700046539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24415791034698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22738122940063</t>
+    <t xml:space="preserve">1.26697432994843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27435624599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401317358017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24348711967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24415814876556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22738146781921</t>
   </si>
   <si>
     <t xml:space="preserve">1.24818432331085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25422418117523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27368521690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24147379398346</t>
+    <t xml:space="preserve">1.25422406196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2736850976944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24147391319275</t>
   </si>
   <si>
     <t xml:space="preserve">1.23006570339203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26831638813019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26294791698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31462001800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3099228143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3105936050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32200193405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34146273136139</t>
+    <t xml:space="preserve">1.26831650733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26294815540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31462025642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30992257595062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31059372425079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32200181484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34146296977997</t>
   </si>
   <si>
     <t xml:space="preserve">1.30455410480499</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">1.35555517673492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35018670558929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35689759254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34481799602509</t>
+    <t xml:space="preserve">1.35018658638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35689747333527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34481811523438</t>
   </si>
   <si>
     <t xml:space="preserve">1.3407918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32669937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32602834701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30388295650482</t>
+    <t xml:space="preserve">1.32669925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32602822780609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30388283729553</t>
   </si>
   <si>
     <t xml:space="preserve">1.30925154685974</t>
@@ -926,43 +926,43 @@
     <t xml:space="preserve">1.29650127887726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34213387966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287125825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31864666938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37300288677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37031865119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38239777088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3743451833725</t>
+    <t xml:space="preserve">1.34213364124298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32871246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31864643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37300300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37031888961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38239789009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37434542179108</t>
   </si>
   <si>
     <t xml:space="preserve">1.44010961055756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43876755237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45084655284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44816255569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4897688627243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46158373355865</t>
+    <t xml:space="preserve">1.43876731395721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45084667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44816243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48976874351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46158349514008</t>
   </si>
   <si>
     <t xml:space="preserve">1.46024179458618</t>
@@ -971,88 +971,88 @@
     <t xml:space="preserve">1.50721645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50453209877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53540134429932</t>
+    <t xml:space="preserve">1.50453186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53540122509003</t>
   </si>
   <si>
     <t xml:space="preserve">1.51929545402527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50050580501556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5058741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46829450130463</t>
+    <t xml:space="preserve">1.50050568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50587427616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46829462051392</t>
   </si>
   <si>
     <t xml:space="preserve">1.45755732059479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48037374019623</t>
+    <t xml:space="preserve">1.48037362098694</t>
   </si>
   <si>
     <t xml:space="preserve">1.44547832012177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44950473308563</t>
+    <t xml:space="preserve">1.44950461387634</t>
   </si>
   <si>
     <t xml:space="preserve">1.45621526241302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45889973640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44279384613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57566487789154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66290390491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62129771709442</t>
+    <t xml:space="preserve">1.45889949798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44279420375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57566523551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66290366649628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62129747867584</t>
   </si>
   <si>
     <t xml:space="preserve">1.58640241622925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59042859077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61727154254913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64411389827728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60787618160248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61458694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59713935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61995577812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64277184009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65350925922394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62398207187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64142990112305</t>
+    <t xml:space="preserve">1.59042835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61727142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64411401748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60787630081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61458683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59713959693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61995542049408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64277195930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65350914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62398183345795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64142978191376</t>
   </si>
   <si>
     <t xml:space="preserve">1.63069272041321</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">1.72330009937286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70987868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66558825969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70853638648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70719408988953</t>
+    <t xml:space="preserve">1.70987856388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66558790206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70853626728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70048344135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7071944475174</t>
   </si>
   <si>
     <t xml:space="preserve">1.72732603549957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69108891487122</t>
+    <t xml:space="preserve">1.69108879566193</t>
   </si>
   <si>
     <t xml:space="preserve">1.6857203245163</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">1.66692996025085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66424596309662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67632508277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65753519535065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6374032497406</t>
+    <t xml:space="preserve">1.66424584388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67632520198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65753543376923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63740336894989</t>
   </si>
   <si>
     <t xml:space="preserve">1.64679825305939</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">1.67364084720612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7649062871933</t>
+    <t xml:space="preserve">1.76490592956543</t>
   </si>
   <si>
     <t xml:space="preserve">1.77430093288422</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">1.75819540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74880039691925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73806309700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72866821289062</t>
+    <t xml:space="preserve">1.74880003929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7380633354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7286684513092</t>
   </si>
   <si>
     <t xml:space="preserve">1.76624822616577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79174888134003</t>
+    <t xml:space="preserve">1.79174876213074</t>
   </si>
   <si>
     <t xml:space="preserve">1.77832746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77161681652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75416874885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77564311027527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74208998680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74074745178223</t>
+    <t xml:space="preserve">1.77161717414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75416886806488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7756427526474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74208974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74074769020081</t>
   </si>
   <si>
     <t xml:space="preserve">1.7353789806366</t>
@@ -1154,181 +1154,181 @@
     <t xml:space="preserve">1.73940551280975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75953722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503835201263</t>
+    <t xml:space="preserve">1.7595374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503799438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.78772246837616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78101170063019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81188070774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79845941066742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82261765003204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802485704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83067059516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88435578346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89911949634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88704073429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88569808006287</t>
+    <t xml:space="preserve">1.7810115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81188082695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82261788845062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80248582363129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83067083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88435590267181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88704025745392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88569796085358</t>
   </si>
   <si>
     <t xml:space="preserve">1.84543406963348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79577493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598421573639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71793127059937</t>
+    <t xml:space="preserve">1.7957751750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7259840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71793150901794</t>
   </si>
   <si>
     <t xml:space="preserve">1.73001074790955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893258094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77698516845703</t>
+    <t xml:space="preserve">1.76893222332001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7769855260849</t>
   </si>
   <si>
     <t xml:space="preserve">1.76222169399261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76356363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70316779613495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69645726680756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68035161495209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69511520862579</t>
+    <t xml:space="preserve">1.76356410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70316815376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69645738601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6803514957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6951150894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.69243085384369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67766726016998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63874530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64814043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60653436183929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6092187166214</t>
+    <t xml:space="preserve">1.67766749858856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63874518871307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64814066886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60653400421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60921847820282</t>
   </si>
   <si>
     <t xml:space="preserve">1.57029664516449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57432293891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57969164848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55687510967255</t>
+    <t xml:space="preserve">1.57432281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5796914100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55687522888184</t>
   </si>
   <si>
     <t xml:space="preserve">1.54345405101776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51392698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63203465938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67229866981506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66827249526978</t>
+    <t xml:space="preserve">1.51392722129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6320344209671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67229855060577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66827237606049</t>
   </si>
   <si>
     <t xml:space="preserve">1.75148451328278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74611616134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7139048576355</t>
+    <t xml:space="preserve">1.74611639976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71390473842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.72195756435394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71658945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63606095314026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60384976863861</t>
+    <t xml:space="preserve">1.71658933162689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63606119155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60385000705719</t>
   </si>
   <si>
     <t xml:space="preserve">1.58371806144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5367431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52197992801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54613828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54882252216339</t>
+    <t xml:space="preserve">1.53674340248108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52197957038879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54613792896271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54882264137268</t>
   </si>
   <si>
     <t xml:space="preserve">1.54748034477234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53271675109863</t>
+    <t xml:space="preserve">1.53271687030792</t>
   </si>
   <si>
     <t xml:space="preserve">1.56895458698273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54076957702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54211187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52869045734406</t>
+    <t xml:space="preserve">1.54076981544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.542111992836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52869057655334</t>
   </si>
   <si>
     <t xml:space="preserve">1.56761229038239</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">1.55955958366394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52600586414337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58774411678314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61190283298492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60519218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61324501037598</t>
+    <t xml:space="preserve">1.52600598335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58774435520172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61190259456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60519206523895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61324512958527</t>
   </si>
   <si>
     <t xml:space="preserve">1.5662704706192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49782156944275</t>
+    <t xml:space="preserve">1.49782145023346</t>
   </si>
   <si>
     <t xml:space="preserve">1.51661109924316</t>
@@ -1364,55 +1364,55 @@
     <t xml:space="preserve">1.50318992137909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49647927284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50990068912506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42266166210175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48171579837799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46292591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46695256233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48305773735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48439979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52332210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53405892848969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57662546634674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5683708190918</t>
+    <t xml:space="preserve">1.49647903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50990056991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42266178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48171591758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46292579174042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46695232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48305785655975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48439991474152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52332186698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53405916690826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57662510871887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56837069988251</t>
   </si>
   <si>
     <t xml:space="preserve">1.53947961330414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51884305477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51609146595001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49958252906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5628674030304</t>
+    <t xml:space="preserve">1.51884317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5160915851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56286764144897</t>
   </si>
   <si>
     <t xml:space="preserve">1.57387375831604</t>
@@ -1421,76 +1421,76 @@
     <t xml:space="preserve">1.5518616437912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52159464359283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50095796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50233387947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498206615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47619426250458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44042456150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46656405925751</t>
+    <t xml:space="preserve">1.52159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50095820426941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50233399868011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49820637702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47619438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44042468070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46656394004822</t>
   </si>
   <si>
     <t xml:space="preserve">1.42804276943207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43767309188843</t>
+    <t xml:space="preserve">1.43767297267914</t>
   </si>
   <si>
     <t xml:space="preserve">1.42391526699066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46518850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46931552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46106100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42116391658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37369990348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40327906608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38814544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45280635356903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44180023670197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43629705905914</t>
+    <t xml:space="preserve">1.46518838405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46931540966034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46106123924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42116379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37370002269745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40327882766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38814532756805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45280659198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44180011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43629693984985</t>
   </si>
   <si>
     <t xml:space="preserve">1.45143055915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41566109657288</t>
+    <t xml:space="preserve">1.4156608581543</t>
   </si>
   <si>
     <t xml:space="preserve">1.45555782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43904900550842</t>
+    <t xml:space="preserve">1.43904876708984</t>
   </si>
   <si>
     <t xml:space="preserve">1.42941856384277</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">1.41841244697571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39640021324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36613345146179</t>
+    <t xml:space="preserve">1.39640009403229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36613357067108</t>
   </si>
   <si>
     <t xml:space="preserve">1.41428506374359</t>
@@ -1511,85 +1511,85 @@
     <t xml:space="preserve">1.53397631645203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4679399728775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48032176494598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48169720172882</t>
+    <t xml:space="preserve">1.46793985366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48032140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48169755935669</t>
   </si>
   <si>
     <t xml:space="preserve">1.47069144248962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48720073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683082103729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50508546829224</t>
+    <t xml:space="preserve">1.48720049858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50508558750153</t>
   </si>
   <si>
     <t xml:space="preserve">1.54085516929626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53122496604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54223108291626</t>
+    <t xml:space="preserve">1.53122508525848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54223096370697</t>
   </si>
   <si>
     <t xml:space="preserve">1.5491099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54773437976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53260052204132</t>
+    <t xml:space="preserve">1.54773414134979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53260064125061</t>
   </si>
   <si>
     <t xml:space="preserve">1.58900701999664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57112193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56561887264252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51746737957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52984929084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53810369968414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55461275577545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53672790527344</t>
+    <t xml:space="preserve">1.57112205028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51746726036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5298490524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53810381889343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55461287498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53672802448273</t>
   </si>
   <si>
     <t xml:space="preserve">1.45830941200256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40878212451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38539385795593</t>
+    <t xml:space="preserve">1.417036652565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40878224372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38539397716522</t>
   </si>
   <si>
     <t xml:space="preserve">1.37851512432098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37576377391815</t>
+    <t xml:space="preserve">1.37576353549957</t>
   </si>
   <si>
     <t xml:space="preserve">1.36406970024109</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">1.40190327167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36888480186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32073318958282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26570248603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28289973735809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28909051418304</t>
+    <t xml:space="preserve">1.36888492107391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32073295116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2657026052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2828996181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28909063339233</t>
   </si>
   <si>
     <t xml:space="preserve">1.29665720462799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33724224567413</t>
+    <t xml:space="preserve">1.33724236488342</t>
   </si>
   <si>
     <t xml:space="preserve">1.34343314170837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33105134963989</t>
+    <t xml:space="preserve">1.3310512304306</t>
   </si>
   <si>
     <t xml:space="preserve">1.36200594902039</t>
@@ -1634,46 +1634,46 @@
     <t xml:space="preserve">1.37989091873169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38264262676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39089715480804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41978776454926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4266664981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43216991424561</t>
+    <t xml:space="preserve">1.38264238834381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39089727401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41978800296783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42666697502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43217027187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.4307941198349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43492150306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41153347492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35581505298615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37301230430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35719084739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32692396640778</t>
+    <t xml:space="preserve">1.43492162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41153359413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35581529140472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37301206588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35719060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32692408561707</t>
   </si>
   <si>
     <t xml:space="preserve">1.28565108776093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29528152942657</t>
+    <t xml:space="preserve">1.29528141021729</t>
   </si>
   <si>
     <t xml:space="preserve">1.28771471977234</t>
@@ -1682,61 +1682,61 @@
     <t xml:space="preserve">1.24506616592407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22924470901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25951159000397</t>
+    <t xml:space="preserve">1.22924482822418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25951147079468</t>
   </si>
   <si>
     <t xml:space="preserve">1.22786903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23130822181702</t>
+    <t xml:space="preserve">1.23130857944489</t>
   </si>
   <si>
     <t xml:space="preserve">1.18315672874451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19553852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19003558158875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24025070667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33380281925201</t>
+    <t xml:space="preserve">1.19553864002228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19003570079803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24025082588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3338029384613</t>
   </si>
   <si>
     <t xml:space="preserve">1.30009663105011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29940903186798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28496325016022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30078458786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29252994060516</t>
+    <t xml:space="preserve">1.2994087934494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28496313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30078446865082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29253005981445</t>
   </si>
   <si>
     <t xml:space="preserve">1.26776623725891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822117805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088738441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27051782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23818719387054</t>
+    <t xml:space="preserve">1.28221154212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27051758766174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23818743228912</t>
   </si>
   <si>
     <t xml:space="preserve">1.25882387161255</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">1.23268437385559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22030258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21204769611359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21411156654358</t>
+    <t xml:space="preserve">1.22030234336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21204781532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21411144733429</t>
   </si>
   <si>
     <t xml:space="preserve">1.18522047996521</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">1.20172953605652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19347488880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19966578483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20104193687439</t>
+    <t xml:space="preserve">1.19347512722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1996659040451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20104157924652</t>
   </si>
   <si>
     <t xml:space="preserve">1.27808463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28083598613739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28152370452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25676000118256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23612380027771</t>
+    <t xml:space="preserve">1.2808358669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28152394294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25676023960114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23612368106842</t>
   </si>
   <si>
     <t xml:space="preserve">1.20792055130005</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">1.20379316806793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19209921360016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21548712253571</t>
+    <t xml:space="preserve">1.19209897518158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.215487241745</t>
   </si>
   <si>
     <t xml:space="preserve">1.29046630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27946019172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2505692243576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27326941490173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34136962890625</t>
+    <t xml:space="preserve">1.2794600725174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25056910514832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27326929569244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34136950969696</t>
   </si>
   <si>
     <t xml:space="preserve">1.30216026306152</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">1.30353605747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32417261600494</t>
+    <t xml:space="preserve">1.32417237758636</t>
   </si>
   <si>
     <t xml:space="preserve">1.32554841041565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33930599689484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3475604057312</t>
+    <t xml:space="preserve">1.33930563926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34756064414978</t>
   </si>
   <si>
     <t xml:space="preserve">1.3317391872406</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">1.31110286712646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31523013114929</t>
+    <t xml:space="preserve">1.31522989273071</t>
   </si>
   <si>
     <t xml:space="preserve">1.34893620014191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36063039302826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38126659393311</t>
+    <t xml:space="preserve">1.36063027381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38126683235168</t>
   </si>
   <si>
     <t xml:space="preserve">1.38401818275452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30422401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32623612880707</t>
+    <t xml:space="preserve">1.30422389507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32623600959778</t>
   </si>
   <si>
     <t xml:space="preserve">1.34480893611908</t>
@@ -1877,46 +1877,46 @@
     <t xml:space="preserve">1.36957275867462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35787856578827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33793020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44455170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48307323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55323696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958856344223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64128577709198</t>
+    <t xml:space="preserve">1.35787868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33793008327484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44455182552338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48307311534882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55323708057404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59588575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64128601551056</t>
   </si>
   <si>
     <t xml:space="preserve">1.59038293361664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60276472568512</t>
+    <t xml:space="preserve">1.60276460647583</t>
   </si>
   <si>
     <t xml:space="preserve">1.598637342453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57937669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5642431974411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52572190761566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50921273231506</t>
+    <t xml:space="preserve">1.57937681674957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56424307823181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52572202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50921261310577</t>
   </si>
   <si>
     <t xml:space="preserve">1.51334011554718</t>
@@ -1925,130 +1925,130 @@
     <t xml:space="preserve">1.51058864593506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49545526504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5972615480423</t>
+    <t xml:space="preserve">1.49545514583588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59726142883301</t>
   </si>
   <si>
     <t xml:space="preserve">1.60001313686371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62340104579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71007406711578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77611100673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7994989156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7843656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85847651958466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77438926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78151512145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79719257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7672632932663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75301110744476</t>
+    <t xml:space="preserve">1.62340116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71007418632507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77611088752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79949879646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78436553478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85847640037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77438879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78151488304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79719185829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76726281642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75301086902618</t>
   </si>
   <si>
     <t xml:space="preserve">1.77153837680817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75728642940521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71025431156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71595525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85420083999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92403638362885</t>
+    <t xml:space="preserve">1.7572865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71025443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71595513820648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85420072078705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92403650283813</t>
   </si>
   <si>
     <t xml:space="preserve">1.89553225040436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81572008132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79434204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298749446869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74018406867981</t>
+    <t xml:space="preserve">1.81572043895721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79434156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7629873752594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74018394947052</t>
   </si>
   <si>
     <t xml:space="preserve">1.70597875118256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73733329772949</t>
+    <t xml:space="preserve">1.73733365535736</t>
   </si>
   <si>
     <t xml:space="preserve">1.73590838909149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78579080104828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76013708114624</t>
+    <t xml:space="preserve">1.7857905626297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76013684272766</t>
   </si>
   <si>
     <t xml:space="preserve">1.80004262924194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79006624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84422409534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84137368202209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77723944187164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016045570374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73020732402802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7131050825119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74588465690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80289304256439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84564936161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83282291889191</t>
+    <t xml:space="preserve">1.79006659984589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84422445297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84137439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77723932266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016057491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7302074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71310484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74588477611542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80289328098297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84564971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83282279968262</t>
   </si>
   <si>
     <t xml:space="preserve">1.78294026851654</t>
@@ -2057,70 +2057,70 @@
     <t xml:space="preserve">1.80146813392639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81001913547516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82854700088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83994889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87415385246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86560261249542</t>
+    <t xml:space="preserve">1.81001901626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8285471200943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83994853496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87415397167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86560237407684</t>
   </si>
   <si>
     <t xml:space="preserve">1.88413023948669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90265834331512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85562610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86417734622955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88555598258972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95396542549133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9311625957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95681643486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94398903846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87842953205109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87700426578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990166664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90978443622589</t>
+    <t xml:space="preserve">1.90265846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8556262254715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86417746543884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88555538654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95396566390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93116223812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95681619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94398891925812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8784294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87700438499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990178585052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9097843170166</t>
   </si>
   <si>
     <t xml:space="preserve">1.89410674571991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8713036775589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524996757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89268147945404</t>
+    <t xml:space="preserve">1.87130296230316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524949073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89268136024475</t>
   </si>
   <si>
     <t xml:space="preserve">1.93543815612793</t>
@@ -2129,100 +2129,100 @@
     <t xml:space="preserve">2.00954914093018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95111525058746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93971335887909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819459438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98532068729401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81714534759521</t>
+    <t xml:space="preserve">1.95111501216888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93971359729767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819411754608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98532056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81714558601379</t>
   </si>
   <si>
     <t xml:space="preserve">1.84279918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83139741420746</t>
+    <t xml:space="preserve">1.83139729499817</t>
   </si>
   <si>
     <t xml:space="preserve">1.94968998432159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97106862068176</t>
+    <t xml:space="preserve">1.97106838226318</t>
   </si>
   <si>
     <t xml:space="preserve">2.04517912864685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00669836997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99672198295593</t>
+    <t xml:space="preserve">2.00669884681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0309271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9967223405838</t>
   </si>
   <si>
     <t xml:space="preserve">1.99957263469696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09363651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06655788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0736837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06228160858154</t>
+    <t xml:space="preserve">2.09648656845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09363627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06655740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07368350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0622820854187</t>
   </si>
   <si>
     <t xml:space="preserve">1.96394217014313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92831182479858</t>
+    <t xml:space="preserve">1.92831230163574</t>
   </si>
   <si>
     <t xml:space="preserve">1.90123248100281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89695715904236</t>
+    <t xml:space="preserve">1.89695727825165</t>
   </si>
   <si>
     <t xml:space="preserve">1.92973685264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91691040992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91263461112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89125657081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90835905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9971706867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94335055351257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91425800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971498966217</t>
+    <t xml:space="preserve">1.9169100522995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91263437271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89125633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90835881233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99717056751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94335007667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91425776481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971522808075</t>
   </si>
   <si>
     <t xml:space="preserve">1.96371471881866</t>
@@ -2231,28 +2231,28 @@
     <t xml:space="preserve">1.97389650344849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95062303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90989446640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89389359951019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9346227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89680278301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88953006267548</t>
+    <t xml:space="preserve">1.95062279701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90989363193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89389371871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93462252616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8968026638031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88952970504761</t>
   </si>
   <si>
     <t xml:space="preserve">1.94916880130768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92880403995514</t>
+    <t xml:space="preserve">1.92880427837372</t>
   </si>
   <si>
     <t xml:space="preserve">1.96953272819519</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">2.02044415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00735282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01026177406311</t>
+    <t xml:space="preserve">2.00735259056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01026201248169</t>
   </si>
   <si>
     <t xml:space="preserve">1.98553347587585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00880742073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02189898490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02917194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03062653541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208065032959</t>
+    <t xml:space="preserve">2.00880765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02189826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02917170524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03062605857849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208041191101</t>
   </si>
   <si>
     <t xml:space="preserve">2.05099081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10044717788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09608364105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16881370544434</t>
+    <t xml:space="preserve">2.10044741630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09608340263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16881346702576</t>
   </si>
   <si>
     <t xml:space="preserve">2.08444666862488</t>
@@ -2303,109 +2303,109 @@
     <t xml:space="preserve">2.09753823280334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08008241653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09462904930115</t>
+    <t xml:space="preserve">2.08008289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09462881088257</t>
   </si>
   <si>
     <t xml:space="preserve">2.23863458633423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2473623752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18917798995972</t>
+    <t xml:space="preserve">2.24736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1891782283783</t>
   </si>
   <si>
     <t xml:space="preserve">2.16590428352356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09899306297302</t>
+    <t xml:space="preserve">2.09899258613586</t>
   </si>
   <si>
     <t xml:space="preserve">2.06844592094421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07717394828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07280969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12808465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11499309539795</t>
+    <t xml:space="preserve">2.07717347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07281017303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.128084897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11499333381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.14553999900818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14699482917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13390302658081</t>
+    <t xml:space="preserve">2.14699459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13390326499939</t>
   </si>
   <si>
     <t xml:space="preserve">2.13099408149719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08299207687378</t>
+    <t xml:space="preserve">2.08299231529236</t>
   </si>
   <si>
     <t xml:space="preserve">2.07426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05826425552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04808139801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02335357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02771687507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0640823841095</t>
+    <t xml:space="preserve">2.05826354026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04808163642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02335381507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06408190727234</t>
   </si>
   <si>
     <t xml:space="preserve">2.04226326942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99426090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03789925575256</t>
+    <t xml:space="preserve">1.99426114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03789949417114</t>
   </si>
   <si>
     <t xml:space="preserve">2.03644466400146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04517269134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02626276016235</t>
+    <t xml:space="preserve">2.04517221450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02626299858093</t>
   </si>
   <si>
     <t xml:space="preserve">2.00589799880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99862492084503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95935046672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97826075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96080505847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99280691146851</t>
+    <t xml:space="preserve">1.99862504005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97826063632965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96080565452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99280655384064</t>
   </si>
   <si>
     <t xml:space="preserve">2.06117296218872</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">2.06990051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04080867767334</t>
+    <t xml:space="preserve">2.04080843925476</t>
   </si>
   <si>
     <t xml:space="preserve">2.03353548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96807825565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91134905815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87643826007843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89098429679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90553057193756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80370855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79352593421936</t>
+    <t xml:space="preserve">1.96807849407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9113484621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87643837928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89098393917084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90553033351898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80370807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79352605342865</t>
   </si>
   <si>
     <t xml:space="preserve">1.80079889297485</t>
@@ -2447,157 +2447,157 @@
     <t xml:space="preserve">1.81970882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84152746200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82552719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80516266822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83279991149902</t>
+    <t xml:space="preserve">1.84152770042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82552707195282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80516278743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83280026912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.85898327827454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85171008110046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84298229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85752856731415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83570945262909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84880113601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87062013149261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79788959026337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61460971832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59860897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68152165412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61751902103424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57388079166412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55351638793945</t>
+    <t xml:space="preserve">1.85171020030975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84298264980316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85752880573273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8357093334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84880065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87062001228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79788970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61460983753204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59860920906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68152153491974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61751914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57388091087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55351626873016</t>
   </si>
   <si>
     <t xml:space="preserve">1.56224405765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62770128250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52733337879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50842332839966</t>
+    <t xml:space="preserve">1.62770104408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5273334980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50842344760895</t>
   </si>
   <si>
     <t xml:space="preserve">1.39278268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36441791057587</t>
+    <t xml:space="preserve">1.36441779136658</t>
   </si>
   <si>
     <t xml:space="preserve">1.35569036006927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19277489185333</t>
+    <t xml:space="preserve">1.19277465343475</t>
   </si>
   <si>
     <t xml:space="preserve">1.21241199970245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16150081157684</t>
+    <t xml:space="preserve">1.16150093078613</t>
   </si>
   <si>
     <t xml:space="preserve">1.1593189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13386332988739</t>
+    <t xml:space="preserve">1.13386344909668</t>
   </si>
   <si>
     <t xml:space="preserve">1.10768043994904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11422622203827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18041086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17968332767487</t>
+    <t xml:space="preserve">1.11422598361969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08440673351288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1804107427597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17968320846558</t>
   </si>
   <si>
     <t xml:space="preserve">1.19713842868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11204433441162</t>
+    <t xml:space="preserve">1.11204421520233</t>
   </si>
   <si>
     <t xml:space="preserve">1.12877225875854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10549855232239</t>
+    <t xml:space="preserve">1.18550169467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10549890995026</t>
   </si>
   <si>
     <t xml:space="preserve">1.09022521972656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04149603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07640659809113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059451580048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24514031410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23641300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20077514648438</t>
+    <t xml:space="preserve">1.04149615764618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07640635967255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24514055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23641276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2007749080658</t>
   </si>
   <si>
     <t xml:space="preserve">1.22186684608459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24223124980927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36005413532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41023778915405</t>
+    <t xml:space="preserve">1.24223113059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36005425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41023802757263</t>
   </si>
   <si>
     <t xml:space="preserve">1.47351312637329</t>
@@ -2606,103 +2606,103 @@
     <t xml:space="preserve">1.58939051628113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55649626255035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61331391334534</t>
+    <t xml:space="preserve">1.55649638175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61331403255463</t>
   </si>
   <si>
     <t xml:space="preserve">1.5624772310257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49967908859253</t>
+    <t xml:space="preserve">1.49967920780182</t>
   </si>
   <si>
     <t xml:space="preserve">1.46080410480499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47575604915619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47500848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60284733772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5206116437912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48397970199585</t>
+    <t xml:space="preserve">1.47575616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47500872612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60284745693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52061176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48397958278656</t>
   </si>
   <si>
     <t xml:space="preserve">1.42192912101746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40473437309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37931632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46005642414093</t>
+    <t xml:space="preserve">1.40473413467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37931597232819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46005630493164</t>
   </si>
   <si>
     <t xml:space="preserve">1.44884240627289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43762850761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49519371986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56546771526337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60733306407928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62228512763977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64321768283844</t>
+    <t xml:space="preserve">1.43762862682343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49519348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56546795368195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60733318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62228500843048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64321792125702</t>
   </si>
   <si>
     <t xml:space="preserve">1.71498715877533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68807339668274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64471292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77479481697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75535690784454</t>
+    <t xml:space="preserve">1.68807327747345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64471304416656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77479493618011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75535750389099</t>
   </si>
   <si>
     <t xml:space="preserve">1.67760717868805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65069365501404</t>
+    <t xml:space="preserve">1.65069389343262</t>
   </si>
   <si>
     <t xml:space="preserve">1.58490514755249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59686684608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62976109981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60583794116974</t>
+    <t xml:space="preserve">1.59686660766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62976098060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125586509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60583782196045</t>
   </si>
   <si>
     <t xml:space="preserve">1.62527537345886</t>
@@ -2711,64 +2711,64 @@
     <t xml:space="preserve">1.58341002464294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59238135814667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60135221481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64172267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71050143241882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71797752380371</t>
+    <t xml:space="preserve">1.59238111972809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60135233402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64172255992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7105016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71797716617584</t>
   </si>
   <si>
     <t xml:space="preserve">1.70601570606232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70003521442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67013120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68956863880157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74788153171539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72545349597931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78077566623688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656429290771</t>
+    <t xml:space="preserve">1.70003509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67013144493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68956887722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7478814125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72545337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78077554702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656417369843</t>
   </si>
   <si>
     <t xml:space="preserve">1.80021286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78675639629364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85404014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86002039909363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79871785640717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83310723304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79423213005066</t>
+    <t xml:space="preserve">1.78675615787506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85404002666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86002063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79871761798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83310759067535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79423236846924</t>
   </si>
   <si>
     <t xml:space="preserve">1.73292934894562</t>
@@ -2780,43 +2780,43 @@
     <t xml:space="preserve">1.83161211013794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85104966163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82264053821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83609747886658</t>
+    <t xml:space="preserve">1.85104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82264113426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83609783649445</t>
   </si>
   <si>
     <t xml:space="preserve">1.85852551460266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89291477203369</t>
+    <t xml:space="preserve">1.89291501045227</t>
   </si>
   <si>
     <t xml:space="preserve">1.90786707401276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90039110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89141964912415</t>
+    <t xml:space="preserve">1.90039086341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89141988754272</t>
   </si>
   <si>
     <t xml:space="preserve">1.88992476463318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90487670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83011698722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79124176502228</t>
+    <t xml:space="preserve">1.90487682819366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8854386806488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83011710643768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79124200344086</t>
   </si>
   <si>
     <t xml:space="preserve">1.85553526878357</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">1.81666052341461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80768883228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77928006649017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83460259437561</t>
+    <t xml:space="preserve">1.80768918991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77928018569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83460247516632</t>
   </si>
   <si>
     <t xml:space="preserve">1.80170834064484</t>
@@ -2840,76 +2840,76 @@
     <t xml:space="preserve">1.84805917739868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84506893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87646806240082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84058356285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83908832073212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82862162590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82114601135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77778518199921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71947264671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7090060710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71349203586578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68508303165436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68059754371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73442435264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72395813465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87497270107269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84207820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.782271027565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7658234834671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74638605117798</t>
+    <t xml:space="preserve">1.8450688123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87646782398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84058332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83908808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82862174510956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82114589214325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77778506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71947240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70900642871857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7134917974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68508315086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68059706687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73442447185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72395837306976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87497246265411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84207856655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78227078914642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76582360267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74638617038727</t>
   </si>
   <si>
     <t xml:space="preserve">1.75685238838196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72246301174164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63424670696259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5176215171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59836184978485</t>
+    <t xml:space="preserve">1.72246277332306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63424646854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51762139797211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59836196899414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74937653541565</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">1.72694849967957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75386190414429</t>
+    <t xml:space="preserve">1.75386202335358</t>
   </si>
   <si>
     <t xml:space="preserve">1.80469858646393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80918431282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81965065002441</t>
+    <t xml:space="preserve">1.80918419361115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81965053081512</t>
   </si>
   <si>
     <t xml:space="preserve">1.86301136016846</t>
@@ -2939,88 +2939,88 @@
     <t xml:space="preserve">1.91235268115997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93926620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96617937088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9915976524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97216010093689</t>
+    <t xml:space="preserve">1.93926632404327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96617960929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97216033935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.00056910514832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01345634460449</t>
+    <t xml:space="preserve">2.01345610618591</t>
   </si>
   <si>
     <t xml:space="preserve">2.014972448349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04074692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02710151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03316617012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99677848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00890755653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00132727622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99981069564819</t>
+    <t xml:space="preserve">2.04074716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02710175514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03316640853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99677872657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00890803337097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00132703781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99981081485748</t>
   </si>
   <si>
     <t xml:space="preserve">2.03165006637573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01800441741943</t>
+    <t xml:space="preserve">2.01800465583801</t>
   </si>
   <si>
     <t xml:space="preserve">2.00435924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0104238986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0301342010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03468227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04681205749512</t>
+    <t xml:space="preserve">2.01042437553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03013372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03468251228333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04681181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.05136036872864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04377937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07561874389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06803774833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10442566871643</t>
+    <t xml:space="preserve">2.04377961158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07561850547791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06803798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10442590713501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05287623405457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261962890625</t>
+    <t xml:space="preserve">2.12261986732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.21358919143677</t>
@@ -3029,22 +3029,22 @@
     <t xml:space="preserve">2.19084692001343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16203999519348</t>
+    <t xml:space="preserve">2.1620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">2.1468780040741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13323259353638</t>
+    <t xml:space="preserve">2.1332323551178</t>
   </si>
   <si>
     <t xml:space="preserve">2.15597534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18023324012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20145964622498</t>
+    <t xml:space="preserve">2.18023300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20145988464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.27120304107666</t>
@@ -3053,85 +3053,85 @@
     <t xml:space="preserve">2.18933033943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26362180709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21510481834412</t>
+    <t xml:space="preserve">2.26362228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2484610080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2151050567627</t>
   </si>
   <si>
     <t xml:space="preserve">2.21662139892578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29546141624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30001020431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3227527141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31062293052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34246230125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35762405395508</t>
+    <t xml:space="preserve">2.29546189308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30000996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32275223731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31062316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34246253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576238155365</t>
   </si>
   <si>
     <t xml:space="preserve">2.34852719306946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35913991928101</t>
+    <t xml:space="preserve">2.35914015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.38794708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36368846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39249563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33639788627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38491439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36520457267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36823701858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430143356323</t>
+    <t xml:space="preserve">2.36368870735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39249515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33639764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38491487503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36520433425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36823678016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.32426857948303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35459136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34549498558044</t>
+    <t xml:space="preserve">2.35459160804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34549474716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.38036632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4410126209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36065649986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3727855682373</t>
+    <t xml:space="preserve">2.44101238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36065602302551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37278532981873</t>
   </si>
   <si>
     <t xml:space="preserve">2.31820392608643</t>
@@ -3143,34 +3143,34 @@
     <t xml:space="preserve">2.40765714645386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41523790359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41978621482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49407815933228</t>
+    <t xml:space="preserve">2.41523766517639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41978597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4940779209137</t>
   </si>
   <si>
     <t xml:space="preserve">2.4349479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41827011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42888307571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40614128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3075909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32730078697205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3439781665802</t>
+    <t xml:space="preserve">2.41827034950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42888355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40614080429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30759048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32730054855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34397864341736</t>
   </si>
   <si>
     <t xml:space="preserve">2.35610795021057</t>
@@ -3179,31 +3179,31 @@
     <t xml:space="preserve">2.45314168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51682066917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48649764060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49862623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043274879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44859337806702</t>
+    <t xml:space="preserve">2.51682043075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48649716377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4986264705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44859313964844</t>
   </si>
   <si>
     <t xml:space="preserve">2.54714345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58959603309631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56685376167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64266180992126</t>
+    <t xml:space="preserve">2.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56685352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64266157150269</t>
   </si>
   <si>
     <t xml:space="preserve">2.65327429771423</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">2.50052428245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157995223999</t>
+    <t xml:space="preserve">2.51579904556274</t>
   </si>
   <si>
     <t xml:space="preserve">2.51427149772644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49899673461914</t>
+    <t xml:space="preserve">2.49899625778198</t>
   </si>
   <si>
     <t xml:space="preserve">2.52343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53412938117981</t>
+    <t xml:space="preserve">2.53412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.60286688804626</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">2.44553399085999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43942379951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47761154174805</t>
+    <t xml:space="preserve">2.43942403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47761130332947</t>
   </si>
   <si>
     <t xml:space="preserve">2.48066663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41192889213562</t>
+    <t xml:space="preserve">2.41192865371704</t>
   </si>
   <si>
     <t xml:space="preserve">2.38443374633789</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">2.42262148857117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46691918373108</t>
+    <t xml:space="preserve">2.4669189453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.45775413513184</t>
@@ -3272,28 +3272,28 @@
     <t xml:space="preserve">2.43025898933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45928168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44706130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43331408500671</t>
+    <t xml:space="preserve">2.45928192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44706177711487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43331384658813</t>
   </si>
   <si>
     <t xml:space="preserve">2.45622634887695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48372149467468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54023933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65938448905945</t>
+    <t xml:space="preserve">2.48372197151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50816178321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54023909568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65938472747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.6486918926239</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">2.67618703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61814212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60439443588257</t>
+    <t xml:space="preserve">2.61814188957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60439467430115</t>
   </si>
   <si>
     <t xml:space="preserve">2.65632963180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68382453918457</t>
+    <t xml:space="preserve">2.68382477760315</t>
   </si>
   <si>
     <t xml:space="preserve">2.73575973510742</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">2.6884069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63952708244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61966919898987</t>
+    <t xml:space="preserve">2.63952732086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61966967582703</t>
   </si>
   <si>
     <t xml:space="preserve">2.59370183944702</t>
@@ -3335,31 +3335,31 @@
     <t xml:space="preserve">2.54634952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53565692901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51885414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54482173919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53260135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5066339969635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58148217201233</t>
+    <t xml:space="preserve">2.53565669059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51885461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54482197761536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53260183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50663423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58148193359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.54329419136047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46997404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49135899543762</t>
+    <t xml:space="preserve">2.46997427940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4913592338562</t>
   </si>
   <si>
     <t xml:space="preserve">2.48830413818359</t>
@@ -3368,94 +3368,94 @@
     <t xml:space="preserve">2.48219418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40734601020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37526893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4104015827179</t>
+    <t xml:space="preserve">2.40734648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37526869773865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41040134429932</t>
   </si>
   <si>
     <t xml:space="preserve">2.38290619850159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4424786567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47455644607544</t>
+    <t xml:space="preserve">2.48524928092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44247889518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47455620765686</t>
   </si>
   <si>
     <t xml:space="preserve">2.52801918983459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48983192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52649164199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52496433258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55856919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55398678779602</t>
+    <t xml:space="preserve">2.4898316860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52649188041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52496409416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55856895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55398726463318</t>
   </si>
   <si>
     <t xml:space="preserve">2.54787683486938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56162428855896</t>
+    <t xml:space="preserve">2.56162452697754</t>
   </si>
   <si>
     <t xml:space="preserve">2.52954697608948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51732635498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45164394378662</t>
+    <t xml:space="preserve">2.51732683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4516441822052</t>
   </si>
   <si>
     <t xml:space="preserve">2.42873167991638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42414927482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42567658424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45011639595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4272038936615</t>
+    <t xml:space="preserve">2.42414903640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42567682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4501166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42720413208008</t>
   </si>
   <si>
     <t xml:space="preserve">2.40581893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510692596436</t>
+    <t xml:space="preserve">2.50510668754578</t>
   </si>
   <si>
     <t xml:space="preserve">2.39818143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38596129417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37221360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40887403488159</t>
+    <t xml:space="preserve">2.38596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37221384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40887355804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.37355303764343</t>
@@ -3464,19 +3464,19 @@
     <t xml:space="preserve">2.36727380752563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4253568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43791508674622</t>
+    <t xml:space="preserve">2.42535662651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43791532516479</t>
   </si>
   <si>
     <t xml:space="preserve">2.42378711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40965890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35157561302185</t>
+    <t xml:space="preserve">2.40965867042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">2.35000610351562</t>
@@ -3485,58 +3485,58 @@
     <t xml:space="preserve">2.34372639656067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34058737754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33116841316223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35471510887146</t>
+    <t xml:space="preserve">2.34058690071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33116817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35471534729004</t>
   </si>
   <si>
     <t xml:space="preserve">2.34686636924744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39396047592163</t>
+    <t xml:space="preserve">2.39396071434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.41593813896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4473340511322</t>
+    <t xml:space="preserve">2.44733428955078</t>
   </si>
   <si>
     <t xml:space="preserve">2.43948531150818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47402048110962</t>
+    <t xml:space="preserve">2.47402095794678</t>
   </si>
   <si>
     <t xml:space="preserve">2.45361351966858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44105505943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45675325393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46931147575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4677414894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4881489276886</t>
+    <t xml:space="preserve">2.4410548210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45675301551819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46931171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46774172782898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48814916610718</t>
   </si>
   <si>
     <t xml:space="preserve">2.50384736061096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45047378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27622509002686</t>
+    <t xml:space="preserve">2.45047402381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27622485160828</t>
   </si>
   <si>
     <t xml:space="preserve">2.26837587356567</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">2.25581741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2573869228363</t>
+    <t xml:space="preserve">2.25738716125488</t>
   </si>
   <si>
     <t xml:space="preserve">2.31547021865845</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">2.27151536941528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36256408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31076097488403</t>
+    <t xml:space="preserve">2.36256456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31076049804688</t>
   </si>
   <si>
     <t xml:space="preserve">2.32017970085144</t>
@@ -3572,28 +3572,28 @@
     <t xml:space="preserve">2.26994562149048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22913074493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22442102432251</t>
+    <t xml:space="preserve">2.2291305065155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22442126274109</t>
   </si>
   <si>
     <t xml:space="preserve">2.24639844894409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244359970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15064024925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16005921363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14122104644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20401382446289</t>
+    <t xml:space="preserve">2.20244407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15064001083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16005873680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14122128486633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20401358604431</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773411750793</t>
@@ -3602,31 +3602,31 @@
     <t xml:space="preserve">2.16319847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17732644081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18674564361572</t>
+    <t xml:space="preserve">2.17732667922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18674540519714</t>
   </si>
   <si>
     <t xml:space="preserve">2.18203639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16633820533752</t>
+    <t xml:space="preserve">2.16633796691895</t>
   </si>
   <si>
     <t xml:space="preserve">2.15534973144531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14750027656555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15848898887634</t>
+    <t xml:space="preserve">2.14750051498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15848922729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.21814203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21186304092407</t>
+    <t xml:space="preserve">2.21186280250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.23070049285889</t>
@@ -3635,52 +3635,52 @@
     <t xml:space="preserve">2.21657204627991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22756099700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26366662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31860947608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29349231719971</t>
+    <t xml:space="preserve">2.22756052017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26366639137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31860971450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29349279403687</t>
   </si>
   <si>
     <t xml:space="preserve">2.24796843528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2354097366333</t>
+    <t xml:space="preserve">2.23540997505188</t>
   </si>
   <si>
     <t xml:space="preserve">2.24011921882629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24482846260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26052665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30291128158569</t>
+    <t xml:space="preserve">2.24482870101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26052689552307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30291199684143</t>
   </si>
   <si>
     <t xml:space="preserve">2.34529662132263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28407382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11924409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20087361335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18831539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22128176689148</t>
+    <t xml:space="preserve">2.28407406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11924362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2008740901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18831586837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2212815284729</t>
   </si>
   <si>
     <t xml:space="preserve">2.23227024078369</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">2.23697972297668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19930386543274</t>
+    <t xml:space="preserve">2.19930410385132</t>
   </si>
   <si>
     <t xml:space="preserve">2.22599101066589</t>
@@ -3698,46 +3698,46 @@
     <t xml:space="preserve">2.27936458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16476821899414</t>
+    <t xml:space="preserve">2.16476845741272</t>
   </si>
   <si>
     <t xml:space="preserve">2.03447413444519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09255695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97953104972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95441389083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0109269618988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92615723609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84766662120819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.800572514534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87592327594757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.822549700737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807405948639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91045916080475</t>
+    <t xml:space="preserve">2.0925567150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05802130699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97953057289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95441377162933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01092720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92615735530853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84766685962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80057239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87592351436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82254981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807429790497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91045904159546</t>
   </si>
   <si>
     <t xml:space="preserve">1.91202914714813</t>
@@ -3746,127 +3746,127 @@
     <t xml:space="preserve">2.00935697555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99365890026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97796070575714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01877617835999</t>
+    <t xml:space="preserve">1.99365901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97796130180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01877593994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.0172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99208915233612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98894953727722</t>
+    <t xml:space="preserve">1.99208950996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98894941806793</t>
   </si>
   <si>
     <t xml:space="preserve">1.99679851531982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05959129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01249670982361</t>
+    <t xml:space="preserve">2.0595908164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01249647140503</t>
   </si>
   <si>
     <t xml:space="preserve">2.01406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96854197978973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97639095783234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88220262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86650454998016</t>
+    <t xml:space="preserve">1.96854174137115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97639083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88220238685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86650407314301</t>
   </si>
   <si>
     <t xml:space="preserve">1.91516852378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92301750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89790034294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89947056770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92124783992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93576598167419</t>
+    <t xml:space="preserve">1.92301774024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89790046215057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89947044849396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92124772071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93576610088348</t>
   </si>
   <si>
     <t xml:space="preserve">2.01642298698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01158356666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96964180469513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93092691898346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89543771743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87608003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770028114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91156888008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90189003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89221119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.847043633461</t>
+    <t xml:space="preserve">2.01158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96964228153229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93092679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89543795585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87607979774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770051956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91156911849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90189015865326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89221143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84704339504242</t>
   </si>
   <si>
     <t xml:space="preserve">1.8260725736618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77122616767883</t>
+    <t xml:space="preserve">1.77122592926025</t>
   </si>
   <si>
     <t xml:space="preserve">1.79703617095947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81316733360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86801421642303</t>
+    <t xml:space="preserve">1.81316745281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86801445484161</t>
   </si>
   <si>
     <t xml:space="preserve">1.90672957897186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94383203983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91963469982147</t>
+    <t xml:space="preserve">1.9438316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91963481903076</t>
   </si>
   <si>
     <t xml:space="preserve">1.89382445812225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91802167892456</t>
+    <t xml:space="preserve">1.91802144050598</t>
   </si>
   <si>
     <t xml:space="preserve">1.93253970146179</t>
@@ -3875,109 +3875,109 @@
     <t xml:space="preserve">1.91479516029358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98254692554474</t>
+    <t xml:space="preserve">1.9631894826889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98254704475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.02932834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609484195709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02448844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01481008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97448122501373</t>
+    <t xml:space="preserve">1.97609448432922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02448868751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01480984687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97448134422302</t>
   </si>
   <si>
     <t xml:space="preserve">1.97770738601685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99061262607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93415307998657</t>
+    <t xml:space="preserve">1.99061274528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9341527223587</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124049663544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8292989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87285387516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88898503780365</t>
+    <t xml:space="preserve">1.82929885387421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87285375595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88898515701294</t>
   </si>
   <si>
     <t xml:space="preserve">1.86317467689514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85833513736725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84381699562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85672223567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88253271579742</t>
+    <t xml:space="preserve">1.85833537578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84381723403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567225933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88253247737885</t>
   </si>
   <si>
     <t xml:space="preserve">1.87769329547882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84865665435791</t>
+    <t xml:space="preserve">1.84865641593933</t>
   </si>
   <si>
     <t xml:space="preserve">1.80187547206879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81155455112457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75993394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78574407100677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81800675392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86962747573853</t>
+    <t xml:space="preserve">1.81155443191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75993406772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78574419021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81800699234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86962723731995</t>
   </si>
   <si>
     <t xml:space="preserve">1.8357515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82768595218658</t>
+    <t xml:space="preserve">1.82768583297729</t>
   </si>
   <si>
     <t xml:space="preserve">1.90350329875946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93899238109589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9518975019455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99383926391602</t>
+    <t xml:space="preserve">1.93899214267731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95189738273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99383878707886</t>
   </si>
   <si>
     <t xml:space="preserve">1.96802890300751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9922262430191</t>
+    <t xml:space="preserve">1.99222588539124</t>
   </si>
   <si>
     <t xml:space="preserve">2.06643033027649</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">2.0744960308075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05029892921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0519118309021</t>
+    <t xml:space="preserve">2.05029940605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05191206932068</t>
   </si>
   <si>
     <t xml:space="preserve">2.03416752815247</t>
@@ -4004,22 +4004,22 @@
     <t xml:space="preserve">2.09546685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07933521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0761091709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00351762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00835704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9889999628067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95512390136719</t>
+    <t xml:space="preserve">2.0793354511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07610893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00351786613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00835728645325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98899960517883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95512366294861</t>
   </si>
   <si>
     <t xml:space="preserve">1.97932076454163</t>
@@ -4028,25 +4028,25 @@
     <t xml:space="preserve">1.89866399765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91318237781525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92931354045868</t>
+    <t xml:space="preserve">1.91318213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92931342124939</t>
   </si>
   <si>
     <t xml:space="preserve">1.9728684425354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96480274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94544470310211</t>
+    <t xml:space="preserve">1.96480286121368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94544506072998</t>
   </si>
   <si>
     <t xml:space="preserve">1.8373646736145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91025590896606</t>
+    <t xml:space="preserve">1.91025602817535</t>
   </si>
   <si>
     <t xml:space="preserve">1.82647287845612</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">1.78290569782257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78458142280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79128384590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77620303630829</t>
+    <t xml:space="preserve">1.7845813035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79128396511078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.776202917099</t>
   </si>
   <si>
     <t xml:space="preserve">1.72928428649902</t>
@@ -4076,28 +4076,28 @@
     <t xml:space="preserve">1.73933839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74604117870331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79798662662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7996621131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86333751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83820247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8566347360611</t>
+    <t xml:space="preserve">1.74604105949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79798638820648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79966235160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86333727836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83820259571075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85663497447968</t>
   </si>
   <si>
     <t xml:space="preserve">1.86166155338287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87674260139465</t>
+    <t xml:space="preserve">1.87674295902252</t>
   </si>
   <si>
     <t xml:space="preserve">1.87171566486359</t>
@@ -4109,31 +4109,31 @@
     <t xml:space="preserve">1.91360723972321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93203949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8968505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90355348587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92701268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94879627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94376945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09625458717346</t>
+    <t xml:space="preserve">1.93203961849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89685070514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90355324745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92701280117035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94879615306854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94376933574677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09625482559204</t>
   </si>
   <si>
     <t xml:space="preserve">2.17836213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19176721572876</t>
+    <t xml:space="preserve">2.19176745414734</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820003509521</t>
@@ -4148,19 +4148,19 @@
     <t xml:space="preserve">2.29900979995728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29230713844299</t>
+    <t xml:space="preserve">2.29230761528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.28895592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32582068443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33419871330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3425772190094</t>
+    <t xml:space="preserve">2.32582092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33419895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34257745742798</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917189598083</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">2.2939829826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30906391143799</t>
+    <t xml:space="preserve">2.30906414985657</t>
   </si>
   <si>
     <t xml:space="preserve">2.30068564414978</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">2.29733443260193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31409072875977</t>
+    <t xml:space="preserve">2.31409120559692</t>
   </si>
   <si>
     <t xml:space="preserve">2.30403685569763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33754992485046</t>
+    <t xml:space="preserve">2.33755016326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.42636013031006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44981932640076</t>
+    <t xml:space="pres